--- a/docs/snapshot/downloads/kisa.xlsx
+++ b/docs/snapshot/downloads/kisa.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K102"/>
+  <dimension ref="A1:K103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,32 +476,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>57381</t>
+          <t>61031</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026 전자문서 유공 포상 공고</t>
+          <t>“새로운 보안 위협, 인공지능(AI)으로 대응” 정보보호 제품 개발 기업 대상 보안 역량 강화 교육 추진</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3761&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2636&amp;page=1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -509,46 +509,42 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-09-10 14:16:31.877229+09:00</t>
+          <t>2026-09-15 14:01:52.540884+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-09-10 14:16:31.877229+09:00</t>
+          <t>2026-09-15 14:01:52.540884+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>57149</t>
+          <t>57381</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026년 클라우드 서비스 보안인증(CSAP) 교육 안내</t>
+          <t>2026 전자문서 유공 포상 공고</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3760&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3761&amp;page=1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -558,7 +554,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -566,7 +562,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -574,19 +574,19 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-09-10 10:46:38.794916+09:00</t>
+          <t>2026-09-10 14:16:31.877229+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-09-10 10:46:38.794916+09:00</t>
+          <t>2026-09-10 14:16:31.877229+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>56431</t>
+          <t>57149</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -596,22 +596,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>보호나라 챗봇, 국민 생활 속 정보보호 성과 인정</t>
+          <t>2026년 클라우드 서비스 보안인증(CSAP) 교육 안내</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2634&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3760&amp;page=1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -622,92 +622,92 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-09-09 12:01:35.142670+09:00</t>
+          <t>2026-09-10 10:46:38.794916+09:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-09-09 12:01:35.142670+09:00</t>
+          <t>2026-09-10 10:46:38.794916+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>56969</t>
+          <t>56431</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1522</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>온마이데이터 서비스 이용 이벤트 안내</t>
+          <t>보호나라 챗봇, 국민 생활 속 정보보호 성과 인정</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3758&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2634&amp;page=1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>402</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-09-10 08:31:37.677434+09:00</t>
+          <t>2026-09-09 12:01:35.142670+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-09-10 08:31:37.677434+09:00</t>
+          <t>2026-09-09 12:01:35.142670+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>54791</t>
+          <t>56969</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1522</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>국내 캐시 도메인이름시스템(DNS) 운영기관, 신규 암호키 반영 여부 확인하세요</t>
+          <t>온마이데이터 서비스 이용 이벤트 안내</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2633&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3758&amp;page=1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -717,60 +717,60 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>402</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-09-07 12:01:35.243341+09:00</t>
+          <t>2026-09-10 08:31:37.677434+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-09-07 12:01:35.243341+09:00</t>
+          <t>2026-09-10 08:31:37.677434+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>54541</t>
+          <t>54791</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(2차, Avalanche)</t>
+          <t>국내 캐시 도메인이름시스템(DNS) 운영기관, 신규 암호키 반영 여부 확인하세요</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3759&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2633&amp;page=1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -778,31 +778,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-09-07 09:01:25.516098+09:00</t>
+          <t>2026-09-07 12:01:35.243341+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-09-07 09:01:25.516098+09:00</t>
+          <t>2026-09-07 12:01:35.243341+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>51281</t>
+          <t>54541</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -812,27 +808,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>(행사 안내) 국외이전 제도 개선 및 CBPR 인증제도 기업 설명회 개최</t>
+          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(2차, Avalanche)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3757&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3759&amp;page=1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -847,52 +843,56 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-09-03 09:16:26.856224+09:00</t>
+          <t>2026-09-07 09:01:25.516098+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-09-03 09:16:26.856224+09:00</t>
+          <t>2026-09-07 09:01:25.516098+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>56970</t>
+          <t>51281</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1521</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026 부산지역 도메인이름 분쟁해결 세미나 개최 안내(9.11)</t>
+          <t>(행사 안내) 국외이전 제도 개선 및 CBPR 인증제도 기업 설명회 개최</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3755&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3757&amp;page=1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>23</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -900,34 +900,34 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-09-10 08:31:37.677434+09:00</t>
+          <t>2026-09-03 09:16:26.856224+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-09-10 08:31:37.677434+09:00</t>
+          <t>2026-09-03 09:16:26.856224+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>51121</t>
+          <t>56970</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1521</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026년 블록체인 수요공급협의체(ABLE) 블록체인 수요기업(비금융분야) 모집 공고</t>
+          <t>2026 부산지역 도메인이름 분쟁해결 세미나 개최 안내(9.11)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3754&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3755&amp;page=1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>242</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -945,11 +945,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -957,19 +953,19 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-09-02 17:31:25.610368+09:00</t>
+          <t>2026-09-10 08:31:37.677434+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-09-02 17:31:25.610368+09:00</t>
+          <t>2026-09-10 08:31:37.677434+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>50601</t>
+          <t>51121</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -979,12 +975,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026년 9차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(9월 추천) (~9.18(금) 18시까지)</t>
+          <t>2026년 블록체인 수요공급협의체(ABLE) 블록체인 수요기업(비금융분야) 모집 공고</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3753&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3754&amp;page=1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -994,7 +990,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>24</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1014,44 +1010,44 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-09-02 11:01:32.173328+09:00</t>
+          <t>2026-09-02 17:31:25.610368+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-09-02 11:01:32.173328+09:00</t>
+          <t>2026-09-02 17:31:25.610368+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>49872</t>
+          <t>50601</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>인공지능(AI) 사이버 위협, 실전 모의훈련으로 대응</t>
+          <t>2026년 9차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(9월 추천) (~9.18(금) 18시까지)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2631&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3753&amp;page=1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1059,27 +1055,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-09-01 12:01:47.858504+09:00</t>
+          <t>2026-09-02 11:01:32.173328+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-09-01 12:01:47.858504+09:00</t>
+          <t>2026-09-02 11:01:32.173328+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>49669</t>
+          <t>49872</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>「2026 위치정보 맞춤형 컨설팅 참여기업 모집」</t>
+          <t>인공지능(AI) 사이버 위협, 실전 모의훈련으로 대응</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3752&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2631&amp;page=1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1104,35 +1104,35 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-09-01 09:31:38.715793+09:00</t>
+          <t>2026-09-01 12:01:47.858504+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-09-01 09:31:38.715793+09:00</t>
+          <t>2026-09-01 12:01:47.858504+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>49631</t>
+          <t>49669</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>물리보안 시스템 간 연동 장벽 낮춘다</t>
+          <t>「2026 위치정보 맞춤형 컨설팅 참여기업 모집」</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2632&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3752&amp;page=1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1157,103 +1157,103 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-09-01 09:01:45.980040+09:00</t>
+          <t>2026-09-01 09:31:38.715793+09:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-09-01 09:01:45.980040+09:00</t>
+          <t>2026-09-01 09:31:38.715793+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>49589</t>
+          <t>49631</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1517</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 23회차 교육생 모집(~9.18)</t>
+          <t>물리보안 시스템 간 연동 장벽 낮춘다</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3751&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2632&amp;page=1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-09-01 08:31:37.253592+09:00</t>
+          <t>2026-09-01 09:01:45.980040+09:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-09-01 08:31:37.253592+09:00</t>
+          <t>2026-09-01 09:01:45.980040+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>48831</t>
+          <t>49589</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1517</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>생성형 인공지능(AI) 기반 실전형 모의해킹 대회 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 23회차 교육생 모집(~9.18)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2630&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3751&amp;page=1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1263,35 +1263,35 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>174</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-08-31 09:16:38.866405+09:00</t>
+          <t>2026-09-01 08:31:37.253592+09:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-08-31 09:16:38.866405+09:00</t>
+          <t>2026-09-01 08:31:37.253592+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>46011</t>
+          <t>48831</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1301,22 +1301,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>자동차 노리는 사이버 위협, 한국인터넷진흥원-한국교통안전공단이 함께 대응한다</t>
+          <t>생성형 인공지능(AI) 기반 실전형 모의해킹 대회 개최</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2628&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2630&amp;page=1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1332,34 +1332,34 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-08-27 15:01:41.552844+09:00</t>
+          <t>2026-08-31 09:16:38.866405+09:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-08-27 15:01:41.552844+09:00</t>
+          <t>2026-08-31 09:16:38.866405+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>45681</t>
+          <t>46011</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>싱가포르 현지 진출 지원 국내 블록체인 기업 모집(~9.16(수) 14시)</t>
+          <t>자동차 노리는 사이버 위협, 한국인터넷진흥원-한국교통안전공단이 함께 대응한다</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3750&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2628&amp;page=1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1377,56 +1377,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-08-27 11:01:31.314899+09:00</t>
+          <t>2026-08-27 15:01:41.552844+09:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-08-27 11:01:31.314899+09:00</t>
+          <t>2026-08-27 15:01:41.552844+09:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>45191</t>
+          <t>45681</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 아·태 지역 사이버공격 대응 공동 훈련 실시</t>
+          <t>싱가포르 현지 진출 지원 국내 블록체인 기업 모집(~9.16(수) 14시)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2629&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3750&amp;page=1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1434,42 +1430,46 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-08-26 15:01:47.261933+09:00</t>
+          <t>2026-08-27 11:01:31.314899+09:00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-08-26 15:01:47.261933+09:00</t>
+          <t>2026-08-27 11:01:31.314899+09:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>44741</t>
+          <t>45191</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>[3차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~9/16)</t>
+          <t>한국인터넷진흥원, 아·태 지역 사이버공격 대응 공동 훈련 실시</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3749&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2629&amp;page=1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1487,56 +1487,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-08-26 09:31:36.427758+09:00</t>
+          <t>2026-08-26 15:01:47.261933+09:00</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-08-26 09:31:36.427758+09:00</t>
+          <t>2026-08-26 15:01:47.261933+09:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>44448</t>
+          <t>44741</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 공고</t>
+          <t>[3차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~9/16)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3748&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3749&amp;page=1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1544,7 +1540,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1552,19 +1552,19 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-08-25 16:01:39.626193+09:00</t>
+          <t>2026-08-26 09:31:36.427758+09:00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-08-25 16:01:39.626193+09:00</t>
+          <t>2026-08-26 09:31:36.427758+09:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>43767</t>
+          <t>44448</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1574,27 +1574,27 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 21회차 교육생 모집(~9.12)</t>
+          <t>정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 공고</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3747&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3748&amp;page=1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
@@ -1605,19 +1605,19 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-08-24 17:46:42.254577+09:00</t>
+          <t>2026-08-25 16:01:39.626193+09:00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-08-24 17:46:42.254577+09:00</t>
+          <t>2026-08-25 16:01:39.626193+09:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>43311</t>
+          <t>43767</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1627,12 +1627,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>양자내성암호 전환, 어떻게 준비해야 할까?</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 21회차 교육생 모집(~9.12)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2627&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3747&amp;page=1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1642,50 +1642,50 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-08-24 12:01:45.511381+09:00</t>
+          <t>2026-08-24 17:46:42.254577+09:00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-08-24 12:01:45.511381+09:00</t>
+          <t>2026-08-24 17:46:42.254577+09:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>43301</t>
+          <t>43311</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>양자내성암호 전문교육 PQC 실무과정 교육생 모집(8.24~)</t>
+          <t>양자내성암호 전환, 어떻게 준비해야 할까?</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3746&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2627&amp;page=1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1703,31 +1703,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-08-24 12:01:36.271108+09:00</t>
+          <t>2026-08-24 12:01:45.511381+09:00</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-08-24 12:01:36.271108+09:00</t>
+          <t>2026-08-24 12:01:45.511381+09:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>41161</t>
+          <t>43301</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1737,27 +1733,27 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>「블록체인 기업 맞춤형 보안 고도화 지원」 기업 모집(~8/31)</t>
+          <t>양자내성암호 전문교육 PQC 실무과정 교육생 모집(8.24~)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3745&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3746&amp;page=1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1772,34 +1768,34 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-08-21 16:01:38.087170+09:00</t>
+          <t>2026-08-24 12:01:36.271108+09:00</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-08-21 16:01:38.087170+09:00</t>
+          <t>2026-08-24 12:01:36.271108+09:00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>41086</t>
+          <t>41161</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026년도 인터넷거버넌스 민간전문가 APrIGF 및 IGF 참석자 모집</t>
+          <t>「블록체인 기업 맞춤형 보안 고도화 지원」 기업 모집(~8/31)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3744&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3745&amp;page=1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1809,15 +1805,19 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1825,19 +1825,19 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-08-21 15:01:32.139445+09:00</t>
+          <t>2026-08-21 16:01:38.087170+09:00</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-08-21 15:01:32.139445+09:00</t>
+          <t>2026-08-21 16:01:38.087170+09:00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>34750</t>
+          <t>41086</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1847,22 +1847,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>｢2026 블록체인 진흥주간｣ 전시부스 참가기업 모집 공고(~9.14)</t>
+          <t>2026년도 인터넷거버넌스 민간전문가 APrIGF 및 IGF 참석자 모집</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3743&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3744&amp;page=1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>59</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1878,34 +1878,34 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-08-13 17:46:21.938331+09:00</t>
+          <t>2026-08-21 15:01:32.139445+09:00</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-08-13 17:46:21.938331+09:00</t>
+          <t>2026-08-21 15:01:32.139445+09:00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>34081</t>
+          <t>34750</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026년 하반기 정보보호 전문서비스 기업 지정에 관한 공고</t>
+          <t>｢2026 블록체인 진흥주간｣ 전시부스 참가기업 모집 공고(~9.14)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3742&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3743&amp;page=1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1923,11 +1923,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1935,44 +1931,44 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:24.927741+09:00</t>
+          <t>2026-08-13 17:46:21.938331+09:00</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:24.927741+09:00</t>
+          <t>2026-08-13 17:46:21.938331+09:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>34071</t>
+          <t>34081</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>"예방 넘어 대응·복구까지" 랜섬웨어 전주기 대응 방안 논의한다</t>
+          <t>2026년 하반기 정보보호 전문서비스 기업 지정에 관한 공고</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2626&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3742&amp;page=1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1980,42 +1976,46 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-08-13 09:16:35.989405+09:00</t>
+          <t>2026-08-13 09:31:24.927741+09:00</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-08-13 09:16:35.989405+09:00</t>
+          <t>2026-08-13 09:31:24.927741+09:00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>33789</t>
+          <t>34071</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>978</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 21회차 교육생 모집(~9.11)</t>
+          <t>"예방 넘어 대응·복구까지" 랜섬웨어 전주기 대응 방안 논의한다</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3741&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2626&amp;page=1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2025,35 +2025,35 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-08-12 16:01:25.579701+09:00</t>
+          <t>2026-08-13 09:16:35.989405+09:00</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-08-12 16:01:25.579701+09:00</t>
+          <t>2026-08-13 09:16:35.989405+09:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>33749</t>
+          <t>33789</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2063,12 +2063,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026년도 블록체인 유공 포상 계획 공고 안내(~9.21 15:00 마감)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 21회차 교육생 모집(~9.11)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3740&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3741&amp;page=1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2078,12 +2078,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
@@ -2094,44 +2094,44 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-08-12 15:31:25.306307+09:00</t>
+          <t>2026-08-12 16:01:25.579701+09:00</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-08-12 15:31:25.306307+09:00</t>
+          <t>2026-08-12 16:01:25.579701+09:00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>31741</t>
+          <t>33749</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026년 블록체인 수요-공급 협의체 (ABLE) 정례세미나 개최 안내(8.13.목)</t>
+          <t>2026년도 블록체인 유공 포상 계획 공고 안내(~9.21 15:00 마감)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3739&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3740&amp;page=1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2139,11 +2139,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2151,52 +2147,56 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-08-10 11:01:30.246604+09:00</t>
+          <t>2026-08-12 15:31:25.306307+09:00</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-08-10 11:01:30.246604+09:00</t>
+          <t>2026-08-12 15:31:25.306307+09:00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>29768</t>
+          <t>31741</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026년 블록체인 신뢰인프라(K-BTF) 활용·확산사업 공모 사전예고</t>
+          <t>2026년 블록체인 수요-공급 협의체 (ABLE) 정례세미나 개최 안내(8.13.목)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3738&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3739&amp;page=1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2204,19 +2204,19 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-08-07 17:01:29.954014+09:00</t>
+          <t>2026-08-10 11:01:30.246604+09:00</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-08-07 17:01:29.954014+09:00</t>
+          <t>2026-08-10 11:01:30.246604+09:00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>29728</t>
+          <t>29768</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2226,12 +2226,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026년도 블록체인 산업 실태조사 실시 및 협조 안내</t>
+          <t>2026년 블록체인 신뢰인프라(K-BTF) 활용·확산사업 공모 사전예고</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3737&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3738&amp;page=1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2257,19 +2257,19 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-08-07 16:31:30.938844+09:00</t>
+          <t>2026-08-07 17:01:29.954014+09:00</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-08-07 16:31:30.938844+09:00</t>
+          <t>2026-08-07 17:01:29.954014+09:00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>28711</t>
+          <t>29728</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2279,50 +2279,50 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원-나주시, 고교생 개인정보·정보보호 진로 탐색 지원</t>
+          <t>2026년도 블록체인 산업 실태조사 실시 및 협조 안내</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2625&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3737&amp;page=1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-08-06 14:01:34.968573+09:00</t>
+          <t>2026-08-07 16:31:30.938844+09:00</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-08-06 14:01:34.968573+09:00</t>
+          <t>2026-08-07 16:31:30.938844+09:00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>27551</t>
+          <t>28711</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2332,22 +2332,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 기업 맞춤형 사이버 위협 알림 서비스 개시</t>
+          <t>한국인터넷진흥원-나주시, 고교생 개인정보·정보보호 진로 탐색 지원</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2624&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2625&amp;page=1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2363,44 +2363,44 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-08-05 09:46:34.063806+09:00</t>
+          <t>2026-08-06 14:01:34.968573+09:00</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-08-05 09:46:34.063806+09:00</t>
+          <t>2026-08-06 14:01:34.968573+09:00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>27511</t>
+          <t>27551</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 기관장 주도 국민 체감 성과 혁신 체계 가동</t>
+          <t>한국인터넷진흥원, 기업 맞춤형 사이버 위협 알림 서비스 개시</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2623&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2624&amp;page=1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2416,34 +2416,34 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-08-05 09:16:33.823896+09:00</t>
+          <t>2026-08-05 09:46:34.063806+09:00</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-08-05 09:16:33.823896+09:00</t>
+          <t>2026-08-05 09:46:34.063806+09:00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>27268</t>
+          <t>27511</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>975</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>양자내성암호 국제 표준화 동향 분석</t>
+          <t>한국인터넷진흥원, 기관장 주도 국민 체감 성과 혁신 체계 가동</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3736&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2623&amp;page=1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>263</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2464,24 +2464,24 @@
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-08-04 16:31:26.502205+09:00</t>
+          <t>2026-08-05 09:16:33.823896+09:00</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-08-04 16:31:26.502205+09:00</t>
+          <t>2026-08-05 09:16:33.823896+09:00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>27128</t>
+          <t>27268</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2491,12 +2491,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 20회차 교육생 모집(~9.4)</t>
+          <t>양자내성암호 국제 표준화 동향 분석</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3735&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3736&amp;page=1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
@@ -2522,19 +2522,19 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-08-04 14:46:28.764255+09:00</t>
+          <t>2026-08-04 16:31:26.502205+09:00</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-08-04 14:46:28.764255+09:00</t>
+          <t>2026-08-04 16:31:26.502205+09:00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>26211</t>
+          <t>27128</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2544,50 +2544,50 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 암호모듈검증 위한 시험 전문인력 양성</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 20회차 교육생 모집(~9.4)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2622&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3735&amp;page=1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-08-03 13:31:41.722921+09:00</t>
+          <t>2026-08-04 14:46:28.764255+09:00</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-08-03 13:31:41.722921+09:00</t>
+          <t>2026-08-04 14:46:28.764255+09:00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>26188</t>
+          <t>26211</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026년 8차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(8월 추천) (~8.21(금) 18시까지)</t>
+          <t>한국인터넷진흥원, 암호모듈검증 위한 시험 전문인력 양성</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3734&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2622&amp;page=1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>273</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2623,24 +2623,24 @@
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-08-03 13:16:30.325331+09:00</t>
+          <t>2026-08-03 13:31:41.722921+09:00</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-08-03 13:16:30.325331+09:00</t>
+          <t>2026-08-03 13:31:41.722921+09:00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>25891</t>
+          <t>26188</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2650,12 +2650,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 지역 상생 3대 사업 참여자 모집</t>
+          <t>2026년 8차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(8월 추천) (~8.21(금) 18시까지)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2621&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3734&amp;page=1</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2665,7 +2665,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2676,39 +2676,39 @@
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-08-03 09:31:46.854132+09:00</t>
+          <t>2026-08-03 13:16:30.325331+09:00</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-08-03 09:31:46.854132+09:00</t>
+          <t>2026-08-03 13:16:30.325331+09:00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>25864</t>
+          <t>25891</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026년 전남광주통합특별시 소상공인·사회적경제기업 판로 확대 지원기업 선발 안내(~8.14)</t>
+          <t>한국인터넷진흥원, 지역 상생 3대 사업 참여자 모집</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3730&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2621&amp;page=1</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>80</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2726,31 +2726,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-08-03 09:16:35.817723+09:00</t>
+          <t>2026-08-03 09:31:46.854132+09:00</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-08-03 09:16:35.817723+09:00</t>
+          <t>2026-08-03 09:31:46.854132+09:00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>25863</t>
+          <t>25864</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2760,12 +2756,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026년 전남광주통합특별시 지역문제 해결 프로젝트 공모전 개최 안내(~8.21)</t>
+          <t>2026년 전남광주통합특별시 소상공인·사회적경제기업 판로 확대 지원기업 선발 안내(~8.14)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3731&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3730&amp;page=1</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2775,7 +2771,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2807,7 +2803,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>25862</t>
+          <t>25863</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2817,12 +2813,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026년 한국인터넷진흥원 지역공부방 참여 대학생 장학금 지원자 모집 안내(~8.28)</t>
+          <t>2026년 전남광주통합특별시 지역문제 해결 프로젝트 공모전 개최 안내(~8.21)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3732&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3731&amp;page=1</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2832,7 +2828,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2864,7 +2860,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>25861</t>
+          <t>25862</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2874,12 +2870,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026년 암호모듈 시험자 양성교육 및 필기시험 안내(8.3~8.21)</t>
+          <t>2026년 한국인터넷진흥원 지역공부방 참여 대학생 장학금 지원자 모집 안내(~8.28)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3733&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3732&amp;page=1</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2889,7 +2885,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2921,7 +2917,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>23221</t>
+          <t>25861</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2931,22 +2927,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026년 블록체인 기업성장허브 입주기업 모집(~8월 27일(목) 16:00까지)</t>
+          <t>2026년 암호모듈 시험자 양성교육 및 필기시험 안내(8.3~8.21)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3729&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3733&amp;page=1</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2966,52 +2962,56 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2026-07-30 17:16:54.540202+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-07-30 17:16:54.540202+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>22504</t>
+          <t>23221</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 19회차 교육생 모집(~8.28)</t>
+          <t>2026년 블록체인 기업성장허브 입주기업 모집(~8월 27일(목) 16:00까지)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3728&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3729&amp;page=1</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I48" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3019,19 +3019,19 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-07-29 18:32:00.075123+09:00</t>
+          <t>2026-07-30 17:16:54.540202+09:00</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-07-29 18:32:00.075123+09:00</t>
+          <t>2026-07-30 17:16:54.540202+09:00</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>22464</t>
+          <t>22504</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026년 연계정보 이용기관 안전조치 실태점검 2차 설명회 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 19회차 교육생 모집(~8.28)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3727&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3728&amp;page=1</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3072,19 +3072,19 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:59.875668+09:00</t>
+          <t>2026-07-29 18:32:00.075123+09:00</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:59.875668+09:00</t>
+          <t>2026-07-29 18:32:00.075123+09:00</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>20771</t>
+          <t>22464</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3094,50 +3094,50 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 성평등가족부와 불법·유해 정보 유통 대응 맞손</t>
+          <t>2026년 연계정보 이용기관 안전조치 실태점검 2차 설명회 개최</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2620&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3727&amp;page=1</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2026-07-27 17:17:05.702970+09:00</t>
+          <t>2026-07-29 18:01:59.875668+09:00</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-07-27 17:17:05.702970+09:00</t>
+          <t>2026-07-29 18:01:59.875668+09:00</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>20191</t>
+          <t>20771</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3147,12 +3147,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 향후 10년 설계한다…전담 추진단(TF) 출범</t>
+          <t>한국인터넷진흥원, 성평등가족부와 불법·유해 정보 유통 대응 맞손</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2619&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2620&amp;page=1</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>150</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3178,34 +3178,34 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2026-07-27 10:02:05.338547+09:00</t>
+          <t>2026-07-27 17:17:05.702970+09:00</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-07-27 10:02:05.338547+09:00</t>
+          <t>2026-07-27 17:17:05.702970+09:00</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>20061</t>
+          <t>20191</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(1차, BreakingPoint)</t>
+          <t>아피가(APIGA) 향후 10년 설계한다…전담 추진단(TF) 출범</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3726&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2619&amp;page=1</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3215,7 +3215,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>287</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3223,64 +3223,64 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2026-07-27 08:31:55.019743+09:00</t>
+          <t>2026-07-27 10:02:05.338547+09:00</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-07-27 08:31:55.019743+09:00</t>
+          <t>2026-07-27 10:02:05.338547+09:00</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>16785</t>
+          <t>20061</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 17회차 교육생 모집(~8.7)</t>
+          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(1차, BreakingPoint)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3724&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3726&amp;page=1</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>246</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I53" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3288,34 +3288,34 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 08:31:55.019743+09:00</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 08:31:55.019743+09:00</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>16784</t>
+          <t>16785</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1497</t>
+          <t>1496</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 18회차 교육생 모집(~8.21)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 17회차 교육생 모집(~8.7)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3725&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3724&amp;page=1</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>236</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3353,22 +3353,22 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>16781</t>
+          <t>16784</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1497</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 16회차 교육생 모집(~7.31)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 18회차 교육생 모집(~8.21)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3723&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3725&amp;page=1</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>260</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3386,11 +3386,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3410,22 +3406,22 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>16691</t>
+          <t>16781</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>'블록체인 기반 예금토큰 결제 인프라 확산' 사업 발대식 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 16회차 교육생 모집(~7.31)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2618&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3723&amp;page=1</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3435,35 +3431,39 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>242</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2026-07-22 17:32:01.526863+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-07-22 17:32:01.526863+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>16464</t>
+          <t>16691</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>[홍보] 정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 안내</t>
+          <t>'블록체인 기반 예금토큰 결제 인프라 확산' 사업 발대식 개최</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3722&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2618&amp;page=1</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3488,35 +3488,35 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>278</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2026-07-22 14:46:48.687665+09:00</t>
+          <t>2026-07-22 17:32:01.526863+09:00</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-07-22 14:46:48.687665+09:00</t>
+          <t>2026-07-22 17:32:01.526863+09:00</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>16051</t>
+          <t>16464</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 보안 인재·글로벌 전문가 교류의 장 열어</t>
+          <t>[홍보] 정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 안내</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2617&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3722&amp;page=1</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3541,35 +3541,35 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>2026-07-22 09:31:50.671841+09:00</t>
+          <t>2026-07-22 14:46:48.687665+09:00</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-07-22 09:31:50.671841+09:00</t>
+          <t>2026-07-22 14:46:48.687665+09:00</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>14611</t>
+          <t>16051</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3579,22 +3579,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
+          <t>한국인터넷진흥원, 보안 인재·글로벌 전문가 교류의 장 열어</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2617&amp;page=1</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>233</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3610,19 +3610,19 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>14431</t>
+          <t>14611</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3647,7 +3647,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>32</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3663,34 +3663,34 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>14431</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3700,7 +3700,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>53</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3708,56 +3708,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>14444</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>1493</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
+          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -3765,7 +3761,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I62" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3773,34 +3773,34 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>11331</t>
+          <t>14444</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -3821,96 +3821,92 @@
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>10981</t>
+          <t>11331</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
+          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>10943</t>
+          <t>10981</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
+          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3920,7 +3916,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -3928,7 +3924,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr"/>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I65" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3936,19 +3936,19 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>10663</t>
+          <t>10943</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
+          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
@@ -3989,19 +3989,19 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>9805</t>
+          <t>10663</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4011,22 +4011,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
+          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -4042,19 +4042,19 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>9691</t>
+          <t>9805</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4064,12 +4064,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
+          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4079,7 +4079,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -4090,96 +4090,92 @@
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>9321</t>
+          <t>9691</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
+          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>8871</t>
+          <t>9321</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
+          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4189,35 +4185,39 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>6685</t>
+          <t>8871</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4227,22 +4227,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
+          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -4253,24 +4253,24 @@
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>6571</t>
+          <t>6685</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4280,12 +4280,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
+          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -4306,24 +4306,24 @@
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>5591</t>
+          <t>6571</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4333,22 +4333,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
+          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -4364,44 +4364,44 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>5591</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
+          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>33</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -4417,44 +4417,44 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>4762</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>961</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>AI 보안 위협 대응 매뉴얼</t>
+          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -4462,31 +4462,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>4761</t>
+          <t>4762</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -4496,12 +4492,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>AI 보안 레드티밍 가이드</t>
+          <t>AI 보안 위협 대응 매뉴얼</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -4511,7 +4507,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -4543,22 +4539,22 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>4251</t>
+          <t>4761</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
+          <t>AI 보안 레드티밍 가이드</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -4568,7 +4564,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -4576,27 +4572,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr"/>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>4251</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -4606,12 +4606,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
+          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -4621,113 +4621,113 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>191</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t>3867</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
+          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4111</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>959</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
+          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>34</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -4735,31 +4735,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4769,12 +4765,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
+          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -4784,7 +4780,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -4816,32 +4812,32 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
+          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>105</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -4849,7 +4845,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr"/>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I82" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -4869,22 +4869,22 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1477</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
+          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -4894,7 +4894,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>386</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -4922,22 +4922,22 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
+          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -4947,19 +4947,15 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>362</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -4979,7 +4975,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4989,12 +4985,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2026년 IoT 보안인증 교육과정 안내</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5004,7 +5000,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>522</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -5036,40 +5032,44 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
+          <t>2026년 IoT 보안인증 교육과정 안내</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>652</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I86" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -5089,22 +5089,22 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
+          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>1529</t>
+          <t>818</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -5122,11 +5122,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -5146,32 +5142,32 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
+          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>1529</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -5179,7 +5175,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr"/>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I88" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -5187,34 +5187,34 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5224,7 +5224,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>76426</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -5235,49 +5235,49 @@
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>958</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
+          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>55906</t>
+          <t>76426</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -5305,22 +5305,22 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>956</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
+          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5330,7 +5330,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>55329</t>
+          <t>55906</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -5358,32 +5358,32 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>957</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
+          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>34467</t>
+          <t>55329</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -5411,22 +5411,22 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>955</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
+          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -5436,39 +5436,35 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2945</t>
+          <t>34467</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -5478,27 +5474,27 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>2945</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -5525,32 +5521,32 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>145255</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -5558,52 +5554,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr"/>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>954</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>26576</t>
+          <t>145255</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -5631,32 +5631,32 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>953</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
+          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>34290</t>
+          <t>26576</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -5684,32 +5684,32 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
+          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>184573</t>
+          <t>34290</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -5737,32 +5737,32 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>14403</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>951</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>6587</t>
+          <t>184573</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -5770,46 +5770,42 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14403</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
+          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -5819,7 +5815,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>51749</t>
+          <t>6587</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -5827,52 +5823,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr"/>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>950</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>78439</t>
+          <t>51749</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -5900,55 +5900,108 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>949</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>78439</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>보도자료</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
           <t>38805</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
+      <c r="B103" t="inlineStr">
         <is>
           <t>공지</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr">
+      <c r="C103" t="inlineStr">
         <is>
           <t>[공유] 지능형 CCTV 성능시험 재개 안내 공지</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr">
+      <c r="D103" t="inlineStr">
         <is>
           <t>https://www.kisa.or.kr/401/form?postSeq=3677&amp;page=1</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr">
+      <c r="E103" t="inlineStr">
         <is>
           <t>2026-06-02</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr">
+      <c r="F103" t="inlineStr">
         <is>
           <t>6525</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr">
+      <c r="G103" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
+      <c r="H103" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>공지사항</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
         <is>
           <t>2026-08-18 17:16:37.364015+09:00</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr">
+      <c r="K103" t="inlineStr">
         <is>
           <t>2026-08-18 17:16:37.364015+09:00</t>
         </is>

--- a/docs/snapshot/downloads/kisa.xlsx
+++ b/docs/snapshot/downloads/kisa.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K103"/>
+  <dimension ref="A1:K104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>61031</t>
+          <t>61111</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -486,12 +486,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>“새로운 보안 위협, 인공지능(AI)으로 대응” 정보보호 제품 개발 기업 대상 보안 역량 강화 교육 추진</t>
+          <t>민관 합동 ‘자동차 사이버 침해사고 대응 모의훈련’ 실시</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2636&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2637&amp;page=1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -517,44 +517,44 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-09-15 14:01:52.540884+09:00</t>
+          <t>2026-09-15 15:01:52.747371+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-09-15 14:01:52.540884+09:00</t>
+          <t>2026-09-15 15:01:52.747371+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>57381</t>
+          <t>61031</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026 전자문서 유공 포상 공고</t>
+          <t>“새로운 보안 위협, 인공지능(AI)으로 대응” 정보보호 제품 개발 기업 대상 보안 역량 강화 교육 추진</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3761&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2636&amp;page=1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -562,46 +562,42 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-09-10 14:16:31.877229+09:00</t>
+          <t>2026-09-15 14:01:52.540884+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-09-10 14:16:31.877229+09:00</t>
+          <t>2026-09-15 14:01:52.540884+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>57149</t>
+          <t>57381</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026년 클라우드 서비스 보안인증(CSAP) 교육 안내</t>
+          <t>2026 전자문서 유공 포상 공고</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3760&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3761&amp;page=1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -611,7 +607,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -619,7 +615,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -627,19 +627,19 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-09-10 10:46:38.794916+09:00</t>
+          <t>2026-09-10 14:16:31.877229+09:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-09-10 10:46:38.794916+09:00</t>
+          <t>2026-09-10 14:16:31.877229+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>56431</t>
+          <t>57149</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -649,22 +649,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>보호나라 챗봇, 국민 생활 속 정보보호 성과 인정</t>
+          <t>2026년 클라우드 서비스 보안인증(CSAP) 교육 안내</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2634&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3760&amp;page=1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -675,92 +675,92 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-09-09 12:01:35.142670+09:00</t>
+          <t>2026-09-10 10:46:38.794916+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-09-09 12:01:35.142670+09:00</t>
+          <t>2026-09-10 10:46:38.794916+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>56969</t>
+          <t>56431</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1522</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>온마이데이터 서비스 이용 이벤트 안내</t>
+          <t>보호나라 챗봇, 국민 생활 속 정보보호 성과 인정</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3758&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2634&amp;page=1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>402</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-09-10 08:31:37.677434+09:00</t>
+          <t>2026-09-09 12:01:35.142670+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-09-10 08:31:37.677434+09:00</t>
+          <t>2026-09-09 12:01:35.142670+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>54791</t>
+          <t>56969</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1522</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>국내 캐시 도메인이름시스템(DNS) 운영기관, 신규 암호키 반영 여부 확인하세요</t>
+          <t>온마이데이터 서비스 이용 이벤트 안내</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2633&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3758&amp;page=1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -770,60 +770,60 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>402</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-09-07 12:01:35.243341+09:00</t>
+          <t>2026-09-10 08:31:37.677434+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-09-07 12:01:35.243341+09:00</t>
+          <t>2026-09-10 08:31:37.677434+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>54541</t>
+          <t>54791</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(2차, Avalanche)</t>
+          <t>국내 캐시 도메인이름시스템(DNS) 운영기관, 신규 암호키 반영 여부 확인하세요</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3759&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2633&amp;page=1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -831,31 +831,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-09-07 09:01:25.516098+09:00</t>
+          <t>2026-09-07 12:01:35.243341+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-09-07 09:01:25.516098+09:00</t>
+          <t>2026-09-07 12:01:35.243341+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>51281</t>
+          <t>54541</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -865,27 +861,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>(행사 안내) 국외이전 제도 개선 및 CBPR 인증제도 기업 설명회 개최</t>
+          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(2차, Avalanche)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3757&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3759&amp;page=1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -900,52 +896,56 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-09-03 09:16:26.856224+09:00</t>
+          <t>2026-09-07 09:01:25.516098+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-09-03 09:16:26.856224+09:00</t>
+          <t>2026-09-07 09:01:25.516098+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>56970</t>
+          <t>51281</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1521</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026 부산지역 도메인이름 분쟁해결 세미나 개최 안내(9.11)</t>
+          <t>(행사 안내) 국외이전 제도 개선 및 CBPR 인증제도 기업 설명회 개최</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3755&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3757&amp;page=1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>23</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -953,34 +953,34 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-09-10 08:31:37.677434+09:00</t>
+          <t>2026-09-03 09:16:26.856224+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-09-10 08:31:37.677434+09:00</t>
+          <t>2026-09-03 09:16:26.856224+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>51121</t>
+          <t>56970</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1521</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026년 블록체인 수요공급협의체(ABLE) 블록체인 수요기업(비금융분야) 모집 공고</t>
+          <t>2026 부산지역 도메인이름 분쟁해결 세미나 개최 안내(9.11)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3754&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3755&amp;page=1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -990,7 +990,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>242</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -998,11 +998,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1010,19 +1006,19 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-09-02 17:31:25.610368+09:00</t>
+          <t>2026-09-10 08:31:37.677434+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-09-02 17:31:25.610368+09:00</t>
+          <t>2026-09-10 08:31:37.677434+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>50601</t>
+          <t>51121</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1032,12 +1028,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026년 9차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(9월 추천) (~9.18(금) 18시까지)</t>
+          <t>2026년 블록체인 수요공급협의체(ABLE) 블록체인 수요기업(비금융분야) 모집 공고</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3753&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3754&amp;page=1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1047,7 +1043,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>24</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1067,44 +1063,44 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-09-02 11:01:32.173328+09:00</t>
+          <t>2026-09-02 17:31:25.610368+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-09-02 11:01:32.173328+09:00</t>
+          <t>2026-09-02 17:31:25.610368+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>49872</t>
+          <t>50601</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>인공지능(AI) 사이버 위협, 실전 모의훈련으로 대응</t>
+          <t>2026년 9차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(9월 추천) (~9.18(금) 18시까지)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2631&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3753&amp;page=1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1112,27 +1108,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-09-01 12:01:47.858504+09:00</t>
+          <t>2026-09-02 11:01:32.173328+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-09-01 12:01:47.858504+09:00</t>
+          <t>2026-09-02 11:01:32.173328+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>49669</t>
+          <t>49872</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>「2026 위치정보 맞춤형 컨설팅 참여기업 모집」</t>
+          <t>인공지능(AI) 사이버 위협, 실전 모의훈련으로 대응</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3752&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2631&amp;page=1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1157,35 +1157,35 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-09-01 09:31:38.715793+09:00</t>
+          <t>2026-09-01 12:01:47.858504+09:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-09-01 09:31:38.715793+09:00</t>
+          <t>2026-09-01 12:01:47.858504+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>49631</t>
+          <t>49669</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>물리보안 시스템 간 연동 장벽 낮춘다</t>
+          <t>「2026 위치정보 맞춤형 컨설팅 참여기업 모집」</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2632&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3752&amp;page=1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1210,103 +1210,103 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-09-01 09:01:45.980040+09:00</t>
+          <t>2026-09-01 09:31:38.715793+09:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-09-01 09:01:45.980040+09:00</t>
+          <t>2026-09-01 09:31:38.715793+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>49589</t>
+          <t>49631</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1517</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 23회차 교육생 모집(~9.18)</t>
+          <t>물리보안 시스템 간 연동 장벽 낮춘다</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3751&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2632&amp;page=1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-09-01 08:31:37.253592+09:00</t>
+          <t>2026-09-01 09:01:45.980040+09:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-09-01 08:31:37.253592+09:00</t>
+          <t>2026-09-01 09:01:45.980040+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>48831</t>
+          <t>49589</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1517</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>생성형 인공지능(AI) 기반 실전형 모의해킹 대회 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 23회차 교육생 모집(~9.18)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2630&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3751&amp;page=1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1316,35 +1316,35 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>174</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-08-31 09:16:38.866405+09:00</t>
+          <t>2026-09-01 08:31:37.253592+09:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-08-31 09:16:38.866405+09:00</t>
+          <t>2026-09-01 08:31:37.253592+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>46011</t>
+          <t>48831</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1354,22 +1354,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>자동차 노리는 사이버 위협, 한국인터넷진흥원-한국교통안전공단이 함께 대응한다</t>
+          <t>생성형 인공지능(AI) 기반 실전형 모의해킹 대회 개최</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2628&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2630&amp;page=1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1385,34 +1385,34 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-08-27 15:01:41.552844+09:00</t>
+          <t>2026-08-31 09:16:38.866405+09:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-08-27 15:01:41.552844+09:00</t>
+          <t>2026-08-31 09:16:38.866405+09:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>45681</t>
+          <t>46011</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>싱가포르 현지 진출 지원 국내 블록체인 기업 모집(~9.16(수) 14시)</t>
+          <t>자동차 노리는 사이버 위협, 한국인터넷진흥원-한국교통안전공단이 함께 대응한다</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3750&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2628&amp;page=1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1430,56 +1430,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-08-27 11:01:31.314899+09:00</t>
+          <t>2026-08-27 15:01:41.552844+09:00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-08-27 11:01:31.314899+09:00</t>
+          <t>2026-08-27 15:01:41.552844+09:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>45191</t>
+          <t>45681</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 아·태 지역 사이버공격 대응 공동 훈련 실시</t>
+          <t>싱가포르 현지 진출 지원 국내 블록체인 기업 모집(~9.16(수) 14시)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2629&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3750&amp;page=1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1487,42 +1483,46 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-08-26 15:01:47.261933+09:00</t>
+          <t>2026-08-27 11:01:31.314899+09:00</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-08-26 15:01:47.261933+09:00</t>
+          <t>2026-08-27 11:01:31.314899+09:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>44741</t>
+          <t>45191</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>[3차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~9/16)</t>
+          <t>한국인터넷진흥원, 아·태 지역 사이버공격 대응 공동 훈련 실시</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3749&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2629&amp;page=1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1540,56 +1540,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-08-26 09:31:36.427758+09:00</t>
+          <t>2026-08-26 15:01:47.261933+09:00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-08-26 09:31:36.427758+09:00</t>
+          <t>2026-08-26 15:01:47.261933+09:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>44448</t>
+          <t>44741</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 공고</t>
+          <t>[3차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~9/16)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3748&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3749&amp;page=1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1597,7 +1593,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1605,19 +1605,19 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-08-25 16:01:39.626193+09:00</t>
+          <t>2026-08-26 09:31:36.427758+09:00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-08-25 16:01:39.626193+09:00</t>
+          <t>2026-08-26 09:31:36.427758+09:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>43767</t>
+          <t>44448</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1627,27 +1627,27 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 21회차 교육생 모집(~9.12)</t>
+          <t>정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 공고</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3747&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3748&amp;page=1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
@@ -1658,19 +1658,19 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-08-24 17:46:42.254577+09:00</t>
+          <t>2026-08-25 16:01:39.626193+09:00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-08-24 17:46:42.254577+09:00</t>
+          <t>2026-08-25 16:01:39.626193+09:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>43311</t>
+          <t>43767</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>양자내성암호 전환, 어떻게 준비해야 할까?</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 21회차 교육생 모집(~9.12)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2627&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3747&amp;page=1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1695,50 +1695,50 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-08-24 12:01:45.511381+09:00</t>
+          <t>2026-08-24 17:46:42.254577+09:00</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-08-24 12:01:45.511381+09:00</t>
+          <t>2026-08-24 17:46:42.254577+09:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>43301</t>
+          <t>43311</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>양자내성암호 전문교육 PQC 실무과정 교육생 모집(8.24~)</t>
+          <t>양자내성암호 전환, 어떻게 준비해야 할까?</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3746&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2627&amp;page=1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1756,31 +1756,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-08-24 12:01:36.271108+09:00</t>
+          <t>2026-08-24 12:01:45.511381+09:00</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-08-24 12:01:36.271108+09:00</t>
+          <t>2026-08-24 12:01:45.511381+09:00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>41161</t>
+          <t>43301</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1790,27 +1786,27 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>「블록체인 기업 맞춤형 보안 고도화 지원」 기업 모집(~8/31)</t>
+          <t>양자내성암호 전문교육 PQC 실무과정 교육생 모집(8.24~)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3745&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3746&amp;page=1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1825,34 +1821,34 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-08-21 16:01:38.087170+09:00</t>
+          <t>2026-08-24 12:01:36.271108+09:00</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-08-21 16:01:38.087170+09:00</t>
+          <t>2026-08-24 12:01:36.271108+09:00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>41086</t>
+          <t>41161</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026년도 인터넷거버넌스 민간전문가 APrIGF 및 IGF 참석자 모집</t>
+          <t>「블록체인 기업 맞춤형 보안 고도화 지원」 기업 모집(~8/31)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3744&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3745&amp;page=1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1862,15 +1858,19 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1878,19 +1878,19 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-08-21 15:01:32.139445+09:00</t>
+          <t>2026-08-21 16:01:38.087170+09:00</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-08-21 15:01:32.139445+09:00</t>
+          <t>2026-08-21 16:01:38.087170+09:00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>34750</t>
+          <t>41086</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1900,22 +1900,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>｢2026 블록체인 진흥주간｣ 전시부스 참가기업 모집 공고(~9.14)</t>
+          <t>2026년도 인터넷거버넌스 민간전문가 APrIGF 및 IGF 참석자 모집</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3743&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3744&amp;page=1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>59</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1931,34 +1931,34 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-08-13 17:46:21.938331+09:00</t>
+          <t>2026-08-21 15:01:32.139445+09:00</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-08-13 17:46:21.938331+09:00</t>
+          <t>2026-08-21 15:01:32.139445+09:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>34081</t>
+          <t>34750</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026년 하반기 정보보호 전문서비스 기업 지정에 관한 공고</t>
+          <t>｢2026 블록체인 진흥주간｣ 전시부스 참가기업 모집 공고(~9.14)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3742&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3743&amp;page=1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1968,7 +1968,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1976,11 +1976,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1988,44 +1984,44 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:24.927741+09:00</t>
+          <t>2026-08-13 17:46:21.938331+09:00</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:24.927741+09:00</t>
+          <t>2026-08-13 17:46:21.938331+09:00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>34071</t>
+          <t>34081</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>"예방 넘어 대응·복구까지" 랜섬웨어 전주기 대응 방안 논의한다</t>
+          <t>2026년 하반기 정보보호 전문서비스 기업 지정에 관한 공고</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2626&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3742&amp;page=1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2033,42 +2029,46 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-08-13 09:16:35.989405+09:00</t>
+          <t>2026-08-13 09:31:24.927741+09:00</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-08-13 09:16:35.989405+09:00</t>
+          <t>2026-08-13 09:31:24.927741+09:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>33789</t>
+          <t>34071</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>978</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 21회차 교육생 모집(~9.11)</t>
+          <t>"예방 넘어 대응·복구까지" 랜섬웨어 전주기 대응 방안 논의한다</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3741&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2626&amp;page=1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2078,35 +2078,35 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-08-12 16:01:25.579701+09:00</t>
+          <t>2026-08-13 09:16:35.989405+09:00</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-08-12 16:01:25.579701+09:00</t>
+          <t>2026-08-13 09:16:35.989405+09:00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>33749</t>
+          <t>33789</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026년도 블록체인 유공 포상 계획 공고 안내(~9.21 15:00 마감)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 21회차 교육생 모집(~9.11)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3740&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3741&amp;page=1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
@@ -2147,44 +2147,44 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-08-12 15:31:25.306307+09:00</t>
+          <t>2026-08-12 16:01:25.579701+09:00</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-08-12 15:31:25.306307+09:00</t>
+          <t>2026-08-12 16:01:25.579701+09:00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>31741</t>
+          <t>33749</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026년 블록체인 수요-공급 협의체 (ABLE) 정례세미나 개최 안내(8.13.목)</t>
+          <t>2026년도 블록체인 유공 포상 계획 공고 안내(~9.21 15:00 마감)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3739&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3740&amp;page=1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2192,11 +2192,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2204,52 +2200,56 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-08-10 11:01:30.246604+09:00</t>
+          <t>2026-08-12 15:31:25.306307+09:00</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-08-10 11:01:30.246604+09:00</t>
+          <t>2026-08-12 15:31:25.306307+09:00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>29768</t>
+          <t>31741</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026년 블록체인 신뢰인프라(K-BTF) 활용·확산사업 공모 사전예고</t>
+          <t>2026년 블록체인 수요-공급 협의체 (ABLE) 정례세미나 개최 안내(8.13.목)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3738&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3739&amp;page=1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2257,19 +2257,19 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-08-07 17:01:29.954014+09:00</t>
+          <t>2026-08-10 11:01:30.246604+09:00</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-08-07 17:01:29.954014+09:00</t>
+          <t>2026-08-10 11:01:30.246604+09:00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>29728</t>
+          <t>29768</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026년도 블록체인 산업 실태조사 실시 및 협조 안내</t>
+          <t>2026년 블록체인 신뢰인프라(K-BTF) 활용·확산사업 공모 사전예고</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3737&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3738&amp;page=1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2294,7 +2294,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2310,19 +2310,19 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-08-07 16:31:30.938844+09:00</t>
+          <t>2026-08-07 17:01:29.954014+09:00</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-08-07 16:31:30.938844+09:00</t>
+          <t>2026-08-07 17:01:29.954014+09:00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>28711</t>
+          <t>29728</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2332,50 +2332,50 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원-나주시, 고교생 개인정보·정보보호 진로 탐색 지원</t>
+          <t>2026년도 블록체인 산업 실태조사 실시 및 협조 안내</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2625&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3737&amp;page=1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-08-06 14:01:34.968573+09:00</t>
+          <t>2026-08-07 16:31:30.938844+09:00</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-08-06 14:01:34.968573+09:00</t>
+          <t>2026-08-07 16:31:30.938844+09:00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>27551</t>
+          <t>28711</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2385,22 +2385,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 기업 맞춤형 사이버 위협 알림 서비스 개시</t>
+          <t>한국인터넷진흥원-나주시, 고교생 개인정보·정보보호 진로 탐색 지원</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2624&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2625&amp;page=1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2416,44 +2416,44 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-08-05 09:46:34.063806+09:00</t>
+          <t>2026-08-06 14:01:34.968573+09:00</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-08-05 09:46:34.063806+09:00</t>
+          <t>2026-08-06 14:01:34.968573+09:00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>27511</t>
+          <t>27551</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 기관장 주도 국민 체감 성과 혁신 체계 가동</t>
+          <t>한국인터넷진흥원, 기업 맞춤형 사이버 위협 알림 서비스 개시</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2623&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2624&amp;page=1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2469,34 +2469,34 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-08-05 09:16:33.823896+09:00</t>
+          <t>2026-08-05 09:46:34.063806+09:00</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-08-05 09:16:33.823896+09:00</t>
+          <t>2026-08-05 09:46:34.063806+09:00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>27268</t>
+          <t>27511</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>975</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>양자내성암호 국제 표준화 동향 분석</t>
+          <t>한국인터넷진흥원, 기관장 주도 국민 체감 성과 혁신 체계 가동</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3736&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2623&amp;page=1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>263</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2517,24 +2517,24 @@
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-08-04 16:31:26.502205+09:00</t>
+          <t>2026-08-05 09:16:33.823896+09:00</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-08-04 16:31:26.502205+09:00</t>
+          <t>2026-08-05 09:16:33.823896+09:00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>27128</t>
+          <t>27268</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2544,12 +2544,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 20회차 교육생 모집(~9.4)</t>
+          <t>양자내성암호 국제 표준화 동향 분석</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3735&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3736&amp;page=1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
@@ -2575,19 +2575,19 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-08-04 14:46:28.764255+09:00</t>
+          <t>2026-08-04 16:31:26.502205+09:00</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-08-04 14:46:28.764255+09:00</t>
+          <t>2026-08-04 16:31:26.502205+09:00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>26211</t>
+          <t>27128</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2597,50 +2597,50 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 암호모듈검증 위한 시험 전문인력 양성</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 20회차 교육생 모집(~9.4)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2622&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3735&amp;page=1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-08-03 13:31:41.722921+09:00</t>
+          <t>2026-08-04 14:46:28.764255+09:00</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-08-03 13:31:41.722921+09:00</t>
+          <t>2026-08-04 14:46:28.764255+09:00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>26188</t>
+          <t>26211</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2650,12 +2650,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026년 8차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(8월 추천) (~8.21(금) 18시까지)</t>
+          <t>한국인터넷진흥원, 암호모듈검증 위한 시험 전문인력 양성</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3734&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2622&amp;page=1</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2665,7 +2665,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>273</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2676,24 +2676,24 @@
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-08-03 13:16:30.325331+09:00</t>
+          <t>2026-08-03 13:31:41.722921+09:00</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-08-03 13:16:30.325331+09:00</t>
+          <t>2026-08-03 13:31:41.722921+09:00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>25891</t>
+          <t>26188</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2703,12 +2703,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 지역 상생 3대 사업 참여자 모집</t>
+          <t>2026년 8차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(8월 추천) (~8.21(금) 18시까지)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2621&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3734&amp;page=1</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2729,39 +2729,39 @@
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-08-03 09:31:46.854132+09:00</t>
+          <t>2026-08-03 13:16:30.325331+09:00</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-08-03 09:31:46.854132+09:00</t>
+          <t>2026-08-03 13:16:30.325331+09:00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>25864</t>
+          <t>25891</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026년 전남광주통합특별시 소상공인·사회적경제기업 판로 확대 지원기업 선발 안내(~8.14)</t>
+          <t>한국인터넷진흥원, 지역 상생 3대 사업 참여자 모집</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3730&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2621&amp;page=1</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>80</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2779,31 +2779,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-08-03 09:16:35.817723+09:00</t>
+          <t>2026-08-03 09:31:46.854132+09:00</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-08-03 09:16:35.817723+09:00</t>
+          <t>2026-08-03 09:31:46.854132+09:00</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>25863</t>
+          <t>25864</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2813,12 +2809,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026년 전남광주통합특별시 지역문제 해결 프로젝트 공모전 개최 안내(~8.21)</t>
+          <t>2026년 전남광주통합특별시 소상공인·사회적경제기업 판로 확대 지원기업 선발 안내(~8.14)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3731&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3730&amp;page=1</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2828,7 +2824,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2860,7 +2856,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>25862</t>
+          <t>25863</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2870,12 +2866,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026년 한국인터넷진흥원 지역공부방 참여 대학생 장학금 지원자 모집 안내(~8.28)</t>
+          <t>2026년 전남광주통합특별시 지역문제 해결 프로젝트 공모전 개최 안내(~8.21)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3732&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3731&amp;page=1</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2885,7 +2881,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2917,7 +2913,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>25861</t>
+          <t>25862</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2927,12 +2923,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026년 암호모듈 시험자 양성교육 및 필기시험 안내(8.3~8.21)</t>
+          <t>2026년 한국인터넷진흥원 지역공부방 참여 대학생 장학금 지원자 모집 안내(~8.28)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3733&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3732&amp;page=1</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2942,7 +2938,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2974,7 +2970,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>23221</t>
+          <t>25861</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2984,22 +2980,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026년 블록체인 기업성장허브 입주기업 모집(~8월 27일(목) 16:00까지)</t>
+          <t>2026년 암호모듈 시험자 양성교육 및 필기시험 안내(8.3~8.21)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3729&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3733&amp;page=1</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3019,52 +3015,56 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-07-30 17:16:54.540202+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-07-30 17:16:54.540202+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>22504</t>
+          <t>23221</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 19회차 교육생 모집(~8.28)</t>
+          <t>2026년 블록체인 기업성장허브 입주기업 모집(~8월 27일(목) 16:00까지)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3728&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3729&amp;page=1</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I49" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3072,19 +3072,19 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-07-29 18:32:00.075123+09:00</t>
+          <t>2026-07-30 17:16:54.540202+09:00</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-07-29 18:32:00.075123+09:00</t>
+          <t>2026-07-30 17:16:54.540202+09:00</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>22464</t>
+          <t>22504</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026년 연계정보 이용기관 안전조치 실태점검 2차 설명회 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 19회차 교육생 모집(~8.28)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3727&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3728&amp;page=1</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3125,19 +3125,19 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:59.875668+09:00</t>
+          <t>2026-07-29 18:32:00.075123+09:00</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:59.875668+09:00</t>
+          <t>2026-07-29 18:32:00.075123+09:00</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>20771</t>
+          <t>22464</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3147,50 +3147,50 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 성평등가족부와 불법·유해 정보 유통 대응 맞손</t>
+          <t>2026년 연계정보 이용기관 안전조치 실태점검 2차 설명회 개최</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2620&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3727&amp;page=1</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2026-07-27 17:17:05.702970+09:00</t>
+          <t>2026-07-29 18:01:59.875668+09:00</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-07-27 17:17:05.702970+09:00</t>
+          <t>2026-07-29 18:01:59.875668+09:00</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>20191</t>
+          <t>20771</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 향후 10년 설계한다…전담 추진단(TF) 출범</t>
+          <t>한국인터넷진흥원, 성평등가족부와 불법·유해 정보 유통 대응 맞손</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2619&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2620&amp;page=1</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3215,7 +3215,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>150</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3231,34 +3231,34 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2026-07-27 10:02:05.338547+09:00</t>
+          <t>2026-07-27 17:17:05.702970+09:00</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-07-27 10:02:05.338547+09:00</t>
+          <t>2026-07-27 17:17:05.702970+09:00</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>20061</t>
+          <t>20191</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(1차, BreakingPoint)</t>
+          <t>아피가(APIGA) 향후 10년 설계한다…전담 추진단(TF) 출범</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3726&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2619&amp;page=1</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3268,7 +3268,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>287</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3276,64 +3276,64 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2026-07-27 08:31:55.019743+09:00</t>
+          <t>2026-07-27 10:02:05.338547+09:00</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-07-27 08:31:55.019743+09:00</t>
+          <t>2026-07-27 10:02:05.338547+09:00</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>16785</t>
+          <t>20061</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 17회차 교육생 모집(~8.7)</t>
+          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(1차, BreakingPoint)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3724&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3726&amp;page=1</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>246</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3341,34 +3341,34 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 08:31:55.019743+09:00</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 08:31:55.019743+09:00</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>16784</t>
+          <t>16785</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1497</t>
+          <t>1496</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 18회차 교육생 모집(~8.21)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 17회차 교육생 모집(~8.7)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3725&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3724&amp;page=1</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>236</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3406,22 +3406,22 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>16781</t>
+          <t>16784</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1497</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 16회차 교육생 모집(~7.31)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 18회차 교육생 모집(~8.21)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3723&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3725&amp;page=1</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>260</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3439,11 +3439,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3463,22 +3459,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>16691</t>
+          <t>16781</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>'블록체인 기반 예금토큰 결제 인프라 확산' 사업 발대식 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 16회차 교육생 모집(~7.31)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2618&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3723&amp;page=1</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3488,35 +3484,39 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>242</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2026-07-22 17:32:01.526863+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-07-22 17:32:01.526863+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>16464</t>
+          <t>16691</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>[홍보] 정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 안내</t>
+          <t>'블록체인 기반 예금토큰 결제 인프라 확산' 사업 발대식 개최</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3722&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2618&amp;page=1</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3541,35 +3541,35 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>278</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>2026-07-22 14:46:48.687665+09:00</t>
+          <t>2026-07-22 17:32:01.526863+09:00</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-07-22 14:46:48.687665+09:00</t>
+          <t>2026-07-22 17:32:01.526863+09:00</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>16051</t>
+          <t>16464</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3579,12 +3579,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 보안 인재·글로벌 전문가 교류의 장 열어</t>
+          <t>[홍보] 정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 안내</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2617&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3722&amp;page=1</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3594,35 +3594,35 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>2026-07-22 09:31:50.671841+09:00</t>
+          <t>2026-07-22 14:46:48.687665+09:00</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-07-22 09:31:50.671841+09:00</t>
+          <t>2026-07-22 14:46:48.687665+09:00</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>14611</t>
+          <t>16051</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3632,22 +3632,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
+          <t>한국인터넷진흥원, 보안 인재·글로벌 전문가 교류의 장 열어</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2617&amp;page=1</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>233</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3663,19 +3663,19 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>14431</t>
+          <t>14611</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3685,12 +3685,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3700,7 +3700,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>32</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3716,34 +3716,34 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>14431</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3753,7 +3753,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>53</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -3761,56 +3761,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>14444</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>1493</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
+          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -3818,7 +3814,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr"/>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I63" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3826,34 +3826,34 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>11331</t>
+          <t>14444</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -3874,96 +3874,92 @@
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>10981</t>
+          <t>11331</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
+          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>10943</t>
+          <t>10981</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
+          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3973,7 +3969,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -3981,7 +3977,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr"/>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I66" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3989,19 +3989,19 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>10663</t>
+          <t>10943</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
+          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
@@ -4042,19 +4042,19 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>9805</t>
+          <t>10663</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4064,22 +4064,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
+          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -4095,19 +4095,19 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>9691</t>
+          <t>9805</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4117,12 +4117,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
+          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -4143,96 +4143,92 @@
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>9321</t>
+          <t>9691</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
+          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>8871</t>
+          <t>9321</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
+          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4242,35 +4238,39 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>6685</t>
+          <t>8871</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4280,22 +4280,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
+          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -4306,24 +4306,24 @@
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>6571</t>
+          <t>6685</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4333,12 +4333,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
+          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4348,7 +4348,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -4359,24 +4359,24 @@
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>5591</t>
+          <t>6571</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4386,22 +4386,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
+          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -4417,44 +4417,44 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>5591</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
+          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>33</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -4470,44 +4470,44 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>4762</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>961</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>AI 보안 위협 대응 매뉴얼</t>
+          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -4515,31 +4515,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>4761</t>
+          <t>4762</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -4549,12 +4545,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>AI 보안 레드티밍 가이드</t>
+          <t>AI 보안 위협 대응 매뉴얼</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -4564,7 +4560,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -4596,22 +4592,22 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>4251</t>
+          <t>4761</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
+          <t>AI 보안 레드티밍 가이드</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -4621,7 +4617,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -4629,27 +4625,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr"/>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>4251</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4659,12 +4659,12 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
+          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -4674,113 +4674,113 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>191</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t>3867</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
+          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4111</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>959</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
+          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>34</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -4788,31 +4788,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -4822,12 +4818,12 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
+          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -4837,7 +4833,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -4869,32 +4865,32 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
+          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>105</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -4902,7 +4898,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr"/>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I83" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -4922,22 +4922,22 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1477</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
+          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -4947,7 +4947,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>386</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -4975,22 +4975,22 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
+          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5000,19 +5000,15 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>362</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -5032,7 +5028,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5042,12 +5038,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026년 IoT 보안인증 교육과정 안내</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5057,7 +5053,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>522</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -5089,40 +5085,44 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
+          <t>2026년 IoT 보안인증 교육과정 안내</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>652</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I87" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -5142,22 +5142,22 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
+          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>1529</t>
+          <t>818</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -5175,11 +5175,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -5199,32 +5195,32 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
+          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>1529</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -5232,7 +5228,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr"/>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I89" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -5240,34 +5240,34 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>76426</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -5288,49 +5288,49 @@
       <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>958</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
+          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>55906</t>
+          <t>76426</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -5358,22 +5358,22 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>956</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
+          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>55329</t>
+          <t>55906</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -5411,32 +5411,32 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>957</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
+          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>34467</t>
+          <t>55329</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -5464,22 +5464,22 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>955</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
+          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -5489,39 +5489,35 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2945</t>
+          <t>34467</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -5531,27 +5527,27 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>2945</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -5578,32 +5574,32 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>145255</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -5611,52 +5607,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr"/>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>954</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>26576</t>
+          <t>145255</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -5684,32 +5684,32 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>953</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
+          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>34290</t>
+          <t>26576</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -5737,32 +5737,32 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
+          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>184573</t>
+          <t>34290</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -5790,32 +5790,32 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>14403</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>951</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>6587</t>
+          <t>184573</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -5823,46 +5823,42 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14403</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
+          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -5872,7 +5868,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>51749</t>
+          <t>6587</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -5880,52 +5876,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr"/>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>950</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>78439</t>
+          <t>51749</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -5953,55 +5953,108 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>949</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>78439</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>보도자료</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
           <t>38805</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
+      <c r="B104" t="inlineStr">
         <is>
           <t>공지</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
+      <c r="C104" t="inlineStr">
         <is>
           <t>[공유] 지능형 CCTV 성능시험 재개 안내 공지</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr">
+      <c r="D104" t="inlineStr">
         <is>
           <t>https://www.kisa.or.kr/401/form?postSeq=3677&amp;page=1</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
+      <c r="E104" t="inlineStr">
         <is>
           <t>2026-06-02</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
+      <c r="F104" t="inlineStr">
         <is>
           <t>6525</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
+      <c r="G104" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
+      <c r="H104" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>공지사항</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
         <is>
           <t>2026-08-18 17:16:37.364015+09:00</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr">
+      <c r="K104" t="inlineStr">
         <is>
           <t>2026-08-18 17:16:37.364015+09:00</t>
         </is>

--- a/docs/snapshot/downloads/kisa.xlsx
+++ b/docs/snapshot/downloads/kisa.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K104"/>
+  <dimension ref="A1:K105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>61111</t>
+          <t>61484</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -486,22 +486,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>민관 합동 ‘자동차 사이버 침해사고 대응 모의훈련’ 실시</t>
+          <t>2026년 제13회 소프트웨어(SW) 개발보안 경진대회 개최</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2637&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3762&amp;page=1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -512,24 +512,24 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-09-15 15:01:52.747371+09:00</t>
+          <t>2026-09-16 09:46:37.058042+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-09-15 15:01:52.747371+09:00</t>
+          <t>2026-09-16 09:46:37.058042+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>61031</t>
+          <t>61111</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>“새로운 보안 위협, 인공지능(AI)으로 대응” 정보보호 제품 개발 기업 대상 보안 역량 강화 교육 추진</t>
+          <t>민관 합동 ‘자동차 사이버 침해사고 대응 모의훈련’ 실시</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2636&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2637&amp;page=1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -570,44 +570,44 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-09-15 14:01:52.540884+09:00</t>
+          <t>2026-09-15 15:01:52.747371+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-09-15 14:01:52.540884+09:00</t>
+          <t>2026-09-15 15:01:52.747371+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>57381</t>
+          <t>61031</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026 전자문서 유공 포상 공고</t>
+          <t>“새로운 보안 위협, 인공지능(AI)으로 대응” 정보보호 제품 개발 기업 대상 보안 역량 강화 교육 추진</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3761&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2636&amp;page=1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -615,46 +615,42 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-09-10 14:16:31.877229+09:00</t>
+          <t>2026-09-15 14:01:52.540884+09:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-09-10 14:16:31.877229+09:00</t>
+          <t>2026-09-15 14:01:52.540884+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>57149</t>
+          <t>57381</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026년 클라우드 서비스 보안인증(CSAP) 교육 안내</t>
+          <t>2026 전자문서 유공 포상 공고</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3760&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3761&amp;page=1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -664,7 +660,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -672,7 +668,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -680,19 +680,19 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-09-10 10:46:38.794916+09:00</t>
+          <t>2026-09-10 14:16:31.877229+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-09-10 10:46:38.794916+09:00</t>
+          <t>2026-09-10 14:16:31.877229+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>56431</t>
+          <t>57149</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -702,22 +702,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>보호나라 챗봇, 국민 생활 속 정보보호 성과 인정</t>
+          <t>2026년 클라우드 서비스 보안인증(CSAP) 교육 안내</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2634&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3760&amp;page=1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -728,92 +728,92 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-09-09 12:01:35.142670+09:00</t>
+          <t>2026-09-10 10:46:38.794916+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-09-09 12:01:35.142670+09:00</t>
+          <t>2026-09-10 10:46:38.794916+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>56969</t>
+          <t>56431</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1522</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>온마이데이터 서비스 이용 이벤트 안내</t>
+          <t>보호나라 챗봇, 국민 생활 속 정보보호 성과 인정</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3758&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2634&amp;page=1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>402</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-09-10 08:31:37.677434+09:00</t>
+          <t>2026-09-09 12:01:35.142670+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-09-10 08:31:37.677434+09:00</t>
+          <t>2026-09-09 12:01:35.142670+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>54791</t>
+          <t>56969</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1522</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>국내 캐시 도메인이름시스템(DNS) 운영기관, 신규 암호키 반영 여부 확인하세요</t>
+          <t>온마이데이터 서비스 이용 이벤트 안내</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2633&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3758&amp;page=1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -823,60 +823,60 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>402</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-09-07 12:01:35.243341+09:00</t>
+          <t>2026-09-10 08:31:37.677434+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-09-07 12:01:35.243341+09:00</t>
+          <t>2026-09-10 08:31:37.677434+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>54541</t>
+          <t>54791</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(2차, Avalanche)</t>
+          <t>국내 캐시 도메인이름시스템(DNS) 운영기관, 신규 암호키 반영 여부 확인하세요</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3759&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2633&amp;page=1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -884,31 +884,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-09-07 09:01:25.516098+09:00</t>
+          <t>2026-09-07 12:01:35.243341+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-09-07 09:01:25.516098+09:00</t>
+          <t>2026-09-07 12:01:35.243341+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>51281</t>
+          <t>54541</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -918,27 +914,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>(행사 안내) 국외이전 제도 개선 및 CBPR 인증제도 기업 설명회 개최</t>
+          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(2차, Avalanche)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3757&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3759&amp;page=1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -953,52 +949,56 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-09-03 09:16:26.856224+09:00</t>
+          <t>2026-09-07 09:01:25.516098+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-09-03 09:16:26.856224+09:00</t>
+          <t>2026-09-07 09:01:25.516098+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>56970</t>
+          <t>51281</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1521</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026 부산지역 도메인이름 분쟁해결 세미나 개최 안내(9.11)</t>
+          <t>(행사 안내) 국외이전 제도 개선 및 CBPR 인증제도 기업 설명회 개최</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3755&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3757&amp;page=1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>23</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1006,34 +1006,34 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-09-10 08:31:37.677434+09:00</t>
+          <t>2026-09-03 09:16:26.856224+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-09-10 08:31:37.677434+09:00</t>
+          <t>2026-09-03 09:16:26.856224+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>51121</t>
+          <t>56970</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1521</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026년 블록체인 수요공급협의체(ABLE) 블록체인 수요기업(비금융분야) 모집 공고</t>
+          <t>2026 부산지역 도메인이름 분쟁해결 세미나 개최 안내(9.11)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3754&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3755&amp;page=1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>242</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1051,11 +1051,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1063,19 +1059,19 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-09-02 17:31:25.610368+09:00</t>
+          <t>2026-09-10 08:31:37.677434+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-09-02 17:31:25.610368+09:00</t>
+          <t>2026-09-10 08:31:37.677434+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>50601</t>
+          <t>51121</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1085,12 +1081,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026년 9차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(9월 추천) (~9.18(금) 18시까지)</t>
+          <t>2026년 블록체인 수요공급협의체(ABLE) 블록체인 수요기업(비금융분야) 모집 공고</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3753&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3754&amp;page=1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1100,7 +1096,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>24</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1120,44 +1116,44 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-09-02 11:01:32.173328+09:00</t>
+          <t>2026-09-02 17:31:25.610368+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-09-02 11:01:32.173328+09:00</t>
+          <t>2026-09-02 17:31:25.610368+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>49872</t>
+          <t>50601</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>인공지능(AI) 사이버 위협, 실전 모의훈련으로 대응</t>
+          <t>2026년 9차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(9월 추천) (~9.18(금) 18시까지)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2631&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3753&amp;page=1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1165,27 +1161,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-09-01 12:01:47.858504+09:00</t>
+          <t>2026-09-02 11:01:32.173328+09:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-09-01 12:01:47.858504+09:00</t>
+          <t>2026-09-02 11:01:32.173328+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>49669</t>
+          <t>49872</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>「2026 위치정보 맞춤형 컨설팅 참여기업 모집」</t>
+          <t>인공지능(AI) 사이버 위협, 실전 모의훈련으로 대응</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3752&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2631&amp;page=1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1210,35 +1210,35 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-09-01 09:31:38.715793+09:00</t>
+          <t>2026-09-01 12:01:47.858504+09:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-09-01 09:31:38.715793+09:00</t>
+          <t>2026-09-01 12:01:47.858504+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>49631</t>
+          <t>49669</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1248,12 +1248,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>물리보안 시스템 간 연동 장벽 낮춘다</t>
+          <t>「2026 위치정보 맞춤형 컨설팅 참여기업 모집」</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2632&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3752&amp;page=1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1263,103 +1263,103 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-09-01 09:01:45.980040+09:00</t>
+          <t>2026-09-01 09:31:38.715793+09:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-09-01 09:01:45.980040+09:00</t>
+          <t>2026-09-01 09:31:38.715793+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>49589</t>
+          <t>49631</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1517</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 23회차 교육생 모집(~9.18)</t>
+          <t>물리보안 시스템 간 연동 장벽 낮춘다</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3751&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2632&amp;page=1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-09-01 08:31:37.253592+09:00</t>
+          <t>2026-09-01 09:01:45.980040+09:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-09-01 08:31:37.253592+09:00</t>
+          <t>2026-09-01 09:01:45.980040+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>48831</t>
+          <t>49589</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1517</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>생성형 인공지능(AI) 기반 실전형 모의해킹 대회 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 23회차 교육생 모집(~9.18)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2630&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3751&amp;page=1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1369,35 +1369,35 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>174</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-08-31 09:16:38.866405+09:00</t>
+          <t>2026-09-01 08:31:37.253592+09:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-08-31 09:16:38.866405+09:00</t>
+          <t>2026-09-01 08:31:37.253592+09:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>46011</t>
+          <t>48831</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>자동차 노리는 사이버 위협, 한국인터넷진흥원-한국교통안전공단이 함께 대응한다</t>
+          <t>생성형 인공지능(AI) 기반 실전형 모의해킹 대회 개최</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2628&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2630&amp;page=1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1438,34 +1438,34 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-08-27 15:01:41.552844+09:00</t>
+          <t>2026-08-31 09:16:38.866405+09:00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-08-27 15:01:41.552844+09:00</t>
+          <t>2026-08-31 09:16:38.866405+09:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>45681</t>
+          <t>46011</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>싱가포르 현지 진출 지원 국내 블록체인 기업 모집(~9.16(수) 14시)</t>
+          <t>자동차 노리는 사이버 위협, 한국인터넷진흥원-한국교통안전공단이 함께 대응한다</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3750&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2628&amp;page=1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1483,56 +1483,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-08-27 11:01:31.314899+09:00</t>
+          <t>2026-08-27 15:01:41.552844+09:00</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-08-27 11:01:31.314899+09:00</t>
+          <t>2026-08-27 15:01:41.552844+09:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>45191</t>
+          <t>45681</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 아·태 지역 사이버공격 대응 공동 훈련 실시</t>
+          <t>싱가포르 현지 진출 지원 국내 블록체인 기업 모집(~9.16(수) 14시)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2629&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3750&amp;page=1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1540,42 +1536,46 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-08-26 15:01:47.261933+09:00</t>
+          <t>2026-08-27 11:01:31.314899+09:00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-08-26 15:01:47.261933+09:00</t>
+          <t>2026-08-27 11:01:31.314899+09:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>44741</t>
+          <t>45191</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>[3차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~9/16)</t>
+          <t>한국인터넷진흥원, 아·태 지역 사이버공격 대응 공동 훈련 실시</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3749&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2629&amp;page=1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1593,56 +1593,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-08-26 09:31:36.427758+09:00</t>
+          <t>2026-08-26 15:01:47.261933+09:00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-08-26 09:31:36.427758+09:00</t>
+          <t>2026-08-26 15:01:47.261933+09:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>44448</t>
+          <t>44741</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 공고</t>
+          <t>[3차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~9/16)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3748&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3749&amp;page=1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1650,7 +1646,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1658,19 +1658,19 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-08-25 16:01:39.626193+09:00</t>
+          <t>2026-08-26 09:31:36.427758+09:00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-08-25 16:01:39.626193+09:00</t>
+          <t>2026-08-26 09:31:36.427758+09:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>43767</t>
+          <t>44448</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1680,27 +1680,27 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 21회차 교육생 모집(~9.12)</t>
+          <t>정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 공고</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3747&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3748&amp;page=1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
@@ -1711,19 +1711,19 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-08-24 17:46:42.254577+09:00</t>
+          <t>2026-08-25 16:01:39.626193+09:00</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-08-24 17:46:42.254577+09:00</t>
+          <t>2026-08-25 16:01:39.626193+09:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>43311</t>
+          <t>43767</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1733,12 +1733,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>양자내성암호 전환, 어떻게 준비해야 할까?</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 21회차 교육생 모집(~9.12)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2627&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3747&amp;page=1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1748,50 +1748,50 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-08-24 12:01:45.511381+09:00</t>
+          <t>2026-08-24 17:46:42.254577+09:00</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-08-24 12:01:45.511381+09:00</t>
+          <t>2026-08-24 17:46:42.254577+09:00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>43301</t>
+          <t>43311</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>양자내성암호 전문교육 PQC 실무과정 교육생 모집(8.24~)</t>
+          <t>양자내성암호 전환, 어떻게 준비해야 할까?</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3746&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2627&amp;page=1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1809,31 +1809,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-08-24 12:01:36.271108+09:00</t>
+          <t>2026-08-24 12:01:45.511381+09:00</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-08-24 12:01:36.271108+09:00</t>
+          <t>2026-08-24 12:01:45.511381+09:00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>41161</t>
+          <t>43301</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1843,27 +1839,27 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>「블록체인 기업 맞춤형 보안 고도화 지원」 기업 모집(~8/31)</t>
+          <t>양자내성암호 전문교육 PQC 실무과정 교육생 모집(8.24~)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3745&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3746&amp;page=1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1878,34 +1874,34 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-08-21 16:01:38.087170+09:00</t>
+          <t>2026-08-24 12:01:36.271108+09:00</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-08-21 16:01:38.087170+09:00</t>
+          <t>2026-08-24 12:01:36.271108+09:00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>41086</t>
+          <t>41161</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026년도 인터넷거버넌스 민간전문가 APrIGF 및 IGF 참석자 모집</t>
+          <t>「블록체인 기업 맞춤형 보안 고도화 지원」 기업 모집(~8/31)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3744&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3745&amp;page=1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1915,15 +1911,19 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1931,19 +1931,19 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-08-21 15:01:32.139445+09:00</t>
+          <t>2026-08-21 16:01:38.087170+09:00</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-08-21 15:01:32.139445+09:00</t>
+          <t>2026-08-21 16:01:38.087170+09:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>34750</t>
+          <t>41086</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1953,22 +1953,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>｢2026 블록체인 진흥주간｣ 전시부스 참가기업 모집 공고(~9.14)</t>
+          <t>2026년도 인터넷거버넌스 민간전문가 APrIGF 및 IGF 참석자 모집</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3743&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3744&amp;page=1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>59</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1984,34 +1984,34 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-08-13 17:46:21.938331+09:00</t>
+          <t>2026-08-21 15:01:32.139445+09:00</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-08-13 17:46:21.938331+09:00</t>
+          <t>2026-08-21 15:01:32.139445+09:00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>34081</t>
+          <t>34750</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026년 하반기 정보보호 전문서비스 기업 지정에 관한 공고</t>
+          <t>｢2026 블록체인 진흥주간｣ 전시부스 참가기업 모집 공고(~9.14)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3742&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3743&amp;page=1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2029,11 +2029,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2041,44 +2037,44 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:24.927741+09:00</t>
+          <t>2026-08-13 17:46:21.938331+09:00</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:24.927741+09:00</t>
+          <t>2026-08-13 17:46:21.938331+09:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>34071</t>
+          <t>34081</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>"예방 넘어 대응·복구까지" 랜섬웨어 전주기 대응 방안 논의한다</t>
+          <t>2026년 하반기 정보보호 전문서비스 기업 지정에 관한 공고</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2626&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3742&amp;page=1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2086,42 +2082,46 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-08-13 09:16:35.989405+09:00</t>
+          <t>2026-08-13 09:31:24.927741+09:00</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-08-13 09:16:35.989405+09:00</t>
+          <t>2026-08-13 09:31:24.927741+09:00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>33789</t>
+          <t>34071</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>978</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 21회차 교육생 모집(~9.11)</t>
+          <t>"예방 넘어 대응·복구까지" 랜섬웨어 전주기 대응 방안 논의한다</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3741&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2626&amp;page=1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2131,35 +2131,35 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-08-12 16:01:25.579701+09:00</t>
+          <t>2026-08-13 09:16:35.989405+09:00</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-08-12 16:01:25.579701+09:00</t>
+          <t>2026-08-13 09:16:35.989405+09:00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>33749</t>
+          <t>33789</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2169,12 +2169,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026년도 블록체인 유공 포상 계획 공고 안내(~9.21 15:00 마감)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 21회차 교육생 모집(~9.11)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3740&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3741&amp;page=1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2184,12 +2184,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
@@ -2200,44 +2200,44 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-08-12 15:31:25.306307+09:00</t>
+          <t>2026-08-12 16:01:25.579701+09:00</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-08-12 15:31:25.306307+09:00</t>
+          <t>2026-08-12 16:01:25.579701+09:00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>31741</t>
+          <t>33749</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026년 블록체인 수요-공급 협의체 (ABLE) 정례세미나 개최 안내(8.13.목)</t>
+          <t>2026년도 블록체인 유공 포상 계획 공고 안내(~9.21 15:00 마감)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3739&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3740&amp;page=1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2245,11 +2245,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2257,52 +2253,56 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-08-10 11:01:30.246604+09:00</t>
+          <t>2026-08-12 15:31:25.306307+09:00</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-08-10 11:01:30.246604+09:00</t>
+          <t>2026-08-12 15:31:25.306307+09:00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>29768</t>
+          <t>31741</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026년 블록체인 신뢰인프라(K-BTF) 활용·확산사업 공모 사전예고</t>
+          <t>2026년 블록체인 수요-공급 협의체 (ABLE) 정례세미나 개최 안내(8.13.목)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3738&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3739&amp;page=1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I35" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2310,19 +2310,19 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-08-07 17:01:29.954014+09:00</t>
+          <t>2026-08-10 11:01:30.246604+09:00</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-08-07 17:01:29.954014+09:00</t>
+          <t>2026-08-10 11:01:30.246604+09:00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>29728</t>
+          <t>29768</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2332,12 +2332,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026년도 블록체인 산업 실태조사 실시 및 협조 안내</t>
+          <t>2026년 블록체인 신뢰인프라(K-BTF) 활용·확산사업 공모 사전예고</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3737&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3738&amp;page=1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2347,7 +2347,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2363,19 +2363,19 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-08-07 16:31:30.938844+09:00</t>
+          <t>2026-08-07 17:01:29.954014+09:00</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-08-07 16:31:30.938844+09:00</t>
+          <t>2026-08-07 17:01:29.954014+09:00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>28711</t>
+          <t>29728</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2385,50 +2385,50 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원-나주시, 고교생 개인정보·정보보호 진로 탐색 지원</t>
+          <t>2026년도 블록체인 산업 실태조사 실시 및 협조 안내</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2625&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3737&amp;page=1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-08-06 14:01:34.968573+09:00</t>
+          <t>2026-08-07 16:31:30.938844+09:00</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-08-06 14:01:34.968573+09:00</t>
+          <t>2026-08-07 16:31:30.938844+09:00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>27551</t>
+          <t>28711</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2438,22 +2438,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 기업 맞춤형 사이버 위협 알림 서비스 개시</t>
+          <t>한국인터넷진흥원-나주시, 고교생 개인정보·정보보호 진로 탐색 지원</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2624&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2625&amp;page=1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2469,44 +2469,44 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-08-05 09:46:34.063806+09:00</t>
+          <t>2026-08-06 14:01:34.968573+09:00</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-08-05 09:46:34.063806+09:00</t>
+          <t>2026-08-06 14:01:34.968573+09:00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>27511</t>
+          <t>27551</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 기관장 주도 국민 체감 성과 혁신 체계 가동</t>
+          <t>한국인터넷진흥원, 기업 맞춤형 사이버 위협 알림 서비스 개시</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2623&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2624&amp;page=1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2522,34 +2522,34 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-08-05 09:16:33.823896+09:00</t>
+          <t>2026-08-05 09:46:34.063806+09:00</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-08-05 09:16:33.823896+09:00</t>
+          <t>2026-08-05 09:46:34.063806+09:00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>27268</t>
+          <t>27511</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>975</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>양자내성암호 국제 표준화 동향 분석</t>
+          <t>한국인터넷진흥원, 기관장 주도 국민 체감 성과 혁신 체계 가동</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3736&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2623&amp;page=1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>263</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2570,24 +2570,24 @@
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-08-04 16:31:26.502205+09:00</t>
+          <t>2026-08-05 09:16:33.823896+09:00</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-08-04 16:31:26.502205+09:00</t>
+          <t>2026-08-05 09:16:33.823896+09:00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>27128</t>
+          <t>27268</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 20회차 교육생 모집(~9.4)</t>
+          <t>양자내성암호 국제 표준화 동향 분석</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3735&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3736&amp;page=1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2612,12 +2612,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
@@ -2628,19 +2628,19 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-08-04 14:46:28.764255+09:00</t>
+          <t>2026-08-04 16:31:26.502205+09:00</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-08-04 14:46:28.764255+09:00</t>
+          <t>2026-08-04 16:31:26.502205+09:00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>26211</t>
+          <t>27128</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2650,50 +2650,50 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 암호모듈검증 위한 시험 전문인력 양성</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 20회차 교육생 모집(~9.4)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2622&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3735&amp;page=1</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-08-03 13:31:41.722921+09:00</t>
+          <t>2026-08-04 14:46:28.764255+09:00</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-08-03 13:31:41.722921+09:00</t>
+          <t>2026-08-04 14:46:28.764255+09:00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>26188</t>
+          <t>26211</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2703,12 +2703,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026년 8차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(8월 추천) (~8.21(금) 18시까지)</t>
+          <t>한국인터넷진흥원, 암호모듈검증 위한 시험 전문인력 양성</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3734&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2622&amp;page=1</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>273</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2729,24 +2729,24 @@
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-08-03 13:16:30.325331+09:00</t>
+          <t>2026-08-03 13:31:41.722921+09:00</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-08-03 13:16:30.325331+09:00</t>
+          <t>2026-08-03 13:31:41.722921+09:00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>25891</t>
+          <t>26188</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2756,12 +2756,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 지역 상생 3대 사업 참여자 모집</t>
+          <t>2026년 8차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(8월 추천) (~8.21(금) 18시까지)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2621&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3734&amp;page=1</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2782,39 +2782,39 @@
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-08-03 09:31:46.854132+09:00</t>
+          <t>2026-08-03 13:16:30.325331+09:00</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-08-03 09:31:46.854132+09:00</t>
+          <t>2026-08-03 13:16:30.325331+09:00</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>25864</t>
+          <t>25891</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026년 전남광주통합특별시 소상공인·사회적경제기업 판로 확대 지원기업 선발 안내(~8.14)</t>
+          <t>한국인터넷진흥원, 지역 상생 3대 사업 참여자 모집</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3730&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2621&amp;page=1</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>80</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2832,31 +2832,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2026-08-03 09:16:35.817723+09:00</t>
+          <t>2026-08-03 09:31:46.854132+09:00</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-08-03 09:16:35.817723+09:00</t>
+          <t>2026-08-03 09:31:46.854132+09:00</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>25863</t>
+          <t>25864</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2866,12 +2862,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026년 전남광주통합특별시 지역문제 해결 프로젝트 공모전 개최 안내(~8.21)</t>
+          <t>2026년 전남광주통합특별시 소상공인·사회적경제기업 판로 확대 지원기업 선발 안내(~8.14)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3731&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3730&amp;page=1</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2881,7 +2877,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2913,7 +2909,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>25862</t>
+          <t>25863</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2923,12 +2919,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026년 한국인터넷진흥원 지역공부방 참여 대학생 장학금 지원자 모집 안내(~8.28)</t>
+          <t>2026년 전남광주통합특별시 지역문제 해결 프로젝트 공모전 개최 안내(~8.21)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3732&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3731&amp;page=1</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2938,7 +2934,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2970,7 +2966,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>25861</t>
+          <t>25862</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2980,12 +2976,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026년 암호모듈 시험자 양성교육 및 필기시험 안내(8.3~8.21)</t>
+          <t>2026년 한국인터넷진흥원 지역공부방 참여 대학생 장학금 지원자 모집 안내(~8.28)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3733&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3732&amp;page=1</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2995,7 +2991,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3027,7 +3023,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>23221</t>
+          <t>25861</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3037,22 +3033,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026년 블록체인 기업성장허브 입주기업 모집(~8월 27일(목) 16:00까지)</t>
+          <t>2026년 암호모듈 시험자 양성교육 및 필기시험 안내(8.3~8.21)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3729&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3733&amp;page=1</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3072,52 +3068,56 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-07-30 17:16:54.540202+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-07-30 17:16:54.540202+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>22504</t>
+          <t>23221</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 19회차 교육생 모집(~8.28)</t>
+          <t>2026년 블록체인 기업성장허브 입주기업 모집(~8월 27일(목) 16:00까지)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3728&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3729&amp;page=1</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I50" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3125,19 +3125,19 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2026-07-29 18:32:00.075123+09:00</t>
+          <t>2026-07-30 17:16:54.540202+09:00</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-07-29 18:32:00.075123+09:00</t>
+          <t>2026-07-30 17:16:54.540202+09:00</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>22464</t>
+          <t>22504</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3147,12 +3147,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026년 연계정보 이용기관 안전조치 실태점검 2차 설명회 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 19회차 교육생 모집(~8.28)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3727&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3728&amp;page=1</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3178,19 +3178,19 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:59.875668+09:00</t>
+          <t>2026-07-29 18:32:00.075123+09:00</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:59.875668+09:00</t>
+          <t>2026-07-29 18:32:00.075123+09:00</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>20771</t>
+          <t>22464</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3200,50 +3200,50 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 성평등가족부와 불법·유해 정보 유통 대응 맞손</t>
+          <t>2026년 연계정보 이용기관 안전조치 실태점검 2차 설명회 개최</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2620&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3727&amp;page=1</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2026-07-27 17:17:05.702970+09:00</t>
+          <t>2026-07-29 18:01:59.875668+09:00</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-07-27 17:17:05.702970+09:00</t>
+          <t>2026-07-29 18:01:59.875668+09:00</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>20191</t>
+          <t>20771</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3253,12 +3253,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 향후 10년 설계한다…전담 추진단(TF) 출범</t>
+          <t>한국인터넷진흥원, 성평등가족부와 불법·유해 정보 유통 대응 맞손</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2619&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2620&amp;page=1</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3268,7 +3268,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>150</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3284,34 +3284,34 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2026-07-27 10:02:05.338547+09:00</t>
+          <t>2026-07-27 17:17:05.702970+09:00</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-07-27 10:02:05.338547+09:00</t>
+          <t>2026-07-27 17:17:05.702970+09:00</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>20061</t>
+          <t>20191</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(1차, BreakingPoint)</t>
+          <t>아피가(APIGA) 향후 10년 설계한다…전담 추진단(TF) 출범</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3726&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2619&amp;page=1</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>287</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3329,64 +3329,64 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2026-07-27 08:31:55.019743+09:00</t>
+          <t>2026-07-27 10:02:05.338547+09:00</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-07-27 08:31:55.019743+09:00</t>
+          <t>2026-07-27 10:02:05.338547+09:00</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>16785</t>
+          <t>20061</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 17회차 교육생 모집(~8.7)</t>
+          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(1차, BreakingPoint)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3724&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3726&amp;page=1</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>246</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I55" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3394,34 +3394,34 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 08:31:55.019743+09:00</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 08:31:55.019743+09:00</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>16784</t>
+          <t>16785</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1497</t>
+          <t>1496</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 18회차 교육생 모집(~8.21)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 17회차 교육생 모집(~8.7)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3725&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3724&amp;page=1</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>236</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3459,22 +3459,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>16781</t>
+          <t>16784</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1497</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 16회차 교육생 모집(~7.31)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 18회차 교육생 모집(~8.21)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3723&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3725&amp;page=1</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3484,7 +3484,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>260</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3492,11 +3492,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3516,22 +3512,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>16691</t>
+          <t>16781</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>'블록체인 기반 예금토큰 결제 인프라 확산' 사업 발대식 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 16회차 교육생 모집(~7.31)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2618&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3723&amp;page=1</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3541,35 +3537,39 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>242</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>2026-07-22 17:32:01.526863+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-07-22 17:32:01.526863+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>16464</t>
+          <t>16691</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3579,12 +3579,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>[홍보] 정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 안내</t>
+          <t>'블록체인 기반 예금토큰 결제 인프라 확산' 사업 발대식 개최</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3722&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2618&amp;page=1</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3594,35 +3594,35 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>278</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>2026-07-22 14:46:48.687665+09:00</t>
+          <t>2026-07-22 17:32:01.526863+09:00</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-07-22 14:46:48.687665+09:00</t>
+          <t>2026-07-22 17:32:01.526863+09:00</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>16051</t>
+          <t>16464</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 보안 인재·글로벌 전문가 교류의 장 열어</t>
+          <t>[홍보] 정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 안내</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2617&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3722&amp;page=1</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3647,35 +3647,35 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>2026-07-22 09:31:50.671841+09:00</t>
+          <t>2026-07-22 14:46:48.687665+09:00</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-07-22 09:31:50.671841+09:00</t>
+          <t>2026-07-22 14:46:48.687665+09:00</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>14611</t>
+          <t>16051</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3685,22 +3685,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
+          <t>한국인터넷진흥원, 보안 인재·글로벌 전문가 교류의 장 열어</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2617&amp;page=1</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>233</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3716,19 +3716,19 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>14431</t>
+          <t>14611</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3753,7 +3753,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>32</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -3769,34 +3769,34 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>14431</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>53</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -3814,56 +3814,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>14444</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>1493</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
+          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -3871,7 +3867,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr"/>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I64" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3879,34 +3879,34 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>11331</t>
+          <t>14444</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -3927,96 +3927,92 @@
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>10981</t>
+          <t>11331</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
+          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>10943</t>
+          <t>10981</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
+          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4026,7 +4022,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -4034,7 +4030,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr"/>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I67" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -4042,19 +4042,19 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>10663</t>
+          <t>10943</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4064,12 +4064,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
+          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4079,12 +4079,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
@@ -4095,19 +4095,19 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>9805</t>
+          <t>10663</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4117,22 +4117,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
+          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -4148,19 +4148,19 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>9691</t>
+          <t>9805</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4170,12 +4170,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
+          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4185,7 +4185,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -4196,96 +4196,92 @@
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>9321</t>
+          <t>9691</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
+          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>8871</t>
+          <t>9321</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
+          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4295,35 +4291,39 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>6685</t>
+          <t>8871</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4333,22 +4333,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
+          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -4359,24 +4359,24 @@
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>6571</t>
+          <t>6685</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4386,12 +4386,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
+          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -4412,24 +4412,24 @@
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>5591</t>
+          <t>6571</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4439,22 +4439,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
+          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -4470,44 +4470,44 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>5591</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
+          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>33</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -4523,44 +4523,44 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>4762</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>961</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>AI 보안 위협 대응 매뉴얼</t>
+          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -4568,31 +4568,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>4761</t>
+          <t>4762</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -4602,12 +4598,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>AI 보안 레드티밍 가이드</t>
+          <t>AI 보안 위협 대응 매뉴얼</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -4617,7 +4613,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -4649,22 +4645,22 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>4251</t>
+          <t>4761</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
+          <t>AI 보안 레드티밍 가이드</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -4674,7 +4670,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -4682,27 +4678,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr"/>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>4251</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
+          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -4727,113 +4727,113 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>191</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t>3867</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
+          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4111</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>959</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
+          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>34</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -4841,31 +4841,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4875,12 +4871,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
+          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -4890,7 +4886,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -4922,32 +4918,32 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
+          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>105</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -4955,7 +4951,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr"/>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I84" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -4975,22 +4975,22 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1477</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
+          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5000,7 +5000,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>386</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -5028,22 +5028,22 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
+          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5053,19 +5053,15 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>362</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -5085,7 +5081,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5095,12 +5091,12 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2026년 IoT 보안인증 교육과정 안내</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5110,7 +5106,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>522</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -5142,40 +5138,44 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
+          <t>2026년 IoT 보안인증 교육과정 안내</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>652</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I88" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -5195,22 +5195,22 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
+          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5220,7 +5220,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>1529</t>
+          <t>818</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -5228,11 +5228,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -5252,32 +5248,32 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
+          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>1529</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -5285,7 +5281,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr"/>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I90" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -5293,34 +5293,34 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5330,7 +5330,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>76426</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -5341,49 +5341,49 @@
       <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>958</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
+          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>55906</t>
+          <t>76426</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -5411,22 +5411,22 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>956</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
+          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -5436,7 +5436,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>55329</t>
+          <t>55906</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -5464,32 +5464,32 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>957</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
+          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>34467</t>
+          <t>55329</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -5517,22 +5517,22 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>955</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
+          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -5542,39 +5542,35 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2945</t>
+          <t>34467</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -5584,27 +5580,27 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>2945</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -5631,32 +5627,32 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>145255</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -5664,52 +5660,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr"/>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>954</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>26576</t>
+          <t>145255</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -5737,32 +5737,32 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>953</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
+          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>34290</t>
+          <t>26576</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -5790,32 +5790,32 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
+          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>184573</t>
+          <t>34290</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -5843,32 +5843,32 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>14403</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>951</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>6587</t>
+          <t>184573</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -5876,46 +5876,42 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14403</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
+          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -5925,7 +5921,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>51749</t>
+          <t>6587</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -5933,52 +5929,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr"/>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>950</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>78439</t>
+          <t>51749</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -6006,55 +6006,108 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>949</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>78439</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>보도자료</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
           <t>38805</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
+      <c r="B105" t="inlineStr">
         <is>
           <t>공지</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
+      <c r="C105" t="inlineStr">
         <is>
           <t>[공유] 지능형 CCTV 성능시험 재개 안내 공지</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr">
+      <c r="D105" t="inlineStr">
         <is>
           <t>https://www.kisa.or.kr/401/form?postSeq=3677&amp;page=1</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
+      <c r="E105" t="inlineStr">
         <is>
           <t>2026-06-02</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr">
+      <c r="F105" t="inlineStr">
         <is>
           <t>6525</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr">
+      <c r="G105" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
+      <c r="H105" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>공지사항</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
         <is>
           <t>2026-08-18 17:16:37.364015+09:00</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr">
+      <c r="K105" t="inlineStr">
         <is>
           <t>2026-08-18 17:16:37.364015+09:00</t>
         </is>

--- a/docs/snapshot/downloads/kisa.xlsx
+++ b/docs/snapshot/downloads/kisa.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K105"/>
+  <dimension ref="A1:K106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>61484</t>
+          <t>62367</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -486,27 +486,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026년 제13회 소프트웨어(SW) 개발보안 경진대회 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 24회차 교육생 모집(~10.9)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3762&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3763&amp;page=1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -517,19 +517,19 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-09-16 09:46:37.058042+09:00</t>
+          <t>2026-09-17 11:46:35.719751+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-09-16 09:46:37.058042+09:00</t>
+          <t>2026-09-17 11:46:35.719751+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>61111</t>
+          <t>61484</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -539,22 +539,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>민관 합동 ‘자동차 사이버 침해사고 대응 모의훈련’ 실시</t>
+          <t>2026년 제13회 소프트웨어(SW) 개발보안 경진대회 개최</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2637&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3762&amp;page=1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -565,24 +565,24 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-09-15 15:01:52.747371+09:00</t>
+          <t>2026-09-16 09:46:37.058042+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-09-15 15:01:52.747371+09:00</t>
+          <t>2026-09-16 09:46:37.058042+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>61031</t>
+          <t>61111</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -592,12 +592,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>“새로운 보안 위협, 인공지능(AI)으로 대응” 정보보호 제품 개발 기업 대상 보안 역량 강화 교육 추진</t>
+          <t>민관 합동 ‘자동차 사이버 침해사고 대응 모의훈련’ 실시</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2636&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2637&amp;page=1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -623,44 +623,44 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-09-15 14:01:52.540884+09:00</t>
+          <t>2026-09-15 15:01:52.747371+09:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-09-15 14:01:52.540884+09:00</t>
+          <t>2026-09-15 15:01:52.747371+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>57381</t>
+          <t>61031</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026 전자문서 유공 포상 공고</t>
+          <t>“새로운 보안 위협, 인공지능(AI)으로 대응” 정보보호 제품 개발 기업 대상 보안 역량 강화 교육 추진</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3761&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2636&amp;page=1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -668,46 +668,42 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-09-10 14:16:31.877229+09:00</t>
+          <t>2026-09-15 14:01:52.540884+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-09-10 14:16:31.877229+09:00</t>
+          <t>2026-09-15 14:01:52.540884+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>57149</t>
+          <t>57381</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026년 클라우드 서비스 보안인증(CSAP) 교육 안내</t>
+          <t>2026 전자문서 유공 포상 공고</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3760&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3761&amp;page=1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -717,7 +713,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -725,7 +721,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -733,19 +733,19 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-09-10 10:46:38.794916+09:00</t>
+          <t>2026-09-10 14:16:31.877229+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-09-10 10:46:38.794916+09:00</t>
+          <t>2026-09-10 14:16:31.877229+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>56431</t>
+          <t>57149</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -755,22 +755,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>보호나라 챗봇, 국민 생활 속 정보보호 성과 인정</t>
+          <t>2026년 클라우드 서비스 보안인증(CSAP) 교육 안내</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2634&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3760&amp;page=1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -781,92 +781,92 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-09-09 12:01:35.142670+09:00</t>
+          <t>2026-09-10 10:46:38.794916+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-09-09 12:01:35.142670+09:00</t>
+          <t>2026-09-10 10:46:38.794916+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>56969</t>
+          <t>56431</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1522</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>온마이데이터 서비스 이용 이벤트 안내</t>
+          <t>보호나라 챗봇, 국민 생활 속 정보보호 성과 인정</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3758&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2634&amp;page=1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>402</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-09-10 08:31:37.677434+09:00</t>
+          <t>2026-09-09 12:01:35.142670+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-09-10 08:31:37.677434+09:00</t>
+          <t>2026-09-09 12:01:35.142670+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>54791</t>
+          <t>56969</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1522</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>국내 캐시 도메인이름시스템(DNS) 운영기관, 신규 암호키 반영 여부 확인하세요</t>
+          <t>온마이데이터 서비스 이용 이벤트 안내</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2633&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3758&amp;page=1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -876,60 +876,60 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>402</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-09-07 12:01:35.243341+09:00</t>
+          <t>2026-09-10 08:31:37.677434+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-09-07 12:01:35.243341+09:00</t>
+          <t>2026-09-10 08:31:37.677434+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>54541</t>
+          <t>54791</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(2차, Avalanche)</t>
+          <t>국내 캐시 도메인이름시스템(DNS) 운영기관, 신규 암호키 반영 여부 확인하세요</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3759&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2633&amp;page=1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -937,31 +937,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-09-07 09:01:25.516098+09:00</t>
+          <t>2026-09-07 12:01:35.243341+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-09-07 09:01:25.516098+09:00</t>
+          <t>2026-09-07 12:01:35.243341+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>51281</t>
+          <t>54541</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -971,27 +967,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>(행사 안내) 국외이전 제도 개선 및 CBPR 인증제도 기업 설명회 개최</t>
+          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(2차, Avalanche)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3757&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3759&amp;page=1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1006,52 +1002,56 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-09-03 09:16:26.856224+09:00</t>
+          <t>2026-09-07 09:01:25.516098+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-09-03 09:16:26.856224+09:00</t>
+          <t>2026-09-07 09:01:25.516098+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>56970</t>
+          <t>51281</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1521</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026 부산지역 도메인이름 분쟁해결 세미나 개최 안내(9.11)</t>
+          <t>(행사 안내) 국외이전 제도 개선 및 CBPR 인증제도 기업 설명회 개최</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3755&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3757&amp;page=1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>23</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1059,34 +1059,34 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-09-10 08:31:37.677434+09:00</t>
+          <t>2026-09-03 09:16:26.856224+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-09-10 08:31:37.677434+09:00</t>
+          <t>2026-09-03 09:16:26.856224+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>51121</t>
+          <t>56970</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1521</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026년 블록체인 수요공급협의체(ABLE) 블록체인 수요기업(비금융분야) 모집 공고</t>
+          <t>2026 부산지역 도메인이름 분쟁해결 세미나 개최 안내(9.11)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3754&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3755&amp;page=1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>242</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1104,11 +1104,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1116,19 +1112,19 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-09-02 17:31:25.610368+09:00</t>
+          <t>2026-09-10 08:31:37.677434+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-09-02 17:31:25.610368+09:00</t>
+          <t>2026-09-10 08:31:37.677434+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>50601</t>
+          <t>51121</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1138,12 +1134,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026년 9차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(9월 추천) (~9.18(금) 18시까지)</t>
+          <t>2026년 블록체인 수요공급협의체(ABLE) 블록체인 수요기업(비금융분야) 모집 공고</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3753&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3754&amp;page=1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1153,7 +1149,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>24</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1173,44 +1169,44 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-09-02 11:01:32.173328+09:00</t>
+          <t>2026-09-02 17:31:25.610368+09:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-09-02 11:01:32.173328+09:00</t>
+          <t>2026-09-02 17:31:25.610368+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>49872</t>
+          <t>50601</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>인공지능(AI) 사이버 위협, 실전 모의훈련으로 대응</t>
+          <t>2026년 9차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(9월 추천) (~9.18(금) 18시까지)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2631&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3753&amp;page=1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1218,27 +1214,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-09-01 12:01:47.858504+09:00</t>
+          <t>2026-09-02 11:01:32.173328+09:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-09-01 12:01:47.858504+09:00</t>
+          <t>2026-09-02 11:01:32.173328+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>49669</t>
+          <t>49872</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1248,12 +1248,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>「2026 위치정보 맞춤형 컨설팅 참여기업 모집」</t>
+          <t>인공지능(AI) 사이버 위협, 실전 모의훈련으로 대응</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3752&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2631&amp;page=1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1263,35 +1263,35 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-09-01 09:31:38.715793+09:00</t>
+          <t>2026-09-01 12:01:47.858504+09:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-09-01 09:31:38.715793+09:00</t>
+          <t>2026-09-01 12:01:47.858504+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>49631</t>
+          <t>49669</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1301,12 +1301,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>물리보안 시스템 간 연동 장벽 낮춘다</t>
+          <t>「2026 위치정보 맞춤형 컨설팅 참여기업 모집」</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2632&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3752&amp;page=1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1316,103 +1316,103 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-09-01 09:01:45.980040+09:00</t>
+          <t>2026-09-01 09:31:38.715793+09:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-09-01 09:01:45.980040+09:00</t>
+          <t>2026-09-01 09:31:38.715793+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>49589</t>
+          <t>49631</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1517</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 23회차 교육생 모집(~9.18)</t>
+          <t>물리보안 시스템 간 연동 장벽 낮춘다</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3751&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2632&amp;page=1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-09-01 08:31:37.253592+09:00</t>
+          <t>2026-09-01 09:01:45.980040+09:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-09-01 08:31:37.253592+09:00</t>
+          <t>2026-09-01 09:01:45.980040+09:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>48831</t>
+          <t>49589</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1517</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>생성형 인공지능(AI) 기반 실전형 모의해킹 대회 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 23회차 교육생 모집(~9.18)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2630&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3751&amp;page=1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1422,35 +1422,35 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>174</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-08-31 09:16:38.866405+09:00</t>
+          <t>2026-09-01 08:31:37.253592+09:00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-08-31 09:16:38.866405+09:00</t>
+          <t>2026-09-01 08:31:37.253592+09:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>46011</t>
+          <t>48831</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1460,22 +1460,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>자동차 노리는 사이버 위협, 한국인터넷진흥원-한국교통안전공단이 함께 대응한다</t>
+          <t>생성형 인공지능(AI) 기반 실전형 모의해킹 대회 개최</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2628&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2630&amp;page=1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1491,34 +1491,34 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-08-27 15:01:41.552844+09:00</t>
+          <t>2026-08-31 09:16:38.866405+09:00</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-08-27 15:01:41.552844+09:00</t>
+          <t>2026-08-31 09:16:38.866405+09:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>45681</t>
+          <t>46011</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>싱가포르 현지 진출 지원 국내 블록체인 기업 모집(~9.16(수) 14시)</t>
+          <t>자동차 노리는 사이버 위협, 한국인터넷진흥원-한국교통안전공단이 함께 대응한다</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3750&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2628&amp;page=1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1536,56 +1536,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-08-27 11:01:31.314899+09:00</t>
+          <t>2026-08-27 15:01:41.552844+09:00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-08-27 11:01:31.314899+09:00</t>
+          <t>2026-08-27 15:01:41.552844+09:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>45191</t>
+          <t>45681</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 아·태 지역 사이버공격 대응 공동 훈련 실시</t>
+          <t>싱가포르 현지 진출 지원 국내 블록체인 기업 모집(~9.16(수) 14시)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2629&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3750&amp;page=1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1593,42 +1589,46 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-08-26 15:01:47.261933+09:00</t>
+          <t>2026-08-27 11:01:31.314899+09:00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-08-26 15:01:47.261933+09:00</t>
+          <t>2026-08-27 11:01:31.314899+09:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>44741</t>
+          <t>45191</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>[3차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~9/16)</t>
+          <t>한국인터넷진흥원, 아·태 지역 사이버공격 대응 공동 훈련 실시</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3749&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2629&amp;page=1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1646,56 +1646,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-08-26 09:31:36.427758+09:00</t>
+          <t>2026-08-26 15:01:47.261933+09:00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-08-26 09:31:36.427758+09:00</t>
+          <t>2026-08-26 15:01:47.261933+09:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>44448</t>
+          <t>44741</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 공고</t>
+          <t>[3차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~9/16)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3748&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3749&amp;page=1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1703,7 +1699,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1711,19 +1711,19 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-08-25 16:01:39.626193+09:00</t>
+          <t>2026-08-26 09:31:36.427758+09:00</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-08-25 16:01:39.626193+09:00</t>
+          <t>2026-08-26 09:31:36.427758+09:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>43767</t>
+          <t>44448</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1733,27 +1733,27 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 21회차 교육생 모집(~9.12)</t>
+          <t>정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 공고</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3747&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3748&amp;page=1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
@@ -1764,19 +1764,19 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-08-24 17:46:42.254577+09:00</t>
+          <t>2026-08-25 16:01:39.626193+09:00</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-08-24 17:46:42.254577+09:00</t>
+          <t>2026-08-25 16:01:39.626193+09:00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>43311</t>
+          <t>43767</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>양자내성암호 전환, 어떻게 준비해야 할까?</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 21회차 교육생 모집(~9.12)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2627&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3747&amp;page=1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1801,50 +1801,50 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-08-24 12:01:45.511381+09:00</t>
+          <t>2026-08-24 17:46:42.254577+09:00</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-08-24 12:01:45.511381+09:00</t>
+          <t>2026-08-24 17:46:42.254577+09:00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>43301</t>
+          <t>43311</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>양자내성암호 전문교육 PQC 실무과정 교육생 모집(8.24~)</t>
+          <t>양자내성암호 전환, 어떻게 준비해야 할까?</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3746&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2627&amp;page=1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1862,31 +1862,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-08-24 12:01:36.271108+09:00</t>
+          <t>2026-08-24 12:01:45.511381+09:00</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-08-24 12:01:36.271108+09:00</t>
+          <t>2026-08-24 12:01:45.511381+09:00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>41161</t>
+          <t>43301</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1896,27 +1892,27 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>「블록체인 기업 맞춤형 보안 고도화 지원」 기업 모집(~8/31)</t>
+          <t>양자내성암호 전문교육 PQC 실무과정 교육생 모집(8.24~)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3745&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3746&amp;page=1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1931,34 +1927,34 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-08-21 16:01:38.087170+09:00</t>
+          <t>2026-08-24 12:01:36.271108+09:00</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-08-21 16:01:38.087170+09:00</t>
+          <t>2026-08-24 12:01:36.271108+09:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>41086</t>
+          <t>41161</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026년도 인터넷거버넌스 민간전문가 APrIGF 및 IGF 참석자 모집</t>
+          <t>「블록체인 기업 맞춤형 보안 고도화 지원」 기업 모집(~8/31)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3744&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3745&amp;page=1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1968,15 +1964,19 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1984,19 +1984,19 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-08-21 15:01:32.139445+09:00</t>
+          <t>2026-08-21 16:01:38.087170+09:00</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-08-21 15:01:32.139445+09:00</t>
+          <t>2026-08-21 16:01:38.087170+09:00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>34750</t>
+          <t>41086</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2006,22 +2006,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>｢2026 블록체인 진흥주간｣ 전시부스 참가기업 모집 공고(~9.14)</t>
+          <t>2026년도 인터넷거버넌스 민간전문가 APrIGF 및 IGF 참석자 모집</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3743&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3744&amp;page=1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>59</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2037,34 +2037,34 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-08-13 17:46:21.938331+09:00</t>
+          <t>2026-08-21 15:01:32.139445+09:00</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-08-13 17:46:21.938331+09:00</t>
+          <t>2026-08-21 15:01:32.139445+09:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>34081</t>
+          <t>34750</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026년 하반기 정보보호 전문서비스 기업 지정에 관한 공고</t>
+          <t>｢2026 블록체인 진흥주간｣ 전시부스 참가기업 모집 공고(~9.14)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3742&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3743&amp;page=1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2082,11 +2082,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2094,44 +2090,44 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:24.927741+09:00</t>
+          <t>2026-08-13 17:46:21.938331+09:00</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:24.927741+09:00</t>
+          <t>2026-08-13 17:46:21.938331+09:00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>34071</t>
+          <t>34081</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>"예방 넘어 대응·복구까지" 랜섬웨어 전주기 대응 방안 논의한다</t>
+          <t>2026년 하반기 정보보호 전문서비스 기업 지정에 관한 공고</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2626&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3742&amp;page=1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2139,42 +2135,46 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-08-13 09:16:35.989405+09:00</t>
+          <t>2026-08-13 09:31:24.927741+09:00</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-08-13 09:16:35.989405+09:00</t>
+          <t>2026-08-13 09:31:24.927741+09:00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>33789</t>
+          <t>34071</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>978</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 21회차 교육생 모집(~9.11)</t>
+          <t>"예방 넘어 대응·복구까지" 랜섬웨어 전주기 대응 방안 논의한다</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3741&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2626&amp;page=1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2184,35 +2184,35 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-08-12 16:01:25.579701+09:00</t>
+          <t>2026-08-13 09:16:35.989405+09:00</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-08-12 16:01:25.579701+09:00</t>
+          <t>2026-08-13 09:16:35.989405+09:00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>33749</t>
+          <t>33789</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026년도 블록체인 유공 포상 계획 공고 안내(~9.21 15:00 마감)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 21회차 교육생 모집(~9.11)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3740&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3741&amp;page=1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2237,12 +2237,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
@@ -2253,44 +2253,44 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-08-12 15:31:25.306307+09:00</t>
+          <t>2026-08-12 16:01:25.579701+09:00</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-08-12 15:31:25.306307+09:00</t>
+          <t>2026-08-12 16:01:25.579701+09:00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>31741</t>
+          <t>33749</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026년 블록체인 수요-공급 협의체 (ABLE) 정례세미나 개최 안내(8.13.목)</t>
+          <t>2026년도 블록체인 유공 포상 계획 공고 안내(~9.21 15:00 마감)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3739&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3740&amp;page=1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2298,11 +2298,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2310,52 +2306,56 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-08-10 11:01:30.246604+09:00</t>
+          <t>2026-08-12 15:31:25.306307+09:00</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-08-10 11:01:30.246604+09:00</t>
+          <t>2026-08-12 15:31:25.306307+09:00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>29768</t>
+          <t>31741</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026년 블록체인 신뢰인프라(K-BTF) 활용·확산사업 공모 사전예고</t>
+          <t>2026년 블록체인 수요-공급 협의체 (ABLE) 정례세미나 개최 안내(8.13.목)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3738&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3739&amp;page=1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2363,19 +2363,19 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-08-07 17:01:29.954014+09:00</t>
+          <t>2026-08-10 11:01:30.246604+09:00</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-08-07 17:01:29.954014+09:00</t>
+          <t>2026-08-10 11:01:30.246604+09:00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>29728</t>
+          <t>29768</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2385,12 +2385,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026년도 블록체인 산업 실태조사 실시 및 협조 안내</t>
+          <t>2026년 블록체인 신뢰인프라(K-BTF) 활용·확산사업 공모 사전예고</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3737&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3738&amp;page=1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2400,7 +2400,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2416,19 +2416,19 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-08-07 16:31:30.938844+09:00</t>
+          <t>2026-08-07 17:01:29.954014+09:00</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-08-07 16:31:30.938844+09:00</t>
+          <t>2026-08-07 17:01:29.954014+09:00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>28711</t>
+          <t>29728</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2438,50 +2438,50 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원-나주시, 고교생 개인정보·정보보호 진로 탐색 지원</t>
+          <t>2026년도 블록체인 산업 실태조사 실시 및 협조 안내</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2625&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3737&amp;page=1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-08-06 14:01:34.968573+09:00</t>
+          <t>2026-08-07 16:31:30.938844+09:00</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-08-06 14:01:34.968573+09:00</t>
+          <t>2026-08-07 16:31:30.938844+09:00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>27551</t>
+          <t>28711</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 기업 맞춤형 사이버 위협 알림 서비스 개시</t>
+          <t>한국인터넷진흥원-나주시, 고교생 개인정보·정보보호 진로 탐색 지원</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2624&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2625&amp;page=1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2522,44 +2522,44 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-08-05 09:46:34.063806+09:00</t>
+          <t>2026-08-06 14:01:34.968573+09:00</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-08-05 09:46:34.063806+09:00</t>
+          <t>2026-08-06 14:01:34.968573+09:00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>27511</t>
+          <t>27551</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 기관장 주도 국민 체감 성과 혁신 체계 가동</t>
+          <t>한국인터넷진흥원, 기업 맞춤형 사이버 위협 알림 서비스 개시</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2623&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2624&amp;page=1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2575,34 +2575,34 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-08-05 09:16:33.823896+09:00</t>
+          <t>2026-08-05 09:46:34.063806+09:00</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-08-05 09:16:33.823896+09:00</t>
+          <t>2026-08-05 09:46:34.063806+09:00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>27268</t>
+          <t>27511</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>975</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>양자내성암호 국제 표준화 동향 분석</t>
+          <t>한국인터넷진흥원, 기관장 주도 국민 체감 성과 혁신 체계 가동</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3736&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2623&amp;page=1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>263</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2623,24 +2623,24 @@
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-08-04 16:31:26.502205+09:00</t>
+          <t>2026-08-05 09:16:33.823896+09:00</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-08-04 16:31:26.502205+09:00</t>
+          <t>2026-08-05 09:16:33.823896+09:00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>27128</t>
+          <t>27268</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2650,12 +2650,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 20회차 교육생 모집(~9.4)</t>
+          <t>양자내성암호 국제 표준화 동향 분석</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3735&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3736&amp;page=1</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2665,12 +2665,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
@@ -2681,19 +2681,19 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-08-04 14:46:28.764255+09:00</t>
+          <t>2026-08-04 16:31:26.502205+09:00</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-08-04 14:46:28.764255+09:00</t>
+          <t>2026-08-04 16:31:26.502205+09:00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>26211</t>
+          <t>27128</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2703,50 +2703,50 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 암호모듈검증 위한 시험 전문인력 양성</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 20회차 교육생 모집(~9.4)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2622&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3735&amp;page=1</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-08-03 13:31:41.722921+09:00</t>
+          <t>2026-08-04 14:46:28.764255+09:00</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-08-03 13:31:41.722921+09:00</t>
+          <t>2026-08-04 14:46:28.764255+09:00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>26188</t>
+          <t>26211</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2756,12 +2756,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026년 8차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(8월 추천) (~8.21(금) 18시까지)</t>
+          <t>한국인터넷진흥원, 암호모듈검증 위한 시험 전문인력 양성</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3734&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2622&amp;page=1</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>273</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2782,24 +2782,24 @@
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-08-03 13:16:30.325331+09:00</t>
+          <t>2026-08-03 13:31:41.722921+09:00</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-08-03 13:16:30.325331+09:00</t>
+          <t>2026-08-03 13:31:41.722921+09:00</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>25891</t>
+          <t>26188</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2809,12 +2809,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 지역 상생 3대 사업 참여자 모집</t>
+          <t>2026년 8차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(8월 추천) (~8.21(금) 18시까지)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2621&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3734&amp;page=1</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2835,39 +2835,39 @@
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2026-08-03 09:31:46.854132+09:00</t>
+          <t>2026-08-03 13:16:30.325331+09:00</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-08-03 09:31:46.854132+09:00</t>
+          <t>2026-08-03 13:16:30.325331+09:00</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>25864</t>
+          <t>25891</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026년 전남광주통합특별시 소상공인·사회적경제기업 판로 확대 지원기업 선발 안내(~8.14)</t>
+          <t>한국인터넷진흥원, 지역 상생 3대 사업 참여자 모집</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3730&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2621&amp;page=1</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>80</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2885,31 +2885,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2026-08-03 09:16:35.817723+09:00</t>
+          <t>2026-08-03 09:31:46.854132+09:00</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-08-03 09:16:35.817723+09:00</t>
+          <t>2026-08-03 09:31:46.854132+09:00</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>25863</t>
+          <t>25864</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2919,12 +2915,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026년 전남광주통합특별시 지역문제 해결 프로젝트 공모전 개최 안내(~8.21)</t>
+          <t>2026년 전남광주통합특별시 소상공인·사회적경제기업 판로 확대 지원기업 선발 안내(~8.14)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3731&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3730&amp;page=1</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2934,7 +2930,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2966,7 +2962,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>25862</t>
+          <t>25863</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2976,12 +2972,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026년 한국인터넷진흥원 지역공부방 참여 대학생 장학금 지원자 모집 안내(~8.28)</t>
+          <t>2026년 전남광주통합특별시 지역문제 해결 프로젝트 공모전 개최 안내(~8.21)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3732&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3731&amp;page=1</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2991,7 +2987,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3023,7 +3019,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>25861</t>
+          <t>25862</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3033,12 +3029,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026년 암호모듈 시험자 양성교육 및 필기시험 안내(8.3~8.21)</t>
+          <t>2026년 한국인터넷진흥원 지역공부방 참여 대학생 장학금 지원자 모집 안내(~8.28)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3733&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3732&amp;page=1</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3048,7 +3044,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3080,7 +3076,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>23221</t>
+          <t>25861</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3090,22 +3086,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026년 블록체인 기업성장허브 입주기업 모집(~8월 27일(목) 16:00까지)</t>
+          <t>2026년 암호모듈 시험자 양성교육 및 필기시험 안내(8.3~8.21)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3729&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3733&amp;page=1</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3125,52 +3121,56 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2026-07-30 17:16:54.540202+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-07-30 17:16:54.540202+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>22504</t>
+          <t>23221</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 19회차 교육생 모집(~8.28)</t>
+          <t>2026년 블록체인 기업성장허브 입주기업 모집(~8월 27일(목) 16:00까지)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3728&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3729&amp;page=1</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I51" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3178,19 +3178,19 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2026-07-29 18:32:00.075123+09:00</t>
+          <t>2026-07-30 17:16:54.540202+09:00</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-07-29 18:32:00.075123+09:00</t>
+          <t>2026-07-30 17:16:54.540202+09:00</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>22464</t>
+          <t>22504</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026년 연계정보 이용기관 안전조치 실태점검 2차 설명회 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 19회차 교육생 모집(~8.28)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3727&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3728&amp;page=1</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3215,7 +3215,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3231,19 +3231,19 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:59.875668+09:00</t>
+          <t>2026-07-29 18:32:00.075123+09:00</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:59.875668+09:00</t>
+          <t>2026-07-29 18:32:00.075123+09:00</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>20771</t>
+          <t>22464</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3253,50 +3253,50 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 성평등가족부와 불법·유해 정보 유통 대응 맞손</t>
+          <t>2026년 연계정보 이용기관 안전조치 실태점검 2차 설명회 개최</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2620&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3727&amp;page=1</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2026-07-27 17:17:05.702970+09:00</t>
+          <t>2026-07-29 18:01:59.875668+09:00</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-07-27 17:17:05.702970+09:00</t>
+          <t>2026-07-29 18:01:59.875668+09:00</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>20191</t>
+          <t>20771</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3306,12 +3306,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 향후 10년 설계한다…전담 추진단(TF) 출범</t>
+          <t>한국인터넷진흥원, 성평등가족부와 불법·유해 정보 유통 대응 맞손</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2619&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2620&amp;page=1</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>150</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3337,34 +3337,34 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2026-07-27 10:02:05.338547+09:00</t>
+          <t>2026-07-27 17:17:05.702970+09:00</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-07-27 10:02:05.338547+09:00</t>
+          <t>2026-07-27 17:17:05.702970+09:00</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>20061</t>
+          <t>20191</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(1차, BreakingPoint)</t>
+          <t>아피가(APIGA) 향후 10년 설계한다…전담 추진단(TF) 출범</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3726&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2619&amp;page=1</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>287</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3382,64 +3382,64 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2026-07-27 08:31:55.019743+09:00</t>
+          <t>2026-07-27 10:02:05.338547+09:00</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-07-27 08:31:55.019743+09:00</t>
+          <t>2026-07-27 10:02:05.338547+09:00</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>16785</t>
+          <t>20061</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 17회차 교육생 모집(~8.7)</t>
+          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(1차, BreakingPoint)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3724&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3726&amp;page=1</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>246</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3447,34 +3447,34 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 08:31:55.019743+09:00</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 08:31:55.019743+09:00</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>16784</t>
+          <t>16785</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1497</t>
+          <t>1496</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 18회차 교육생 모집(~8.21)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 17회차 교육생 모집(~8.7)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3725&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3724&amp;page=1</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3484,7 +3484,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>236</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3512,22 +3512,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>16781</t>
+          <t>16784</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1497</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 16회차 교육생 모집(~7.31)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 18회차 교육생 모집(~8.21)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3723&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3725&amp;page=1</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>260</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3545,11 +3545,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3569,22 +3565,22 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>16691</t>
+          <t>16781</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>'블록체인 기반 예금토큰 결제 인프라 확산' 사업 발대식 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 16회차 교육생 모집(~7.31)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2618&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3723&amp;page=1</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3594,35 +3590,39 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>242</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>2026-07-22 17:32:01.526863+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-07-22 17:32:01.526863+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>16464</t>
+          <t>16691</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>[홍보] 정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 안내</t>
+          <t>'블록체인 기반 예금토큰 결제 인프라 확산' 사업 발대식 개최</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3722&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2618&amp;page=1</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3647,35 +3647,35 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>278</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>2026-07-22 14:46:48.687665+09:00</t>
+          <t>2026-07-22 17:32:01.526863+09:00</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-07-22 14:46:48.687665+09:00</t>
+          <t>2026-07-22 17:32:01.526863+09:00</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>16051</t>
+          <t>16464</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3685,12 +3685,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 보안 인재·글로벌 전문가 교류의 장 열어</t>
+          <t>[홍보] 정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 안내</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2617&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3722&amp;page=1</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3700,35 +3700,35 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>2026-07-22 09:31:50.671841+09:00</t>
+          <t>2026-07-22 14:46:48.687665+09:00</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-07-22 09:31:50.671841+09:00</t>
+          <t>2026-07-22 14:46:48.687665+09:00</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>14611</t>
+          <t>16051</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3738,22 +3738,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
+          <t>한국인터넷진흥원, 보안 인재·글로벌 전문가 교류의 장 열어</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2617&amp;page=1</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>233</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -3769,19 +3769,19 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>14431</t>
+          <t>14611</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3791,12 +3791,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>32</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -3822,34 +3822,34 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>14431</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>53</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -3867,56 +3867,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>14444</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>1493</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
+          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -3924,7 +3920,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr"/>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I65" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3932,34 +3932,34 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>11331</t>
+          <t>14444</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -3980,96 +3980,92 @@
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>10981</t>
+          <t>11331</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
+          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>10943</t>
+          <t>10981</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
+          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4079,7 +4075,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -4087,7 +4083,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr"/>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I68" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -4095,19 +4095,19 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>10663</t>
+          <t>10943</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4117,12 +4117,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
+          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4132,12 +4132,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
@@ -4148,19 +4148,19 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>9805</t>
+          <t>10663</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4170,22 +4170,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
+          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -4201,19 +4201,19 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>9691</t>
+          <t>9805</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4223,12 +4223,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
+          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4238,7 +4238,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -4249,96 +4249,92 @@
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>9321</t>
+          <t>9691</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
+          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>8871</t>
+          <t>9321</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
+          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4348,35 +4344,39 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>6685</t>
+          <t>8871</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4386,22 +4386,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
+          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -4412,24 +4412,24 @@
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>6571</t>
+          <t>6685</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4439,12 +4439,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
+          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4454,7 +4454,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -4465,24 +4465,24 @@
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>5591</t>
+          <t>6571</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -4492,22 +4492,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
+          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -4523,44 +4523,44 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>5591</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
+          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>33</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -4576,44 +4576,44 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>4762</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>961</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>AI 보안 위협 대응 매뉴얼</t>
+          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -4621,31 +4621,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>4761</t>
+          <t>4762</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4655,12 +4651,12 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>AI 보안 레드티밍 가이드</t>
+          <t>AI 보안 위협 대응 매뉴얼</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -4670,7 +4666,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -4702,22 +4698,22 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>4251</t>
+          <t>4761</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
+          <t>AI 보안 레드티밍 가이드</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -4727,7 +4723,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -4735,27 +4731,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr"/>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>4251</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4765,12 +4765,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
+          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -4780,113 +4780,113 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>191</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t>3867</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
+          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4111</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>959</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
+          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>34</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -4894,31 +4894,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4928,12 +4924,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
+          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -4943,7 +4939,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -4975,32 +4971,32 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
+          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>105</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -5008,7 +5004,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr"/>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I85" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -5028,22 +5028,22 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1477</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
+          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5053,7 +5053,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>386</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -5081,22 +5081,22 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
+          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5106,19 +5106,15 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>362</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -5138,7 +5134,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5148,12 +5144,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2026년 IoT 보안인증 교육과정 안내</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5163,7 +5159,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>522</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -5195,40 +5191,44 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
+          <t>2026년 IoT 보안인증 교육과정 안내</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>652</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I89" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -5248,22 +5248,22 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
+          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5273,7 +5273,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>1529</t>
+          <t>818</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -5281,11 +5281,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -5305,32 +5301,32 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
+          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>1529</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -5338,7 +5334,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr"/>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I91" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -5346,34 +5346,34 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>76426</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -5394,49 +5394,49 @@
       <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>958</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
+          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>55906</t>
+          <t>76426</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -5464,22 +5464,22 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>956</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
+          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -5489,7 +5489,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>55329</t>
+          <t>55906</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -5517,32 +5517,32 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>957</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
+          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>34467</t>
+          <t>55329</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -5570,22 +5570,22 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>955</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
+          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -5595,39 +5595,35 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2945</t>
+          <t>34467</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -5637,27 +5633,27 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>2945</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -5684,32 +5680,32 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>145255</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -5717,52 +5713,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr"/>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>954</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>26576</t>
+          <t>145255</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -5790,32 +5790,32 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>953</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
+          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>34290</t>
+          <t>26576</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -5843,32 +5843,32 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
+          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>184573</t>
+          <t>34290</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -5896,32 +5896,32 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>14403</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>951</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>6587</t>
+          <t>184573</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -5929,46 +5929,42 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14403</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
+          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -5978,7 +5974,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>51749</t>
+          <t>6587</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -5986,52 +5982,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr"/>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>950</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>78439</t>
+          <t>51749</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -6059,55 +6059,108 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>949</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>78439</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>보도자료</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
           <t>38805</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
+      <c r="B106" t="inlineStr">
         <is>
           <t>공지</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
+      <c r="C106" t="inlineStr">
         <is>
           <t>[공유] 지능형 CCTV 성능시험 재개 안내 공지</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr">
+      <c r="D106" t="inlineStr">
         <is>
           <t>https://www.kisa.or.kr/401/form?postSeq=3677&amp;page=1</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr">
+      <c r="E106" t="inlineStr">
         <is>
           <t>2026-06-02</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr">
+      <c r="F106" t="inlineStr">
         <is>
           <t>6525</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr">
+      <c r="G106" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
+      <c r="H106" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>공지사항</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
         <is>
           <t>2026-08-18 17:16:37.364015+09:00</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr">
+      <c r="K106" t="inlineStr">
         <is>
           <t>2026-08-18 17:16:37.364015+09:00</t>
         </is>

--- a/docs/snapshot/downloads/kisa.xlsx
+++ b/docs/snapshot/downloads/kisa.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K106"/>
+  <dimension ref="A1:K107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>62367</t>
+          <t>62507</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -486,12 +486,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 24회차 교육생 모집(~10.9)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 25회차 교육생 모집(~10.10)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3763&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3764&amp;page=1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -501,7 +501,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -517,19 +517,19 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-09-17 11:46:35.719751+09:00</t>
+          <t>2026-09-17 13:31:33.789948+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-09-17 11:46:35.719751+09:00</t>
+          <t>2026-09-17 13:31:33.789948+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>61484</t>
+          <t>62367</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -539,27 +539,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026년 제13회 소프트웨어(SW) 개발보안 경진대회 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 24회차 교육생 모집(~10.9)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3762&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3763&amp;page=1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -570,19 +570,19 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-09-16 09:46:37.058042+09:00</t>
+          <t>2026-09-17 11:46:35.719751+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-09-16 09:46:37.058042+09:00</t>
+          <t>2026-09-17 11:46:35.719751+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>61111</t>
+          <t>61484</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -592,22 +592,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>민관 합동 ‘자동차 사이버 침해사고 대응 모의훈련’ 실시</t>
+          <t>2026년 제13회 소프트웨어(SW) 개발보안 경진대회 개최</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2637&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3762&amp;page=1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -618,24 +618,24 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-09-15 15:01:52.747371+09:00</t>
+          <t>2026-09-16 09:46:37.058042+09:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-09-15 15:01:52.747371+09:00</t>
+          <t>2026-09-16 09:46:37.058042+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>61031</t>
+          <t>61111</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -645,12 +645,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>“새로운 보안 위협, 인공지능(AI)으로 대응” 정보보호 제품 개발 기업 대상 보안 역량 강화 교육 추진</t>
+          <t>민관 합동 ‘자동차 사이버 침해사고 대응 모의훈련’ 실시</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2636&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2637&amp;page=1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -676,44 +676,44 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-09-15 14:01:52.540884+09:00</t>
+          <t>2026-09-15 15:01:52.747371+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-09-15 14:01:52.540884+09:00</t>
+          <t>2026-09-15 15:01:52.747371+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>57381</t>
+          <t>61031</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026 전자문서 유공 포상 공고</t>
+          <t>“새로운 보안 위협, 인공지능(AI)으로 대응” 정보보호 제품 개발 기업 대상 보안 역량 강화 교육 추진</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3761&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2636&amp;page=1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -721,46 +721,42 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-09-10 14:16:31.877229+09:00</t>
+          <t>2026-09-15 14:01:52.540884+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-09-10 14:16:31.877229+09:00</t>
+          <t>2026-09-15 14:01:52.540884+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>57149</t>
+          <t>57381</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026년 클라우드 서비스 보안인증(CSAP) 교육 안내</t>
+          <t>2026 전자문서 유공 포상 공고</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3760&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3761&amp;page=1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -770,7 +766,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -778,7 +774,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -786,19 +786,19 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-09-10 10:46:38.794916+09:00</t>
+          <t>2026-09-10 14:16:31.877229+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-09-10 10:46:38.794916+09:00</t>
+          <t>2026-09-10 14:16:31.877229+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>56431</t>
+          <t>57149</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -808,22 +808,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>보호나라 챗봇, 국민 생활 속 정보보호 성과 인정</t>
+          <t>2026년 클라우드 서비스 보안인증(CSAP) 교육 안내</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2634&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3760&amp;page=1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -834,92 +834,92 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-09-09 12:01:35.142670+09:00</t>
+          <t>2026-09-10 10:46:38.794916+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-09-09 12:01:35.142670+09:00</t>
+          <t>2026-09-10 10:46:38.794916+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>56969</t>
+          <t>56431</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1522</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>온마이데이터 서비스 이용 이벤트 안내</t>
+          <t>보호나라 챗봇, 국민 생활 속 정보보호 성과 인정</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3758&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2634&amp;page=1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>402</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-09-10 08:31:37.677434+09:00</t>
+          <t>2026-09-09 12:01:35.142670+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-09-10 08:31:37.677434+09:00</t>
+          <t>2026-09-09 12:01:35.142670+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>54791</t>
+          <t>56969</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1522</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>국내 캐시 도메인이름시스템(DNS) 운영기관, 신규 암호키 반영 여부 확인하세요</t>
+          <t>온마이데이터 서비스 이용 이벤트 안내</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2633&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3758&amp;page=1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -929,60 +929,60 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>402</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-09-07 12:01:35.243341+09:00</t>
+          <t>2026-09-10 08:31:37.677434+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-09-07 12:01:35.243341+09:00</t>
+          <t>2026-09-10 08:31:37.677434+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>54541</t>
+          <t>54791</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(2차, Avalanche)</t>
+          <t>국내 캐시 도메인이름시스템(DNS) 운영기관, 신규 암호키 반영 여부 확인하세요</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3759&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2633&amp;page=1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -990,31 +990,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-09-07 09:01:25.516098+09:00</t>
+          <t>2026-09-07 12:01:35.243341+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-09-07 09:01:25.516098+09:00</t>
+          <t>2026-09-07 12:01:35.243341+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>51281</t>
+          <t>54541</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1024,27 +1020,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>(행사 안내) 국외이전 제도 개선 및 CBPR 인증제도 기업 설명회 개최</t>
+          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(2차, Avalanche)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3757&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3759&amp;page=1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1059,52 +1055,56 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-09-03 09:16:26.856224+09:00</t>
+          <t>2026-09-07 09:01:25.516098+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-09-03 09:16:26.856224+09:00</t>
+          <t>2026-09-07 09:01:25.516098+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>56970</t>
+          <t>51281</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1521</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026 부산지역 도메인이름 분쟁해결 세미나 개최 안내(9.11)</t>
+          <t>(행사 안내) 국외이전 제도 개선 및 CBPR 인증제도 기업 설명회 개최</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3755&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3757&amp;page=1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>23</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1112,34 +1112,34 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-09-10 08:31:37.677434+09:00</t>
+          <t>2026-09-03 09:16:26.856224+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-09-10 08:31:37.677434+09:00</t>
+          <t>2026-09-03 09:16:26.856224+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>51121</t>
+          <t>56970</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1521</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026년 블록체인 수요공급협의체(ABLE) 블록체인 수요기업(비금융분야) 모집 공고</t>
+          <t>2026 부산지역 도메인이름 분쟁해결 세미나 개최 안내(9.11)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3754&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3755&amp;page=1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>242</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1157,11 +1157,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1169,19 +1165,19 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-09-02 17:31:25.610368+09:00</t>
+          <t>2026-09-10 08:31:37.677434+09:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-09-02 17:31:25.610368+09:00</t>
+          <t>2026-09-10 08:31:37.677434+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>50601</t>
+          <t>51121</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1191,12 +1187,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026년 9차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(9월 추천) (~9.18(금) 18시까지)</t>
+          <t>2026년 블록체인 수요공급협의체(ABLE) 블록체인 수요기업(비금융분야) 모집 공고</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3753&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3754&amp;page=1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1206,7 +1202,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>24</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1226,44 +1222,44 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-09-02 11:01:32.173328+09:00</t>
+          <t>2026-09-02 17:31:25.610368+09:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-09-02 11:01:32.173328+09:00</t>
+          <t>2026-09-02 17:31:25.610368+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>49872</t>
+          <t>50601</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>인공지능(AI) 사이버 위협, 실전 모의훈련으로 대응</t>
+          <t>2026년 9차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(9월 추천) (~9.18(금) 18시까지)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2631&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3753&amp;page=1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1271,27 +1267,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-09-01 12:01:47.858504+09:00</t>
+          <t>2026-09-02 11:01:32.173328+09:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-09-01 12:01:47.858504+09:00</t>
+          <t>2026-09-02 11:01:32.173328+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>49669</t>
+          <t>49872</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1301,12 +1301,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>「2026 위치정보 맞춤형 컨설팅 참여기업 모집」</t>
+          <t>인공지능(AI) 사이버 위협, 실전 모의훈련으로 대응</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3752&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2631&amp;page=1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1316,35 +1316,35 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-09-01 09:31:38.715793+09:00</t>
+          <t>2026-09-01 12:01:47.858504+09:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-09-01 09:31:38.715793+09:00</t>
+          <t>2026-09-01 12:01:47.858504+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>49631</t>
+          <t>49669</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>물리보안 시스템 간 연동 장벽 낮춘다</t>
+          <t>「2026 위치정보 맞춤형 컨설팅 참여기업 모집」</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2632&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3752&amp;page=1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1369,103 +1369,103 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-09-01 09:01:45.980040+09:00</t>
+          <t>2026-09-01 09:31:38.715793+09:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-09-01 09:01:45.980040+09:00</t>
+          <t>2026-09-01 09:31:38.715793+09:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>49589</t>
+          <t>49631</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1517</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 23회차 교육생 모집(~9.18)</t>
+          <t>물리보안 시스템 간 연동 장벽 낮춘다</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3751&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2632&amp;page=1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-09-01 08:31:37.253592+09:00</t>
+          <t>2026-09-01 09:01:45.980040+09:00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-09-01 08:31:37.253592+09:00</t>
+          <t>2026-09-01 09:01:45.980040+09:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>48831</t>
+          <t>49589</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1517</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>생성형 인공지능(AI) 기반 실전형 모의해킹 대회 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 23회차 교육생 모집(~9.18)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2630&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3751&amp;page=1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1475,35 +1475,35 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>174</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-08-31 09:16:38.866405+09:00</t>
+          <t>2026-09-01 08:31:37.253592+09:00</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-08-31 09:16:38.866405+09:00</t>
+          <t>2026-09-01 08:31:37.253592+09:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>46011</t>
+          <t>48831</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1513,22 +1513,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>자동차 노리는 사이버 위협, 한국인터넷진흥원-한국교통안전공단이 함께 대응한다</t>
+          <t>생성형 인공지능(AI) 기반 실전형 모의해킹 대회 개최</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2628&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2630&amp;page=1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1544,34 +1544,34 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-08-27 15:01:41.552844+09:00</t>
+          <t>2026-08-31 09:16:38.866405+09:00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-08-27 15:01:41.552844+09:00</t>
+          <t>2026-08-31 09:16:38.866405+09:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>45681</t>
+          <t>46011</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>싱가포르 현지 진출 지원 국내 블록체인 기업 모집(~9.16(수) 14시)</t>
+          <t>자동차 노리는 사이버 위협, 한국인터넷진흥원-한국교통안전공단이 함께 대응한다</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3750&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2628&amp;page=1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1589,56 +1589,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-08-27 11:01:31.314899+09:00</t>
+          <t>2026-08-27 15:01:41.552844+09:00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-08-27 11:01:31.314899+09:00</t>
+          <t>2026-08-27 15:01:41.552844+09:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>45191</t>
+          <t>45681</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 아·태 지역 사이버공격 대응 공동 훈련 실시</t>
+          <t>싱가포르 현지 진출 지원 국내 블록체인 기업 모집(~9.16(수) 14시)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2629&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3750&amp;page=1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1646,42 +1642,46 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-08-26 15:01:47.261933+09:00</t>
+          <t>2026-08-27 11:01:31.314899+09:00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-08-26 15:01:47.261933+09:00</t>
+          <t>2026-08-27 11:01:31.314899+09:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>44741</t>
+          <t>45191</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>[3차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~9/16)</t>
+          <t>한국인터넷진흥원, 아·태 지역 사이버공격 대응 공동 훈련 실시</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3749&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2629&amp;page=1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1699,56 +1699,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-08-26 09:31:36.427758+09:00</t>
+          <t>2026-08-26 15:01:47.261933+09:00</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-08-26 09:31:36.427758+09:00</t>
+          <t>2026-08-26 15:01:47.261933+09:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>44448</t>
+          <t>44741</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 공고</t>
+          <t>[3차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~9/16)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3748&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3749&amp;page=1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1756,7 +1752,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1764,19 +1764,19 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-08-25 16:01:39.626193+09:00</t>
+          <t>2026-08-26 09:31:36.427758+09:00</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-08-25 16:01:39.626193+09:00</t>
+          <t>2026-08-26 09:31:36.427758+09:00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>43767</t>
+          <t>44448</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1786,27 +1786,27 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 21회차 교육생 모집(~9.12)</t>
+          <t>정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 공고</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3747&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3748&amp;page=1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
@@ -1817,19 +1817,19 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-08-24 17:46:42.254577+09:00</t>
+          <t>2026-08-25 16:01:39.626193+09:00</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-08-24 17:46:42.254577+09:00</t>
+          <t>2026-08-25 16:01:39.626193+09:00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>43311</t>
+          <t>43767</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>양자내성암호 전환, 어떻게 준비해야 할까?</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 21회차 교육생 모집(~9.12)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2627&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3747&amp;page=1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1854,50 +1854,50 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-08-24 12:01:45.511381+09:00</t>
+          <t>2026-08-24 17:46:42.254577+09:00</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-08-24 12:01:45.511381+09:00</t>
+          <t>2026-08-24 17:46:42.254577+09:00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>43301</t>
+          <t>43311</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>양자내성암호 전문교육 PQC 실무과정 교육생 모집(8.24~)</t>
+          <t>양자내성암호 전환, 어떻게 준비해야 할까?</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3746&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2627&amp;page=1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1915,31 +1915,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-08-24 12:01:36.271108+09:00</t>
+          <t>2026-08-24 12:01:45.511381+09:00</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-08-24 12:01:36.271108+09:00</t>
+          <t>2026-08-24 12:01:45.511381+09:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>41161</t>
+          <t>43301</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1949,27 +1945,27 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>「블록체인 기업 맞춤형 보안 고도화 지원」 기업 모집(~8/31)</t>
+          <t>양자내성암호 전문교육 PQC 실무과정 교육생 모집(8.24~)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3745&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3746&amp;page=1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1984,34 +1980,34 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-08-21 16:01:38.087170+09:00</t>
+          <t>2026-08-24 12:01:36.271108+09:00</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-08-21 16:01:38.087170+09:00</t>
+          <t>2026-08-24 12:01:36.271108+09:00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>41086</t>
+          <t>41161</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026년도 인터넷거버넌스 민간전문가 APrIGF 및 IGF 참석자 모집</t>
+          <t>「블록체인 기업 맞춤형 보안 고도화 지원」 기업 모집(~8/31)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3744&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3745&amp;page=1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2021,15 +2017,19 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2037,19 +2037,19 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-08-21 15:01:32.139445+09:00</t>
+          <t>2026-08-21 16:01:38.087170+09:00</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-08-21 15:01:32.139445+09:00</t>
+          <t>2026-08-21 16:01:38.087170+09:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>34750</t>
+          <t>41086</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2059,22 +2059,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>｢2026 블록체인 진흥주간｣ 전시부스 참가기업 모집 공고(~9.14)</t>
+          <t>2026년도 인터넷거버넌스 민간전문가 APrIGF 및 IGF 참석자 모집</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3743&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3744&amp;page=1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>59</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2090,34 +2090,34 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-08-13 17:46:21.938331+09:00</t>
+          <t>2026-08-21 15:01:32.139445+09:00</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-08-13 17:46:21.938331+09:00</t>
+          <t>2026-08-21 15:01:32.139445+09:00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>34081</t>
+          <t>34750</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026년 하반기 정보보호 전문서비스 기업 지정에 관한 공고</t>
+          <t>｢2026 블록체인 진흥주간｣ 전시부스 참가기업 모집 공고(~9.14)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3742&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3743&amp;page=1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2127,7 +2127,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2135,11 +2135,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2147,44 +2143,44 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:24.927741+09:00</t>
+          <t>2026-08-13 17:46:21.938331+09:00</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:24.927741+09:00</t>
+          <t>2026-08-13 17:46:21.938331+09:00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>34071</t>
+          <t>34081</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>"예방 넘어 대응·복구까지" 랜섬웨어 전주기 대응 방안 논의한다</t>
+          <t>2026년 하반기 정보보호 전문서비스 기업 지정에 관한 공고</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2626&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3742&amp;page=1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2192,42 +2188,46 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-08-13 09:16:35.989405+09:00</t>
+          <t>2026-08-13 09:31:24.927741+09:00</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-08-13 09:16:35.989405+09:00</t>
+          <t>2026-08-13 09:31:24.927741+09:00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>33789</t>
+          <t>34071</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>978</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 21회차 교육생 모집(~9.11)</t>
+          <t>"예방 넘어 대응·복구까지" 랜섬웨어 전주기 대응 방안 논의한다</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3741&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2626&amp;page=1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2237,35 +2237,35 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-08-12 16:01:25.579701+09:00</t>
+          <t>2026-08-13 09:16:35.989405+09:00</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-08-12 16:01:25.579701+09:00</t>
+          <t>2026-08-13 09:16:35.989405+09:00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>33749</t>
+          <t>33789</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2275,12 +2275,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026년도 블록체인 유공 포상 계획 공고 안내(~9.21 15:00 마감)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 21회차 교육생 모집(~9.11)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3740&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3741&amp;page=1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2290,12 +2290,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
@@ -2306,44 +2306,44 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-08-12 15:31:25.306307+09:00</t>
+          <t>2026-08-12 16:01:25.579701+09:00</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-08-12 15:31:25.306307+09:00</t>
+          <t>2026-08-12 16:01:25.579701+09:00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>31741</t>
+          <t>33749</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026년 블록체인 수요-공급 협의체 (ABLE) 정례세미나 개최 안내(8.13.목)</t>
+          <t>2026년도 블록체인 유공 포상 계획 공고 안내(~9.21 15:00 마감)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3739&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3740&amp;page=1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2351,11 +2351,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2363,52 +2359,56 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-08-10 11:01:30.246604+09:00</t>
+          <t>2026-08-12 15:31:25.306307+09:00</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-08-10 11:01:30.246604+09:00</t>
+          <t>2026-08-12 15:31:25.306307+09:00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>29768</t>
+          <t>31741</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026년 블록체인 신뢰인프라(K-BTF) 활용·확산사업 공모 사전예고</t>
+          <t>2026년 블록체인 수요-공급 협의체 (ABLE) 정례세미나 개최 안내(8.13.목)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3738&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3739&amp;page=1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2416,19 +2416,19 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-08-07 17:01:29.954014+09:00</t>
+          <t>2026-08-10 11:01:30.246604+09:00</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-08-07 17:01:29.954014+09:00</t>
+          <t>2026-08-10 11:01:30.246604+09:00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>29728</t>
+          <t>29768</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2438,12 +2438,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026년도 블록체인 산업 실태조사 실시 및 협조 안내</t>
+          <t>2026년 블록체인 신뢰인프라(K-BTF) 활용·확산사업 공모 사전예고</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3737&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3738&amp;page=1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2469,19 +2469,19 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-08-07 16:31:30.938844+09:00</t>
+          <t>2026-08-07 17:01:29.954014+09:00</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-08-07 16:31:30.938844+09:00</t>
+          <t>2026-08-07 17:01:29.954014+09:00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>28711</t>
+          <t>29728</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2491,50 +2491,50 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원-나주시, 고교생 개인정보·정보보호 진로 탐색 지원</t>
+          <t>2026년도 블록체인 산업 실태조사 실시 및 협조 안내</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2625&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3737&amp;page=1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-08-06 14:01:34.968573+09:00</t>
+          <t>2026-08-07 16:31:30.938844+09:00</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-08-06 14:01:34.968573+09:00</t>
+          <t>2026-08-07 16:31:30.938844+09:00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>27551</t>
+          <t>28711</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2544,22 +2544,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 기업 맞춤형 사이버 위협 알림 서비스 개시</t>
+          <t>한국인터넷진흥원-나주시, 고교생 개인정보·정보보호 진로 탐색 지원</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2624&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2625&amp;page=1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2575,44 +2575,44 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-08-05 09:46:34.063806+09:00</t>
+          <t>2026-08-06 14:01:34.968573+09:00</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-08-05 09:46:34.063806+09:00</t>
+          <t>2026-08-06 14:01:34.968573+09:00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>27511</t>
+          <t>27551</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 기관장 주도 국민 체감 성과 혁신 체계 가동</t>
+          <t>한국인터넷진흥원, 기업 맞춤형 사이버 위협 알림 서비스 개시</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2623&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2624&amp;page=1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2628,34 +2628,34 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-08-05 09:16:33.823896+09:00</t>
+          <t>2026-08-05 09:46:34.063806+09:00</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-08-05 09:16:33.823896+09:00</t>
+          <t>2026-08-05 09:46:34.063806+09:00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>27268</t>
+          <t>27511</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>975</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>양자내성암호 국제 표준화 동향 분석</t>
+          <t>한국인터넷진흥원, 기관장 주도 국민 체감 성과 혁신 체계 가동</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3736&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2623&amp;page=1</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2665,7 +2665,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>263</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2676,24 +2676,24 @@
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-08-04 16:31:26.502205+09:00</t>
+          <t>2026-08-05 09:16:33.823896+09:00</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-08-04 16:31:26.502205+09:00</t>
+          <t>2026-08-05 09:16:33.823896+09:00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>27128</t>
+          <t>27268</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2703,12 +2703,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 20회차 교육생 모집(~9.4)</t>
+          <t>양자내성암호 국제 표준화 동향 분석</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3735&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3736&amp;page=1</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2718,12 +2718,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
@@ -2734,19 +2734,19 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-08-04 14:46:28.764255+09:00</t>
+          <t>2026-08-04 16:31:26.502205+09:00</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-08-04 14:46:28.764255+09:00</t>
+          <t>2026-08-04 16:31:26.502205+09:00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>26211</t>
+          <t>27128</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2756,50 +2756,50 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 암호모듈검증 위한 시험 전문인력 양성</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 20회차 교육생 모집(~9.4)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2622&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3735&amp;page=1</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-08-03 13:31:41.722921+09:00</t>
+          <t>2026-08-04 14:46:28.764255+09:00</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-08-03 13:31:41.722921+09:00</t>
+          <t>2026-08-04 14:46:28.764255+09:00</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>26188</t>
+          <t>26211</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2809,12 +2809,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026년 8차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(8월 추천) (~8.21(금) 18시까지)</t>
+          <t>한국인터넷진흥원, 암호모듈검증 위한 시험 전문인력 양성</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3734&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2622&amp;page=1</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>273</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2835,24 +2835,24 @@
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2026-08-03 13:16:30.325331+09:00</t>
+          <t>2026-08-03 13:31:41.722921+09:00</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-08-03 13:16:30.325331+09:00</t>
+          <t>2026-08-03 13:31:41.722921+09:00</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>25891</t>
+          <t>26188</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 지역 상생 3대 사업 참여자 모집</t>
+          <t>2026년 8차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(8월 추천) (~8.21(금) 18시까지)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2621&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3734&amp;page=1</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2888,39 +2888,39 @@
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2026-08-03 09:31:46.854132+09:00</t>
+          <t>2026-08-03 13:16:30.325331+09:00</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-08-03 09:31:46.854132+09:00</t>
+          <t>2026-08-03 13:16:30.325331+09:00</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>25864</t>
+          <t>25891</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026년 전남광주통합특별시 소상공인·사회적경제기업 판로 확대 지원기업 선발 안내(~8.14)</t>
+          <t>한국인터넷진흥원, 지역 상생 3대 사업 참여자 모집</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3730&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2621&amp;page=1</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>80</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2938,31 +2938,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2026-08-03 09:16:35.817723+09:00</t>
+          <t>2026-08-03 09:31:46.854132+09:00</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-08-03 09:16:35.817723+09:00</t>
+          <t>2026-08-03 09:31:46.854132+09:00</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>25863</t>
+          <t>25864</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2972,12 +2968,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026년 전남광주통합특별시 지역문제 해결 프로젝트 공모전 개최 안내(~8.21)</t>
+          <t>2026년 전남광주통합특별시 소상공인·사회적경제기업 판로 확대 지원기업 선발 안내(~8.14)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3731&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3730&amp;page=1</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2987,7 +2983,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3019,7 +3015,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>25862</t>
+          <t>25863</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3029,12 +3025,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026년 한국인터넷진흥원 지역공부방 참여 대학생 장학금 지원자 모집 안내(~8.28)</t>
+          <t>2026년 전남광주통합특별시 지역문제 해결 프로젝트 공모전 개최 안내(~8.21)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3732&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3731&amp;page=1</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3044,7 +3040,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3076,7 +3072,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>25861</t>
+          <t>25862</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3086,12 +3082,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026년 암호모듈 시험자 양성교육 및 필기시험 안내(8.3~8.21)</t>
+          <t>2026년 한국인터넷진흥원 지역공부방 참여 대학생 장학금 지원자 모집 안내(~8.28)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3733&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3732&amp;page=1</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3101,7 +3097,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3133,7 +3129,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>23221</t>
+          <t>25861</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3143,22 +3139,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026년 블록체인 기업성장허브 입주기업 모집(~8월 27일(목) 16:00까지)</t>
+          <t>2026년 암호모듈 시험자 양성교육 및 필기시험 안내(8.3~8.21)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3729&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3733&amp;page=1</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3178,52 +3174,56 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2026-07-30 17:16:54.540202+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-07-30 17:16:54.540202+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>22504</t>
+          <t>23221</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 19회차 교육생 모집(~8.28)</t>
+          <t>2026년 블록체인 기업성장허브 입주기업 모집(~8월 27일(목) 16:00까지)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3728&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3729&amp;page=1</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I52" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3231,19 +3231,19 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2026-07-29 18:32:00.075123+09:00</t>
+          <t>2026-07-30 17:16:54.540202+09:00</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-07-29 18:32:00.075123+09:00</t>
+          <t>2026-07-30 17:16:54.540202+09:00</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>22464</t>
+          <t>22504</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3253,12 +3253,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026년 연계정보 이용기관 안전조치 실태점검 2차 설명회 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 19회차 교육생 모집(~8.28)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3727&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3728&amp;page=1</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3268,7 +3268,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3284,19 +3284,19 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:59.875668+09:00</t>
+          <t>2026-07-29 18:32:00.075123+09:00</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:59.875668+09:00</t>
+          <t>2026-07-29 18:32:00.075123+09:00</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>20771</t>
+          <t>22464</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3306,50 +3306,50 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 성평등가족부와 불법·유해 정보 유통 대응 맞손</t>
+          <t>2026년 연계정보 이용기관 안전조치 실태점검 2차 설명회 개최</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2620&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3727&amp;page=1</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2026-07-27 17:17:05.702970+09:00</t>
+          <t>2026-07-29 18:01:59.875668+09:00</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-07-27 17:17:05.702970+09:00</t>
+          <t>2026-07-29 18:01:59.875668+09:00</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>20191</t>
+          <t>20771</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3359,12 +3359,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 향후 10년 설계한다…전담 추진단(TF) 출범</t>
+          <t>한국인터넷진흥원, 성평등가족부와 불법·유해 정보 유통 대응 맞손</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2619&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2620&amp;page=1</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>150</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3390,34 +3390,34 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2026-07-27 10:02:05.338547+09:00</t>
+          <t>2026-07-27 17:17:05.702970+09:00</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-07-27 10:02:05.338547+09:00</t>
+          <t>2026-07-27 17:17:05.702970+09:00</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>20061</t>
+          <t>20191</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(1차, BreakingPoint)</t>
+          <t>아피가(APIGA) 향후 10년 설계한다…전담 추진단(TF) 출범</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3726&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2619&amp;page=1</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>287</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3435,64 +3435,64 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2026-07-27 08:31:55.019743+09:00</t>
+          <t>2026-07-27 10:02:05.338547+09:00</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-07-27 08:31:55.019743+09:00</t>
+          <t>2026-07-27 10:02:05.338547+09:00</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>16785</t>
+          <t>20061</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 17회차 교육생 모집(~8.7)</t>
+          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(1차, BreakingPoint)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3724&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3726&amp;page=1</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>246</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3500,34 +3500,34 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 08:31:55.019743+09:00</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 08:31:55.019743+09:00</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>16784</t>
+          <t>16785</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>1497</t>
+          <t>1496</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 18회차 교육생 모집(~8.21)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 17회차 교육생 모집(~8.7)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3725&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3724&amp;page=1</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>236</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3565,22 +3565,22 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>16781</t>
+          <t>16784</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1497</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 16회차 교육생 모집(~7.31)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 18회차 교육생 모집(~8.21)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3723&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3725&amp;page=1</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>260</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3598,11 +3598,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3622,22 +3618,22 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>16691</t>
+          <t>16781</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>'블록체인 기반 예금토큰 결제 인프라 확산' 사업 발대식 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 16회차 교육생 모집(~7.31)</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2618&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3723&amp;page=1</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3647,35 +3643,39 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>242</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>2026-07-22 17:32:01.526863+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-07-22 17:32:01.526863+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>16464</t>
+          <t>16691</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3685,12 +3685,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>[홍보] 정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 안내</t>
+          <t>'블록체인 기반 예금토큰 결제 인프라 확산' 사업 발대식 개최</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3722&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2618&amp;page=1</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3700,35 +3700,35 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>278</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>2026-07-22 14:46:48.687665+09:00</t>
+          <t>2026-07-22 17:32:01.526863+09:00</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-07-22 14:46:48.687665+09:00</t>
+          <t>2026-07-22 17:32:01.526863+09:00</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>16051</t>
+          <t>16464</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 보안 인재·글로벌 전문가 교류의 장 열어</t>
+          <t>[홍보] 정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 안내</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2617&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3722&amp;page=1</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3753,35 +3753,35 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2026-07-22 09:31:50.671841+09:00</t>
+          <t>2026-07-22 14:46:48.687665+09:00</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-07-22 09:31:50.671841+09:00</t>
+          <t>2026-07-22 14:46:48.687665+09:00</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>14611</t>
+          <t>16051</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3791,22 +3791,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
+          <t>한국인터넷진흥원, 보안 인재·글로벌 전문가 교류의 장 열어</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2617&amp;page=1</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>233</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -3822,19 +3822,19 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>14431</t>
+          <t>14611</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3844,12 +3844,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>32</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -3875,34 +3875,34 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>14431</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>53</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -3920,56 +3920,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>14444</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>1493</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
+          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -3977,7 +3973,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr"/>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I66" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3985,34 +3985,34 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>11331</t>
+          <t>14444</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -4033,96 +4033,92 @@
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>10981</t>
+          <t>11331</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
+          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>10943</t>
+          <t>10981</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
+          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4132,7 +4128,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -4140,7 +4136,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I69" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -4148,19 +4148,19 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>10663</t>
+          <t>10943</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4170,12 +4170,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
+          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4185,12 +4185,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
@@ -4201,19 +4201,19 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>9805</t>
+          <t>10663</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4223,22 +4223,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
+          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -4254,19 +4254,19 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>9691</t>
+          <t>9805</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4276,12 +4276,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
+          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4291,7 +4291,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -4302,96 +4302,92 @@
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>9321</t>
+          <t>9691</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
+          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>8871</t>
+          <t>9321</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
+          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4401,35 +4397,39 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>6685</t>
+          <t>8871</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4439,22 +4439,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
+          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -4465,24 +4465,24 @@
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>6571</t>
+          <t>6685</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -4492,12 +4492,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
+          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -4518,24 +4518,24 @@
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>5591</t>
+          <t>6571</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -4545,22 +4545,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
+          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -4576,44 +4576,44 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>5591</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
+          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>33</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -4629,44 +4629,44 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>4762</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>961</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>AI 보안 위협 대응 매뉴얼</t>
+          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -4674,31 +4674,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>4761</t>
+          <t>4762</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -4708,12 +4704,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>AI 보안 레드티밍 가이드</t>
+          <t>AI 보안 위협 대응 매뉴얼</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -4723,7 +4719,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -4755,22 +4751,22 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>4251</t>
+          <t>4761</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
+          <t>AI 보안 레드티밍 가이드</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -4780,7 +4776,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -4788,27 +4784,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr"/>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>4251</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -4818,12 +4818,12 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
+          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -4833,113 +4833,113 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>191</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t>3867</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
+          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4111</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>959</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
+          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>34</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -4947,31 +4947,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4981,12 +4977,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
+          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -4996,7 +4992,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -5028,32 +5024,32 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
+          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>105</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -5061,7 +5057,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr"/>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I86" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -5081,22 +5081,22 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1477</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
+          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>386</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -5134,22 +5134,22 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
+          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5159,19 +5159,15 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>362</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -5191,7 +5187,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5201,12 +5197,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2026년 IoT 보안인증 교육과정 안내</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5216,7 +5212,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>522</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -5248,40 +5244,44 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
+          <t>2026년 IoT 보안인증 교육과정 안내</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>652</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I90" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -5301,22 +5301,22 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
+          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>1529</t>
+          <t>818</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -5334,11 +5334,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -5358,32 +5354,32 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
+          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>1529</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -5391,7 +5387,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr"/>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I92" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -5399,34 +5399,34 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -5436,7 +5436,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>76426</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -5447,49 +5447,49 @@
       <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>958</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
+          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>55906</t>
+          <t>76426</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -5517,22 +5517,22 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>956</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
+          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -5542,7 +5542,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>55329</t>
+          <t>55906</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -5570,32 +5570,32 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>957</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
+          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>34467</t>
+          <t>55329</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -5623,22 +5623,22 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>955</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
+          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -5648,39 +5648,35 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2945</t>
+          <t>34467</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -5690,27 +5686,27 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>2945</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -5737,32 +5733,32 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>145255</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -5770,52 +5766,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr"/>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>954</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>26576</t>
+          <t>145255</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -5843,32 +5843,32 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>953</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
+          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>34290</t>
+          <t>26576</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -5896,32 +5896,32 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
+          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>184573</t>
+          <t>34290</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -5949,32 +5949,32 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>14403</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>951</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>6587</t>
+          <t>184573</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -5982,46 +5982,42 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14403</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
+          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6031,7 +6027,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>51749</t>
+          <t>6587</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -6039,52 +6035,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr"/>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>950</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>78439</t>
+          <t>51749</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -6112,55 +6112,108 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>949</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>78439</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>보도자료</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
           <t>38805</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
+      <c r="B107" t="inlineStr">
         <is>
           <t>공지</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr">
+      <c r="C107" t="inlineStr">
         <is>
           <t>[공유] 지능형 CCTV 성능시험 재개 안내 공지</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr">
+      <c r="D107" t="inlineStr">
         <is>
           <t>https://www.kisa.or.kr/401/form?postSeq=3677&amp;page=1</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr">
+      <c r="E107" t="inlineStr">
         <is>
           <t>2026-06-02</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr">
+      <c r="F107" t="inlineStr">
         <is>
           <t>6525</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr">
+      <c r="G107" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
+      <c r="H107" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>공지사항</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
         <is>
           <t>2026-08-18 17:16:37.364015+09:00</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr">
+      <c r="K107" t="inlineStr">
         <is>
           <t>2026-08-18 17:16:37.364015+09:00</t>
         </is>

--- a/docs/snapshot/downloads/kisa.xlsx
+++ b/docs/snapshot/downloads/kisa.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K107"/>
+  <dimension ref="A1:K108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,22 +476,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>62507</t>
+          <t>62781</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 25회차 교육생 모집(~10.10)</t>
+          <t>2026년 블록체인 기업성장허브 입주기업 모집(~10월 7일(수) 16:00까지)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3764&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3765&amp;page=1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -501,15 +501,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -517,19 +521,19 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:31:33.789948+09:00</t>
+          <t>2026-09-17 17:16:36.514530+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:31:33.789948+09:00</t>
+          <t>2026-09-17 17:16:36.514530+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>62367</t>
+          <t>62507</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -539,12 +543,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 24회차 교육생 모집(~10.9)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 25회차 교육생 모집(~10.10)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3763&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3764&amp;page=1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -554,7 +558,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -570,19 +574,19 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-09-17 11:46:35.719751+09:00</t>
+          <t>2026-09-17 13:31:33.789948+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-09-17 11:46:35.719751+09:00</t>
+          <t>2026-09-17 13:31:33.789948+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>61484</t>
+          <t>62367</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -592,27 +596,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026년 제13회 소프트웨어(SW) 개발보안 경진대회 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 24회차 교육생 모집(~10.9)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3762&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3763&amp;page=1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -623,19 +627,19 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-09-16 09:46:37.058042+09:00</t>
+          <t>2026-09-17 11:46:35.719751+09:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-09-16 09:46:37.058042+09:00</t>
+          <t>2026-09-17 11:46:35.719751+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>61111</t>
+          <t>61484</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -645,22 +649,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>민관 합동 ‘자동차 사이버 침해사고 대응 모의훈련’ 실시</t>
+          <t>2026년 제13회 소프트웨어(SW) 개발보안 경진대회 개최</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2637&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3762&amp;page=1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -671,24 +675,24 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-09-15 15:01:52.747371+09:00</t>
+          <t>2026-09-16 09:46:37.058042+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-09-15 15:01:52.747371+09:00</t>
+          <t>2026-09-16 09:46:37.058042+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>61031</t>
+          <t>61111</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -698,12 +702,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>“새로운 보안 위협, 인공지능(AI)으로 대응” 정보보호 제품 개발 기업 대상 보안 역량 강화 교육 추진</t>
+          <t>민관 합동 ‘자동차 사이버 침해사고 대응 모의훈련’ 실시</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2636&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2637&amp;page=1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -729,44 +733,44 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-09-15 14:01:52.540884+09:00</t>
+          <t>2026-09-15 15:01:52.747371+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-09-15 14:01:52.540884+09:00</t>
+          <t>2026-09-15 15:01:52.747371+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>57381</t>
+          <t>61031</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026 전자문서 유공 포상 공고</t>
+          <t>“새로운 보안 위협, 인공지능(AI)으로 대응” 정보보호 제품 개발 기업 대상 보안 역량 강화 교육 추진</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3761&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2636&amp;page=1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -774,46 +778,42 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-09-10 14:16:31.877229+09:00</t>
+          <t>2026-09-15 14:01:52.540884+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-09-10 14:16:31.877229+09:00</t>
+          <t>2026-09-15 14:01:52.540884+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>57149</t>
+          <t>57381</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026년 클라우드 서비스 보안인증(CSAP) 교육 안내</t>
+          <t>2026 전자문서 유공 포상 공고</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3760&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3761&amp;page=1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -831,7 +831,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -839,19 +843,19 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-09-10 10:46:38.794916+09:00</t>
+          <t>2026-09-10 14:16:31.877229+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-09-10 10:46:38.794916+09:00</t>
+          <t>2026-09-10 14:16:31.877229+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>56431</t>
+          <t>57149</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -861,22 +865,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>보호나라 챗봇, 국민 생활 속 정보보호 성과 인정</t>
+          <t>2026년 클라우드 서비스 보안인증(CSAP) 교육 안내</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2634&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3760&amp;page=1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -887,92 +891,92 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-09-09 12:01:35.142670+09:00</t>
+          <t>2026-09-10 10:46:38.794916+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-09-09 12:01:35.142670+09:00</t>
+          <t>2026-09-10 10:46:38.794916+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>56969</t>
+          <t>56431</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1522</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>온마이데이터 서비스 이용 이벤트 안내</t>
+          <t>보호나라 챗봇, 국민 생활 속 정보보호 성과 인정</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3758&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2634&amp;page=1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>402</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-09-10 08:31:37.677434+09:00</t>
+          <t>2026-09-09 12:01:35.142670+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-09-10 08:31:37.677434+09:00</t>
+          <t>2026-09-09 12:01:35.142670+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>54791</t>
+          <t>56969</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1522</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>국내 캐시 도메인이름시스템(DNS) 운영기관, 신규 암호키 반영 여부 확인하세요</t>
+          <t>온마이데이터 서비스 이용 이벤트 안내</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2633&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3758&amp;page=1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -982,60 +986,60 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>402</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-09-07 12:01:35.243341+09:00</t>
+          <t>2026-09-10 08:31:37.677434+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-09-07 12:01:35.243341+09:00</t>
+          <t>2026-09-10 08:31:37.677434+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>54541</t>
+          <t>54791</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(2차, Avalanche)</t>
+          <t>국내 캐시 도메인이름시스템(DNS) 운영기관, 신규 암호키 반영 여부 확인하세요</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3759&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2633&amp;page=1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1043,31 +1047,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-09-07 09:01:25.516098+09:00</t>
+          <t>2026-09-07 12:01:35.243341+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-09-07 09:01:25.516098+09:00</t>
+          <t>2026-09-07 12:01:35.243341+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>51281</t>
+          <t>54541</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1077,27 +1077,27 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>(행사 안내) 국외이전 제도 개선 및 CBPR 인증제도 기업 설명회 개최</t>
+          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(2차, Avalanche)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3757&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3759&amp;page=1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1112,52 +1112,56 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-09-03 09:16:26.856224+09:00</t>
+          <t>2026-09-07 09:01:25.516098+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-09-03 09:16:26.856224+09:00</t>
+          <t>2026-09-07 09:01:25.516098+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>56970</t>
+          <t>51281</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1521</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026 부산지역 도메인이름 분쟁해결 세미나 개최 안내(9.11)</t>
+          <t>(행사 안내) 국외이전 제도 개선 및 CBPR 인증제도 기업 설명회 개최</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3755&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3757&amp;page=1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>23</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1165,34 +1169,34 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-09-10 08:31:37.677434+09:00</t>
+          <t>2026-09-03 09:16:26.856224+09:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-09-10 08:31:37.677434+09:00</t>
+          <t>2026-09-03 09:16:26.856224+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>51121</t>
+          <t>56970</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1521</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026년 블록체인 수요공급협의체(ABLE) 블록체인 수요기업(비금융분야) 모집 공고</t>
+          <t>2026 부산지역 도메인이름 분쟁해결 세미나 개최 안내(9.11)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3754&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3755&amp;page=1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1202,7 +1206,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>242</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1210,11 +1214,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1222,19 +1222,19 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-09-02 17:31:25.610368+09:00</t>
+          <t>2026-09-10 08:31:37.677434+09:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-09-02 17:31:25.610368+09:00</t>
+          <t>2026-09-10 08:31:37.677434+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>50601</t>
+          <t>51121</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1244,12 +1244,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026년 9차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(9월 추천) (~9.18(금) 18시까지)</t>
+          <t>2026년 블록체인 수요공급협의체(ABLE) 블록체인 수요기업(비금융분야) 모집 공고</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3753&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3754&amp;page=1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>24</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1279,44 +1279,44 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-09-02 11:01:32.173328+09:00</t>
+          <t>2026-09-02 17:31:25.610368+09:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-09-02 11:01:32.173328+09:00</t>
+          <t>2026-09-02 17:31:25.610368+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>49872</t>
+          <t>50601</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>인공지능(AI) 사이버 위협, 실전 모의훈련으로 대응</t>
+          <t>2026년 9차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(9월 추천) (~9.18(금) 18시까지)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2631&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3753&amp;page=1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1324,27 +1324,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-09-01 12:01:47.858504+09:00</t>
+          <t>2026-09-02 11:01:32.173328+09:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-09-01 12:01:47.858504+09:00</t>
+          <t>2026-09-02 11:01:32.173328+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>49669</t>
+          <t>49872</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1354,12 +1358,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>「2026 위치정보 맞춤형 컨설팅 참여기업 모집」</t>
+          <t>인공지능(AI) 사이버 위협, 실전 모의훈련으로 대응</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3752&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2631&amp;page=1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1369,35 +1373,35 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-09-01 09:31:38.715793+09:00</t>
+          <t>2026-09-01 12:01:47.858504+09:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-09-01 09:31:38.715793+09:00</t>
+          <t>2026-09-01 12:01:47.858504+09:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>49631</t>
+          <t>49669</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1407,12 +1411,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>물리보안 시스템 간 연동 장벽 낮춘다</t>
+          <t>「2026 위치정보 맞춤형 컨설팅 참여기업 모집」</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2632&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3752&amp;page=1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1422,103 +1426,103 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-09-01 09:01:45.980040+09:00</t>
+          <t>2026-09-01 09:31:38.715793+09:00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-09-01 09:01:45.980040+09:00</t>
+          <t>2026-09-01 09:31:38.715793+09:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>49589</t>
+          <t>49631</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1517</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 23회차 교육생 모집(~9.18)</t>
+          <t>물리보안 시스템 간 연동 장벽 낮춘다</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3751&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2632&amp;page=1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-09-01 08:31:37.253592+09:00</t>
+          <t>2026-09-01 09:01:45.980040+09:00</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-09-01 08:31:37.253592+09:00</t>
+          <t>2026-09-01 09:01:45.980040+09:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>48831</t>
+          <t>49589</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1517</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>생성형 인공지능(AI) 기반 실전형 모의해킹 대회 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 23회차 교육생 모집(~9.18)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2630&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3751&amp;page=1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1528,35 +1532,35 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>174</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-08-31 09:16:38.866405+09:00</t>
+          <t>2026-09-01 08:31:37.253592+09:00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-08-31 09:16:38.866405+09:00</t>
+          <t>2026-09-01 08:31:37.253592+09:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>46011</t>
+          <t>48831</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1566,22 +1570,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>자동차 노리는 사이버 위협, 한국인터넷진흥원-한국교통안전공단이 함께 대응한다</t>
+          <t>생성형 인공지능(AI) 기반 실전형 모의해킹 대회 개최</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2628&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2630&amp;page=1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1597,34 +1601,34 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-08-27 15:01:41.552844+09:00</t>
+          <t>2026-08-31 09:16:38.866405+09:00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-08-27 15:01:41.552844+09:00</t>
+          <t>2026-08-31 09:16:38.866405+09:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>45681</t>
+          <t>46011</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>싱가포르 현지 진출 지원 국내 블록체인 기업 모집(~9.16(수) 14시)</t>
+          <t>자동차 노리는 사이버 위협, 한국인터넷진흥원-한국교통안전공단이 함께 대응한다</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3750&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2628&amp;page=1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1642,56 +1646,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-08-27 11:01:31.314899+09:00</t>
+          <t>2026-08-27 15:01:41.552844+09:00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-08-27 11:01:31.314899+09:00</t>
+          <t>2026-08-27 15:01:41.552844+09:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>45191</t>
+          <t>45681</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 아·태 지역 사이버공격 대응 공동 훈련 실시</t>
+          <t>싱가포르 현지 진출 지원 국내 블록체인 기업 모집(~9.16(수) 14시)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2629&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3750&amp;page=1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1699,42 +1699,46 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-08-26 15:01:47.261933+09:00</t>
+          <t>2026-08-27 11:01:31.314899+09:00</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-08-26 15:01:47.261933+09:00</t>
+          <t>2026-08-27 11:01:31.314899+09:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>44741</t>
+          <t>45191</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>[3차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~9/16)</t>
+          <t>한국인터넷진흥원, 아·태 지역 사이버공격 대응 공동 훈련 실시</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3749&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2629&amp;page=1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1744,7 +1748,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1752,56 +1756,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-08-26 09:31:36.427758+09:00</t>
+          <t>2026-08-26 15:01:47.261933+09:00</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-08-26 09:31:36.427758+09:00</t>
+          <t>2026-08-26 15:01:47.261933+09:00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>44448</t>
+          <t>44741</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 공고</t>
+          <t>[3차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~9/16)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3748&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3749&amp;page=1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1809,7 +1809,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1817,19 +1821,19 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-08-25 16:01:39.626193+09:00</t>
+          <t>2026-08-26 09:31:36.427758+09:00</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-08-25 16:01:39.626193+09:00</t>
+          <t>2026-08-26 09:31:36.427758+09:00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>43767</t>
+          <t>44448</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1839,27 +1843,27 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 21회차 교육생 모집(~9.12)</t>
+          <t>정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 공고</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3747&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3748&amp;page=1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
@@ -1870,19 +1874,19 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-08-24 17:46:42.254577+09:00</t>
+          <t>2026-08-25 16:01:39.626193+09:00</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-08-24 17:46:42.254577+09:00</t>
+          <t>2026-08-25 16:01:39.626193+09:00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>43311</t>
+          <t>43767</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1892,12 +1896,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>양자내성암호 전환, 어떻게 준비해야 할까?</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 21회차 교육생 모집(~9.12)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2627&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3747&amp;page=1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1907,50 +1911,50 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-08-24 12:01:45.511381+09:00</t>
+          <t>2026-08-24 17:46:42.254577+09:00</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-08-24 12:01:45.511381+09:00</t>
+          <t>2026-08-24 17:46:42.254577+09:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>43301</t>
+          <t>43311</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>양자내성암호 전문교육 PQC 실무과정 교육생 모집(8.24~)</t>
+          <t>양자내성암호 전환, 어떻게 준비해야 할까?</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3746&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2627&amp;page=1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1960,7 +1964,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1968,31 +1972,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-08-24 12:01:36.271108+09:00</t>
+          <t>2026-08-24 12:01:45.511381+09:00</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-08-24 12:01:36.271108+09:00</t>
+          <t>2026-08-24 12:01:45.511381+09:00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>41161</t>
+          <t>43301</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2002,27 +2002,27 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>「블록체인 기업 맞춤형 보안 고도화 지원」 기업 모집(~8/31)</t>
+          <t>양자내성암호 전문교육 PQC 실무과정 교육생 모집(8.24~)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3745&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3746&amp;page=1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2037,34 +2037,34 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-08-21 16:01:38.087170+09:00</t>
+          <t>2026-08-24 12:01:36.271108+09:00</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-08-21 16:01:38.087170+09:00</t>
+          <t>2026-08-24 12:01:36.271108+09:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>41086</t>
+          <t>41161</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026년도 인터넷거버넌스 민간전문가 APrIGF 및 IGF 참석자 모집</t>
+          <t>「블록체인 기업 맞춤형 보안 고도화 지원」 기업 모집(~8/31)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3744&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3745&amp;page=1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2074,15 +2074,19 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2090,19 +2094,19 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-08-21 15:01:32.139445+09:00</t>
+          <t>2026-08-21 16:01:38.087170+09:00</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-08-21 15:01:32.139445+09:00</t>
+          <t>2026-08-21 16:01:38.087170+09:00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>34750</t>
+          <t>41086</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2112,22 +2116,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>｢2026 블록체인 진흥주간｣ 전시부스 참가기업 모집 공고(~9.14)</t>
+          <t>2026년도 인터넷거버넌스 민간전문가 APrIGF 및 IGF 참석자 모집</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3743&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3744&amp;page=1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>59</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2143,34 +2147,34 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-08-13 17:46:21.938331+09:00</t>
+          <t>2026-08-21 15:01:32.139445+09:00</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-08-13 17:46:21.938331+09:00</t>
+          <t>2026-08-21 15:01:32.139445+09:00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>34081</t>
+          <t>34750</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026년 하반기 정보보호 전문서비스 기업 지정에 관한 공고</t>
+          <t>｢2026 블록체인 진흥주간｣ 전시부스 참가기업 모집 공고(~9.14)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3742&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3743&amp;page=1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2180,7 +2184,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2188,11 +2192,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2200,44 +2200,44 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:24.927741+09:00</t>
+          <t>2026-08-13 17:46:21.938331+09:00</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:24.927741+09:00</t>
+          <t>2026-08-13 17:46:21.938331+09:00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>34071</t>
+          <t>34081</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>"예방 넘어 대응·복구까지" 랜섬웨어 전주기 대응 방안 논의한다</t>
+          <t>2026년 하반기 정보보호 전문서비스 기업 지정에 관한 공고</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2626&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3742&amp;page=1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2245,42 +2245,46 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-08-13 09:16:35.989405+09:00</t>
+          <t>2026-08-13 09:31:24.927741+09:00</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-08-13 09:16:35.989405+09:00</t>
+          <t>2026-08-13 09:31:24.927741+09:00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>33789</t>
+          <t>34071</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>978</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 21회차 교육생 모집(~9.11)</t>
+          <t>"예방 넘어 대응·복구까지" 랜섬웨어 전주기 대응 방안 논의한다</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3741&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2626&amp;page=1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2290,35 +2294,35 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-08-12 16:01:25.579701+09:00</t>
+          <t>2026-08-13 09:16:35.989405+09:00</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-08-12 16:01:25.579701+09:00</t>
+          <t>2026-08-13 09:16:35.989405+09:00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>33749</t>
+          <t>33789</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2328,12 +2332,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026년도 블록체인 유공 포상 계획 공고 안내(~9.21 15:00 마감)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 21회차 교육생 모집(~9.11)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3740&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3741&amp;page=1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2343,12 +2347,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
@@ -2359,44 +2363,44 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-08-12 15:31:25.306307+09:00</t>
+          <t>2026-08-12 16:01:25.579701+09:00</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-08-12 15:31:25.306307+09:00</t>
+          <t>2026-08-12 16:01:25.579701+09:00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>31741</t>
+          <t>33749</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026년 블록체인 수요-공급 협의체 (ABLE) 정례세미나 개최 안내(8.13.목)</t>
+          <t>2026년도 블록체인 유공 포상 계획 공고 안내(~9.21 15:00 마감)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3739&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3740&amp;page=1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2404,11 +2408,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2416,52 +2416,56 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-08-10 11:01:30.246604+09:00</t>
+          <t>2026-08-12 15:31:25.306307+09:00</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-08-10 11:01:30.246604+09:00</t>
+          <t>2026-08-12 15:31:25.306307+09:00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>29768</t>
+          <t>31741</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026년 블록체인 신뢰인프라(K-BTF) 활용·확산사업 공모 사전예고</t>
+          <t>2026년 블록체인 수요-공급 협의체 (ABLE) 정례세미나 개최 안내(8.13.목)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3738&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3739&amp;page=1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2469,19 +2473,19 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-08-07 17:01:29.954014+09:00</t>
+          <t>2026-08-10 11:01:30.246604+09:00</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-08-07 17:01:29.954014+09:00</t>
+          <t>2026-08-10 11:01:30.246604+09:00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>29728</t>
+          <t>29768</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2491,12 +2495,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026년도 블록체인 산업 실태조사 실시 및 협조 안내</t>
+          <t>2026년 블록체인 신뢰인프라(K-BTF) 활용·확산사업 공모 사전예고</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3737&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3738&amp;page=1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2506,7 +2510,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2522,19 +2526,19 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-08-07 16:31:30.938844+09:00</t>
+          <t>2026-08-07 17:01:29.954014+09:00</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-08-07 16:31:30.938844+09:00</t>
+          <t>2026-08-07 17:01:29.954014+09:00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>28711</t>
+          <t>29728</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2544,50 +2548,50 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원-나주시, 고교생 개인정보·정보보호 진로 탐색 지원</t>
+          <t>2026년도 블록체인 산업 실태조사 실시 및 협조 안내</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2625&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3737&amp;page=1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-08-06 14:01:34.968573+09:00</t>
+          <t>2026-08-07 16:31:30.938844+09:00</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-08-06 14:01:34.968573+09:00</t>
+          <t>2026-08-07 16:31:30.938844+09:00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>27551</t>
+          <t>28711</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2597,22 +2601,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 기업 맞춤형 사이버 위협 알림 서비스 개시</t>
+          <t>한국인터넷진흥원-나주시, 고교생 개인정보·정보보호 진로 탐색 지원</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2624&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2625&amp;page=1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2628,44 +2632,44 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-08-05 09:46:34.063806+09:00</t>
+          <t>2026-08-06 14:01:34.968573+09:00</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-08-05 09:46:34.063806+09:00</t>
+          <t>2026-08-06 14:01:34.968573+09:00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>27511</t>
+          <t>27551</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 기관장 주도 국민 체감 성과 혁신 체계 가동</t>
+          <t>한국인터넷진흥원, 기업 맞춤형 사이버 위협 알림 서비스 개시</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2623&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2624&amp;page=1</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2681,34 +2685,34 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-08-05 09:16:33.823896+09:00</t>
+          <t>2026-08-05 09:46:34.063806+09:00</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-08-05 09:16:33.823896+09:00</t>
+          <t>2026-08-05 09:46:34.063806+09:00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>27268</t>
+          <t>27511</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>975</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>양자내성암호 국제 표준화 동향 분석</t>
+          <t>한국인터넷진흥원, 기관장 주도 국민 체감 성과 혁신 체계 가동</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3736&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2623&amp;page=1</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2718,7 +2722,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>263</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2729,24 +2733,24 @@
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-08-04 16:31:26.502205+09:00</t>
+          <t>2026-08-05 09:16:33.823896+09:00</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-08-04 16:31:26.502205+09:00</t>
+          <t>2026-08-05 09:16:33.823896+09:00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>27128</t>
+          <t>27268</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2756,12 +2760,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 20회차 교육생 모집(~9.4)</t>
+          <t>양자내성암호 국제 표준화 동향 분석</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3735&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3736&amp;page=1</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2771,12 +2775,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
@@ -2787,19 +2791,19 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-08-04 14:46:28.764255+09:00</t>
+          <t>2026-08-04 16:31:26.502205+09:00</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-08-04 14:46:28.764255+09:00</t>
+          <t>2026-08-04 16:31:26.502205+09:00</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>26211</t>
+          <t>27128</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2809,50 +2813,50 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 암호모듈검증 위한 시험 전문인력 양성</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 20회차 교육생 모집(~9.4)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2622&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3735&amp;page=1</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2026-08-03 13:31:41.722921+09:00</t>
+          <t>2026-08-04 14:46:28.764255+09:00</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-08-03 13:31:41.722921+09:00</t>
+          <t>2026-08-04 14:46:28.764255+09:00</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>26188</t>
+          <t>26211</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2862,12 +2866,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026년 8차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(8월 추천) (~8.21(금) 18시까지)</t>
+          <t>한국인터넷진흥원, 암호모듈검증 위한 시험 전문인력 양성</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3734&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2622&amp;page=1</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2877,7 +2881,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>273</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2888,24 +2892,24 @@
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2026-08-03 13:16:30.325331+09:00</t>
+          <t>2026-08-03 13:31:41.722921+09:00</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-08-03 13:16:30.325331+09:00</t>
+          <t>2026-08-03 13:31:41.722921+09:00</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>25891</t>
+          <t>26188</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2915,12 +2919,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 지역 상생 3대 사업 참여자 모집</t>
+          <t>2026년 8차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(8월 추천) (~8.21(금) 18시까지)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2621&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3734&amp;page=1</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2930,7 +2934,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2941,39 +2945,39 @@
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2026-08-03 09:31:46.854132+09:00</t>
+          <t>2026-08-03 13:16:30.325331+09:00</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-08-03 09:31:46.854132+09:00</t>
+          <t>2026-08-03 13:16:30.325331+09:00</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>25864</t>
+          <t>25891</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026년 전남광주통합특별시 소상공인·사회적경제기업 판로 확대 지원기업 선발 안내(~8.14)</t>
+          <t>한국인터넷진흥원, 지역 상생 3대 사업 참여자 모집</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3730&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2621&amp;page=1</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2983,7 +2987,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>80</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2991,31 +2995,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-08-03 09:16:35.817723+09:00</t>
+          <t>2026-08-03 09:31:46.854132+09:00</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-08-03 09:16:35.817723+09:00</t>
+          <t>2026-08-03 09:31:46.854132+09:00</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>25863</t>
+          <t>25864</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3025,12 +3025,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026년 전남광주통합특별시 지역문제 해결 프로젝트 공모전 개최 안내(~8.21)</t>
+          <t>2026년 전남광주통합특별시 소상공인·사회적경제기업 판로 확대 지원기업 선발 안내(~8.14)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3731&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3730&amp;page=1</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3040,7 +3040,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3072,7 +3072,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>25862</t>
+          <t>25863</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026년 한국인터넷진흥원 지역공부방 참여 대학생 장학금 지원자 모집 안내(~8.28)</t>
+          <t>2026년 전남광주통합특별시 지역문제 해결 프로젝트 공모전 개최 안내(~8.21)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3732&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3731&amp;page=1</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3129,7 +3129,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>25861</t>
+          <t>25862</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3139,12 +3139,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026년 암호모듈 시험자 양성교육 및 필기시험 안내(8.3~8.21)</t>
+          <t>2026년 한국인터넷진흥원 지역공부방 참여 대학생 장학금 지원자 모집 안내(~8.28)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3733&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3732&amp;page=1</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3186,7 +3186,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>23221</t>
+          <t>25861</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3196,22 +3196,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026년 블록체인 기업성장허브 입주기업 모집(~8월 27일(목) 16:00까지)</t>
+          <t>2026년 암호모듈 시험자 양성교육 및 필기시험 안내(8.3~8.21)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3729&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3733&amp;page=1</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3231,52 +3231,56 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2026-07-30 17:16:54.540202+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-07-30 17:16:54.540202+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>22504</t>
+          <t>23221</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 19회차 교육생 모집(~8.28)</t>
+          <t>2026년 블록체인 기업성장허브 입주기업 모집(~8월 27일(목) 16:00까지)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3728&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3729&amp;page=1</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I53" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3284,19 +3288,19 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2026-07-29 18:32:00.075123+09:00</t>
+          <t>2026-07-30 17:16:54.540202+09:00</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-07-29 18:32:00.075123+09:00</t>
+          <t>2026-07-30 17:16:54.540202+09:00</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>22464</t>
+          <t>22504</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3306,12 +3310,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026년 연계정보 이용기관 안전조치 실태점검 2차 설명회 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 19회차 교육생 모집(~8.28)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3727&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3728&amp;page=1</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3321,7 +3325,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3337,19 +3341,19 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:59.875668+09:00</t>
+          <t>2026-07-29 18:32:00.075123+09:00</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:59.875668+09:00</t>
+          <t>2026-07-29 18:32:00.075123+09:00</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>20771</t>
+          <t>22464</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3359,50 +3363,50 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 성평등가족부와 불법·유해 정보 유통 대응 맞손</t>
+          <t>2026년 연계정보 이용기관 안전조치 실태점검 2차 설명회 개최</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2620&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3727&amp;page=1</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2026-07-27 17:17:05.702970+09:00</t>
+          <t>2026-07-29 18:01:59.875668+09:00</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-07-27 17:17:05.702970+09:00</t>
+          <t>2026-07-29 18:01:59.875668+09:00</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>20191</t>
+          <t>20771</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3412,12 +3416,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 향후 10년 설계한다…전담 추진단(TF) 출범</t>
+          <t>한국인터넷진흥원, 성평등가족부와 불법·유해 정보 유통 대응 맞손</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2619&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2620&amp;page=1</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3427,7 +3431,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>150</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3443,34 +3447,34 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2026-07-27 10:02:05.338547+09:00</t>
+          <t>2026-07-27 17:17:05.702970+09:00</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-07-27 10:02:05.338547+09:00</t>
+          <t>2026-07-27 17:17:05.702970+09:00</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>20061</t>
+          <t>20191</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(1차, BreakingPoint)</t>
+          <t>아피가(APIGA) 향후 10년 설계한다…전담 추진단(TF) 출범</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3726&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2619&amp;page=1</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3480,7 +3484,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>287</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3488,64 +3492,64 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2026-07-27 08:31:55.019743+09:00</t>
+          <t>2026-07-27 10:02:05.338547+09:00</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-07-27 08:31:55.019743+09:00</t>
+          <t>2026-07-27 10:02:05.338547+09:00</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>16785</t>
+          <t>20061</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 17회차 교육생 모집(~8.7)</t>
+          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(1차, BreakingPoint)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3724&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3726&amp;page=1</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>246</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I58" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3553,34 +3557,34 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 08:31:55.019743+09:00</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 08:31:55.019743+09:00</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>16784</t>
+          <t>16785</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>1497</t>
+          <t>1496</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 18회차 교육생 모집(~8.21)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 17회차 교육생 모집(~8.7)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3725&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3724&amp;page=1</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3590,7 +3594,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>236</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3618,22 +3622,22 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>16781</t>
+          <t>16784</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1497</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 16회차 교육생 모집(~7.31)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 18회차 교육생 모집(~8.21)</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3723&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3725&amp;page=1</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3643,7 +3647,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>260</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3651,11 +3655,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3675,22 +3675,22 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>16691</t>
+          <t>16781</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>'블록체인 기반 예금토큰 결제 인프라 확산' 사업 발대식 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 16회차 교육생 모집(~7.31)</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2618&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3723&amp;page=1</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3700,35 +3700,39 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>242</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>2026-07-22 17:32:01.526863+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-07-22 17:32:01.526863+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>16464</t>
+          <t>16691</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3738,12 +3742,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>[홍보] 정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 안내</t>
+          <t>'블록체인 기반 예금토큰 결제 인프라 확산' 사업 발대식 개최</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3722&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2618&amp;page=1</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3753,35 +3757,35 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>278</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2026-07-22 14:46:48.687665+09:00</t>
+          <t>2026-07-22 17:32:01.526863+09:00</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-07-22 14:46:48.687665+09:00</t>
+          <t>2026-07-22 17:32:01.526863+09:00</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>16051</t>
+          <t>16464</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3791,12 +3795,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 보안 인재·글로벌 전문가 교류의 장 열어</t>
+          <t>[홍보] 정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 안내</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2617&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3722&amp;page=1</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3806,35 +3810,35 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>2026-07-22 09:31:50.671841+09:00</t>
+          <t>2026-07-22 14:46:48.687665+09:00</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-07-22 09:31:50.671841+09:00</t>
+          <t>2026-07-22 14:46:48.687665+09:00</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>14611</t>
+          <t>16051</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3844,22 +3848,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
+          <t>한국인터넷진흥원, 보안 인재·글로벌 전문가 교류의 장 열어</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2617&amp;page=1</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>233</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -3875,19 +3879,19 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>14431</t>
+          <t>14611</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3897,12 +3901,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3912,7 +3916,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>32</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -3928,34 +3932,34 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>14431</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3965,7 +3969,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>53</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -3973,56 +3977,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>14444</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>1493</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
+          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -4030,7 +4030,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr"/>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I67" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -4038,34 +4042,34 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>11331</t>
+          <t>14444</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4075,7 +4079,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -4086,96 +4090,92 @@
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>10981</t>
+          <t>11331</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
+          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>10943</t>
+          <t>10981</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
+          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4185,7 +4185,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -4193,7 +4193,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr"/>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I70" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -4201,19 +4205,19 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>10663</t>
+          <t>10943</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4223,12 +4227,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
+          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4238,12 +4242,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
@@ -4254,19 +4258,19 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>9805</t>
+          <t>10663</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4276,22 +4280,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
+          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -4307,19 +4311,19 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>9691</t>
+          <t>9805</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4329,12 +4333,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
+          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4344,7 +4348,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -4355,96 +4359,92 @@
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>9321</t>
+          <t>9691</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
+          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>8871</t>
+          <t>9321</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
+          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4454,35 +4454,39 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>6685</t>
+          <t>8871</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -4492,22 +4496,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
+          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -4518,24 +4522,24 @@
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>6571</t>
+          <t>6685</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -4545,12 +4549,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
+          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -4560,7 +4564,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -4571,24 +4575,24 @@
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>5591</t>
+          <t>6571</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -4598,22 +4602,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
+          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -4629,44 +4633,44 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>5591</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
+          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>33</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -4682,44 +4686,44 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>4762</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>961</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>AI 보안 위협 대응 매뉴얼</t>
+          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -4727,31 +4731,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>4761</t>
+          <t>4762</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>AI 보안 레드티밍 가이드</t>
+          <t>AI 보안 위협 대응 매뉴얼</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -4776,7 +4776,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -4808,22 +4808,22 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>4251</t>
+          <t>4761</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
+          <t>AI 보안 레드티밍 가이드</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -4833,7 +4833,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -4841,27 +4841,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr"/>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>4251</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4871,12 +4875,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
+          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -4886,113 +4890,113 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>191</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t>3867</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
+          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4111</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>959</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
+          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>34</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -5000,31 +5004,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
+          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5049,7 +5049,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -5081,32 +5081,32 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
+          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>105</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -5114,7 +5114,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr"/>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I87" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -5134,22 +5138,22 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1477</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
+          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5159,7 +5163,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>386</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -5187,22 +5191,22 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
+          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5212,19 +5216,15 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>362</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -5244,7 +5244,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2026년 IoT 보안인증 교육과정 안내</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5269,7 +5269,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>522</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -5301,40 +5301,44 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
+          <t>2026년 IoT 보안인증 교육과정 안내</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>652</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I91" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -5354,22 +5358,22 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
+          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -5379,7 +5383,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>1529</t>
+          <t>818</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -5387,11 +5391,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -5411,32 +5411,32 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
+          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>1529</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -5444,7 +5444,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr"/>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I93" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -5452,34 +5456,34 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -5489,7 +5493,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>76426</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -5500,49 +5504,49 @@
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>958</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
+          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>55906</t>
+          <t>76426</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -5570,22 +5574,22 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>956</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
+          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -5595,7 +5599,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>55329</t>
+          <t>55906</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -5623,32 +5627,32 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>957</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
+          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>34467</t>
+          <t>55329</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -5676,22 +5680,22 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>955</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
+          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -5701,39 +5705,35 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2945</t>
+          <t>34467</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -5743,27 +5743,27 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>2945</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -5790,32 +5790,32 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>145255</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -5823,52 +5823,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr"/>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>954</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>26576</t>
+          <t>145255</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -5896,32 +5900,32 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>953</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
+          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>34290</t>
+          <t>26576</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -5949,32 +5953,32 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
+          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>184573</t>
+          <t>34290</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -6002,32 +6006,32 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>14403</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>951</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>6587</t>
+          <t>184573</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -6035,46 +6039,42 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14403</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
+          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -6084,7 +6084,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>51749</t>
+          <t>6587</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -6092,52 +6092,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr"/>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>950</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>78439</t>
+          <t>51749</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -6165,55 +6169,108 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>949</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>78439</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>보도자료</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
           <t>38805</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
+      <c r="B108" t="inlineStr">
         <is>
           <t>공지</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr">
+      <c r="C108" t="inlineStr">
         <is>
           <t>[공유] 지능형 CCTV 성능시험 재개 안내 공지</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr">
+      <c r="D108" t="inlineStr">
         <is>
           <t>https://www.kisa.or.kr/401/form?postSeq=3677&amp;page=1</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr">
+      <c r="E108" t="inlineStr">
         <is>
           <t>2026-06-02</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr">
+      <c r="F108" t="inlineStr">
         <is>
           <t>6525</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr">
+      <c r="G108" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
+      <c r="H108" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>공지사항</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
         <is>
           <t>2026-08-18 17:16:37.364015+09:00</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr">
+      <c r="K108" t="inlineStr">
         <is>
           <t>2026-08-18 17:16:37.364015+09:00</t>
         </is>

--- a/docs/snapshot/downloads/kisa.xlsx
+++ b/docs/snapshot/downloads/kisa.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K108"/>
+  <dimension ref="A1:K110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,32 +476,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>62781</t>
+          <t>63068</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026년 블록체인 기업성장허브 입주기업 모집(~10월 7일(수) 16:00까지)</t>
+          <t>대국민 혁신 정책·제안 공모전 개최</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3765&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3766&amp;page=1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -509,11 +509,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -521,19 +517,19 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-09-17 17:16:36.514530+09:00</t>
+          <t>2026-09-18 10:46:37.266535+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-09-17 17:16:36.514530+09:00</t>
+          <t>2026-09-18 10:46:37.266535+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>62507</t>
+          <t>63051</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -543,65 +539,65 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 25회차 교육생 모집(~10.10)</t>
+          <t>세계경제포럼·싱가포르 사이버보안청과 인공지능(AI) 위협 대비 사이버보안 협력 강화</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3764&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2638&amp;page=1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-09-17 13:31:33.789948+09:00</t>
+          <t>2026-09-18 10:31:43.770443+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-09-17 13:31:33.789948+09:00</t>
+          <t>2026-09-18 10:31:43.770443+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>62367</t>
+          <t>62781</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 24회차 교육생 모집(~10.9)</t>
+          <t>2026년 블록체인 기업성장허브 입주기업 모집(~10월 7일(수) 16:00까지)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3763&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3765&amp;page=1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -611,15 +607,19 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -627,19 +627,19 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-09-17 11:46:35.719751+09:00</t>
+          <t>2026-09-17 17:16:36.514530+09:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-09-17 11:46:35.719751+09:00</t>
+          <t>2026-09-17 17:16:36.514530+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>61484</t>
+          <t>62507</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -649,27 +649,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026년 제13회 소프트웨어(SW) 개발보안 경진대회 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 25회차 교육생 모집(~10.10)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3762&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3764&amp;page=1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -680,19 +680,19 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-09-16 09:46:37.058042+09:00</t>
+          <t>2026-09-17 13:31:33.789948+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-09-16 09:46:37.058042+09:00</t>
+          <t>2026-09-17 13:31:33.789948+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>61111</t>
+          <t>62367</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -702,50 +702,50 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>민관 합동 ‘자동차 사이버 침해사고 대응 모의훈련’ 실시</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 24회차 교육생 모집(~10.9)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2637&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3763&amp;page=1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-09-15 15:01:52.747371+09:00</t>
+          <t>2026-09-17 11:46:35.719751+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-09-15 15:01:52.747371+09:00</t>
+          <t>2026-09-17 11:46:35.719751+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>61031</t>
+          <t>61484</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -755,22 +755,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>“새로운 보안 위협, 인공지능(AI)으로 대응” 정보보호 제품 개발 기업 대상 보안 역량 강화 교육 추진</t>
+          <t>2026년 제13회 소프트웨어(SW) 개발보안 경진대회 개최</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2636&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3762&amp;page=1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -781,49 +781,49 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-09-15 14:01:52.540884+09:00</t>
+          <t>2026-09-16 09:46:37.058042+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-09-15 14:01:52.540884+09:00</t>
+          <t>2026-09-16 09:46:37.058042+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>57381</t>
+          <t>61111</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026 전자문서 유공 포상 공고</t>
+          <t>민관 합동 ‘자동차 사이버 침해사고 대응 모의훈련’ 실시</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3761&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2637&amp;page=1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -831,31 +831,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-09-10 14:16:31.877229+09:00</t>
+          <t>2026-09-15 15:01:52.747371+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-09-10 14:16:31.877229+09:00</t>
+          <t>2026-09-15 15:01:52.747371+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>57149</t>
+          <t>61031</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -865,22 +861,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026년 클라우드 서비스 보안인증(CSAP) 교육 안내</t>
+          <t>“새로운 보안 위협, 인공지능(AI)으로 대응” 정보보호 제품 개발 기업 대상 보안 역량 강화 교육 추진</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3760&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2636&amp;page=1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -891,49 +887,49 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-09-10 10:46:38.794916+09:00</t>
+          <t>2026-09-15 14:01:52.540884+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-09-10 10:46:38.794916+09:00</t>
+          <t>2026-09-15 14:01:52.540884+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>56431</t>
+          <t>57381</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>보호나라 챗봇, 국민 생활 속 정보보호 성과 인정</t>
+          <t>2026 전자문서 유공 포상 공고</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2634&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3761&amp;page=1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -941,57 +937,61 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-09-09 12:01:35.142670+09:00</t>
+          <t>2026-09-10 14:16:31.877229+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-09-09 12:01:35.142670+09:00</t>
+          <t>2026-09-10 14:16:31.877229+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>56969</t>
+          <t>57149</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1522</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>온마이데이터 서비스 이용 이벤트 안내</t>
+          <t>2026년 클라우드 서비스 보안인증(CSAP) 교육 안내</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3758&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3760&amp;page=1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>402</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
@@ -1002,19 +1002,19 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-09-10 08:31:37.677434+09:00</t>
+          <t>2026-09-10 10:46:38.794916+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-09-10 08:31:37.677434+09:00</t>
+          <t>2026-09-10 10:46:38.794916+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>54791</t>
+          <t>56431</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1024,22 +1024,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>국내 캐시 도메인이름시스템(DNS) 운영기관, 신규 암호키 반영 여부 확인하세요</t>
+          <t>보호나라 챗봇, 국민 생활 속 정보보호 성과 인정</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2633&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2634&amp;page=1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1055,56 +1055,52 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-09-07 12:01:35.243341+09:00</t>
+          <t>2026-09-09 12:01:35.142670+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-09-07 12:01:35.243341+09:00</t>
+          <t>2026-09-09 12:01:35.142670+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>54541</t>
+          <t>56969</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1522</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(2차, Avalanche)</t>
+          <t>온마이데이터 서비스 이용 이벤트 안내</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3759&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3758&amp;page=1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>402</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1112,101 +1108,97 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-09-07 09:01:25.516098+09:00</t>
+          <t>2026-09-10 08:31:37.677434+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-09-07 09:01:25.516098+09:00</t>
+          <t>2026-09-10 08:31:37.677434+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>51281</t>
+          <t>54791</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>(행사 안내) 국외이전 제도 개선 및 CBPR 인증제도 기업 설명회 개최</t>
+          <t>국내 캐시 도메인이름시스템(DNS) 운영기관, 신규 암호키 반영 여부 확인하세요</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3757&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2633&amp;page=1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-09-03 09:16:26.856224+09:00</t>
+          <t>2026-09-07 12:01:35.243341+09:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-09-03 09:16:26.856224+09:00</t>
+          <t>2026-09-07 12:01:35.243341+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>56970</t>
+          <t>54541</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1521</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026 부산지역 도메인이름 분쟁해결 세미나 개최 안내(9.11)</t>
+          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(2차, Avalanche)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3755&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3759&amp;page=1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1214,7 +1206,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1222,19 +1218,19 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-09-10 08:31:37.677434+09:00</t>
+          <t>2026-09-07 09:01:25.516098+09:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-09-10 08:31:37.677434+09:00</t>
+          <t>2026-09-07 09:01:25.516098+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>51121</t>
+          <t>51281</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1244,27 +1240,27 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026년 블록체인 수요공급협의체(ABLE) 블록체인 수요기업(비금융분야) 모집 공고</t>
+          <t>(행사 안내) 국외이전 제도 개선 및 CBPR 인증제도 기업 설명회 개최</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3754&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3757&amp;page=1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1279,34 +1275,34 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-09-02 17:31:25.610368+09:00</t>
+          <t>2026-09-03 09:16:26.856224+09:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-09-02 17:31:25.610368+09:00</t>
+          <t>2026-09-03 09:16:26.856224+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>50601</t>
+          <t>56970</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1521</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026년 9차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(9월 추천) (~9.18(금) 18시까지)</t>
+          <t>2026 부산지역 도메인이름 분쟁해결 세미나 개최 안내(9.11)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3753&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3755&amp;page=1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1316,7 +1312,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>242</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1324,11 +1320,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1336,44 +1328,44 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-09-02 11:01:32.173328+09:00</t>
+          <t>2026-09-10 08:31:37.677434+09:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-09-02 11:01:32.173328+09:00</t>
+          <t>2026-09-10 08:31:37.677434+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>49872</t>
+          <t>51121</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>인공지능(AI) 사이버 위협, 실전 모의훈련으로 대응</t>
+          <t>2026년 블록체인 수요공급협의체(ABLE) 블록체인 수요기업(비금융분야) 모집 공고</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2631&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3754&amp;page=1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>24</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1381,60 +1373,68 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-09-01 12:01:47.858504+09:00</t>
+          <t>2026-09-02 17:31:25.610368+09:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-09-01 12:01:47.858504+09:00</t>
+          <t>2026-09-02 17:31:25.610368+09:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>49669</t>
+          <t>50601</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>「2026 위치정보 맞춤형 컨설팅 참여기업 모집」</t>
+          <t>2026년 9차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(9월 추천) (~9.18(금) 18시까지)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3752&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3753&amp;page=1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1442,19 +1442,19 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-09-01 09:31:38.715793+09:00</t>
+          <t>2026-09-02 11:01:32.173328+09:00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-09-01 09:31:38.715793+09:00</t>
+          <t>2026-09-02 11:01:32.173328+09:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>49631</t>
+          <t>49872</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>물리보안 시스템 간 연동 장벽 낮춘다</t>
+          <t>인공지능(AI) 사이버 위협, 실전 모의훈련으로 대응</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2632&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2631&amp;page=1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1495,44 +1495,44 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-09-01 09:01:45.980040+09:00</t>
+          <t>2026-09-01 12:01:47.858504+09:00</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-09-01 09:01:45.980040+09:00</t>
+          <t>2026-09-01 12:01:47.858504+09:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>49589</t>
+          <t>49669</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1517</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 23회차 교육생 모집(~9.18)</t>
+          <t>「2026 위치정보 맞춤형 컨설팅 참여기업 모집」</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3751&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3752&amp;page=1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1548,19 +1548,19 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-09-01 08:31:37.253592+09:00</t>
+          <t>2026-09-01 09:31:38.715793+09:00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-09-01 08:31:37.253592+09:00</t>
+          <t>2026-09-01 09:31:38.715793+09:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>48831</t>
+          <t>49631</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1570,22 +1570,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>생성형 인공지능(AI) 기반 실전형 모의해킹 대회 개최</t>
+          <t>물리보안 시스템 간 연동 장벽 낮춘다</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2630&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2632&amp;page=1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1601,97 +1601,97 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-08-31 09:16:38.866405+09:00</t>
+          <t>2026-09-01 09:01:45.980040+09:00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-08-31 09:16:38.866405+09:00</t>
+          <t>2026-09-01 09:01:45.980040+09:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>46011</t>
+          <t>49589</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1517</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>자동차 노리는 사이버 위협, 한국인터넷진흥원-한국교통안전공단이 함께 대응한다</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 23회차 교육생 모집(~9.18)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2628&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3751&amp;page=1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>174</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-08-27 15:01:41.552844+09:00</t>
+          <t>2026-09-01 08:31:37.253592+09:00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-08-27 15:01:41.552844+09:00</t>
+          <t>2026-09-01 08:31:37.253592+09:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>45681</t>
+          <t>48831</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>싱가포르 현지 진출 지원 국내 블록체인 기업 모집(~9.16(수) 14시)</t>
+          <t>생성형 인공지능(AI) 기반 실전형 모의해킹 대회 개최</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3750&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2630&amp;page=1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1699,31 +1699,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-08-27 11:01:31.314899+09:00</t>
+          <t>2026-08-31 09:16:38.866405+09:00</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-08-27 11:01:31.314899+09:00</t>
+          <t>2026-08-31 09:16:38.866405+09:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>45191</t>
+          <t>46011</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1733,22 +1729,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 아·태 지역 사이버공격 대응 공동 훈련 실시</t>
+          <t>자동차 노리는 사이버 위협, 한국인터넷진흥원-한국교통안전공단이 함께 대응한다</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2629&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2628&amp;page=1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1764,19 +1760,19 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-08-26 15:01:47.261933+09:00</t>
+          <t>2026-08-27 15:01:41.552844+09:00</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-08-26 15:01:47.261933+09:00</t>
+          <t>2026-08-27 15:01:41.552844+09:00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>44741</t>
+          <t>45681</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1786,22 +1782,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>[3차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~9/16)</t>
+          <t>싱가포르 현지 진출 지원 국내 블록체인 기업 모집(~9.16(수) 14시)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3749&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3750&amp;page=1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1821,19 +1817,19 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-08-26 09:31:36.427758+09:00</t>
+          <t>2026-08-27 11:01:31.314899+09:00</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-08-26 09:31:36.427758+09:00</t>
+          <t>2026-08-27 11:01:31.314899+09:00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>44448</t>
+          <t>45191</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1843,22 +1839,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 공고</t>
+          <t>한국인터넷진흥원, 아·태 지역 사이버공격 대응 공동 훈련 실시</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3748&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2629&amp;page=1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1869,57 +1865,61 @@
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-08-25 16:01:39.626193+09:00</t>
+          <t>2026-08-26 15:01:47.261933+09:00</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-08-25 16:01:39.626193+09:00</t>
+          <t>2026-08-26 15:01:47.261933+09:00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>43767</t>
+          <t>44741</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 21회차 교육생 모집(~9.12)</t>
+          <t>[3차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~9/16)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3747&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3749&amp;page=1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1927,19 +1927,19 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-08-24 17:46:42.254577+09:00</t>
+          <t>2026-08-26 09:31:36.427758+09:00</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-08-24 17:46:42.254577+09:00</t>
+          <t>2026-08-26 09:31:36.427758+09:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>43311</t>
+          <t>44448</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1949,22 +1949,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>양자내성암호 전환, 어떻게 준비해야 할까?</t>
+          <t>정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 공고</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2627&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3748&amp;page=1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1975,39 +1975,39 @@
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-08-24 12:01:45.511381+09:00</t>
+          <t>2026-08-25 16:01:39.626193+09:00</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-08-24 12:01:45.511381+09:00</t>
+          <t>2026-08-25 16:01:39.626193+09:00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>43301</t>
+          <t>43767</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>양자내성암호 전문교육 PQC 실무과정 교육생 모집(8.24~)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 21회차 교육생 모집(~9.12)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3746&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3747&amp;page=1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2017,19 +2017,15 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2037,101 +2033,97 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-08-24 12:01:36.271108+09:00</t>
+          <t>2026-08-24 17:46:42.254577+09:00</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-08-24 12:01:36.271108+09:00</t>
+          <t>2026-08-24 17:46:42.254577+09:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>41161</t>
+          <t>43311</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>「블록체인 기업 맞춤형 보안 고도화 지원」 기업 모집(~8/31)</t>
+          <t>양자내성암호 전환, 어떻게 준비해야 할까?</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3745&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2627&amp;page=1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-08-21 16:01:38.087170+09:00</t>
+          <t>2026-08-24 12:01:45.511381+09:00</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-08-21 16:01:38.087170+09:00</t>
+          <t>2026-08-24 12:01:45.511381+09:00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>41086</t>
+          <t>43301</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026년도 인터넷거버넌스 민간전문가 APrIGF 및 IGF 참석자 모집</t>
+          <t>양자내성암호 전문교육 PQC 실무과정 교육생 모집(8.24~)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3744&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3746&amp;page=1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2139,7 +2131,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2147,52 +2143,56 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-08-21 15:01:32.139445+09:00</t>
+          <t>2026-08-24 12:01:36.271108+09:00</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-08-21 15:01:32.139445+09:00</t>
+          <t>2026-08-24 12:01:36.271108+09:00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>34750</t>
+          <t>41161</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>｢2026 블록체인 진흥주간｣ 전시부스 참가기업 모집 공고(~9.14)</t>
+          <t>「블록체인 기업 맞춤형 보안 고도화 지원」 기업 모집(~8/31)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3743&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3745&amp;page=1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2200,44 +2200,44 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-08-13 17:46:21.938331+09:00</t>
+          <t>2026-08-21 16:01:38.087170+09:00</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-08-13 17:46:21.938331+09:00</t>
+          <t>2026-08-21 16:01:38.087170+09:00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>34081</t>
+          <t>41086</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026년 하반기 정보보호 전문서비스 기업 지정에 관한 공고</t>
+          <t>2026년도 인터넷거버넌스 민간전문가 APrIGF 및 IGF 참석자 모집</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3742&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3744&amp;page=1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>59</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2245,11 +2245,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2257,44 +2253,44 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:24.927741+09:00</t>
+          <t>2026-08-21 15:01:32.139445+09:00</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:24.927741+09:00</t>
+          <t>2026-08-21 15:01:32.139445+09:00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>34071</t>
+          <t>34750</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>"예방 넘어 대응·복구까지" 랜섬웨어 전주기 대응 방안 논의한다</t>
+          <t>｢2026 블록체인 진흥주간｣ 전시부스 참가기업 모집 공고(~9.14)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2626&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3743&amp;page=1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2305,57 +2301,61 @@
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-08-13 09:16:35.989405+09:00</t>
+          <t>2026-08-13 17:46:21.938331+09:00</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-08-13 09:16:35.989405+09:00</t>
+          <t>2026-08-13 17:46:21.938331+09:00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>33789</t>
+          <t>34081</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 21회차 교육생 모집(~9.11)</t>
+          <t>2026년 하반기 정보보호 전문서비스 기업 지정에 관한 공고</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3741&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3742&amp;page=1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2363,34 +2363,34 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-08-12 16:01:25.579701+09:00</t>
+          <t>2026-08-13 09:31:24.927741+09:00</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-08-12 16:01:25.579701+09:00</t>
+          <t>2026-08-13 09:31:24.927741+09:00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>33749</t>
+          <t>34071</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>978</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026년도 블록체인 유공 포상 계획 공고 안내(~9.21 15:00 마감)</t>
+          <t>"예방 넘어 대응·복구까지" 랜섬웨어 전주기 대응 방안 논의한다</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3740&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2626&amp;page=1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2400,7 +2400,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2411,61 +2411,57 @@
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-08-12 15:31:25.306307+09:00</t>
+          <t>2026-08-13 09:16:35.989405+09:00</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-08-12 15:31:25.306307+09:00</t>
+          <t>2026-08-13 09:16:35.989405+09:00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>31741</t>
+          <t>33789</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026년 블록체인 수요-공급 협의체 (ABLE) 정례세미나 개최 안내(8.13.목)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 21회차 교육생 모집(~9.11)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3739&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3741&amp;page=1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2473,19 +2469,19 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-08-10 11:01:30.246604+09:00</t>
+          <t>2026-08-12 16:01:25.579701+09:00</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-08-10 11:01:30.246604+09:00</t>
+          <t>2026-08-12 16:01:25.579701+09:00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>29768</t>
+          <t>33749</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2495,27 +2491,27 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026년 블록체인 신뢰인프라(K-BTF) 활용·확산사업 공모 사전예고</t>
+          <t>2026년도 블록체인 유공 포상 계획 공고 안내(~9.21 15:00 마감)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3738&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3740&amp;page=1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
@@ -2526,52 +2522,56 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-08-07 17:01:29.954014+09:00</t>
+          <t>2026-08-12 15:31:25.306307+09:00</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-08-07 17:01:29.954014+09:00</t>
+          <t>2026-08-12 15:31:25.306307+09:00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>29728</t>
+          <t>31741</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026년도 블록체인 산업 실태조사 실시 및 협조 안내</t>
+          <t>2026년 블록체인 수요-공급 협의체 (ABLE) 정례세미나 개최 안내(8.13.목)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3737&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3739&amp;page=1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2579,19 +2579,19 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-08-07 16:31:30.938844+09:00</t>
+          <t>2026-08-10 11:01:30.246604+09:00</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-08-07 16:31:30.938844+09:00</t>
+          <t>2026-08-10 11:01:30.246604+09:00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>28711</t>
+          <t>29768</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2601,50 +2601,50 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원-나주시, 고교생 개인정보·정보보호 진로 탐색 지원</t>
+          <t>2026년 블록체인 신뢰인프라(K-BTF) 활용·확산사업 공모 사전예고</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2625&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3738&amp;page=1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-08-06 14:01:34.968573+09:00</t>
+          <t>2026-08-07 17:01:29.954014+09:00</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-08-06 14:01:34.968573+09:00</t>
+          <t>2026-08-07 17:01:29.954014+09:00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>27551</t>
+          <t>29728</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2654,75 +2654,75 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 기업 맞춤형 사이버 위협 알림 서비스 개시</t>
+          <t>2026년도 블록체인 산업 실태조사 실시 및 협조 안내</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2624&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3737&amp;page=1</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-08-05 09:46:34.063806+09:00</t>
+          <t>2026-08-07 16:31:30.938844+09:00</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-08-05 09:46:34.063806+09:00</t>
+          <t>2026-08-07 16:31:30.938844+09:00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>27511</t>
+          <t>28711</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 기관장 주도 국민 체감 성과 혁신 체계 가동</t>
+          <t>한국인터넷진흥원-나주시, 고교생 개인정보·정보보호 진로 탐색 지원</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2623&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2625&amp;page=1</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2738,19 +2738,19 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-08-05 09:16:33.823896+09:00</t>
+          <t>2026-08-06 14:01:34.968573+09:00</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-08-05 09:16:33.823896+09:00</t>
+          <t>2026-08-06 14:01:34.968573+09:00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>27268</t>
+          <t>27551</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2760,22 +2760,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>양자내성암호 국제 표준화 동향 분석</t>
+          <t>한국인터넷진흥원, 기업 맞춤형 사이버 위협 알림 서비스 개시</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3736&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2624&amp;page=1</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2786,39 +2786,39 @@
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-08-04 16:31:26.502205+09:00</t>
+          <t>2026-08-05 09:46:34.063806+09:00</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-08-04 16:31:26.502205+09:00</t>
+          <t>2026-08-05 09:46:34.063806+09:00</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>27128</t>
+          <t>27511</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>975</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 20회차 교육생 모집(~9.4)</t>
+          <t>한국인터넷진흥원, 기관장 주도 국민 체감 성과 혁신 체계 가동</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3735&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2623&amp;page=1</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2828,35 +2828,35 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>263</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2026-08-04 14:46:28.764255+09:00</t>
+          <t>2026-08-05 09:16:33.823896+09:00</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-08-04 14:46:28.764255+09:00</t>
+          <t>2026-08-05 09:16:33.823896+09:00</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>26211</t>
+          <t>27268</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2866,22 +2866,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 암호모듈검증 위한 시험 전문인력 양성</t>
+          <t>양자내성암호 국제 표준화 동향 분석</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2622&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3736&amp;page=1</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2892,24 +2892,24 @@
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2026-08-03 13:31:41.722921+09:00</t>
+          <t>2026-08-04 16:31:26.502205+09:00</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-08-03 13:31:41.722921+09:00</t>
+          <t>2026-08-04 16:31:26.502205+09:00</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>26188</t>
+          <t>27128</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2919,27 +2919,27 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026년 8차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(8월 추천) (~8.21(금) 18시까지)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 20회차 교육생 모집(~9.4)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3734&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3735&amp;page=1</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
@@ -2950,19 +2950,19 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2026-08-03 13:16:30.325331+09:00</t>
+          <t>2026-08-04 14:46:28.764255+09:00</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-08-03 13:16:30.325331+09:00</t>
+          <t>2026-08-04 14:46:28.764255+09:00</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>25891</t>
+          <t>26211</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 지역 상생 3대 사업 참여자 모집</t>
+          <t>한국인터넷진흥원, 암호모듈검증 위한 시험 전문인력 양성</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2621&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2622&amp;page=1</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>273</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3003,34 +3003,34 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-08-03 09:31:46.854132+09:00</t>
+          <t>2026-08-03 13:31:41.722921+09:00</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-08-03 09:31:46.854132+09:00</t>
+          <t>2026-08-03 13:31:41.722921+09:00</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>25864</t>
+          <t>26188</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026년 전남광주통합특별시 소상공인·사회적경제기업 판로 확대 지원기업 선발 안내(~8.14)</t>
+          <t>2026년 8차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(8월 추천) (~8.21(금) 18시까지)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3730&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3734&amp;page=1</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3040,7 +3040,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3048,11 +3048,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3060,34 +3056,34 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-08-03 09:16:35.817723+09:00</t>
+          <t>2026-08-03 13:16:30.325331+09:00</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-08-03 09:16:35.817723+09:00</t>
+          <t>2026-08-03 13:16:30.325331+09:00</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>25863</t>
+          <t>25891</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026년 전남광주통합특별시 지역문제 해결 프로젝트 공모전 개최 안내(~8.21)</t>
+          <t>한국인터넷진흥원, 지역 상생 3대 사업 참여자 모집</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3731&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2621&amp;page=1</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3097,7 +3093,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>80</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3105,31 +3101,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2026-08-03 09:16:35.817723+09:00</t>
+          <t>2026-08-03 09:31:46.854132+09:00</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-08-03 09:16:35.817723+09:00</t>
+          <t>2026-08-03 09:31:46.854132+09:00</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>25862</t>
+          <t>25864</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3139,12 +3131,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026년 한국인터넷진흥원 지역공부방 참여 대학생 장학금 지원자 모집 안내(~8.28)</t>
+          <t>2026년 전남광주통합특별시 소상공인·사회적경제기업 판로 확대 지원기업 선발 안내(~8.14)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3732&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3730&amp;page=1</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3154,7 +3146,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3186,7 +3178,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>25861</t>
+          <t>25863</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3196,12 +3188,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026년 암호모듈 시험자 양성교육 및 필기시험 안내(8.3~8.21)</t>
+          <t>2026년 전남광주통합특별시 지역문제 해결 프로젝트 공모전 개최 안내(~8.21)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3733&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3731&amp;page=1</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3243,7 +3235,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>23221</t>
+          <t>25862</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3253,22 +3245,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026년 블록체인 기업성장허브 입주기업 모집(~8월 27일(목) 16:00까지)</t>
+          <t>2026년 한국인터넷진흥원 지역공부방 참여 대학생 장학금 지원자 모집 안내(~8.28)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3729&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3732&amp;page=1</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3288,52 +3280,56 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2026-07-30 17:16:54.540202+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-07-30 17:16:54.540202+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>22504</t>
+          <t>25861</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 19회차 교육생 모집(~8.28)</t>
+          <t>2026년 암호모듈 시험자 양성교육 및 필기시험 안내(8.3~8.21)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3728&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3733&amp;page=1</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3341,52 +3337,56 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2026-07-29 18:32:00.075123+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-07-29 18:32:00.075123+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>22464</t>
+          <t>23221</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026년 연계정보 이용기관 안전조치 실태점검 2차 설명회 개최</t>
+          <t>2026년 블록체인 기업성장허브 입주기업 모집(~8월 27일(목) 16:00까지)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3727&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3729&amp;page=1</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I55" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3394,19 +3394,19 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:59.875668+09:00</t>
+          <t>2026-07-30 17:16:54.540202+09:00</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:59.875668+09:00</t>
+          <t>2026-07-30 17:16:54.540202+09:00</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>20771</t>
+          <t>22504</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3416,50 +3416,50 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 성평등가족부와 불법·유해 정보 유통 대응 맞손</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 19회차 교육생 모집(~8.28)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2620&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3728&amp;page=1</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2026-07-27 17:17:05.702970+09:00</t>
+          <t>2026-07-29 18:32:00.075123+09:00</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-07-27 17:17:05.702970+09:00</t>
+          <t>2026-07-29 18:32:00.075123+09:00</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>20191</t>
+          <t>22464</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3469,65 +3469,65 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 향후 10년 설계한다…전담 추진단(TF) 출범</t>
+          <t>2026년 연계정보 이용기관 안전조치 실태점검 2차 설명회 개최</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2619&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3727&amp;page=1</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2026-07-27 10:02:05.338547+09:00</t>
+          <t>2026-07-29 18:01:59.875668+09:00</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-07-27 10:02:05.338547+09:00</t>
+          <t>2026-07-29 18:01:59.875668+09:00</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>20061</t>
+          <t>20771</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(1차, BreakingPoint)</t>
+          <t>한국인터넷진흥원, 성평등가족부와 불법·유해 정보 유통 대응 맞손</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3726&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2620&amp;page=1</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>150</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3545,117 +3545,117 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>2026-07-27 08:31:55.019743+09:00</t>
+          <t>2026-07-27 17:17:05.702970+09:00</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-07-27 08:31:55.019743+09:00</t>
+          <t>2026-07-27 17:17:05.702970+09:00</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>16785</t>
+          <t>20191</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 17회차 교육생 모집(~8.7)</t>
+          <t>아피가(APIGA) 향후 10년 설계한다…전담 추진단(TF) 출범</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3724&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2619&amp;page=1</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>287</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 10:02:05.338547+09:00</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 10:02:05.338547+09:00</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>16784</t>
+          <t>20061</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>1497</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 18회차 교육생 모집(~8.21)</t>
+          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(1차, BreakingPoint)</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3725&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3726&amp;page=1</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>246</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I60" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3663,34 +3663,34 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 08:31:55.019743+09:00</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 08:31:55.019743+09:00</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>16781</t>
+          <t>16785</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1496</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 16회차 교육생 모집(~7.31)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 17회차 교육생 모집(~8.7)</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3723&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3724&amp;page=1</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3700,7 +3700,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>236</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3708,11 +3708,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3732,22 +3728,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>16691</t>
+          <t>16784</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1497</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>'블록체인 기반 예금토큰 결제 인프라 확산' 사업 발대식 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 18회차 교육생 모집(~8.21)</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2618&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3725&amp;page=1</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3757,50 +3753,50 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>260</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2026-07-22 17:32:01.526863+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-07-22 17:32:01.526863+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>16464</t>
+          <t>16781</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>[홍보] 정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 안내</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 16회차 교육생 모집(~7.31)</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3722&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3723&amp;page=1</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3810,7 +3806,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>242</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -3818,7 +3814,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr"/>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I63" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3826,19 +3826,19 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>2026-07-22 14:46:48.687665+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-07-22 14:46:48.687665+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>16051</t>
+          <t>16691</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 보안 인재·글로벌 전문가 교류의 장 열어</t>
+          <t>'블록체인 기반 예금토큰 결제 인프라 확산' 사업 발대식 개최</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2617&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2618&amp;page=1</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>278</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -3879,19 +3879,19 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>2026-07-22 09:31:50.671841+09:00</t>
+          <t>2026-07-22 17:32:01.526863+09:00</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-07-22 09:31:50.671841+09:00</t>
+          <t>2026-07-22 17:32:01.526863+09:00</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>14611</t>
+          <t>16464</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3901,50 +3901,50 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
+          <t>[홍보] 정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 안내</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3722&amp;page=1</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-22 14:46:48.687665+09:00</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-22 14:46:48.687665+09:00</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>14431</t>
+          <t>16051</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3954,22 +3954,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>한국인터넷진흥원, 보안 인재·글로벌 전문가 교류의 장 열어</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2617&amp;page=1</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>233</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -3985,34 +3985,34 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>14611</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>32</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -4030,56 +4030,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>14444</t>
+          <t>14431</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>1493</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>53</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -4090,49 +4086,49 @@
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>11331</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
+          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -4140,64 +4136,64 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>10981</t>
+          <t>14444</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -4205,19 +4201,19 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>10943</t>
+          <t>11331</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4227,65 +4223,65 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
+          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>10663</t>
+          <t>10981</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
+          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4295,15 +4291,19 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I72" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -4311,19 +4311,19 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>9805</t>
+          <t>10943</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4333,27 +4333,27 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
+          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
@@ -4364,19 +4364,19 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>9691</t>
+          <t>10663</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4386,22 +4386,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
+          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -4412,61 +4412,57 @@
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>9321</t>
+          <t>9805</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
+          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -4474,19 +4470,19 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>8871</t>
+          <t>9691</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -4496,22 +4492,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
+          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -4527,52 +4523,56 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>6685</t>
+          <t>9321</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
+          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I77" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -4580,19 +4580,19 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>6571</t>
+          <t>8871</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -4602,22 +4602,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
+          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -4633,19 +4633,19 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>5591</t>
+          <t>6685</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4655,22 +4655,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
+          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -4681,49 +4681,49 @@
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>6571</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
+          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -4739,44 +4739,44 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>4762</t>
+          <t>5591</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>AI 보안 위협 대응 매뉴얼</t>
+          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>33</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -4784,56 +4784,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>4761</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>961</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>AI 보안 레드티밍 가이드</t>
+          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -4841,46 +4837,42 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>4251</t>
+          <t>4762</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
+          <t>AI 보안 위협 대응 매뉴얼</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -4890,7 +4882,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -4898,42 +4890,46 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr"/>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>4761</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
+          <t>AI 보안 레드티밍 가이드</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -4943,15 +4939,19 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I84" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -4959,44 +4959,44 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t>4251</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
+          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>191</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -5012,56 +5012,52 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3867</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
+          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -5069,44 +5065,44 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4111</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>959</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
+          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>34</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -5114,56 +5110,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
+          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -5171,7 +5163,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr"/>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I88" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -5191,32 +5187,32 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
+          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>105</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -5224,7 +5220,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr"/>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I89" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -5244,22 +5244,22 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1477</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
+          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5269,19 +5269,15 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>386</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -5301,22 +5297,22 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2026년 IoT 보안인증 교육과정 안내</t>
+          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5326,19 +5322,15 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>362</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -5358,40 +5350,44 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>522</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I92" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -5411,7 +5407,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -5421,27 +5417,27 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
+          <t>2026년 IoT 보안인증 교육과정 안내</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>1529</t>
+          <t>652</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -5468,7 +5464,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -5478,22 +5474,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
+          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>818</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -5509,44 +5505,44 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
+          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>76426</t>
+          <t>1529</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -5554,52 +5550,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr"/>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>55906</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -5610,49 +5610,49 @@
       <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>958</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
+          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>55329</t>
+          <t>76426</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -5680,32 +5680,32 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>956</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
+          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>34467</t>
+          <t>55906</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -5733,89 +5733,85 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>957</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
+          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2945</t>
+          <t>55329</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>955</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
+          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>34467</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -5823,109 +5819,109 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>145255</t>
+          <t>2945</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
+          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>26576</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -5933,52 +5929,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr"/>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>954</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>34290</t>
+          <t>145255</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -6006,32 +6006,32 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>953</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
+          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>184573</t>
+          <t>26576</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -6059,32 +6059,32 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>14403</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>6587</t>
+          <t>34290</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -6092,56 +6092,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>951</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
+          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>51749</t>
+          <t>184573</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -6169,32 +6165,32 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>14403</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>78439</t>
+          <t>6587</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -6202,75 +6198,185 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr"/>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>51749</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>보도자료</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>949</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>78439</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>보도자료</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
           <t>38805</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
+      <c r="B110" t="inlineStr">
         <is>
           <t>공지</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr">
+      <c r="C110" t="inlineStr">
         <is>
           <t>[공유] 지능형 CCTV 성능시험 재개 안내 공지</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr">
+      <c r="D110" t="inlineStr">
         <is>
           <t>https://www.kisa.or.kr/401/form?postSeq=3677&amp;page=1</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr">
+      <c r="E110" t="inlineStr">
         <is>
           <t>2026-06-02</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr">
+      <c r="F110" t="inlineStr">
         <is>
           <t>6525</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr">
+      <c r="G110" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
+      <c r="H110" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>공지사항</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
         <is>
           <t>2026-08-18 17:16:37.364015+09:00</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr">
+      <c r="K110" t="inlineStr">
         <is>
           <t>2026-08-18 17:16:37.364015+09:00</t>
         </is>

--- a/docs/snapshot/downloads/kisa.xlsx
+++ b/docs/snapshot/downloads/kisa.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K110"/>
+  <dimension ref="A1:K111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,22 +476,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>63068</t>
+          <t>64631</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>990</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>대국민 혁신 정책·제안 공모전 개최</t>
+          <t>한국인터넷진흥원, 인터넷 주소 자원 관리 역량 국제적 인정받아</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3766&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2639&amp;page=1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -501,7 +501,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -512,24 +512,24 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-09-18 10:46:37.266535+09:00</t>
+          <t>2026-09-20 12:01:47.233521+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-09-18 10:46:37.266535+09:00</t>
+          <t>2026-09-20 12:01:47.233521+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>63051</t>
+          <t>63068</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>세계경제포럼·싱가포르 사이버보안청과 인공지능(AI) 위협 대비 사이버보안 협력 강화</t>
+          <t>대국민 혁신 정책·제안 공모전 개최</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2638&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3766&amp;page=1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -565,49 +565,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-09-18 10:31:43.770443+09:00</t>
+          <t>2026-09-18 10:46:37.266535+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-09-18 10:31:43.770443+09:00</t>
+          <t>2026-09-18 10:46:37.266535+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>62781</t>
+          <t>63051</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026년 블록체인 기업성장허브 입주기업 모집(~10월 7일(수) 16:00까지)</t>
+          <t>세계경제포럼·싱가포르 사이버보안청과 인공지능(AI) 위협 대비 사이버보안 협력 강화</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3765&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2638&amp;page=1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -615,46 +615,42 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-09-17 17:16:36.514530+09:00</t>
+          <t>2026-09-18 10:31:43.770443+09:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-09-17 17:16:36.514530+09:00</t>
+          <t>2026-09-18 10:31:43.770443+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>62507</t>
+          <t>62781</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 25회차 교육생 모집(~10.10)</t>
+          <t>2026년 블록체인 기업성장허브 입주기업 모집(~10월 7일(수) 16:00까지)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3764&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3765&amp;page=1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -664,15 +660,19 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -680,19 +680,19 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-09-17 13:31:33.789948+09:00</t>
+          <t>2026-09-17 17:16:36.514530+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-09-17 13:31:33.789948+09:00</t>
+          <t>2026-09-17 17:16:36.514530+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>62367</t>
+          <t>62507</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -702,12 +702,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 24회차 교육생 모집(~10.9)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 25회차 교육생 모집(~10.10)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3763&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3764&amp;page=1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -733,19 +733,19 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-09-17 11:46:35.719751+09:00</t>
+          <t>2026-09-17 13:31:33.789948+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-09-17 11:46:35.719751+09:00</t>
+          <t>2026-09-17 13:31:33.789948+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>61484</t>
+          <t>62367</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -755,27 +755,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026년 제13회 소프트웨어(SW) 개발보안 경진대회 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 24회차 교육생 모집(~10.9)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3762&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3763&amp;page=1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
@@ -786,19 +786,19 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-09-16 09:46:37.058042+09:00</t>
+          <t>2026-09-17 11:46:35.719751+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-09-16 09:46:37.058042+09:00</t>
+          <t>2026-09-17 11:46:35.719751+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>61111</t>
+          <t>61484</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -808,22 +808,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>민관 합동 ‘자동차 사이버 침해사고 대응 모의훈련’ 실시</t>
+          <t>2026년 제13회 소프트웨어(SW) 개발보안 경진대회 개최</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2637&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3762&amp;page=1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -834,24 +834,24 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-09-15 15:01:52.747371+09:00</t>
+          <t>2026-09-16 09:46:37.058042+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-09-15 15:01:52.747371+09:00</t>
+          <t>2026-09-16 09:46:37.058042+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>61031</t>
+          <t>61111</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>“새로운 보안 위협, 인공지능(AI)으로 대응” 정보보호 제품 개발 기업 대상 보안 역량 강화 교육 추진</t>
+          <t>민관 합동 ‘자동차 사이버 침해사고 대응 모의훈련’ 실시</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2636&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2637&amp;page=1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -892,44 +892,44 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-09-15 14:01:52.540884+09:00</t>
+          <t>2026-09-15 15:01:52.747371+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-09-15 14:01:52.540884+09:00</t>
+          <t>2026-09-15 15:01:52.747371+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>57381</t>
+          <t>61031</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026 전자문서 유공 포상 공고</t>
+          <t>“새로운 보안 위협, 인공지능(AI)으로 대응” 정보보호 제품 개발 기업 대상 보안 역량 강화 교육 추진</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3761&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2636&amp;page=1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -937,46 +937,42 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-09-10 14:16:31.877229+09:00</t>
+          <t>2026-09-15 14:01:52.540884+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-09-10 14:16:31.877229+09:00</t>
+          <t>2026-09-15 14:01:52.540884+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>57149</t>
+          <t>57381</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026년 클라우드 서비스 보안인증(CSAP) 교육 안내</t>
+          <t>2026 전자문서 유공 포상 공고</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3760&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3761&amp;page=1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -986,7 +982,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -994,7 +990,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1002,19 +1002,19 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-09-10 10:46:38.794916+09:00</t>
+          <t>2026-09-10 14:16:31.877229+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-09-10 10:46:38.794916+09:00</t>
+          <t>2026-09-10 14:16:31.877229+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>56431</t>
+          <t>57149</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1024,22 +1024,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>보호나라 챗봇, 국민 생활 속 정보보호 성과 인정</t>
+          <t>2026년 클라우드 서비스 보안인증(CSAP) 교육 안내</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2634&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3760&amp;page=1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1050,92 +1050,92 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-09-09 12:01:35.142670+09:00</t>
+          <t>2026-09-10 10:46:38.794916+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-09-09 12:01:35.142670+09:00</t>
+          <t>2026-09-10 10:46:38.794916+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>56969</t>
+          <t>56431</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1522</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>온마이데이터 서비스 이용 이벤트 안내</t>
+          <t>보호나라 챗봇, 국민 생활 속 정보보호 성과 인정</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3758&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2634&amp;page=1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>402</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-09-10 08:31:37.677434+09:00</t>
+          <t>2026-09-09 12:01:35.142670+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-09-10 08:31:37.677434+09:00</t>
+          <t>2026-09-09 12:01:35.142670+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>54791</t>
+          <t>56969</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1522</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>국내 캐시 도메인이름시스템(DNS) 운영기관, 신규 암호키 반영 여부 확인하세요</t>
+          <t>온마이데이터 서비스 이용 이벤트 안내</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2633&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3758&amp;page=1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1145,60 +1145,60 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>402</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-09-07 12:01:35.243341+09:00</t>
+          <t>2026-09-10 08:31:37.677434+09:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-09-07 12:01:35.243341+09:00</t>
+          <t>2026-09-10 08:31:37.677434+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>54541</t>
+          <t>54791</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(2차, Avalanche)</t>
+          <t>국내 캐시 도메인이름시스템(DNS) 운영기관, 신규 암호키 반영 여부 확인하세요</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3759&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2633&amp;page=1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1206,31 +1206,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-09-07 09:01:25.516098+09:00</t>
+          <t>2026-09-07 12:01:35.243341+09:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-09-07 09:01:25.516098+09:00</t>
+          <t>2026-09-07 12:01:35.243341+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>51281</t>
+          <t>54541</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1240,27 +1236,27 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>(행사 안내) 국외이전 제도 개선 및 CBPR 인증제도 기업 설명회 개최</t>
+          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(2차, Avalanche)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3757&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3759&amp;page=1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1275,52 +1271,56 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-09-03 09:16:26.856224+09:00</t>
+          <t>2026-09-07 09:01:25.516098+09:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-09-03 09:16:26.856224+09:00</t>
+          <t>2026-09-07 09:01:25.516098+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>56970</t>
+          <t>51281</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1521</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026 부산지역 도메인이름 분쟁해결 세미나 개최 안내(9.11)</t>
+          <t>(행사 안내) 국외이전 제도 개선 및 CBPR 인증제도 기업 설명회 개최</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3755&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3757&amp;page=1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>23</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1328,34 +1328,34 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-09-10 08:31:37.677434+09:00</t>
+          <t>2026-09-03 09:16:26.856224+09:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-09-10 08:31:37.677434+09:00</t>
+          <t>2026-09-03 09:16:26.856224+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>51121</t>
+          <t>56970</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1521</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026년 블록체인 수요공급협의체(ABLE) 블록체인 수요기업(비금융분야) 모집 공고</t>
+          <t>2026 부산지역 도메인이름 분쟁해결 세미나 개최 안내(9.11)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3754&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3755&amp;page=1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>242</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1373,11 +1373,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1385,19 +1381,19 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-09-02 17:31:25.610368+09:00</t>
+          <t>2026-09-10 08:31:37.677434+09:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-09-02 17:31:25.610368+09:00</t>
+          <t>2026-09-10 08:31:37.677434+09:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>50601</t>
+          <t>51121</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1407,12 +1403,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026년 9차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(9월 추천) (~9.18(금) 18시까지)</t>
+          <t>2026년 블록체인 수요공급협의체(ABLE) 블록체인 수요기업(비금융분야) 모집 공고</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3753&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3754&amp;page=1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1422,7 +1418,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>24</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1442,44 +1438,44 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-09-02 11:01:32.173328+09:00</t>
+          <t>2026-09-02 17:31:25.610368+09:00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-09-02 11:01:32.173328+09:00</t>
+          <t>2026-09-02 17:31:25.610368+09:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>49872</t>
+          <t>50601</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>인공지능(AI) 사이버 위협, 실전 모의훈련으로 대응</t>
+          <t>2026년 9차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(9월 추천) (~9.18(금) 18시까지)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2631&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3753&amp;page=1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1487,27 +1483,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-09-01 12:01:47.858504+09:00</t>
+          <t>2026-09-02 11:01:32.173328+09:00</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-09-01 12:01:47.858504+09:00</t>
+          <t>2026-09-02 11:01:32.173328+09:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>49669</t>
+          <t>49872</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1517,12 +1517,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>「2026 위치정보 맞춤형 컨설팅 참여기업 모집」</t>
+          <t>인공지능(AI) 사이버 위협, 실전 모의훈련으로 대응</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3752&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2631&amp;page=1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1532,35 +1532,35 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-09-01 09:31:38.715793+09:00</t>
+          <t>2026-09-01 12:01:47.858504+09:00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-09-01 09:31:38.715793+09:00</t>
+          <t>2026-09-01 12:01:47.858504+09:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>49631</t>
+          <t>49669</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1570,12 +1570,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>물리보안 시스템 간 연동 장벽 낮춘다</t>
+          <t>「2026 위치정보 맞춤형 컨설팅 참여기업 모집」</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2632&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3752&amp;page=1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1585,103 +1585,103 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-09-01 09:01:45.980040+09:00</t>
+          <t>2026-09-01 09:31:38.715793+09:00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-09-01 09:01:45.980040+09:00</t>
+          <t>2026-09-01 09:31:38.715793+09:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>49589</t>
+          <t>49631</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1517</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 23회차 교육생 모집(~9.18)</t>
+          <t>물리보안 시스템 간 연동 장벽 낮춘다</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3751&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2632&amp;page=1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-09-01 08:31:37.253592+09:00</t>
+          <t>2026-09-01 09:01:45.980040+09:00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-09-01 08:31:37.253592+09:00</t>
+          <t>2026-09-01 09:01:45.980040+09:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>48831</t>
+          <t>49589</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1517</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>생성형 인공지능(AI) 기반 실전형 모의해킹 대회 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 23회차 교육생 모집(~9.18)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2630&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3751&amp;page=1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1691,35 +1691,35 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>174</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-08-31 09:16:38.866405+09:00</t>
+          <t>2026-09-01 08:31:37.253592+09:00</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-08-31 09:16:38.866405+09:00</t>
+          <t>2026-09-01 08:31:37.253592+09:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>46011</t>
+          <t>48831</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1729,22 +1729,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>자동차 노리는 사이버 위협, 한국인터넷진흥원-한국교통안전공단이 함께 대응한다</t>
+          <t>생성형 인공지능(AI) 기반 실전형 모의해킹 대회 개최</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2628&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2630&amp;page=1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1760,34 +1760,34 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-08-27 15:01:41.552844+09:00</t>
+          <t>2026-08-31 09:16:38.866405+09:00</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-08-27 15:01:41.552844+09:00</t>
+          <t>2026-08-31 09:16:38.866405+09:00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>45681</t>
+          <t>46011</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>싱가포르 현지 진출 지원 국내 블록체인 기업 모집(~9.16(수) 14시)</t>
+          <t>자동차 노리는 사이버 위협, 한국인터넷진흥원-한국교통안전공단이 함께 대응한다</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3750&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2628&amp;page=1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1805,56 +1805,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-08-27 11:01:31.314899+09:00</t>
+          <t>2026-08-27 15:01:41.552844+09:00</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-08-27 11:01:31.314899+09:00</t>
+          <t>2026-08-27 15:01:41.552844+09:00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>45191</t>
+          <t>45681</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 아·태 지역 사이버공격 대응 공동 훈련 실시</t>
+          <t>싱가포르 현지 진출 지원 국내 블록체인 기업 모집(~9.16(수) 14시)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2629&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3750&amp;page=1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1862,42 +1858,46 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-08-26 15:01:47.261933+09:00</t>
+          <t>2026-08-27 11:01:31.314899+09:00</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-08-26 15:01:47.261933+09:00</t>
+          <t>2026-08-27 11:01:31.314899+09:00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>44741</t>
+          <t>45191</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>[3차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~9/16)</t>
+          <t>한국인터넷진흥원, 아·태 지역 사이버공격 대응 공동 훈련 실시</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3749&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2629&amp;page=1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1915,56 +1915,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-08-26 09:31:36.427758+09:00</t>
+          <t>2026-08-26 15:01:47.261933+09:00</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-08-26 09:31:36.427758+09:00</t>
+          <t>2026-08-26 15:01:47.261933+09:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>44448</t>
+          <t>44741</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 공고</t>
+          <t>[3차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~9/16)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3748&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3749&amp;page=1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1972,7 +1968,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1980,19 +1980,19 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-08-25 16:01:39.626193+09:00</t>
+          <t>2026-08-26 09:31:36.427758+09:00</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-08-25 16:01:39.626193+09:00</t>
+          <t>2026-08-26 09:31:36.427758+09:00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>43767</t>
+          <t>44448</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2002,27 +2002,27 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 21회차 교육생 모집(~9.12)</t>
+          <t>정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 공고</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3747&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3748&amp;page=1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
@@ -2033,19 +2033,19 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-08-24 17:46:42.254577+09:00</t>
+          <t>2026-08-25 16:01:39.626193+09:00</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-08-24 17:46:42.254577+09:00</t>
+          <t>2026-08-25 16:01:39.626193+09:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>43311</t>
+          <t>43767</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2055,12 +2055,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>양자내성암호 전환, 어떻게 준비해야 할까?</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 21회차 교육생 모집(~9.12)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2627&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3747&amp;page=1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2070,50 +2070,50 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-08-24 12:01:45.511381+09:00</t>
+          <t>2026-08-24 17:46:42.254577+09:00</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-08-24 12:01:45.511381+09:00</t>
+          <t>2026-08-24 17:46:42.254577+09:00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>43301</t>
+          <t>43311</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>양자내성암호 전문교육 PQC 실무과정 교육생 모집(8.24~)</t>
+          <t>양자내성암호 전환, 어떻게 준비해야 할까?</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3746&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2627&amp;page=1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2131,31 +2131,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-08-24 12:01:36.271108+09:00</t>
+          <t>2026-08-24 12:01:45.511381+09:00</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-08-24 12:01:36.271108+09:00</t>
+          <t>2026-08-24 12:01:45.511381+09:00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>41161</t>
+          <t>43301</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2165,27 +2161,27 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>「블록체인 기업 맞춤형 보안 고도화 지원」 기업 모집(~8/31)</t>
+          <t>양자내성암호 전문교육 PQC 실무과정 교육생 모집(8.24~)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3745&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3746&amp;page=1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2200,34 +2196,34 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-08-21 16:01:38.087170+09:00</t>
+          <t>2026-08-24 12:01:36.271108+09:00</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-08-21 16:01:38.087170+09:00</t>
+          <t>2026-08-24 12:01:36.271108+09:00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>41086</t>
+          <t>41161</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026년도 인터넷거버넌스 민간전문가 APrIGF 및 IGF 참석자 모집</t>
+          <t>「블록체인 기업 맞춤형 보안 고도화 지원」 기업 모집(~8/31)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3744&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3745&amp;page=1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2237,15 +2233,19 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2253,19 +2253,19 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-08-21 15:01:32.139445+09:00</t>
+          <t>2026-08-21 16:01:38.087170+09:00</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-08-21 15:01:32.139445+09:00</t>
+          <t>2026-08-21 16:01:38.087170+09:00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>34750</t>
+          <t>41086</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2275,22 +2275,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>｢2026 블록체인 진흥주간｣ 전시부스 참가기업 모집 공고(~9.14)</t>
+          <t>2026년도 인터넷거버넌스 민간전문가 APrIGF 및 IGF 참석자 모집</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3743&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3744&amp;page=1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>59</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-08-13 17:46:21.938331+09:00</t>
+          <t>2026-08-21 15:01:32.139445+09:00</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-08-13 17:46:21.938331+09:00</t>
+          <t>2026-08-21 15:01:32.139445+09:00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>34081</t>
+          <t>34750</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026년 하반기 정보보호 전문서비스 기업 지정에 관한 공고</t>
+          <t>｢2026 블록체인 진흥주간｣ 전시부스 참가기업 모집 공고(~9.14)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3742&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3743&amp;page=1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2351,11 +2351,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2363,44 +2359,44 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:24.927741+09:00</t>
+          <t>2026-08-13 17:46:21.938331+09:00</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:24.927741+09:00</t>
+          <t>2026-08-13 17:46:21.938331+09:00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>34071</t>
+          <t>34081</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>"예방 넘어 대응·복구까지" 랜섬웨어 전주기 대응 방안 논의한다</t>
+          <t>2026년 하반기 정보보호 전문서비스 기업 지정에 관한 공고</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2626&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3742&amp;page=1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2408,42 +2404,46 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-08-13 09:16:35.989405+09:00</t>
+          <t>2026-08-13 09:31:24.927741+09:00</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-08-13 09:16:35.989405+09:00</t>
+          <t>2026-08-13 09:31:24.927741+09:00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>33789</t>
+          <t>34071</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>978</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 21회차 교육생 모집(~9.11)</t>
+          <t>"예방 넘어 대응·복구까지" 랜섬웨어 전주기 대응 방안 논의한다</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3741&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2626&amp;page=1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2453,35 +2453,35 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-08-12 16:01:25.579701+09:00</t>
+          <t>2026-08-13 09:16:35.989405+09:00</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-08-12 16:01:25.579701+09:00</t>
+          <t>2026-08-13 09:16:35.989405+09:00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>33749</t>
+          <t>33789</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2491,12 +2491,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026년도 블록체인 유공 포상 계획 공고 안내(~9.21 15:00 마감)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 21회차 교육생 모집(~9.11)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3740&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3741&amp;page=1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
@@ -2522,44 +2522,44 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-08-12 15:31:25.306307+09:00</t>
+          <t>2026-08-12 16:01:25.579701+09:00</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-08-12 15:31:25.306307+09:00</t>
+          <t>2026-08-12 16:01:25.579701+09:00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>31741</t>
+          <t>33749</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026년 블록체인 수요-공급 협의체 (ABLE) 정례세미나 개최 안내(8.13.목)</t>
+          <t>2026년도 블록체인 유공 포상 계획 공고 안내(~9.21 15:00 마감)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3739&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3740&amp;page=1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2567,11 +2567,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2579,52 +2575,56 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-08-10 11:01:30.246604+09:00</t>
+          <t>2026-08-12 15:31:25.306307+09:00</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-08-10 11:01:30.246604+09:00</t>
+          <t>2026-08-12 15:31:25.306307+09:00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>29768</t>
+          <t>31741</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026년 블록체인 신뢰인프라(K-BTF) 활용·확산사업 공모 사전예고</t>
+          <t>2026년 블록체인 수요-공급 협의체 (ABLE) 정례세미나 개최 안내(8.13.목)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3738&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3739&amp;page=1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2632,19 +2632,19 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-08-07 17:01:29.954014+09:00</t>
+          <t>2026-08-10 11:01:30.246604+09:00</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-08-07 17:01:29.954014+09:00</t>
+          <t>2026-08-10 11:01:30.246604+09:00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>29728</t>
+          <t>29768</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2654,12 +2654,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026년도 블록체인 산업 실태조사 실시 및 협조 안내</t>
+          <t>2026년 블록체인 신뢰인프라(K-BTF) 활용·확산사업 공모 사전예고</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3737&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3738&amp;page=1</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2669,7 +2669,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2685,19 +2685,19 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-08-07 16:31:30.938844+09:00</t>
+          <t>2026-08-07 17:01:29.954014+09:00</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-08-07 16:31:30.938844+09:00</t>
+          <t>2026-08-07 17:01:29.954014+09:00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>28711</t>
+          <t>29728</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2707,50 +2707,50 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원-나주시, 고교생 개인정보·정보보호 진로 탐색 지원</t>
+          <t>2026년도 블록체인 산업 실태조사 실시 및 협조 안내</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2625&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3737&amp;page=1</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-08-06 14:01:34.968573+09:00</t>
+          <t>2026-08-07 16:31:30.938844+09:00</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-08-06 14:01:34.968573+09:00</t>
+          <t>2026-08-07 16:31:30.938844+09:00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>27551</t>
+          <t>28711</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2760,22 +2760,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 기업 맞춤형 사이버 위협 알림 서비스 개시</t>
+          <t>한국인터넷진흥원-나주시, 고교생 개인정보·정보보호 진로 탐색 지원</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2624&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2625&amp;page=1</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2791,44 +2791,44 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-08-05 09:46:34.063806+09:00</t>
+          <t>2026-08-06 14:01:34.968573+09:00</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-08-05 09:46:34.063806+09:00</t>
+          <t>2026-08-06 14:01:34.968573+09:00</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>27511</t>
+          <t>27551</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 기관장 주도 국민 체감 성과 혁신 체계 가동</t>
+          <t>한국인터넷진흥원, 기업 맞춤형 사이버 위협 알림 서비스 개시</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2623&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2624&amp;page=1</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2844,34 +2844,34 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2026-08-05 09:16:33.823896+09:00</t>
+          <t>2026-08-05 09:46:34.063806+09:00</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-08-05 09:16:33.823896+09:00</t>
+          <t>2026-08-05 09:46:34.063806+09:00</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>27268</t>
+          <t>27511</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>975</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>양자내성암호 국제 표준화 동향 분석</t>
+          <t>한국인터넷진흥원, 기관장 주도 국민 체감 성과 혁신 체계 가동</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3736&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2623&amp;page=1</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>263</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2892,24 +2892,24 @@
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2026-08-04 16:31:26.502205+09:00</t>
+          <t>2026-08-05 09:16:33.823896+09:00</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-08-04 16:31:26.502205+09:00</t>
+          <t>2026-08-05 09:16:33.823896+09:00</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>27128</t>
+          <t>27268</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 20회차 교육생 모집(~9.4)</t>
+          <t>양자내성암호 국제 표준화 동향 분석</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3735&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3736&amp;page=1</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2934,12 +2934,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
@@ -2950,19 +2950,19 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2026-08-04 14:46:28.764255+09:00</t>
+          <t>2026-08-04 16:31:26.502205+09:00</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-08-04 14:46:28.764255+09:00</t>
+          <t>2026-08-04 16:31:26.502205+09:00</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>26211</t>
+          <t>27128</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2972,50 +2972,50 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 암호모듈검증 위한 시험 전문인력 양성</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 20회차 교육생 모집(~9.4)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2622&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3735&amp;page=1</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-08-03 13:31:41.722921+09:00</t>
+          <t>2026-08-04 14:46:28.764255+09:00</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-08-03 13:31:41.722921+09:00</t>
+          <t>2026-08-04 14:46:28.764255+09:00</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>26188</t>
+          <t>26211</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3025,12 +3025,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026년 8차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(8월 추천) (~8.21(금) 18시까지)</t>
+          <t>한국인터넷진흥원, 암호모듈검증 위한 시험 전문인력 양성</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3734&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2622&amp;page=1</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3040,7 +3040,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>273</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3051,24 +3051,24 @@
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-08-03 13:16:30.325331+09:00</t>
+          <t>2026-08-03 13:31:41.722921+09:00</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-08-03 13:16:30.325331+09:00</t>
+          <t>2026-08-03 13:31:41.722921+09:00</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>25891</t>
+          <t>26188</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 지역 상생 3대 사업 참여자 모집</t>
+          <t>2026년 8차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(8월 추천) (~8.21(금) 18시까지)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2621&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3734&amp;page=1</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3104,39 +3104,39 @@
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2026-08-03 09:31:46.854132+09:00</t>
+          <t>2026-08-03 13:16:30.325331+09:00</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-08-03 09:31:46.854132+09:00</t>
+          <t>2026-08-03 13:16:30.325331+09:00</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>25864</t>
+          <t>25891</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026년 전남광주통합특별시 소상공인·사회적경제기업 판로 확대 지원기업 선발 안내(~8.14)</t>
+          <t>한국인터넷진흥원, 지역 상생 3대 사업 참여자 모집</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3730&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2621&amp;page=1</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>80</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3154,31 +3154,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2026-08-03 09:16:35.817723+09:00</t>
+          <t>2026-08-03 09:31:46.854132+09:00</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-08-03 09:16:35.817723+09:00</t>
+          <t>2026-08-03 09:31:46.854132+09:00</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>25863</t>
+          <t>25864</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3188,12 +3184,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026년 전남광주통합특별시 지역문제 해결 프로젝트 공모전 개최 안내(~8.21)</t>
+          <t>2026년 전남광주통합특별시 소상공인·사회적경제기업 판로 확대 지원기업 선발 안내(~8.14)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3731&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3730&amp;page=1</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3203,7 +3199,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3235,7 +3231,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>25862</t>
+          <t>25863</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3245,12 +3241,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026년 한국인터넷진흥원 지역공부방 참여 대학생 장학금 지원자 모집 안내(~8.28)</t>
+          <t>2026년 전남광주통합특별시 지역문제 해결 프로젝트 공모전 개최 안내(~8.21)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3732&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3731&amp;page=1</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3260,7 +3256,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3292,7 +3288,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>25861</t>
+          <t>25862</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3302,12 +3298,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026년 암호모듈 시험자 양성교육 및 필기시험 안내(8.3~8.21)</t>
+          <t>2026년 한국인터넷진흥원 지역공부방 참여 대학생 장학금 지원자 모집 안내(~8.28)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3733&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3732&amp;page=1</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3317,7 +3313,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3349,7 +3345,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>23221</t>
+          <t>25861</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3359,22 +3355,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026년 블록체인 기업성장허브 입주기업 모집(~8월 27일(목) 16:00까지)</t>
+          <t>2026년 암호모듈 시험자 양성교육 및 필기시험 안내(8.3~8.21)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3729&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3733&amp;page=1</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3394,52 +3390,56 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2026-07-30 17:16:54.540202+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-07-30 17:16:54.540202+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>22504</t>
+          <t>23221</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 19회차 교육생 모집(~8.28)</t>
+          <t>2026년 블록체인 기업성장허브 입주기업 모집(~8월 27일(목) 16:00까지)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3728&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3729&amp;page=1</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3447,19 +3447,19 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2026-07-29 18:32:00.075123+09:00</t>
+          <t>2026-07-30 17:16:54.540202+09:00</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-07-29 18:32:00.075123+09:00</t>
+          <t>2026-07-30 17:16:54.540202+09:00</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>22464</t>
+          <t>22504</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3469,12 +3469,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026년 연계정보 이용기관 안전조치 실태점검 2차 설명회 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 19회차 교육생 모집(~8.28)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3727&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3728&amp;page=1</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3484,7 +3484,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3500,19 +3500,19 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:59.875668+09:00</t>
+          <t>2026-07-29 18:32:00.075123+09:00</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:59.875668+09:00</t>
+          <t>2026-07-29 18:32:00.075123+09:00</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>20771</t>
+          <t>22464</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3522,50 +3522,50 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 성평등가족부와 불법·유해 정보 유통 대응 맞손</t>
+          <t>2026년 연계정보 이용기관 안전조치 실태점검 2차 설명회 개최</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2620&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3727&amp;page=1</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>2026-07-27 17:17:05.702970+09:00</t>
+          <t>2026-07-29 18:01:59.875668+09:00</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-07-27 17:17:05.702970+09:00</t>
+          <t>2026-07-29 18:01:59.875668+09:00</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>20191</t>
+          <t>20771</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3575,12 +3575,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 향후 10년 설계한다…전담 추진단(TF) 출범</t>
+          <t>한국인터넷진흥원, 성평등가족부와 불법·유해 정보 유통 대응 맞손</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2619&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2620&amp;page=1</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>150</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3606,34 +3606,34 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>2026-07-27 10:02:05.338547+09:00</t>
+          <t>2026-07-27 17:17:05.702970+09:00</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-07-27 10:02:05.338547+09:00</t>
+          <t>2026-07-27 17:17:05.702970+09:00</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>20061</t>
+          <t>20191</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(1차, BreakingPoint)</t>
+          <t>아피가(APIGA) 향후 10년 설계한다…전담 추진단(TF) 출범</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3726&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2619&amp;page=1</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3643,7 +3643,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>287</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3651,64 +3651,64 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>2026-07-27 08:31:55.019743+09:00</t>
+          <t>2026-07-27 10:02:05.338547+09:00</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-07-27 08:31:55.019743+09:00</t>
+          <t>2026-07-27 10:02:05.338547+09:00</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>16785</t>
+          <t>20061</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 17회차 교육생 모집(~8.7)</t>
+          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(1차, BreakingPoint)</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3724&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3726&amp;page=1</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>246</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I61" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3716,34 +3716,34 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 08:31:55.019743+09:00</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 08:31:55.019743+09:00</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>16784</t>
+          <t>16785</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>1497</t>
+          <t>1496</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 18회차 교육생 모집(~8.21)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 17회차 교육생 모집(~8.7)</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3725&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3724&amp;page=1</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3753,7 +3753,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>236</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -3781,22 +3781,22 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>16781</t>
+          <t>16784</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1497</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 16회차 교육생 모집(~7.31)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 18회차 교육생 모집(~8.21)</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3723&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3725&amp;page=1</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>260</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -3814,11 +3814,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3838,22 +3834,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>16691</t>
+          <t>16781</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>'블록체인 기반 예금토큰 결제 인프라 확산' 사업 발대식 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 16회차 교육생 모집(~7.31)</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2618&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3723&amp;page=1</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3863,35 +3859,39 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>242</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>2026-07-22 17:32:01.526863+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-07-22 17:32:01.526863+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>16464</t>
+          <t>16691</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3901,12 +3901,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>[홍보] 정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 안내</t>
+          <t>'블록체인 기반 예금토큰 결제 인프라 확산' 사업 발대식 개최</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3722&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2618&amp;page=1</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3916,35 +3916,35 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>278</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>2026-07-22 14:46:48.687665+09:00</t>
+          <t>2026-07-22 17:32:01.526863+09:00</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-07-22 14:46:48.687665+09:00</t>
+          <t>2026-07-22 17:32:01.526863+09:00</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>16051</t>
+          <t>16464</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 보안 인재·글로벌 전문가 교류의 장 열어</t>
+          <t>[홍보] 정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 안내</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2617&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3722&amp;page=1</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3969,35 +3969,35 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>2026-07-22 09:31:50.671841+09:00</t>
+          <t>2026-07-22 14:46:48.687665+09:00</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-07-22 09:31:50.671841+09:00</t>
+          <t>2026-07-22 14:46:48.687665+09:00</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>14611</t>
+          <t>16051</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4007,22 +4007,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
+          <t>한국인터넷진흥원, 보안 인재·글로벌 전문가 교류의 장 열어</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2617&amp;page=1</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>233</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -4038,19 +4038,19 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>14431</t>
+          <t>14611</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4060,12 +4060,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>32</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>14431</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>53</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -4136,56 +4136,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>14444</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>1493</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
+          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -4193,7 +4189,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr"/>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I70" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -4201,34 +4201,34 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>11331</t>
+          <t>14444</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4238,7 +4238,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -4249,96 +4249,92 @@
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>10981</t>
+          <t>11331</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
+          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>10943</t>
+          <t>10981</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
+          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4348,7 +4344,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -4356,7 +4352,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr"/>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I73" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -4364,19 +4364,19 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>10663</t>
+          <t>10943</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4386,12 +4386,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
+          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
@@ -4417,19 +4417,19 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>9805</t>
+          <t>10663</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4439,22 +4439,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
+          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -4470,19 +4470,19 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>9691</t>
+          <t>9805</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -4492,12 +4492,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
+          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -4518,96 +4518,92 @@
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>9321</t>
+          <t>9691</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
+          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>8871</t>
+          <t>9321</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
+          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -4617,35 +4613,39 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>6685</t>
+          <t>8871</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4655,22 +4655,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
+          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -4681,24 +4681,24 @@
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>6571</t>
+          <t>6685</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -4708,12 +4708,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
+          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -4723,7 +4723,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -4734,24 +4734,24 @@
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>5591</t>
+          <t>6571</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
+          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -4792,44 +4792,44 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>5591</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
+          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>33</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -4845,44 +4845,44 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>4762</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>961</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>AI 보안 위협 대응 매뉴얼</t>
+          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -4890,31 +4890,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>4761</t>
+          <t>4762</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4924,12 +4920,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>AI 보안 레드티밍 가이드</t>
+          <t>AI 보안 위협 대응 매뉴얼</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -4939,7 +4935,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -4971,22 +4967,22 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>4251</t>
+          <t>4761</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
+          <t>AI 보안 레드티밍 가이드</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -4996,7 +4992,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -5004,27 +5000,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr"/>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>4251</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
+          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5049,113 +5049,113 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>191</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t>3867</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
+          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4111</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>959</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
+          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>34</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -5163,31 +5163,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5197,12 +5193,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
+          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5212,7 +5208,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -5244,32 +5240,32 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
+          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>105</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -5277,7 +5273,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr"/>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I90" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -5297,22 +5297,22 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1477</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
+          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5322,7 +5322,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>386</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -5350,22 +5350,22 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
+          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -5375,19 +5375,15 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>362</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -5407,7 +5403,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -5417,12 +5413,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2026년 IoT 보안인증 교육과정 안내</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -5432,7 +5428,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>522</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -5464,40 +5460,44 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
+          <t>2026년 IoT 보안인증 교육과정 안내</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>652</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I94" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -5517,22 +5517,22 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
+          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -5542,7 +5542,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>1529</t>
+          <t>818</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -5550,11 +5550,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -5574,32 +5570,32 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
+          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>1529</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -5607,7 +5603,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr"/>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I96" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -5615,34 +5615,34 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -5652,7 +5652,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>76426</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -5663,49 +5663,49 @@
       <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>958</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
+          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>55906</t>
+          <t>76426</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -5733,22 +5733,22 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>956</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
+          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>55329</t>
+          <t>55906</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -5786,32 +5786,32 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>957</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
+          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>34467</t>
+          <t>55329</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -5839,22 +5839,22 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>955</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
+          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -5864,39 +5864,35 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2945</t>
+          <t>34467</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -5906,27 +5902,27 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>2945</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -5953,32 +5949,32 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>145255</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -5986,52 +5982,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr"/>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>954</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>26576</t>
+          <t>145255</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -6059,32 +6059,32 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>953</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
+          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>34290</t>
+          <t>26576</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -6112,32 +6112,32 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
+          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>184573</t>
+          <t>34290</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -6165,32 +6165,32 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>14403</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>951</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>6587</t>
+          <t>184573</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -6198,46 +6198,42 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14403</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
+          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -6247,7 +6243,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>51749</t>
+          <t>6587</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -6255,52 +6251,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr"/>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>950</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>78439</t>
+          <t>51749</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -6328,55 +6328,108 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>949</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>78439</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>보도자료</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
           <t>38805</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr">
+      <c r="B111" t="inlineStr">
         <is>
           <t>공지</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr">
+      <c r="C111" t="inlineStr">
         <is>
           <t>[공유] 지능형 CCTV 성능시험 재개 안내 공지</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr">
+      <c r="D111" t="inlineStr">
         <is>
           <t>https://www.kisa.or.kr/401/form?postSeq=3677&amp;page=1</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr">
+      <c r="E111" t="inlineStr">
         <is>
           <t>2026-06-02</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr">
+      <c r="F111" t="inlineStr">
         <is>
           <t>6525</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr">
+      <c r="G111" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
+      <c r="H111" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>공지사항</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
         <is>
           <t>2026-08-18 17:16:37.364015+09:00</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr">
+      <c r="K111" t="inlineStr">
         <is>
           <t>2026-08-18 17:16:37.364015+09:00</t>
         </is>

--- a/docs/snapshot/downloads/kisa.xlsx
+++ b/docs/snapshot/downloads/kisa.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K111"/>
+  <dimension ref="A1:K112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,75 +476,75 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>64631</t>
+          <t>65748</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 인터넷 주소 자원 관리 역량 국제적 인정받아</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 26회차 교육생 모집(~10.16)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2639&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3767&amp;page=1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-09-20 12:01:47.233521+09:00</t>
+          <t>2026-09-21 17:01:40.203969+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-09-20 12:01:47.233521+09:00</t>
+          <t>2026-09-21 17:01:40.203969+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>63068</t>
+          <t>64631</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>990</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>대국민 혁신 정책·제안 공모전 개최</t>
+          <t>한국인터넷진흥원, 인터넷 주소 자원 관리 역량 국제적 인정받아</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3766&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2639&amp;page=1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -565,24 +565,24 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-09-18 10:46:37.266535+09:00</t>
+          <t>2026-09-20 12:01:47.233521+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-09-18 10:46:37.266535+09:00</t>
+          <t>2026-09-20 12:01:47.233521+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>63051</t>
+          <t>63068</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -592,12 +592,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>세계경제포럼·싱가포르 사이버보안청과 인공지능(AI) 위협 대비 사이버보안 협력 강화</t>
+          <t>대국민 혁신 정책·제안 공모전 개최</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2638&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3766&amp;page=1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -618,49 +618,49 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-09-18 10:31:43.770443+09:00</t>
+          <t>2026-09-18 10:46:37.266535+09:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-09-18 10:31:43.770443+09:00</t>
+          <t>2026-09-18 10:46:37.266535+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>62781</t>
+          <t>63051</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026년 블록체인 기업성장허브 입주기업 모집(~10월 7일(수) 16:00까지)</t>
+          <t>세계경제포럼·싱가포르 사이버보안청과 인공지능(AI) 위협 대비 사이버보안 협력 강화</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3765&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2638&amp;page=1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -668,46 +668,42 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-09-17 17:16:36.514530+09:00</t>
+          <t>2026-09-18 10:31:43.770443+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-09-17 17:16:36.514530+09:00</t>
+          <t>2026-09-18 10:31:43.770443+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>62507</t>
+          <t>62781</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 25회차 교육생 모집(~10.10)</t>
+          <t>2026년 블록체인 기업성장허브 입주기업 모집(~10월 7일(수) 16:00까지)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3764&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3765&amp;page=1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -717,15 +713,19 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -733,19 +733,19 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-09-17 13:31:33.789948+09:00</t>
+          <t>2026-09-17 17:16:36.514530+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-09-17 13:31:33.789948+09:00</t>
+          <t>2026-09-17 17:16:36.514530+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>62367</t>
+          <t>62507</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -755,12 +755,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 24회차 교육생 모집(~10.9)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 25회차 교육생 모집(~10.10)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3763&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3764&amp;page=1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -786,19 +786,19 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-09-17 11:46:35.719751+09:00</t>
+          <t>2026-09-17 13:31:33.789948+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-09-17 11:46:35.719751+09:00</t>
+          <t>2026-09-17 13:31:33.789948+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>61484</t>
+          <t>62367</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -808,27 +808,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026년 제13회 소프트웨어(SW) 개발보안 경진대회 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 24회차 교육생 모집(~10.9)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3762&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3763&amp;page=1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
@@ -839,19 +839,19 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-09-16 09:46:37.058042+09:00</t>
+          <t>2026-09-17 11:46:35.719751+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-09-16 09:46:37.058042+09:00</t>
+          <t>2026-09-17 11:46:35.719751+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>61111</t>
+          <t>61484</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -861,22 +861,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>민관 합동 ‘자동차 사이버 침해사고 대응 모의훈련’ 실시</t>
+          <t>2026년 제13회 소프트웨어(SW) 개발보안 경진대회 개최</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2637&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3762&amp;page=1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -887,24 +887,24 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-09-15 15:01:52.747371+09:00</t>
+          <t>2026-09-16 09:46:37.058042+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-09-15 15:01:52.747371+09:00</t>
+          <t>2026-09-16 09:46:37.058042+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>61031</t>
+          <t>61111</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>“새로운 보안 위협, 인공지능(AI)으로 대응” 정보보호 제품 개발 기업 대상 보안 역량 강화 교육 추진</t>
+          <t>민관 합동 ‘자동차 사이버 침해사고 대응 모의훈련’ 실시</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2636&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2637&amp;page=1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -945,44 +945,44 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-09-15 14:01:52.540884+09:00</t>
+          <t>2026-09-15 15:01:52.747371+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-09-15 14:01:52.540884+09:00</t>
+          <t>2026-09-15 15:01:52.747371+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>57381</t>
+          <t>61031</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026 전자문서 유공 포상 공고</t>
+          <t>“새로운 보안 위협, 인공지능(AI)으로 대응” 정보보호 제품 개발 기업 대상 보안 역량 강화 교육 추진</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3761&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2636&amp;page=1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -990,46 +990,42 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-09-10 14:16:31.877229+09:00</t>
+          <t>2026-09-15 14:01:52.540884+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-09-10 14:16:31.877229+09:00</t>
+          <t>2026-09-15 14:01:52.540884+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>57149</t>
+          <t>57381</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026년 클라우드 서비스 보안인증(CSAP) 교육 안내</t>
+          <t>2026 전자문서 유공 포상 공고</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3760&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3761&amp;page=1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1039,7 +1035,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1047,7 +1043,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1055,19 +1055,19 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-09-10 10:46:38.794916+09:00</t>
+          <t>2026-09-10 14:16:31.877229+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-09-10 10:46:38.794916+09:00</t>
+          <t>2026-09-10 14:16:31.877229+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>56431</t>
+          <t>57149</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1077,22 +1077,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>보호나라 챗봇, 국민 생활 속 정보보호 성과 인정</t>
+          <t>2026년 클라우드 서비스 보안인증(CSAP) 교육 안내</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2634&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3760&amp;page=1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1103,92 +1103,92 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-09-09 12:01:35.142670+09:00</t>
+          <t>2026-09-10 10:46:38.794916+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-09-09 12:01:35.142670+09:00</t>
+          <t>2026-09-10 10:46:38.794916+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>56969</t>
+          <t>56431</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1522</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>온마이데이터 서비스 이용 이벤트 안내</t>
+          <t>보호나라 챗봇, 국민 생활 속 정보보호 성과 인정</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3758&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2634&amp;page=1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>402</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-09-10 08:31:37.677434+09:00</t>
+          <t>2026-09-09 12:01:35.142670+09:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-09-10 08:31:37.677434+09:00</t>
+          <t>2026-09-09 12:01:35.142670+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>54791</t>
+          <t>56969</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1522</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>국내 캐시 도메인이름시스템(DNS) 운영기관, 신규 암호키 반영 여부 확인하세요</t>
+          <t>온마이데이터 서비스 이용 이벤트 안내</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2633&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3758&amp;page=1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1198,60 +1198,60 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>402</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-09-07 12:01:35.243341+09:00</t>
+          <t>2026-09-10 08:31:37.677434+09:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-09-07 12:01:35.243341+09:00</t>
+          <t>2026-09-10 08:31:37.677434+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>54541</t>
+          <t>54791</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(2차, Avalanche)</t>
+          <t>국내 캐시 도메인이름시스템(DNS) 운영기관, 신규 암호키 반영 여부 확인하세요</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3759&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2633&amp;page=1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1259,31 +1259,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-09-07 09:01:25.516098+09:00</t>
+          <t>2026-09-07 12:01:35.243341+09:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-09-07 09:01:25.516098+09:00</t>
+          <t>2026-09-07 12:01:35.243341+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>51281</t>
+          <t>54541</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1293,27 +1289,27 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>(행사 안내) 국외이전 제도 개선 및 CBPR 인증제도 기업 설명회 개최</t>
+          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(2차, Avalanche)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3757&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3759&amp;page=1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1328,52 +1324,56 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-09-03 09:16:26.856224+09:00</t>
+          <t>2026-09-07 09:01:25.516098+09:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-09-03 09:16:26.856224+09:00</t>
+          <t>2026-09-07 09:01:25.516098+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>56970</t>
+          <t>51281</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1521</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026 부산지역 도메인이름 분쟁해결 세미나 개최 안내(9.11)</t>
+          <t>(행사 안내) 국외이전 제도 개선 및 CBPR 인증제도 기업 설명회 개최</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3755&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3757&amp;page=1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>23</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1381,34 +1381,34 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-09-10 08:31:37.677434+09:00</t>
+          <t>2026-09-03 09:16:26.856224+09:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-09-10 08:31:37.677434+09:00</t>
+          <t>2026-09-03 09:16:26.856224+09:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>51121</t>
+          <t>56970</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1521</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026년 블록체인 수요공급협의체(ABLE) 블록체인 수요기업(비금융분야) 모집 공고</t>
+          <t>2026 부산지역 도메인이름 분쟁해결 세미나 개최 안내(9.11)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3754&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3755&amp;page=1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>242</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1426,11 +1426,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1438,19 +1434,19 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-09-02 17:31:25.610368+09:00</t>
+          <t>2026-09-10 08:31:37.677434+09:00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-09-02 17:31:25.610368+09:00</t>
+          <t>2026-09-10 08:31:37.677434+09:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>50601</t>
+          <t>51121</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1460,12 +1456,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026년 9차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(9월 추천) (~9.18(금) 18시까지)</t>
+          <t>2026년 블록체인 수요공급협의체(ABLE) 블록체인 수요기업(비금융분야) 모집 공고</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3753&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3754&amp;page=1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1475,7 +1471,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>24</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1495,44 +1491,44 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-09-02 11:01:32.173328+09:00</t>
+          <t>2026-09-02 17:31:25.610368+09:00</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-09-02 11:01:32.173328+09:00</t>
+          <t>2026-09-02 17:31:25.610368+09:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>49872</t>
+          <t>50601</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>인공지능(AI) 사이버 위협, 실전 모의훈련으로 대응</t>
+          <t>2026년 9차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(9월 추천) (~9.18(금) 18시까지)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2631&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3753&amp;page=1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1540,27 +1536,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-09-01 12:01:47.858504+09:00</t>
+          <t>2026-09-02 11:01:32.173328+09:00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-09-01 12:01:47.858504+09:00</t>
+          <t>2026-09-02 11:01:32.173328+09:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>49669</t>
+          <t>49872</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1570,12 +1570,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>「2026 위치정보 맞춤형 컨설팅 참여기업 모집」</t>
+          <t>인공지능(AI) 사이버 위협, 실전 모의훈련으로 대응</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3752&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2631&amp;page=1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1585,35 +1585,35 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-09-01 09:31:38.715793+09:00</t>
+          <t>2026-09-01 12:01:47.858504+09:00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-09-01 09:31:38.715793+09:00</t>
+          <t>2026-09-01 12:01:47.858504+09:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>49631</t>
+          <t>49669</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1623,12 +1623,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>물리보안 시스템 간 연동 장벽 낮춘다</t>
+          <t>「2026 위치정보 맞춤형 컨설팅 참여기업 모집」</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2632&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3752&amp;page=1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1638,103 +1638,103 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-09-01 09:01:45.980040+09:00</t>
+          <t>2026-09-01 09:31:38.715793+09:00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-09-01 09:01:45.980040+09:00</t>
+          <t>2026-09-01 09:31:38.715793+09:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>49589</t>
+          <t>49631</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1517</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 23회차 교육생 모집(~9.18)</t>
+          <t>물리보안 시스템 간 연동 장벽 낮춘다</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3751&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2632&amp;page=1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-09-01 08:31:37.253592+09:00</t>
+          <t>2026-09-01 09:01:45.980040+09:00</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-09-01 08:31:37.253592+09:00</t>
+          <t>2026-09-01 09:01:45.980040+09:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>48831</t>
+          <t>49589</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1517</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>생성형 인공지능(AI) 기반 실전형 모의해킹 대회 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 23회차 교육생 모집(~9.18)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2630&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3751&amp;page=1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1744,35 +1744,35 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>174</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-08-31 09:16:38.866405+09:00</t>
+          <t>2026-09-01 08:31:37.253592+09:00</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-08-31 09:16:38.866405+09:00</t>
+          <t>2026-09-01 08:31:37.253592+09:00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>46011</t>
+          <t>48831</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1782,22 +1782,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>자동차 노리는 사이버 위협, 한국인터넷진흥원-한국교통안전공단이 함께 대응한다</t>
+          <t>생성형 인공지능(AI) 기반 실전형 모의해킹 대회 개최</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2628&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2630&amp;page=1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1813,34 +1813,34 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-08-27 15:01:41.552844+09:00</t>
+          <t>2026-08-31 09:16:38.866405+09:00</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-08-27 15:01:41.552844+09:00</t>
+          <t>2026-08-31 09:16:38.866405+09:00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>45681</t>
+          <t>46011</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>싱가포르 현지 진출 지원 국내 블록체인 기업 모집(~9.16(수) 14시)</t>
+          <t>자동차 노리는 사이버 위협, 한국인터넷진흥원-한국교통안전공단이 함께 대응한다</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3750&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2628&amp;page=1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1858,56 +1858,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-08-27 11:01:31.314899+09:00</t>
+          <t>2026-08-27 15:01:41.552844+09:00</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-08-27 11:01:31.314899+09:00</t>
+          <t>2026-08-27 15:01:41.552844+09:00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>45191</t>
+          <t>45681</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 아·태 지역 사이버공격 대응 공동 훈련 실시</t>
+          <t>싱가포르 현지 진출 지원 국내 블록체인 기업 모집(~9.16(수) 14시)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2629&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3750&amp;page=1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1915,42 +1911,46 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-08-26 15:01:47.261933+09:00</t>
+          <t>2026-08-27 11:01:31.314899+09:00</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-08-26 15:01:47.261933+09:00</t>
+          <t>2026-08-27 11:01:31.314899+09:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>44741</t>
+          <t>45191</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>[3차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~9/16)</t>
+          <t>한국인터넷진흥원, 아·태 지역 사이버공격 대응 공동 훈련 실시</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3749&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2629&amp;page=1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1968,56 +1968,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-08-26 09:31:36.427758+09:00</t>
+          <t>2026-08-26 15:01:47.261933+09:00</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-08-26 09:31:36.427758+09:00</t>
+          <t>2026-08-26 15:01:47.261933+09:00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>44448</t>
+          <t>44741</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 공고</t>
+          <t>[3차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~9/16)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3748&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3749&amp;page=1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2025,7 +2021,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2033,19 +2033,19 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-08-25 16:01:39.626193+09:00</t>
+          <t>2026-08-26 09:31:36.427758+09:00</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-08-25 16:01:39.626193+09:00</t>
+          <t>2026-08-26 09:31:36.427758+09:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>43767</t>
+          <t>44448</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2055,27 +2055,27 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 21회차 교육생 모집(~9.12)</t>
+          <t>정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 공고</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3747&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3748&amp;page=1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
@@ -2086,19 +2086,19 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-08-24 17:46:42.254577+09:00</t>
+          <t>2026-08-25 16:01:39.626193+09:00</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-08-24 17:46:42.254577+09:00</t>
+          <t>2026-08-25 16:01:39.626193+09:00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>43311</t>
+          <t>43767</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2108,12 +2108,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>양자내성암호 전환, 어떻게 준비해야 할까?</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 21회차 교육생 모집(~9.12)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2627&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3747&amp;page=1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2123,50 +2123,50 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-08-24 12:01:45.511381+09:00</t>
+          <t>2026-08-24 17:46:42.254577+09:00</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-08-24 12:01:45.511381+09:00</t>
+          <t>2026-08-24 17:46:42.254577+09:00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>43301</t>
+          <t>43311</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>양자내성암호 전문교육 PQC 실무과정 교육생 모집(8.24~)</t>
+          <t>양자내성암호 전환, 어떻게 준비해야 할까?</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3746&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2627&amp;page=1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2184,31 +2184,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-08-24 12:01:36.271108+09:00</t>
+          <t>2026-08-24 12:01:45.511381+09:00</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-08-24 12:01:36.271108+09:00</t>
+          <t>2026-08-24 12:01:45.511381+09:00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>41161</t>
+          <t>43301</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2218,27 +2214,27 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>「블록체인 기업 맞춤형 보안 고도화 지원」 기업 모집(~8/31)</t>
+          <t>양자내성암호 전문교육 PQC 실무과정 교육생 모집(8.24~)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3745&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3746&amp;page=1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2253,34 +2249,34 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-08-21 16:01:38.087170+09:00</t>
+          <t>2026-08-24 12:01:36.271108+09:00</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-08-21 16:01:38.087170+09:00</t>
+          <t>2026-08-24 12:01:36.271108+09:00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>41086</t>
+          <t>41161</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026년도 인터넷거버넌스 민간전문가 APrIGF 및 IGF 참석자 모집</t>
+          <t>「블록체인 기업 맞춤형 보안 고도화 지원」 기업 모집(~8/31)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3744&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3745&amp;page=1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2290,15 +2286,19 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I35" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2306,19 +2306,19 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-08-21 15:01:32.139445+09:00</t>
+          <t>2026-08-21 16:01:38.087170+09:00</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-08-21 15:01:32.139445+09:00</t>
+          <t>2026-08-21 16:01:38.087170+09:00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>34750</t>
+          <t>41086</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2328,22 +2328,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>｢2026 블록체인 진흥주간｣ 전시부스 참가기업 모집 공고(~9.14)</t>
+          <t>2026년도 인터넷거버넌스 민간전문가 APrIGF 및 IGF 참석자 모집</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3743&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3744&amp;page=1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>59</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2359,34 +2359,34 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-08-13 17:46:21.938331+09:00</t>
+          <t>2026-08-21 15:01:32.139445+09:00</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-08-13 17:46:21.938331+09:00</t>
+          <t>2026-08-21 15:01:32.139445+09:00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>34081</t>
+          <t>34750</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026년 하반기 정보보호 전문서비스 기업 지정에 관한 공고</t>
+          <t>｢2026 블록체인 진흥주간｣ 전시부스 참가기업 모집 공고(~9.14)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3742&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3743&amp;page=1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2404,11 +2404,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2416,44 +2412,44 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:24.927741+09:00</t>
+          <t>2026-08-13 17:46:21.938331+09:00</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:24.927741+09:00</t>
+          <t>2026-08-13 17:46:21.938331+09:00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>34071</t>
+          <t>34081</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>"예방 넘어 대응·복구까지" 랜섬웨어 전주기 대응 방안 논의한다</t>
+          <t>2026년 하반기 정보보호 전문서비스 기업 지정에 관한 공고</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2626&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3742&amp;page=1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2461,42 +2457,46 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-08-13 09:16:35.989405+09:00</t>
+          <t>2026-08-13 09:31:24.927741+09:00</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-08-13 09:16:35.989405+09:00</t>
+          <t>2026-08-13 09:31:24.927741+09:00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>33789</t>
+          <t>34071</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>978</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 21회차 교육생 모집(~9.11)</t>
+          <t>"예방 넘어 대응·복구까지" 랜섬웨어 전주기 대응 방안 논의한다</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3741&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2626&amp;page=1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2506,35 +2506,35 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-08-12 16:01:25.579701+09:00</t>
+          <t>2026-08-13 09:16:35.989405+09:00</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-08-12 16:01:25.579701+09:00</t>
+          <t>2026-08-13 09:16:35.989405+09:00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>33749</t>
+          <t>33789</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2544,12 +2544,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026년도 블록체인 유공 포상 계획 공고 안내(~9.21 15:00 마감)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 21회차 교육생 모집(~9.11)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3740&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3741&amp;page=1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
@@ -2575,44 +2575,44 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-08-12 15:31:25.306307+09:00</t>
+          <t>2026-08-12 16:01:25.579701+09:00</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-08-12 15:31:25.306307+09:00</t>
+          <t>2026-08-12 16:01:25.579701+09:00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>31741</t>
+          <t>33749</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026년 블록체인 수요-공급 협의체 (ABLE) 정례세미나 개최 안내(8.13.목)</t>
+          <t>2026년도 블록체인 유공 포상 계획 공고 안내(~9.21 15:00 마감)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3739&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3740&amp;page=1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2620,11 +2620,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2632,52 +2628,56 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-08-10 11:01:30.246604+09:00</t>
+          <t>2026-08-12 15:31:25.306307+09:00</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-08-10 11:01:30.246604+09:00</t>
+          <t>2026-08-12 15:31:25.306307+09:00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>29768</t>
+          <t>31741</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026년 블록체인 신뢰인프라(K-BTF) 활용·확산사업 공모 사전예고</t>
+          <t>2026년 블록체인 수요-공급 협의체 (ABLE) 정례세미나 개최 안내(8.13.목)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3738&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3739&amp;page=1</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I42" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2685,19 +2685,19 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-08-07 17:01:29.954014+09:00</t>
+          <t>2026-08-10 11:01:30.246604+09:00</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-08-07 17:01:29.954014+09:00</t>
+          <t>2026-08-10 11:01:30.246604+09:00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>29728</t>
+          <t>29768</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026년도 블록체인 산업 실태조사 실시 및 협조 안내</t>
+          <t>2026년 블록체인 신뢰인프라(K-BTF) 활용·확산사업 공모 사전예고</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3737&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3738&amp;page=1</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2738,19 +2738,19 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-08-07 16:31:30.938844+09:00</t>
+          <t>2026-08-07 17:01:29.954014+09:00</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-08-07 16:31:30.938844+09:00</t>
+          <t>2026-08-07 17:01:29.954014+09:00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>28711</t>
+          <t>29728</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2760,50 +2760,50 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원-나주시, 고교생 개인정보·정보보호 진로 탐색 지원</t>
+          <t>2026년도 블록체인 산업 실태조사 실시 및 협조 안내</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2625&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3737&amp;page=1</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-08-06 14:01:34.968573+09:00</t>
+          <t>2026-08-07 16:31:30.938844+09:00</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-08-06 14:01:34.968573+09:00</t>
+          <t>2026-08-07 16:31:30.938844+09:00</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>27551</t>
+          <t>28711</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2813,22 +2813,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 기업 맞춤형 사이버 위협 알림 서비스 개시</t>
+          <t>한국인터넷진흥원-나주시, 고교생 개인정보·정보보호 진로 탐색 지원</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2624&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2625&amp;page=1</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2844,44 +2844,44 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2026-08-05 09:46:34.063806+09:00</t>
+          <t>2026-08-06 14:01:34.968573+09:00</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-08-05 09:46:34.063806+09:00</t>
+          <t>2026-08-06 14:01:34.968573+09:00</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>27511</t>
+          <t>27551</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 기관장 주도 국민 체감 성과 혁신 체계 가동</t>
+          <t>한국인터넷진흥원, 기업 맞춤형 사이버 위협 알림 서비스 개시</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2623&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2624&amp;page=1</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2897,34 +2897,34 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2026-08-05 09:16:33.823896+09:00</t>
+          <t>2026-08-05 09:46:34.063806+09:00</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-08-05 09:16:33.823896+09:00</t>
+          <t>2026-08-05 09:46:34.063806+09:00</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>27268</t>
+          <t>27511</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>975</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>양자내성암호 국제 표준화 동향 분석</t>
+          <t>한국인터넷진흥원, 기관장 주도 국민 체감 성과 혁신 체계 가동</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3736&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2623&amp;page=1</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>263</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2945,24 +2945,24 @@
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2026-08-04 16:31:26.502205+09:00</t>
+          <t>2026-08-05 09:16:33.823896+09:00</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-08-04 16:31:26.502205+09:00</t>
+          <t>2026-08-05 09:16:33.823896+09:00</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>27128</t>
+          <t>27268</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 20회차 교육생 모집(~9.4)</t>
+          <t>양자내성암호 국제 표준화 동향 분석</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3735&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3736&amp;page=1</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
@@ -3003,19 +3003,19 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-08-04 14:46:28.764255+09:00</t>
+          <t>2026-08-04 16:31:26.502205+09:00</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-08-04 14:46:28.764255+09:00</t>
+          <t>2026-08-04 16:31:26.502205+09:00</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>26211</t>
+          <t>27128</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3025,50 +3025,50 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 암호모듈검증 위한 시험 전문인력 양성</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 20회차 교육생 모집(~9.4)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2622&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3735&amp;page=1</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-08-03 13:31:41.722921+09:00</t>
+          <t>2026-08-04 14:46:28.764255+09:00</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-08-03 13:31:41.722921+09:00</t>
+          <t>2026-08-04 14:46:28.764255+09:00</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>26188</t>
+          <t>26211</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026년 8차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(8월 추천) (~8.21(금) 18시까지)</t>
+          <t>한국인터넷진흥원, 암호모듈검증 위한 시험 전문인력 양성</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3734&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2622&amp;page=1</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>273</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3104,24 +3104,24 @@
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2026-08-03 13:16:30.325331+09:00</t>
+          <t>2026-08-03 13:31:41.722921+09:00</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-08-03 13:16:30.325331+09:00</t>
+          <t>2026-08-03 13:31:41.722921+09:00</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>25891</t>
+          <t>26188</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 지역 상생 3대 사업 참여자 모집</t>
+          <t>2026년 8차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(8월 추천) (~8.21(금) 18시까지)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2621&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3734&amp;page=1</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3157,39 +3157,39 @@
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2026-08-03 09:31:46.854132+09:00</t>
+          <t>2026-08-03 13:16:30.325331+09:00</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-08-03 09:31:46.854132+09:00</t>
+          <t>2026-08-03 13:16:30.325331+09:00</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>25864</t>
+          <t>25891</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026년 전남광주통합특별시 소상공인·사회적경제기업 판로 확대 지원기업 선발 안내(~8.14)</t>
+          <t>한국인터넷진흥원, 지역 상생 3대 사업 참여자 모집</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3730&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2621&amp;page=1</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3199,7 +3199,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>80</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3207,31 +3207,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2026-08-03 09:16:35.817723+09:00</t>
+          <t>2026-08-03 09:31:46.854132+09:00</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-08-03 09:16:35.817723+09:00</t>
+          <t>2026-08-03 09:31:46.854132+09:00</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>25863</t>
+          <t>25864</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3241,12 +3237,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026년 전남광주통합특별시 지역문제 해결 프로젝트 공모전 개최 안내(~8.21)</t>
+          <t>2026년 전남광주통합특별시 소상공인·사회적경제기업 판로 확대 지원기업 선발 안내(~8.14)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3731&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3730&amp;page=1</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3256,7 +3252,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3288,7 +3284,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>25862</t>
+          <t>25863</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3298,12 +3294,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026년 한국인터넷진흥원 지역공부방 참여 대학생 장학금 지원자 모집 안내(~8.28)</t>
+          <t>2026년 전남광주통합특별시 지역문제 해결 프로젝트 공모전 개최 안내(~8.21)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3732&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3731&amp;page=1</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3313,7 +3309,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3345,7 +3341,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>25861</t>
+          <t>25862</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3355,12 +3351,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026년 암호모듈 시험자 양성교육 및 필기시험 안내(8.3~8.21)</t>
+          <t>2026년 한국인터넷진흥원 지역공부방 참여 대학생 장학금 지원자 모집 안내(~8.28)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3733&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3732&amp;page=1</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3370,7 +3366,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3402,7 +3398,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>23221</t>
+          <t>25861</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3412,22 +3408,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026년 블록체인 기업성장허브 입주기업 모집(~8월 27일(목) 16:00까지)</t>
+          <t>2026년 암호모듈 시험자 양성교육 및 필기시험 안내(8.3~8.21)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3729&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3733&amp;page=1</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3447,52 +3443,56 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2026-07-30 17:16:54.540202+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-07-30 17:16:54.540202+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>22504</t>
+          <t>23221</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 19회차 교육생 모집(~8.28)</t>
+          <t>2026년 블록체인 기업성장허브 입주기업 모집(~8월 27일(목) 16:00까지)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3728&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3729&amp;page=1</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3500,19 +3500,19 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2026-07-29 18:32:00.075123+09:00</t>
+          <t>2026-07-30 17:16:54.540202+09:00</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-07-29 18:32:00.075123+09:00</t>
+          <t>2026-07-30 17:16:54.540202+09:00</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>22464</t>
+          <t>22504</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3522,12 +3522,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026년 연계정보 이용기관 안전조치 실태점검 2차 설명회 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 19회차 교육생 모집(~8.28)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3727&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3728&amp;page=1</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3553,19 +3553,19 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:59.875668+09:00</t>
+          <t>2026-07-29 18:32:00.075123+09:00</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:59.875668+09:00</t>
+          <t>2026-07-29 18:32:00.075123+09:00</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>20771</t>
+          <t>22464</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3575,50 +3575,50 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 성평등가족부와 불법·유해 정보 유통 대응 맞손</t>
+          <t>2026년 연계정보 이용기관 안전조치 실태점검 2차 설명회 개최</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2620&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3727&amp;page=1</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>2026-07-27 17:17:05.702970+09:00</t>
+          <t>2026-07-29 18:01:59.875668+09:00</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-07-27 17:17:05.702970+09:00</t>
+          <t>2026-07-29 18:01:59.875668+09:00</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>20191</t>
+          <t>20771</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3628,12 +3628,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 향후 10년 설계한다…전담 추진단(TF) 출범</t>
+          <t>한국인터넷진흥원, 성평등가족부와 불법·유해 정보 유통 대응 맞손</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2619&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2620&amp;page=1</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3643,7 +3643,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>150</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3659,34 +3659,34 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>2026-07-27 10:02:05.338547+09:00</t>
+          <t>2026-07-27 17:17:05.702970+09:00</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-07-27 10:02:05.338547+09:00</t>
+          <t>2026-07-27 17:17:05.702970+09:00</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>20061</t>
+          <t>20191</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(1차, BreakingPoint)</t>
+          <t>아피가(APIGA) 향후 10년 설계한다…전담 추진단(TF) 출범</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3726&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2619&amp;page=1</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>287</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3704,64 +3704,64 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>2026-07-27 08:31:55.019743+09:00</t>
+          <t>2026-07-27 10:02:05.338547+09:00</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-07-27 08:31:55.019743+09:00</t>
+          <t>2026-07-27 10:02:05.338547+09:00</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>16785</t>
+          <t>20061</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 17회차 교육생 모집(~8.7)</t>
+          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(1차, BreakingPoint)</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3724&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3726&amp;page=1</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>246</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I62" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3769,34 +3769,34 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 08:31:55.019743+09:00</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 08:31:55.019743+09:00</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>16784</t>
+          <t>16785</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>1497</t>
+          <t>1496</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 18회차 교육생 모집(~8.21)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 17회차 교육생 모집(~8.7)</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3725&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3724&amp;page=1</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>236</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -3834,22 +3834,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>16781</t>
+          <t>16784</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1497</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 16회차 교육생 모집(~7.31)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 18회차 교육생 모집(~8.21)</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3723&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3725&amp;page=1</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>260</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -3867,11 +3867,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3891,22 +3887,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>16691</t>
+          <t>16781</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>'블록체인 기반 예금토큰 결제 인프라 확산' 사업 발대식 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 16회차 교육생 모집(~7.31)</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2618&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3723&amp;page=1</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3916,35 +3912,39 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>242</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>2026-07-22 17:32:01.526863+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-07-22 17:32:01.526863+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>16464</t>
+          <t>16691</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>[홍보] 정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 안내</t>
+          <t>'블록체인 기반 예금토큰 결제 인프라 확산' 사업 발대식 개최</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3722&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2618&amp;page=1</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3969,35 +3969,35 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>278</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>2026-07-22 14:46:48.687665+09:00</t>
+          <t>2026-07-22 17:32:01.526863+09:00</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-07-22 14:46:48.687665+09:00</t>
+          <t>2026-07-22 17:32:01.526863+09:00</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>16051</t>
+          <t>16464</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 보안 인재·글로벌 전문가 교류의 장 열어</t>
+          <t>[홍보] 정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 안내</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2617&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3722&amp;page=1</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4022,35 +4022,35 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>2026-07-22 09:31:50.671841+09:00</t>
+          <t>2026-07-22 14:46:48.687665+09:00</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-07-22 09:31:50.671841+09:00</t>
+          <t>2026-07-22 14:46:48.687665+09:00</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>14611</t>
+          <t>16051</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4060,22 +4060,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
+          <t>한국인터넷진흥원, 보안 인재·글로벌 전문가 교류의 장 열어</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2617&amp;page=1</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>233</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -4091,19 +4091,19 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>14431</t>
+          <t>14611</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4113,12 +4113,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>32</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -4144,34 +4144,34 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>14431</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>53</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -4189,56 +4189,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>14444</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>1493</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
+          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -4246,7 +4242,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr"/>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I71" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -4254,34 +4254,34 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>11331</t>
+          <t>14444</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4291,7 +4291,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -4302,96 +4302,92 @@
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>10981</t>
+          <t>11331</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
+          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>10943</t>
+          <t>10981</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
+          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4401,7 +4397,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -4409,7 +4405,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr"/>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I74" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -4417,19 +4417,19 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>10663</t>
+          <t>10943</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4439,12 +4439,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
+          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4454,12 +4454,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
@@ -4470,19 +4470,19 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>9805</t>
+          <t>10663</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -4492,22 +4492,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
+          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -4523,19 +4523,19 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>9691</t>
+          <t>9805</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
+          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -4571,96 +4571,92 @@
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>9321</t>
+          <t>9691</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
+          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>8871</t>
+          <t>9321</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
+          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -4670,35 +4666,39 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>6685</t>
+          <t>8871</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -4708,22 +4708,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
+          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -4734,24 +4734,24 @@
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>6571</t>
+          <t>6685</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
+          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -4776,7 +4776,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -4787,24 +4787,24 @@
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>5591</t>
+          <t>6571</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -4814,22 +4814,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
+          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -4845,44 +4845,44 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>5591</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
+          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>33</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -4898,44 +4898,44 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>4762</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>961</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>AI 보안 위협 대응 매뉴얼</t>
+          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -4943,31 +4943,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>4761</t>
+          <t>4762</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4977,12 +4973,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>AI 보안 레드티밍 가이드</t>
+          <t>AI 보안 위협 대응 매뉴얼</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -4992,7 +4988,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -5024,22 +5020,22 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>4251</t>
+          <t>4761</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
+          <t>AI 보안 레드티밍 가이드</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5049,7 +5045,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -5057,27 +5053,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr"/>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>4251</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
+          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5102,113 +5102,113 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>191</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t>3867</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
+          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4111</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>959</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
+          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>34</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -5216,31 +5216,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5250,12 +5246,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
+          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5265,7 +5261,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -5297,32 +5293,32 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
+          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>105</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -5330,7 +5326,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr"/>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I91" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -5350,22 +5350,22 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1477</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
+          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -5375,7 +5375,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>386</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -5403,22 +5403,22 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
+          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -5428,19 +5428,15 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>362</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -5460,7 +5456,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -5470,12 +5466,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2026년 IoT 보안인증 교육과정 안내</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -5485,7 +5481,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>522</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -5517,40 +5513,44 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
+          <t>2026년 IoT 보안인증 교육과정 안내</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>652</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I95" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -5570,22 +5570,22 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
+          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -5595,7 +5595,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>1529</t>
+          <t>818</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -5603,11 +5603,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -5627,32 +5623,32 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
+          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>1529</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -5660,7 +5656,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr"/>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I97" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -5668,34 +5668,34 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -5705,7 +5705,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>76426</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -5716,49 +5716,49 @@
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>958</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
+          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>55906</t>
+          <t>76426</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -5786,22 +5786,22 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>956</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
+          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>55329</t>
+          <t>55906</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -5839,32 +5839,32 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>957</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
+          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>34467</t>
+          <t>55329</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -5892,22 +5892,22 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>955</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
+          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -5917,39 +5917,35 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2945</t>
+          <t>34467</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -5959,27 +5955,27 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>2945</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6006,32 +6002,32 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>145255</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -6039,52 +6035,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr"/>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>954</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>26576</t>
+          <t>145255</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -6112,32 +6112,32 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>953</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
+          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>34290</t>
+          <t>26576</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -6165,32 +6165,32 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
+          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>184573</t>
+          <t>34290</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -6218,32 +6218,32 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>14403</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>951</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>6587</t>
+          <t>184573</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -6251,46 +6251,42 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14403</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
+          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -6300,7 +6296,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>51749</t>
+          <t>6587</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -6308,52 +6304,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr"/>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>950</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>78439</t>
+          <t>51749</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -6381,55 +6381,108 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>949</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>78439</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>보도자료</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
           <t>38805</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr">
+      <c r="B112" t="inlineStr">
         <is>
           <t>공지</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr">
+      <c r="C112" t="inlineStr">
         <is>
           <t>[공유] 지능형 CCTV 성능시험 재개 안내 공지</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr">
+      <c r="D112" t="inlineStr">
         <is>
           <t>https://www.kisa.or.kr/401/form?postSeq=3677&amp;page=1</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr">
+      <c r="E112" t="inlineStr">
         <is>
           <t>2026-06-02</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr">
+      <c r="F112" t="inlineStr">
         <is>
           <t>6525</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr">
+      <c r="G112" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
+      <c r="H112" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>공지사항</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
         <is>
           <t>2026-08-18 17:16:37.364015+09:00</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr">
+      <c r="K112" t="inlineStr">
         <is>
           <t>2026-08-18 17:16:37.364015+09:00</t>
         </is>

--- a/docs/snapshot/downloads/kisa.xlsx
+++ b/docs/snapshot/downloads/kisa.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K112"/>
+  <dimension ref="A1:K113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>65748</t>
+          <t>65988</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -486,27 +486,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 26회차 교육생 모집(~10.16)</t>
+          <t>2026년도 K-Cybersecurity Business Day in Japan 세미나(10/20) 참석 수요조사 안내</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3767&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3768&amp;page=1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -517,87 +517,87 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:01:40.203969+09:00</t>
+          <t>2026-09-22 10:01:34.273734+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:01:40.203969+09:00</t>
+          <t>2026-09-22 10:01:34.273734+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>64631</t>
+          <t>65748</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 인터넷 주소 자원 관리 역량 국제적 인정받아</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 26회차 교육생 모집(~10.16)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2639&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3767&amp;page=1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-09-20 12:01:47.233521+09:00</t>
+          <t>2026-09-21 17:01:40.203969+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-09-20 12:01:47.233521+09:00</t>
+          <t>2026-09-21 17:01:40.203969+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>63068</t>
+          <t>64631</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>990</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>대국민 혁신 정책·제안 공모전 개최</t>
+          <t>한국인터넷진흥원, 인터넷 주소 자원 관리 역량 국제적 인정받아</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3766&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2639&amp;page=1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -618,24 +618,24 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-09-18 10:46:37.266535+09:00</t>
+          <t>2026-09-20 12:01:47.233521+09:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-09-18 10:46:37.266535+09:00</t>
+          <t>2026-09-20 12:01:47.233521+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>63051</t>
+          <t>63068</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -645,12 +645,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>세계경제포럼·싱가포르 사이버보안청과 인공지능(AI) 위협 대비 사이버보안 협력 강화</t>
+          <t>대국민 혁신 정책·제안 공모전 개최</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2638&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3766&amp;page=1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -671,49 +671,49 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-09-18 10:31:43.770443+09:00</t>
+          <t>2026-09-18 10:46:37.266535+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-09-18 10:31:43.770443+09:00</t>
+          <t>2026-09-18 10:46:37.266535+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>62781</t>
+          <t>63051</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026년 블록체인 기업성장허브 입주기업 모집(~10월 7일(수) 16:00까지)</t>
+          <t>세계경제포럼·싱가포르 사이버보안청과 인공지능(AI) 위협 대비 사이버보안 협력 강화</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3765&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2638&amp;page=1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -721,46 +721,42 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-09-17 17:16:36.514530+09:00</t>
+          <t>2026-09-18 10:31:43.770443+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-09-17 17:16:36.514530+09:00</t>
+          <t>2026-09-18 10:31:43.770443+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>62507</t>
+          <t>62781</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 25회차 교육생 모집(~10.10)</t>
+          <t>2026년 블록체인 기업성장허브 입주기업 모집(~10월 7일(수) 16:00까지)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3764&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3765&amp;page=1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -770,15 +766,19 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -786,19 +786,19 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-09-17 13:31:33.789948+09:00</t>
+          <t>2026-09-17 17:16:36.514530+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-09-17 13:31:33.789948+09:00</t>
+          <t>2026-09-17 17:16:36.514530+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>62367</t>
+          <t>62507</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -808,12 +808,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 24회차 교육생 모집(~10.9)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 25회차 교육생 모집(~10.10)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3763&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3764&amp;page=1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -839,19 +839,19 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-09-17 11:46:35.719751+09:00</t>
+          <t>2026-09-17 13:31:33.789948+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-09-17 11:46:35.719751+09:00</t>
+          <t>2026-09-17 13:31:33.789948+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>61484</t>
+          <t>62367</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -861,27 +861,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026년 제13회 소프트웨어(SW) 개발보안 경진대회 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 24회차 교육생 모집(~10.9)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3762&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3763&amp;page=1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
@@ -892,19 +892,19 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-09-16 09:46:37.058042+09:00</t>
+          <t>2026-09-17 11:46:35.719751+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-09-16 09:46:37.058042+09:00</t>
+          <t>2026-09-17 11:46:35.719751+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>61111</t>
+          <t>61484</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -914,22 +914,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>민관 합동 ‘자동차 사이버 침해사고 대응 모의훈련’ 실시</t>
+          <t>2026년 제13회 소프트웨어(SW) 개발보안 경진대회 개최</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2637&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3762&amp;page=1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -940,24 +940,24 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-09-15 15:01:52.747371+09:00</t>
+          <t>2026-09-16 09:46:37.058042+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-09-15 15:01:52.747371+09:00</t>
+          <t>2026-09-16 09:46:37.058042+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>61031</t>
+          <t>61111</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -967,12 +967,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>“새로운 보안 위협, 인공지능(AI)으로 대응” 정보보호 제품 개발 기업 대상 보안 역량 강화 교육 추진</t>
+          <t>민관 합동 ‘자동차 사이버 침해사고 대응 모의훈련’ 실시</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2636&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2637&amp;page=1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -998,44 +998,44 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-09-15 14:01:52.540884+09:00</t>
+          <t>2026-09-15 15:01:52.747371+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-09-15 14:01:52.540884+09:00</t>
+          <t>2026-09-15 15:01:52.747371+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>57381</t>
+          <t>61031</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026 전자문서 유공 포상 공고</t>
+          <t>“새로운 보안 위협, 인공지능(AI)으로 대응” 정보보호 제품 개발 기업 대상 보안 역량 강화 교육 추진</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3761&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2636&amp;page=1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1043,46 +1043,42 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-09-10 14:16:31.877229+09:00</t>
+          <t>2026-09-15 14:01:52.540884+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-09-10 14:16:31.877229+09:00</t>
+          <t>2026-09-15 14:01:52.540884+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>57149</t>
+          <t>57381</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026년 클라우드 서비스 보안인증(CSAP) 교육 안내</t>
+          <t>2026 전자문서 유공 포상 공고</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3760&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3761&amp;page=1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1092,7 +1088,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1100,7 +1096,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1108,19 +1108,19 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-09-10 10:46:38.794916+09:00</t>
+          <t>2026-09-10 14:16:31.877229+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-09-10 10:46:38.794916+09:00</t>
+          <t>2026-09-10 14:16:31.877229+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>56431</t>
+          <t>57149</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1130,22 +1130,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>보호나라 챗봇, 국민 생활 속 정보보호 성과 인정</t>
+          <t>2026년 클라우드 서비스 보안인증(CSAP) 교육 안내</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2634&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3760&amp;page=1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1156,92 +1156,92 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-09-09 12:01:35.142670+09:00</t>
+          <t>2026-09-10 10:46:38.794916+09:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-09-09 12:01:35.142670+09:00</t>
+          <t>2026-09-10 10:46:38.794916+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>56969</t>
+          <t>56431</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1522</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>온마이데이터 서비스 이용 이벤트 안내</t>
+          <t>보호나라 챗봇, 국민 생활 속 정보보호 성과 인정</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3758&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2634&amp;page=1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>402</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-09-10 08:31:37.677434+09:00</t>
+          <t>2026-09-09 12:01:35.142670+09:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-09-10 08:31:37.677434+09:00</t>
+          <t>2026-09-09 12:01:35.142670+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>54791</t>
+          <t>56969</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1522</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>국내 캐시 도메인이름시스템(DNS) 운영기관, 신규 암호키 반영 여부 확인하세요</t>
+          <t>온마이데이터 서비스 이용 이벤트 안내</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2633&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3758&amp;page=1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1251,60 +1251,60 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>402</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-09-07 12:01:35.243341+09:00</t>
+          <t>2026-09-10 08:31:37.677434+09:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-09-07 12:01:35.243341+09:00</t>
+          <t>2026-09-10 08:31:37.677434+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>54541</t>
+          <t>54791</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(2차, Avalanche)</t>
+          <t>국내 캐시 도메인이름시스템(DNS) 운영기관, 신규 암호키 반영 여부 확인하세요</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3759&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2633&amp;page=1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1312,31 +1312,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-09-07 09:01:25.516098+09:00</t>
+          <t>2026-09-07 12:01:35.243341+09:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-09-07 09:01:25.516098+09:00</t>
+          <t>2026-09-07 12:01:35.243341+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>51281</t>
+          <t>54541</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1346,27 +1342,27 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>(행사 안내) 국외이전 제도 개선 및 CBPR 인증제도 기업 설명회 개최</t>
+          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(2차, Avalanche)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3757&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3759&amp;page=1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1381,52 +1377,56 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-09-03 09:16:26.856224+09:00</t>
+          <t>2026-09-07 09:01:25.516098+09:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-09-03 09:16:26.856224+09:00</t>
+          <t>2026-09-07 09:01:25.516098+09:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>56970</t>
+          <t>51281</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1521</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026 부산지역 도메인이름 분쟁해결 세미나 개최 안내(9.11)</t>
+          <t>(행사 안내) 국외이전 제도 개선 및 CBPR 인증제도 기업 설명회 개최</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3755&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3757&amp;page=1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>23</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1434,34 +1434,34 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-09-10 08:31:37.677434+09:00</t>
+          <t>2026-09-03 09:16:26.856224+09:00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-09-10 08:31:37.677434+09:00</t>
+          <t>2026-09-03 09:16:26.856224+09:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>51121</t>
+          <t>56970</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1521</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026년 블록체인 수요공급협의체(ABLE) 블록체인 수요기업(비금융분야) 모집 공고</t>
+          <t>2026 부산지역 도메인이름 분쟁해결 세미나 개최 안내(9.11)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3754&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3755&amp;page=1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>242</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1479,11 +1479,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1491,19 +1487,19 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-09-02 17:31:25.610368+09:00</t>
+          <t>2026-09-10 08:31:37.677434+09:00</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-09-02 17:31:25.610368+09:00</t>
+          <t>2026-09-10 08:31:37.677434+09:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>50601</t>
+          <t>51121</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1513,12 +1509,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026년 9차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(9월 추천) (~9.18(금) 18시까지)</t>
+          <t>2026년 블록체인 수요공급협의체(ABLE) 블록체인 수요기업(비금융분야) 모집 공고</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3753&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3754&amp;page=1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1528,7 +1524,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>24</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1548,44 +1544,44 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-09-02 11:01:32.173328+09:00</t>
+          <t>2026-09-02 17:31:25.610368+09:00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-09-02 11:01:32.173328+09:00</t>
+          <t>2026-09-02 17:31:25.610368+09:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>49872</t>
+          <t>50601</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>인공지능(AI) 사이버 위협, 실전 모의훈련으로 대응</t>
+          <t>2026년 9차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(9월 추천) (~9.18(금) 18시까지)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2631&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3753&amp;page=1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1593,27 +1589,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-09-01 12:01:47.858504+09:00</t>
+          <t>2026-09-02 11:01:32.173328+09:00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-09-01 12:01:47.858504+09:00</t>
+          <t>2026-09-02 11:01:32.173328+09:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>49669</t>
+          <t>49872</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1623,12 +1623,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>「2026 위치정보 맞춤형 컨설팅 참여기업 모집」</t>
+          <t>인공지능(AI) 사이버 위협, 실전 모의훈련으로 대응</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3752&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2631&amp;page=1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1638,35 +1638,35 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-09-01 09:31:38.715793+09:00</t>
+          <t>2026-09-01 12:01:47.858504+09:00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-09-01 09:31:38.715793+09:00</t>
+          <t>2026-09-01 12:01:47.858504+09:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>49631</t>
+          <t>49669</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>물리보안 시스템 간 연동 장벽 낮춘다</t>
+          <t>「2026 위치정보 맞춤형 컨설팅 참여기업 모집」</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2632&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3752&amp;page=1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1691,103 +1691,103 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-09-01 09:01:45.980040+09:00</t>
+          <t>2026-09-01 09:31:38.715793+09:00</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-09-01 09:01:45.980040+09:00</t>
+          <t>2026-09-01 09:31:38.715793+09:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>49589</t>
+          <t>49631</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1517</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 23회차 교육생 모집(~9.18)</t>
+          <t>물리보안 시스템 간 연동 장벽 낮춘다</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3751&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2632&amp;page=1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-09-01 08:31:37.253592+09:00</t>
+          <t>2026-09-01 09:01:45.980040+09:00</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-09-01 08:31:37.253592+09:00</t>
+          <t>2026-09-01 09:01:45.980040+09:00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>48831</t>
+          <t>49589</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1517</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>생성형 인공지능(AI) 기반 실전형 모의해킹 대회 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 23회차 교육생 모집(~9.18)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2630&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3751&amp;page=1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1797,35 +1797,35 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>174</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-08-31 09:16:38.866405+09:00</t>
+          <t>2026-09-01 08:31:37.253592+09:00</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-08-31 09:16:38.866405+09:00</t>
+          <t>2026-09-01 08:31:37.253592+09:00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>46011</t>
+          <t>48831</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1835,22 +1835,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>자동차 노리는 사이버 위협, 한국인터넷진흥원-한국교통안전공단이 함께 대응한다</t>
+          <t>생성형 인공지능(AI) 기반 실전형 모의해킹 대회 개최</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2628&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2630&amp;page=1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1866,34 +1866,34 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-08-27 15:01:41.552844+09:00</t>
+          <t>2026-08-31 09:16:38.866405+09:00</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-08-27 15:01:41.552844+09:00</t>
+          <t>2026-08-31 09:16:38.866405+09:00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>45681</t>
+          <t>46011</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>싱가포르 현지 진출 지원 국내 블록체인 기업 모집(~9.16(수) 14시)</t>
+          <t>자동차 노리는 사이버 위협, 한국인터넷진흥원-한국교통안전공단이 함께 대응한다</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3750&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2628&amp;page=1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1911,56 +1911,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-08-27 11:01:31.314899+09:00</t>
+          <t>2026-08-27 15:01:41.552844+09:00</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-08-27 11:01:31.314899+09:00</t>
+          <t>2026-08-27 15:01:41.552844+09:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>45191</t>
+          <t>45681</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 아·태 지역 사이버공격 대응 공동 훈련 실시</t>
+          <t>싱가포르 현지 진출 지원 국내 블록체인 기업 모집(~9.16(수) 14시)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2629&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3750&amp;page=1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1968,42 +1964,46 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-08-26 15:01:47.261933+09:00</t>
+          <t>2026-08-27 11:01:31.314899+09:00</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-08-26 15:01:47.261933+09:00</t>
+          <t>2026-08-27 11:01:31.314899+09:00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>44741</t>
+          <t>45191</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>[3차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~9/16)</t>
+          <t>한국인터넷진흥원, 아·태 지역 사이버공격 대응 공동 훈련 실시</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3749&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2629&amp;page=1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2021,56 +2021,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-08-26 09:31:36.427758+09:00</t>
+          <t>2026-08-26 15:01:47.261933+09:00</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-08-26 09:31:36.427758+09:00</t>
+          <t>2026-08-26 15:01:47.261933+09:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>44448</t>
+          <t>44741</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 공고</t>
+          <t>[3차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~9/16)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3748&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3749&amp;page=1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2078,7 +2074,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2086,19 +2086,19 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-08-25 16:01:39.626193+09:00</t>
+          <t>2026-08-26 09:31:36.427758+09:00</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-08-25 16:01:39.626193+09:00</t>
+          <t>2026-08-26 09:31:36.427758+09:00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>43767</t>
+          <t>44448</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2108,27 +2108,27 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 21회차 교육생 모집(~9.12)</t>
+          <t>정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 공고</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3747&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3748&amp;page=1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
@@ -2139,19 +2139,19 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-08-24 17:46:42.254577+09:00</t>
+          <t>2026-08-25 16:01:39.626193+09:00</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-08-24 17:46:42.254577+09:00</t>
+          <t>2026-08-25 16:01:39.626193+09:00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>43311</t>
+          <t>43767</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2161,12 +2161,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>양자내성암호 전환, 어떻게 준비해야 할까?</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 21회차 교육생 모집(~9.12)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2627&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3747&amp;page=1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2176,50 +2176,50 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-08-24 12:01:45.511381+09:00</t>
+          <t>2026-08-24 17:46:42.254577+09:00</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-08-24 12:01:45.511381+09:00</t>
+          <t>2026-08-24 17:46:42.254577+09:00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>43301</t>
+          <t>43311</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>양자내성암호 전문교육 PQC 실무과정 교육생 모집(8.24~)</t>
+          <t>양자내성암호 전환, 어떻게 준비해야 할까?</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3746&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2627&amp;page=1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2237,31 +2237,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-08-24 12:01:36.271108+09:00</t>
+          <t>2026-08-24 12:01:45.511381+09:00</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-08-24 12:01:36.271108+09:00</t>
+          <t>2026-08-24 12:01:45.511381+09:00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>41161</t>
+          <t>43301</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2271,27 +2267,27 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>「블록체인 기업 맞춤형 보안 고도화 지원」 기업 모집(~8/31)</t>
+          <t>양자내성암호 전문교육 PQC 실무과정 교육생 모집(8.24~)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3745&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3746&amp;page=1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2306,34 +2302,34 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-08-21 16:01:38.087170+09:00</t>
+          <t>2026-08-24 12:01:36.271108+09:00</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-08-21 16:01:38.087170+09:00</t>
+          <t>2026-08-24 12:01:36.271108+09:00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>41086</t>
+          <t>41161</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026년도 인터넷거버넌스 민간전문가 APrIGF 및 IGF 참석자 모집</t>
+          <t>「블록체인 기업 맞춤형 보안 고도화 지원」 기업 모집(~8/31)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3744&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3745&amp;page=1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2343,15 +2339,19 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2359,19 +2359,19 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-08-21 15:01:32.139445+09:00</t>
+          <t>2026-08-21 16:01:38.087170+09:00</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-08-21 15:01:32.139445+09:00</t>
+          <t>2026-08-21 16:01:38.087170+09:00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>34750</t>
+          <t>41086</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2381,22 +2381,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>｢2026 블록체인 진흥주간｣ 전시부스 참가기업 모집 공고(~9.14)</t>
+          <t>2026년도 인터넷거버넌스 민간전문가 APrIGF 및 IGF 참석자 모집</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3743&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3744&amp;page=1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>59</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2412,34 +2412,34 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-08-13 17:46:21.938331+09:00</t>
+          <t>2026-08-21 15:01:32.139445+09:00</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-08-13 17:46:21.938331+09:00</t>
+          <t>2026-08-21 15:01:32.139445+09:00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>34081</t>
+          <t>34750</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026년 하반기 정보보호 전문서비스 기업 지정에 관한 공고</t>
+          <t>｢2026 블록체인 진흥주간｣ 전시부스 참가기업 모집 공고(~9.14)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3742&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3743&amp;page=1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2457,11 +2457,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2469,44 +2465,44 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:24.927741+09:00</t>
+          <t>2026-08-13 17:46:21.938331+09:00</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:24.927741+09:00</t>
+          <t>2026-08-13 17:46:21.938331+09:00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>34071</t>
+          <t>34081</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>"예방 넘어 대응·복구까지" 랜섬웨어 전주기 대응 방안 논의한다</t>
+          <t>2026년 하반기 정보보호 전문서비스 기업 지정에 관한 공고</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2626&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3742&amp;page=1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2514,42 +2510,46 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-08-13 09:16:35.989405+09:00</t>
+          <t>2026-08-13 09:31:24.927741+09:00</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-08-13 09:16:35.989405+09:00</t>
+          <t>2026-08-13 09:31:24.927741+09:00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>33789</t>
+          <t>34071</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>978</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 21회차 교육생 모집(~9.11)</t>
+          <t>"예방 넘어 대응·복구까지" 랜섬웨어 전주기 대응 방안 논의한다</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3741&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2626&amp;page=1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2559,35 +2559,35 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-08-12 16:01:25.579701+09:00</t>
+          <t>2026-08-13 09:16:35.989405+09:00</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-08-12 16:01:25.579701+09:00</t>
+          <t>2026-08-13 09:16:35.989405+09:00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>33749</t>
+          <t>33789</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026년도 블록체인 유공 포상 계획 공고 안내(~9.21 15:00 마감)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 21회차 교육생 모집(~9.11)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3740&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3741&amp;page=1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2612,12 +2612,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
@@ -2628,44 +2628,44 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-08-12 15:31:25.306307+09:00</t>
+          <t>2026-08-12 16:01:25.579701+09:00</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-08-12 15:31:25.306307+09:00</t>
+          <t>2026-08-12 16:01:25.579701+09:00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>31741</t>
+          <t>33749</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026년 블록체인 수요-공급 협의체 (ABLE) 정례세미나 개최 안내(8.13.목)</t>
+          <t>2026년도 블록체인 유공 포상 계획 공고 안내(~9.21 15:00 마감)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3739&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3740&amp;page=1</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2673,11 +2673,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2685,52 +2681,56 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-08-10 11:01:30.246604+09:00</t>
+          <t>2026-08-12 15:31:25.306307+09:00</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-08-10 11:01:30.246604+09:00</t>
+          <t>2026-08-12 15:31:25.306307+09:00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>29768</t>
+          <t>31741</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026년 블록체인 신뢰인프라(K-BTF) 활용·확산사업 공모 사전예고</t>
+          <t>2026년 블록체인 수요-공급 협의체 (ABLE) 정례세미나 개최 안내(8.13.목)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3738&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3739&amp;page=1</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I43" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2738,19 +2738,19 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-08-07 17:01:29.954014+09:00</t>
+          <t>2026-08-10 11:01:30.246604+09:00</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-08-07 17:01:29.954014+09:00</t>
+          <t>2026-08-10 11:01:30.246604+09:00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>29728</t>
+          <t>29768</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026년도 블록체인 산업 실태조사 실시 및 협조 안내</t>
+          <t>2026년 블록체인 신뢰인프라(K-BTF) 활용·확산사업 공모 사전예고</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3737&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3738&amp;page=1</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2775,7 +2775,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2791,19 +2791,19 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-08-07 16:31:30.938844+09:00</t>
+          <t>2026-08-07 17:01:29.954014+09:00</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-08-07 16:31:30.938844+09:00</t>
+          <t>2026-08-07 17:01:29.954014+09:00</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>28711</t>
+          <t>29728</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2813,50 +2813,50 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원-나주시, 고교생 개인정보·정보보호 진로 탐색 지원</t>
+          <t>2026년도 블록체인 산업 실태조사 실시 및 협조 안내</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2625&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3737&amp;page=1</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2026-08-06 14:01:34.968573+09:00</t>
+          <t>2026-08-07 16:31:30.938844+09:00</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-08-06 14:01:34.968573+09:00</t>
+          <t>2026-08-07 16:31:30.938844+09:00</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>27551</t>
+          <t>28711</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2866,22 +2866,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 기업 맞춤형 사이버 위협 알림 서비스 개시</t>
+          <t>한국인터넷진흥원-나주시, 고교생 개인정보·정보보호 진로 탐색 지원</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2624&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2625&amp;page=1</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2897,44 +2897,44 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2026-08-05 09:46:34.063806+09:00</t>
+          <t>2026-08-06 14:01:34.968573+09:00</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-08-05 09:46:34.063806+09:00</t>
+          <t>2026-08-06 14:01:34.968573+09:00</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>27511</t>
+          <t>27551</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 기관장 주도 국민 체감 성과 혁신 체계 가동</t>
+          <t>한국인터넷진흥원, 기업 맞춤형 사이버 위협 알림 서비스 개시</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2623&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2624&amp;page=1</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2950,34 +2950,34 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2026-08-05 09:16:33.823896+09:00</t>
+          <t>2026-08-05 09:46:34.063806+09:00</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-08-05 09:16:33.823896+09:00</t>
+          <t>2026-08-05 09:46:34.063806+09:00</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>27268</t>
+          <t>27511</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>975</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>양자내성암호 국제 표준화 동향 분석</t>
+          <t>한국인터넷진흥원, 기관장 주도 국민 체감 성과 혁신 체계 가동</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3736&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2623&amp;page=1</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>263</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2998,24 +2998,24 @@
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-08-04 16:31:26.502205+09:00</t>
+          <t>2026-08-05 09:16:33.823896+09:00</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-08-04 16:31:26.502205+09:00</t>
+          <t>2026-08-05 09:16:33.823896+09:00</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>27128</t>
+          <t>27268</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3025,12 +3025,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 20회차 교육생 모집(~9.4)</t>
+          <t>양자내성암호 국제 표준화 동향 분석</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3735&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3736&amp;page=1</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
@@ -3056,19 +3056,19 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-08-04 14:46:28.764255+09:00</t>
+          <t>2026-08-04 16:31:26.502205+09:00</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-08-04 14:46:28.764255+09:00</t>
+          <t>2026-08-04 16:31:26.502205+09:00</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>26211</t>
+          <t>27128</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3078,50 +3078,50 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 암호모듈검증 위한 시험 전문인력 양성</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 20회차 교육생 모집(~9.4)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2622&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3735&amp;page=1</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2026-08-03 13:31:41.722921+09:00</t>
+          <t>2026-08-04 14:46:28.764255+09:00</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-08-03 13:31:41.722921+09:00</t>
+          <t>2026-08-04 14:46:28.764255+09:00</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>26188</t>
+          <t>26211</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026년 8차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(8월 추천) (~8.21(금) 18시까지)</t>
+          <t>한국인터넷진흥원, 암호모듈검증 위한 시험 전문인력 양성</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3734&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2622&amp;page=1</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>273</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3157,24 +3157,24 @@
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2026-08-03 13:16:30.325331+09:00</t>
+          <t>2026-08-03 13:31:41.722921+09:00</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-08-03 13:16:30.325331+09:00</t>
+          <t>2026-08-03 13:31:41.722921+09:00</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>25891</t>
+          <t>26188</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 지역 상생 3대 사업 참여자 모집</t>
+          <t>2026년 8차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(8월 추천) (~8.21(금) 18시까지)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2621&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3734&amp;page=1</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3199,7 +3199,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3210,39 +3210,39 @@
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2026-08-03 09:31:46.854132+09:00</t>
+          <t>2026-08-03 13:16:30.325331+09:00</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-08-03 09:31:46.854132+09:00</t>
+          <t>2026-08-03 13:16:30.325331+09:00</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>25864</t>
+          <t>25891</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026년 전남광주통합특별시 소상공인·사회적경제기업 판로 확대 지원기업 선발 안내(~8.14)</t>
+          <t>한국인터넷진흥원, 지역 상생 3대 사업 참여자 모집</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3730&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2621&amp;page=1</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3252,7 +3252,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>80</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3260,31 +3260,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2026-08-03 09:16:35.817723+09:00</t>
+          <t>2026-08-03 09:31:46.854132+09:00</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-08-03 09:16:35.817723+09:00</t>
+          <t>2026-08-03 09:31:46.854132+09:00</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>25863</t>
+          <t>25864</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3294,12 +3290,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026년 전남광주통합특별시 지역문제 해결 프로젝트 공모전 개최 안내(~8.21)</t>
+          <t>2026년 전남광주통합특별시 소상공인·사회적경제기업 판로 확대 지원기업 선발 안내(~8.14)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3731&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3730&amp;page=1</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3309,7 +3305,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3341,7 +3337,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>25862</t>
+          <t>25863</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3351,12 +3347,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026년 한국인터넷진흥원 지역공부방 참여 대학생 장학금 지원자 모집 안내(~8.28)</t>
+          <t>2026년 전남광주통합특별시 지역문제 해결 프로젝트 공모전 개최 안내(~8.21)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3732&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3731&amp;page=1</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3366,7 +3362,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3398,7 +3394,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>25861</t>
+          <t>25862</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3408,12 +3404,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026년 암호모듈 시험자 양성교육 및 필기시험 안내(8.3~8.21)</t>
+          <t>2026년 한국인터넷진흥원 지역공부방 참여 대학생 장학금 지원자 모집 안내(~8.28)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3733&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3732&amp;page=1</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3423,7 +3419,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3455,7 +3451,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>23221</t>
+          <t>25861</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3465,22 +3461,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026년 블록체인 기업성장허브 입주기업 모집(~8월 27일(목) 16:00까지)</t>
+          <t>2026년 암호모듈 시험자 양성교육 및 필기시험 안내(8.3~8.21)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3729&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3733&amp;page=1</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3500,52 +3496,56 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2026-07-30 17:16:54.540202+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-07-30 17:16:54.540202+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>22504</t>
+          <t>23221</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 19회차 교육생 모집(~8.28)</t>
+          <t>2026년 블록체인 기업성장허브 입주기업 모집(~8월 27일(목) 16:00까지)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3728&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3729&amp;page=1</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I58" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3553,19 +3553,19 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>2026-07-29 18:32:00.075123+09:00</t>
+          <t>2026-07-30 17:16:54.540202+09:00</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-07-29 18:32:00.075123+09:00</t>
+          <t>2026-07-30 17:16:54.540202+09:00</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>22464</t>
+          <t>22504</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3575,12 +3575,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026년 연계정보 이용기관 안전조치 실태점검 2차 설명회 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 19회차 교육생 모집(~8.28)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3727&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3728&amp;page=1</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3606,19 +3606,19 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:59.875668+09:00</t>
+          <t>2026-07-29 18:32:00.075123+09:00</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:59.875668+09:00</t>
+          <t>2026-07-29 18:32:00.075123+09:00</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>20771</t>
+          <t>22464</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3628,50 +3628,50 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 성평등가족부와 불법·유해 정보 유통 대응 맞손</t>
+          <t>2026년 연계정보 이용기관 안전조치 실태점검 2차 설명회 개최</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2620&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3727&amp;page=1</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>2026-07-27 17:17:05.702970+09:00</t>
+          <t>2026-07-29 18:01:59.875668+09:00</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-07-27 17:17:05.702970+09:00</t>
+          <t>2026-07-29 18:01:59.875668+09:00</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>20191</t>
+          <t>20771</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3681,12 +3681,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 향후 10년 설계한다…전담 추진단(TF) 출범</t>
+          <t>한국인터넷진흥원, 성평등가족부와 불법·유해 정보 유통 대응 맞손</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2619&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2620&amp;page=1</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>150</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3712,34 +3712,34 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>2026-07-27 10:02:05.338547+09:00</t>
+          <t>2026-07-27 17:17:05.702970+09:00</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-07-27 10:02:05.338547+09:00</t>
+          <t>2026-07-27 17:17:05.702970+09:00</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>20061</t>
+          <t>20191</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(1차, BreakingPoint)</t>
+          <t>아피가(APIGA) 향후 10년 설계한다…전담 추진단(TF) 출범</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3726&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2619&amp;page=1</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>287</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -3757,64 +3757,64 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2026-07-27 08:31:55.019743+09:00</t>
+          <t>2026-07-27 10:02:05.338547+09:00</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-07-27 08:31:55.019743+09:00</t>
+          <t>2026-07-27 10:02:05.338547+09:00</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>16785</t>
+          <t>20061</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 17회차 교육생 모집(~8.7)</t>
+          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(1차, BreakingPoint)</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3724&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3726&amp;page=1</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>246</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I63" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3822,34 +3822,34 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 08:31:55.019743+09:00</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 08:31:55.019743+09:00</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>16784</t>
+          <t>16785</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>1497</t>
+          <t>1496</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 18회차 교육생 모집(~8.21)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 17회차 교육생 모집(~8.7)</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3725&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3724&amp;page=1</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>236</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -3887,22 +3887,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>16781</t>
+          <t>16784</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1497</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 16회차 교육생 모집(~7.31)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 18회차 교육생 모집(~8.21)</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3723&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3725&amp;page=1</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>260</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -3920,11 +3920,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3944,22 +3940,22 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>16691</t>
+          <t>16781</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>'블록체인 기반 예금토큰 결제 인프라 확산' 사업 발대식 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 16회차 교육생 모집(~7.31)</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2618&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3723&amp;page=1</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3969,35 +3965,39 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>242</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>2026-07-22 17:32:01.526863+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-07-22 17:32:01.526863+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>16464</t>
+          <t>16691</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>[홍보] 정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 안내</t>
+          <t>'블록체인 기반 예금토큰 결제 인프라 확산' 사업 발대식 개최</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3722&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2618&amp;page=1</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4022,35 +4022,35 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>278</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>2026-07-22 14:46:48.687665+09:00</t>
+          <t>2026-07-22 17:32:01.526863+09:00</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-07-22 14:46:48.687665+09:00</t>
+          <t>2026-07-22 17:32:01.526863+09:00</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>16051</t>
+          <t>16464</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4060,12 +4060,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 보안 인재·글로벌 전문가 교류의 장 열어</t>
+          <t>[홍보] 정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 안내</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2617&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3722&amp;page=1</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4075,35 +4075,35 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>2026-07-22 09:31:50.671841+09:00</t>
+          <t>2026-07-22 14:46:48.687665+09:00</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-07-22 09:31:50.671841+09:00</t>
+          <t>2026-07-22 14:46:48.687665+09:00</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>14611</t>
+          <t>16051</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4113,22 +4113,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
+          <t>한국인터넷진흥원, 보안 인재·글로벌 전문가 교류의 장 열어</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2617&amp;page=1</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>233</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -4144,19 +4144,19 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>14431</t>
+          <t>14611</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>32</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -4197,34 +4197,34 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>14431</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>53</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -4242,56 +4242,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>14444</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>1493</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
+          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -4299,7 +4295,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr"/>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I72" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -4307,34 +4307,34 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>11331</t>
+          <t>14444</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4344,7 +4344,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -4355,96 +4355,92 @@
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>10981</t>
+          <t>11331</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
+          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>10943</t>
+          <t>10981</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
+          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4454,7 +4450,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -4462,7 +4458,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr"/>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I75" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -4470,19 +4470,19 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>10663</t>
+          <t>10943</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -4492,12 +4492,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
+          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -4507,12 +4507,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
@@ -4523,19 +4523,19 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>9805</t>
+          <t>10663</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -4545,22 +4545,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
+          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -4576,19 +4576,19 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>9691</t>
+          <t>9805</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -4598,12 +4598,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
+          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -4613,7 +4613,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -4624,96 +4624,92 @@
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>9321</t>
+          <t>9691</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
+          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>8871</t>
+          <t>9321</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
+          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -4723,35 +4719,39 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>6685</t>
+          <t>8871</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
+          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -4787,24 +4787,24 @@
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>6571</t>
+          <t>6685</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -4814,12 +4814,12 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
+          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -4829,7 +4829,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -4840,24 +4840,24 @@
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>5591</t>
+          <t>6571</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4867,22 +4867,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
+          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -4898,44 +4898,44 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>5591</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
+          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>33</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -4951,44 +4951,44 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>4762</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>961</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>AI 보안 위협 대응 매뉴얼</t>
+          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -4996,31 +4996,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>4761</t>
+          <t>4762</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5030,12 +5026,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>AI 보안 레드티밍 가이드</t>
+          <t>AI 보안 위협 대응 매뉴얼</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5045,7 +5041,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -5077,22 +5073,22 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>4251</t>
+          <t>4761</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
+          <t>AI 보안 레드티밍 가이드</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5102,7 +5098,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -5110,27 +5106,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr"/>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>4251</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
+          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5155,113 +5155,113 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>191</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t>3867</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
+          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4111</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>959</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
+          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>34</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -5269,31 +5269,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5303,12 +5299,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
+          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5318,7 +5314,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -5350,32 +5346,32 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
+          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>105</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -5383,7 +5379,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr"/>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I92" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -5403,22 +5403,22 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1477</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
+          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -5428,7 +5428,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>386</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -5456,22 +5456,22 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
+          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -5481,19 +5481,15 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>362</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -5513,7 +5509,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -5523,12 +5519,12 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2026년 IoT 보안인증 교육과정 안내</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -5538,7 +5534,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>522</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -5570,40 +5566,44 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
+          <t>2026년 IoT 보안인증 교육과정 안내</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>652</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I96" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -5623,22 +5623,22 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
+          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -5648,7 +5648,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>1529</t>
+          <t>818</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -5656,11 +5656,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -5680,32 +5676,32 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
+          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>1529</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -5713,7 +5709,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr"/>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I98" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -5721,34 +5721,34 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>76426</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -5769,49 +5769,49 @@
       <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>958</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
+          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>55906</t>
+          <t>76426</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -5839,22 +5839,22 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>956</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
+          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -5864,7 +5864,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>55329</t>
+          <t>55906</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -5892,32 +5892,32 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>957</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
+          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>34467</t>
+          <t>55329</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -5945,22 +5945,22 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>955</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
+          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -5970,39 +5970,35 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2945</t>
+          <t>34467</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6012,27 +6008,27 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>2945</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6059,32 +6055,32 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>145255</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -6092,52 +6088,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr"/>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>954</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>26576</t>
+          <t>145255</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -6165,32 +6165,32 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>953</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
+          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>34290</t>
+          <t>26576</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -6218,32 +6218,32 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
+          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>184573</t>
+          <t>34290</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -6271,32 +6271,32 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>14403</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>951</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>6587</t>
+          <t>184573</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -6304,46 +6304,42 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14403</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
+          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -6353,7 +6349,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>51749</t>
+          <t>6587</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -6361,52 +6357,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr"/>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>950</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>78439</t>
+          <t>51749</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -6434,55 +6434,108 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>949</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>78439</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>보도자료</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
           <t>38805</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr">
+      <c r="B113" t="inlineStr">
         <is>
           <t>공지</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr">
+      <c r="C113" t="inlineStr">
         <is>
           <t>[공유] 지능형 CCTV 성능시험 재개 안내 공지</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr">
+      <c r="D113" t="inlineStr">
         <is>
           <t>https://www.kisa.or.kr/401/form?postSeq=3677&amp;page=1</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr">
+      <c r="E113" t="inlineStr">
         <is>
           <t>2026-06-02</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr">
+      <c r="F113" t="inlineStr">
         <is>
           <t>6525</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr">
+      <c r="G113" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
+      <c r="H113" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>공지사항</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
         <is>
           <t>2026-08-18 17:16:37.364015+09:00</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr">
+      <c r="K113" t="inlineStr">
         <is>
           <t>2026-08-18 17:16:37.364015+09:00</t>
         </is>

--- a/docs/snapshot/downloads/kisa.xlsx
+++ b/docs/snapshot/downloads/kisa.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K113"/>
+  <dimension ref="A1:K114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>65988</t>
+          <t>66888</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -486,22 +486,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026년도 K-Cybersecurity Business Day in Japan 세미나(10/20) 참석 수요조사 안내</t>
+          <t>(행사 안내) 글로벌 AI 프라이버시 포럼 개최(9.29.)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3768&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3769&amp;page=1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -517,19 +517,19 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-09-22 10:01:34.273734+09:00</t>
+          <t>2026-09-23 13:31:32.429525+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-09-22 10:01:34.273734+09:00</t>
+          <t>2026-09-23 13:31:32.429525+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>65748</t>
+          <t>65988</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -539,27 +539,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 26회차 교육생 모집(~10.16)</t>
+          <t>2026년도 K-Cybersecurity Business Day in Japan 세미나(10/20) 참석 수요조사 안내</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3767&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3768&amp;page=1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -570,87 +570,87 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-09-21 17:01:40.203969+09:00</t>
+          <t>2026-09-22 10:01:34.273734+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-09-21 17:01:40.203969+09:00</t>
+          <t>2026-09-22 10:01:34.273734+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>64631</t>
+          <t>65748</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 인터넷 주소 자원 관리 역량 국제적 인정받아</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 26회차 교육생 모집(~10.16)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2639&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3767&amp;page=1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-09-20 12:01:47.233521+09:00</t>
+          <t>2026-09-21 17:01:40.203969+09:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-09-20 12:01:47.233521+09:00</t>
+          <t>2026-09-21 17:01:40.203969+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>63068</t>
+          <t>64631</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>990</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>대국민 혁신 정책·제안 공모전 개최</t>
+          <t>한국인터넷진흥원, 인터넷 주소 자원 관리 역량 국제적 인정받아</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3766&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2639&amp;page=1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -671,24 +671,24 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-09-18 10:46:37.266535+09:00</t>
+          <t>2026-09-20 12:01:47.233521+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-09-18 10:46:37.266535+09:00</t>
+          <t>2026-09-20 12:01:47.233521+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>63051</t>
+          <t>63068</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -698,12 +698,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>세계경제포럼·싱가포르 사이버보안청과 인공지능(AI) 위협 대비 사이버보안 협력 강화</t>
+          <t>대국민 혁신 정책·제안 공모전 개최</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2638&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3766&amp;page=1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -724,49 +724,49 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-09-18 10:31:43.770443+09:00</t>
+          <t>2026-09-18 10:46:37.266535+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-09-18 10:31:43.770443+09:00</t>
+          <t>2026-09-18 10:46:37.266535+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>62781</t>
+          <t>63051</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026년 블록체인 기업성장허브 입주기업 모집(~10월 7일(수) 16:00까지)</t>
+          <t>세계경제포럼·싱가포르 사이버보안청과 인공지능(AI) 위협 대비 사이버보안 협력 강화</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3765&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2638&amp;page=1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -774,46 +774,42 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-09-17 17:16:36.514530+09:00</t>
+          <t>2026-09-18 10:31:43.770443+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-09-17 17:16:36.514530+09:00</t>
+          <t>2026-09-18 10:31:43.770443+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>62507</t>
+          <t>62781</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 25회차 교육생 모집(~10.10)</t>
+          <t>2026년 블록체인 기업성장허브 입주기업 모집(~10월 7일(수) 16:00까지)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3764&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3765&amp;page=1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -823,15 +819,19 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -839,19 +839,19 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-09-17 13:31:33.789948+09:00</t>
+          <t>2026-09-17 17:16:36.514530+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-09-17 13:31:33.789948+09:00</t>
+          <t>2026-09-17 17:16:36.514530+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>62367</t>
+          <t>62507</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 24회차 교육생 모집(~10.9)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 25회차 교육생 모집(~10.10)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3763&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3764&amp;page=1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -892,19 +892,19 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-09-17 11:46:35.719751+09:00</t>
+          <t>2026-09-17 13:31:33.789948+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-09-17 11:46:35.719751+09:00</t>
+          <t>2026-09-17 13:31:33.789948+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>61484</t>
+          <t>62367</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -914,27 +914,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026년 제13회 소프트웨어(SW) 개발보안 경진대회 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 24회차 교육생 모집(~10.9)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3762&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3763&amp;page=1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
@@ -945,19 +945,19 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-09-16 09:46:37.058042+09:00</t>
+          <t>2026-09-17 11:46:35.719751+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-09-16 09:46:37.058042+09:00</t>
+          <t>2026-09-17 11:46:35.719751+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>61111</t>
+          <t>61484</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -967,22 +967,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>민관 합동 ‘자동차 사이버 침해사고 대응 모의훈련’ 실시</t>
+          <t>2026년 제13회 소프트웨어(SW) 개발보안 경진대회 개최</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2637&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3762&amp;page=1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -993,24 +993,24 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-09-15 15:01:52.747371+09:00</t>
+          <t>2026-09-16 09:46:37.058042+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-09-15 15:01:52.747371+09:00</t>
+          <t>2026-09-16 09:46:37.058042+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>61031</t>
+          <t>61111</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1020,12 +1020,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>“새로운 보안 위협, 인공지능(AI)으로 대응” 정보보호 제품 개발 기업 대상 보안 역량 강화 교육 추진</t>
+          <t>민관 합동 ‘자동차 사이버 침해사고 대응 모의훈련’ 실시</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2636&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2637&amp;page=1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1051,44 +1051,44 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-09-15 14:01:52.540884+09:00</t>
+          <t>2026-09-15 15:01:52.747371+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-09-15 14:01:52.540884+09:00</t>
+          <t>2026-09-15 15:01:52.747371+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>57381</t>
+          <t>61031</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026 전자문서 유공 포상 공고</t>
+          <t>“새로운 보안 위협, 인공지능(AI)으로 대응” 정보보호 제품 개발 기업 대상 보안 역량 강화 교육 추진</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3761&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2636&amp;page=1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1096,46 +1096,42 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-09-10 14:16:31.877229+09:00</t>
+          <t>2026-09-15 14:01:52.540884+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-09-10 14:16:31.877229+09:00</t>
+          <t>2026-09-15 14:01:52.540884+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>57149</t>
+          <t>57381</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026년 클라우드 서비스 보안인증(CSAP) 교육 안내</t>
+          <t>2026 전자문서 유공 포상 공고</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3760&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3761&amp;page=1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1145,7 +1141,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1153,7 +1149,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1161,19 +1161,19 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-09-10 10:46:38.794916+09:00</t>
+          <t>2026-09-10 14:16:31.877229+09:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-09-10 10:46:38.794916+09:00</t>
+          <t>2026-09-10 14:16:31.877229+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>56431</t>
+          <t>57149</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1183,22 +1183,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>보호나라 챗봇, 국민 생활 속 정보보호 성과 인정</t>
+          <t>2026년 클라우드 서비스 보안인증(CSAP) 교육 안내</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2634&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3760&amp;page=1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1209,92 +1209,92 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-09-09 12:01:35.142670+09:00</t>
+          <t>2026-09-10 10:46:38.794916+09:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-09-09 12:01:35.142670+09:00</t>
+          <t>2026-09-10 10:46:38.794916+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>56969</t>
+          <t>56431</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1522</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>온마이데이터 서비스 이용 이벤트 안내</t>
+          <t>보호나라 챗봇, 국민 생활 속 정보보호 성과 인정</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3758&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2634&amp;page=1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>402</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-09-10 08:31:37.677434+09:00</t>
+          <t>2026-09-09 12:01:35.142670+09:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-09-10 08:31:37.677434+09:00</t>
+          <t>2026-09-09 12:01:35.142670+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>54791</t>
+          <t>56969</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1522</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>국내 캐시 도메인이름시스템(DNS) 운영기관, 신규 암호키 반영 여부 확인하세요</t>
+          <t>온마이데이터 서비스 이용 이벤트 안내</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2633&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3758&amp;page=1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1304,60 +1304,60 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>402</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-09-07 12:01:35.243341+09:00</t>
+          <t>2026-09-10 08:31:37.677434+09:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-09-07 12:01:35.243341+09:00</t>
+          <t>2026-09-10 08:31:37.677434+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>54541</t>
+          <t>54791</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(2차, Avalanche)</t>
+          <t>국내 캐시 도메인이름시스템(DNS) 운영기관, 신규 암호키 반영 여부 확인하세요</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3759&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2633&amp;page=1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1365,31 +1365,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-09-07 09:01:25.516098+09:00</t>
+          <t>2026-09-07 12:01:35.243341+09:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-09-07 09:01:25.516098+09:00</t>
+          <t>2026-09-07 12:01:35.243341+09:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>51281</t>
+          <t>54541</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1399,27 +1395,27 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>(행사 안내) 국외이전 제도 개선 및 CBPR 인증제도 기업 설명회 개최</t>
+          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(2차, Avalanche)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3757&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3759&amp;page=1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1434,52 +1430,56 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-09-03 09:16:26.856224+09:00</t>
+          <t>2026-09-07 09:01:25.516098+09:00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-09-03 09:16:26.856224+09:00</t>
+          <t>2026-09-07 09:01:25.516098+09:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>56970</t>
+          <t>51281</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1521</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026 부산지역 도메인이름 분쟁해결 세미나 개최 안내(9.11)</t>
+          <t>(행사 안내) 국외이전 제도 개선 및 CBPR 인증제도 기업 설명회 개최</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3755&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3757&amp;page=1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>23</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1487,34 +1487,34 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-09-10 08:31:37.677434+09:00</t>
+          <t>2026-09-03 09:16:26.856224+09:00</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-09-10 08:31:37.677434+09:00</t>
+          <t>2026-09-03 09:16:26.856224+09:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>51121</t>
+          <t>56970</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1521</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026년 블록체인 수요공급협의체(ABLE) 블록체인 수요기업(비금융분야) 모집 공고</t>
+          <t>2026 부산지역 도메인이름 분쟁해결 세미나 개최 안내(9.11)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3754&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3755&amp;page=1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>242</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1532,11 +1532,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1544,19 +1540,19 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-09-02 17:31:25.610368+09:00</t>
+          <t>2026-09-10 08:31:37.677434+09:00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-09-02 17:31:25.610368+09:00</t>
+          <t>2026-09-10 08:31:37.677434+09:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>50601</t>
+          <t>51121</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1566,12 +1562,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026년 9차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(9월 추천) (~9.18(금) 18시까지)</t>
+          <t>2026년 블록체인 수요공급협의체(ABLE) 블록체인 수요기업(비금융분야) 모집 공고</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3753&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3754&amp;page=1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1581,7 +1577,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>24</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1601,44 +1597,44 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-09-02 11:01:32.173328+09:00</t>
+          <t>2026-09-02 17:31:25.610368+09:00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-09-02 11:01:32.173328+09:00</t>
+          <t>2026-09-02 17:31:25.610368+09:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>49872</t>
+          <t>50601</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>인공지능(AI) 사이버 위협, 실전 모의훈련으로 대응</t>
+          <t>2026년 9차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(9월 추천) (~9.18(금) 18시까지)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2631&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3753&amp;page=1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1646,27 +1642,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-09-01 12:01:47.858504+09:00</t>
+          <t>2026-09-02 11:01:32.173328+09:00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-09-01 12:01:47.858504+09:00</t>
+          <t>2026-09-02 11:01:32.173328+09:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>49669</t>
+          <t>49872</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>「2026 위치정보 맞춤형 컨설팅 참여기업 모집」</t>
+          <t>인공지능(AI) 사이버 위협, 실전 모의훈련으로 대응</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3752&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2631&amp;page=1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1691,35 +1691,35 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-09-01 09:31:38.715793+09:00</t>
+          <t>2026-09-01 12:01:47.858504+09:00</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-09-01 09:31:38.715793+09:00</t>
+          <t>2026-09-01 12:01:47.858504+09:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>49631</t>
+          <t>49669</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>물리보안 시스템 간 연동 장벽 낮춘다</t>
+          <t>「2026 위치정보 맞춤형 컨설팅 참여기업 모집」</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2632&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3752&amp;page=1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1744,103 +1744,103 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-09-01 09:01:45.980040+09:00</t>
+          <t>2026-09-01 09:31:38.715793+09:00</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-09-01 09:01:45.980040+09:00</t>
+          <t>2026-09-01 09:31:38.715793+09:00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>49589</t>
+          <t>49631</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1517</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 23회차 교육생 모집(~9.18)</t>
+          <t>물리보안 시스템 간 연동 장벽 낮춘다</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3751&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2632&amp;page=1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-09-01 08:31:37.253592+09:00</t>
+          <t>2026-09-01 09:01:45.980040+09:00</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-09-01 08:31:37.253592+09:00</t>
+          <t>2026-09-01 09:01:45.980040+09:00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>48831</t>
+          <t>49589</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1517</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>생성형 인공지능(AI) 기반 실전형 모의해킹 대회 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 23회차 교육생 모집(~9.18)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2630&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3751&amp;page=1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1850,35 +1850,35 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>174</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-08-31 09:16:38.866405+09:00</t>
+          <t>2026-09-01 08:31:37.253592+09:00</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-08-31 09:16:38.866405+09:00</t>
+          <t>2026-09-01 08:31:37.253592+09:00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>46011</t>
+          <t>48831</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1888,22 +1888,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>자동차 노리는 사이버 위협, 한국인터넷진흥원-한국교통안전공단이 함께 대응한다</t>
+          <t>생성형 인공지능(AI) 기반 실전형 모의해킹 대회 개최</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2628&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2630&amp;page=1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1919,34 +1919,34 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-08-27 15:01:41.552844+09:00</t>
+          <t>2026-08-31 09:16:38.866405+09:00</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-08-27 15:01:41.552844+09:00</t>
+          <t>2026-08-31 09:16:38.866405+09:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>45681</t>
+          <t>46011</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>싱가포르 현지 진출 지원 국내 블록체인 기업 모집(~9.16(수) 14시)</t>
+          <t>자동차 노리는 사이버 위협, 한국인터넷진흥원-한국교통안전공단이 함께 대응한다</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3750&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2628&amp;page=1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1964,56 +1964,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-08-27 11:01:31.314899+09:00</t>
+          <t>2026-08-27 15:01:41.552844+09:00</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-08-27 11:01:31.314899+09:00</t>
+          <t>2026-08-27 15:01:41.552844+09:00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>45191</t>
+          <t>45681</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 아·태 지역 사이버공격 대응 공동 훈련 실시</t>
+          <t>싱가포르 현지 진출 지원 국내 블록체인 기업 모집(~9.16(수) 14시)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2629&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3750&amp;page=1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2021,42 +2017,46 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-08-26 15:01:47.261933+09:00</t>
+          <t>2026-08-27 11:01:31.314899+09:00</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-08-26 15:01:47.261933+09:00</t>
+          <t>2026-08-27 11:01:31.314899+09:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>44741</t>
+          <t>45191</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>[3차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~9/16)</t>
+          <t>한국인터넷진흥원, 아·태 지역 사이버공격 대응 공동 훈련 실시</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3749&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2629&amp;page=1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2074,56 +2074,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-08-26 09:31:36.427758+09:00</t>
+          <t>2026-08-26 15:01:47.261933+09:00</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-08-26 09:31:36.427758+09:00</t>
+          <t>2026-08-26 15:01:47.261933+09:00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>44448</t>
+          <t>44741</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 공고</t>
+          <t>[3차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~9/16)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3748&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3749&amp;page=1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2131,7 +2127,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2139,19 +2139,19 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-08-25 16:01:39.626193+09:00</t>
+          <t>2026-08-26 09:31:36.427758+09:00</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-08-25 16:01:39.626193+09:00</t>
+          <t>2026-08-26 09:31:36.427758+09:00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>43767</t>
+          <t>44448</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2161,27 +2161,27 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 21회차 교육생 모집(~9.12)</t>
+          <t>정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 공고</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3747&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3748&amp;page=1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
@@ -2192,19 +2192,19 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-08-24 17:46:42.254577+09:00</t>
+          <t>2026-08-25 16:01:39.626193+09:00</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-08-24 17:46:42.254577+09:00</t>
+          <t>2026-08-25 16:01:39.626193+09:00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>43311</t>
+          <t>43767</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>양자내성암호 전환, 어떻게 준비해야 할까?</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 21회차 교육생 모집(~9.12)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2627&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3747&amp;page=1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2229,50 +2229,50 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-08-24 12:01:45.511381+09:00</t>
+          <t>2026-08-24 17:46:42.254577+09:00</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-08-24 12:01:45.511381+09:00</t>
+          <t>2026-08-24 17:46:42.254577+09:00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>43301</t>
+          <t>43311</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>양자내성암호 전문교육 PQC 실무과정 교육생 모집(8.24~)</t>
+          <t>양자내성암호 전환, 어떻게 준비해야 할까?</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3746&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2627&amp;page=1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2290,31 +2290,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-08-24 12:01:36.271108+09:00</t>
+          <t>2026-08-24 12:01:45.511381+09:00</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-08-24 12:01:36.271108+09:00</t>
+          <t>2026-08-24 12:01:45.511381+09:00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>41161</t>
+          <t>43301</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2324,27 +2320,27 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>「블록체인 기업 맞춤형 보안 고도화 지원」 기업 모집(~8/31)</t>
+          <t>양자내성암호 전문교육 PQC 실무과정 교육생 모집(8.24~)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3745&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3746&amp;page=1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2359,34 +2355,34 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-08-21 16:01:38.087170+09:00</t>
+          <t>2026-08-24 12:01:36.271108+09:00</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-08-21 16:01:38.087170+09:00</t>
+          <t>2026-08-24 12:01:36.271108+09:00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>41086</t>
+          <t>41161</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026년도 인터넷거버넌스 민간전문가 APrIGF 및 IGF 참석자 모집</t>
+          <t>「블록체인 기업 맞춤형 보안 고도화 지원」 기업 모집(~8/31)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3744&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3745&amp;page=1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2396,15 +2392,19 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2412,19 +2412,19 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-08-21 15:01:32.139445+09:00</t>
+          <t>2026-08-21 16:01:38.087170+09:00</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-08-21 15:01:32.139445+09:00</t>
+          <t>2026-08-21 16:01:38.087170+09:00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>34750</t>
+          <t>41086</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2434,22 +2434,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>｢2026 블록체인 진흥주간｣ 전시부스 참가기업 모집 공고(~9.14)</t>
+          <t>2026년도 인터넷거버넌스 민간전문가 APrIGF 및 IGF 참석자 모집</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3743&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3744&amp;page=1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>59</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2465,34 +2465,34 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-08-13 17:46:21.938331+09:00</t>
+          <t>2026-08-21 15:01:32.139445+09:00</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-08-13 17:46:21.938331+09:00</t>
+          <t>2026-08-21 15:01:32.139445+09:00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>34081</t>
+          <t>34750</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026년 하반기 정보보호 전문서비스 기업 지정에 관한 공고</t>
+          <t>｢2026 블록체인 진흥주간｣ 전시부스 참가기업 모집 공고(~9.14)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3742&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3743&amp;page=1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2510,11 +2510,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2522,44 +2518,44 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:24.927741+09:00</t>
+          <t>2026-08-13 17:46:21.938331+09:00</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:24.927741+09:00</t>
+          <t>2026-08-13 17:46:21.938331+09:00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>34071</t>
+          <t>34081</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>"예방 넘어 대응·복구까지" 랜섬웨어 전주기 대응 방안 논의한다</t>
+          <t>2026년 하반기 정보보호 전문서비스 기업 지정에 관한 공고</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2626&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3742&amp;page=1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2567,42 +2563,46 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-08-13 09:16:35.989405+09:00</t>
+          <t>2026-08-13 09:31:24.927741+09:00</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-08-13 09:16:35.989405+09:00</t>
+          <t>2026-08-13 09:31:24.927741+09:00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>33789</t>
+          <t>34071</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>978</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 21회차 교육생 모집(~9.11)</t>
+          <t>"예방 넘어 대응·복구까지" 랜섬웨어 전주기 대응 방안 논의한다</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3741&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2626&amp;page=1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2612,35 +2612,35 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-08-12 16:01:25.579701+09:00</t>
+          <t>2026-08-13 09:16:35.989405+09:00</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-08-12 16:01:25.579701+09:00</t>
+          <t>2026-08-13 09:16:35.989405+09:00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>33749</t>
+          <t>33789</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2650,12 +2650,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026년도 블록체인 유공 포상 계획 공고 안내(~9.21 15:00 마감)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 21회차 교육생 모집(~9.11)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3740&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3741&amp;page=1</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2665,12 +2665,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
@@ -2681,44 +2681,44 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-08-12 15:31:25.306307+09:00</t>
+          <t>2026-08-12 16:01:25.579701+09:00</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-08-12 15:31:25.306307+09:00</t>
+          <t>2026-08-12 16:01:25.579701+09:00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>31741</t>
+          <t>33749</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026년 블록체인 수요-공급 협의체 (ABLE) 정례세미나 개최 안내(8.13.목)</t>
+          <t>2026년도 블록체인 유공 포상 계획 공고 안내(~9.21 15:00 마감)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3739&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3740&amp;page=1</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2726,11 +2726,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2738,52 +2734,56 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-08-10 11:01:30.246604+09:00</t>
+          <t>2026-08-12 15:31:25.306307+09:00</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-08-10 11:01:30.246604+09:00</t>
+          <t>2026-08-12 15:31:25.306307+09:00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>29768</t>
+          <t>31741</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026년 블록체인 신뢰인프라(K-BTF) 활용·확산사업 공모 사전예고</t>
+          <t>2026년 블록체인 수요-공급 협의체 (ABLE) 정례세미나 개최 안내(8.13.목)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3738&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3739&amp;page=1</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I44" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2791,19 +2791,19 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-08-07 17:01:29.954014+09:00</t>
+          <t>2026-08-10 11:01:30.246604+09:00</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-08-07 17:01:29.954014+09:00</t>
+          <t>2026-08-10 11:01:30.246604+09:00</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>29728</t>
+          <t>29768</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026년도 블록체인 산업 실태조사 실시 및 협조 안내</t>
+          <t>2026년 블록체인 신뢰인프라(K-BTF) 활용·확산사업 공모 사전예고</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3737&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3738&amp;page=1</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2828,7 +2828,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2844,19 +2844,19 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2026-08-07 16:31:30.938844+09:00</t>
+          <t>2026-08-07 17:01:29.954014+09:00</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-08-07 16:31:30.938844+09:00</t>
+          <t>2026-08-07 17:01:29.954014+09:00</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>28711</t>
+          <t>29728</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2866,50 +2866,50 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원-나주시, 고교생 개인정보·정보보호 진로 탐색 지원</t>
+          <t>2026년도 블록체인 산업 실태조사 실시 및 협조 안내</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2625&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3737&amp;page=1</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2026-08-06 14:01:34.968573+09:00</t>
+          <t>2026-08-07 16:31:30.938844+09:00</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-08-06 14:01:34.968573+09:00</t>
+          <t>2026-08-07 16:31:30.938844+09:00</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>27551</t>
+          <t>28711</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2919,22 +2919,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 기업 맞춤형 사이버 위협 알림 서비스 개시</t>
+          <t>한국인터넷진흥원-나주시, 고교생 개인정보·정보보호 진로 탐색 지원</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2624&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2625&amp;page=1</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2950,44 +2950,44 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2026-08-05 09:46:34.063806+09:00</t>
+          <t>2026-08-06 14:01:34.968573+09:00</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-08-05 09:46:34.063806+09:00</t>
+          <t>2026-08-06 14:01:34.968573+09:00</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>27511</t>
+          <t>27551</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 기관장 주도 국민 체감 성과 혁신 체계 가동</t>
+          <t>한국인터넷진흥원, 기업 맞춤형 사이버 위협 알림 서비스 개시</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2623&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2624&amp;page=1</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3003,34 +3003,34 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-08-05 09:16:33.823896+09:00</t>
+          <t>2026-08-05 09:46:34.063806+09:00</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-08-05 09:16:33.823896+09:00</t>
+          <t>2026-08-05 09:46:34.063806+09:00</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>27268</t>
+          <t>27511</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>975</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>양자내성암호 국제 표준화 동향 분석</t>
+          <t>한국인터넷진흥원, 기관장 주도 국민 체감 성과 혁신 체계 가동</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3736&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2623&amp;page=1</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3040,7 +3040,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>263</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3051,24 +3051,24 @@
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-08-04 16:31:26.502205+09:00</t>
+          <t>2026-08-05 09:16:33.823896+09:00</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-08-04 16:31:26.502205+09:00</t>
+          <t>2026-08-05 09:16:33.823896+09:00</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>27128</t>
+          <t>27268</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 20회차 교육생 모집(~9.4)</t>
+          <t>양자내성암호 국제 표준화 동향 분석</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3735&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3736&amp;page=1</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
@@ -3109,19 +3109,19 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2026-08-04 14:46:28.764255+09:00</t>
+          <t>2026-08-04 16:31:26.502205+09:00</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-08-04 14:46:28.764255+09:00</t>
+          <t>2026-08-04 16:31:26.502205+09:00</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>26211</t>
+          <t>27128</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3131,50 +3131,50 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 암호모듈검증 위한 시험 전문인력 양성</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 20회차 교육생 모집(~9.4)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2622&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3735&amp;page=1</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2026-08-03 13:31:41.722921+09:00</t>
+          <t>2026-08-04 14:46:28.764255+09:00</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-08-03 13:31:41.722921+09:00</t>
+          <t>2026-08-04 14:46:28.764255+09:00</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>26188</t>
+          <t>26211</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026년 8차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(8월 추천) (~8.21(금) 18시까지)</t>
+          <t>한국인터넷진흥원, 암호모듈검증 위한 시험 전문인력 양성</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3734&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2622&amp;page=1</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3199,7 +3199,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>273</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3210,24 +3210,24 @@
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2026-08-03 13:16:30.325331+09:00</t>
+          <t>2026-08-03 13:31:41.722921+09:00</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-08-03 13:16:30.325331+09:00</t>
+          <t>2026-08-03 13:31:41.722921+09:00</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>25891</t>
+          <t>26188</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 지역 상생 3대 사업 참여자 모집</t>
+          <t>2026년 8차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(8월 추천) (~8.21(금) 18시까지)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2621&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3734&amp;page=1</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3252,7 +3252,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3263,39 +3263,39 @@
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2026-08-03 09:31:46.854132+09:00</t>
+          <t>2026-08-03 13:16:30.325331+09:00</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-08-03 09:31:46.854132+09:00</t>
+          <t>2026-08-03 13:16:30.325331+09:00</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>25864</t>
+          <t>25891</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026년 전남광주통합특별시 소상공인·사회적경제기업 판로 확대 지원기업 선발 안내(~8.14)</t>
+          <t>한국인터넷진흥원, 지역 상생 3대 사업 참여자 모집</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3730&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2621&amp;page=1</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3305,7 +3305,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>80</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3313,31 +3313,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2026-08-03 09:16:35.817723+09:00</t>
+          <t>2026-08-03 09:31:46.854132+09:00</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-08-03 09:16:35.817723+09:00</t>
+          <t>2026-08-03 09:31:46.854132+09:00</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>25863</t>
+          <t>25864</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3347,12 +3343,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026년 전남광주통합특별시 지역문제 해결 프로젝트 공모전 개최 안내(~8.21)</t>
+          <t>2026년 전남광주통합특별시 소상공인·사회적경제기업 판로 확대 지원기업 선발 안내(~8.14)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3731&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3730&amp;page=1</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3362,7 +3358,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3394,7 +3390,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>25862</t>
+          <t>25863</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3404,12 +3400,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026년 한국인터넷진흥원 지역공부방 참여 대학생 장학금 지원자 모집 안내(~8.28)</t>
+          <t>2026년 전남광주통합특별시 지역문제 해결 프로젝트 공모전 개최 안내(~8.21)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3732&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3731&amp;page=1</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3419,7 +3415,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3451,7 +3447,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>25861</t>
+          <t>25862</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3461,12 +3457,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026년 암호모듈 시험자 양성교육 및 필기시험 안내(8.3~8.21)</t>
+          <t>2026년 한국인터넷진흥원 지역공부방 참여 대학생 장학금 지원자 모집 안내(~8.28)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3733&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3732&amp;page=1</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3476,7 +3472,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3508,7 +3504,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>23221</t>
+          <t>25861</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3518,22 +3514,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026년 블록체인 기업성장허브 입주기업 모집(~8월 27일(목) 16:00까지)</t>
+          <t>2026년 암호모듈 시험자 양성교육 및 필기시험 안내(8.3~8.21)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3729&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3733&amp;page=1</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3553,52 +3549,56 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>2026-07-30 17:16:54.540202+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-07-30 17:16:54.540202+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>22504</t>
+          <t>23221</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 19회차 교육생 모집(~8.28)</t>
+          <t>2026년 블록체인 기업성장허브 입주기업 모집(~8월 27일(목) 16:00까지)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3728&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3729&amp;page=1</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I59" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3606,19 +3606,19 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>2026-07-29 18:32:00.075123+09:00</t>
+          <t>2026-07-30 17:16:54.540202+09:00</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-07-29 18:32:00.075123+09:00</t>
+          <t>2026-07-30 17:16:54.540202+09:00</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>22464</t>
+          <t>22504</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3628,12 +3628,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026년 연계정보 이용기관 안전조치 실태점검 2차 설명회 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 19회차 교육생 모집(~8.28)</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3727&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3728&amp;page=1</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3643,7 +3643,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3659,19 +3659,19 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:59.875668+09:00</t>
+          <t>2026-07-29 18:32:00.075123+09:00</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:59.875668+09:00</t>
+          <t>2026-07-29 18:32:00.075123+09:00</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>20771</t>
+          <t>22464</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3681,50 +3681,50 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 성평등가족부와 불법·유해 정보 유통 대응 맞손</t>
+          <t>2026년 연계정보 이용기관 안전조치 실태점검 2차 설명회 개최</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2620&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3727&amp;page=1</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>2026-07-27 17:17:05.702970+09:00</t>
+          <t>2026-07-29 18:01:59.875668+09:00</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-07-27 17:17:05.702970+09:00</t>
+          <t>2026-07-29 18:01:59.875668+09:00</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>20191</t>
+          <t>20771</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 향후 10년 설계한다…전담 추진단(TF) 출범</t>
+          <t>한국인터넷진흥원, 성평등가족부와 불법·유해 정보 유통 대응 맞손</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2619&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2620&amp;page=1</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>150</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -3765,34 +3765,34 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2026-07-27 10:02:05.338547+09:00</t>
+          <t>2026-07-27 17:17:05.702970+09:00</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-07-27 10:02:05.338547+09:00</t>
+          <t>2026-07-27 17:17:05.702970+09:00</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>20061</t>
+          <t>20191</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(1차, BreakingPoint)</t>
+          <t>아피가(APIGA) 향후 10년 설계한다…전담 추진단(TF) 출범</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3726&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2619&amp;page=1</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>287</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -3810,64 +3810,64 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>2026-07-27 08:31:55.019743+09:00</t>
+          <t>2026-07-27 10:02:05.338547+09:00</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-07-27 08:31:55.019743+09:00</t>
+          <t>2026-07-27 10:02:05.338547+09:00</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>16785</t>
+          <t>20061</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 17회차 교육생 모집(~8.7)</t>
+          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(1차, BreakingPoint)</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3724&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3726&amp;page=1</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>246</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I64" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3875,34 +3875,34 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 08:31:55.019743+09:00</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 08:31:55.019743+09:00</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>16784</t>
+          <t>16785</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>1497</t>
+          <t>1496</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 18회차 교육생 모집(~8.21)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 17회차 교육생 모집(~8.7)</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3725&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3724&amp;page=1</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>236</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -3940,22 +3940,22 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>16781</t>
+          <t>16784</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1497</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 16회차 교육생 모집(~7.31)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 18회차 교육생 모집(~8.21)</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3723&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3725&amp;page=1</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>260</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -3973,11 +3973,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3997,22 +3993,22 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>16691</t>
+          <t>16781</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>'블록체인 기반 예금토큰 결제 인프라 확산' 사업 발대식 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 16회차 교육생 모집(~7.31)</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2618&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3723&amp;page=1</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4022,35 +4018,39 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>242</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>2026-07-22 17:32:01.526863+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-07-22 17:32:01.526863+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>16464</t>
+          <t>16691</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4060,12 +4060,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>[홍보] 정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 안내</t>
+          <t>'블록체인 기반 예금토큰 결제 인프라 확산' 사업 발대식 개최</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3722&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2618&amp;page=1</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4075,35 +4075,35 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>278</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>2026-07-22 14:46:48.687665+09:00</t>
+          <t>2026-07-22 17:32:01.526863+09:00</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-07-22 14:46:48.687665+09:00</t>
+          <t>2026-07-22 17:32:01.526863+09:00</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>16051</t>
+          <t>16464</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4113,12 +4113,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 보안 인재·글로벌 전문가 교류의 장 열어</t>
+          <t>[홍보] 정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 안내</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2617&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3722&amp;page=1</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4128,35 +4128,35 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>2026-07-22 09:31:50.671841+09:00</t>
+          <t>2026-07-22 14:46:48.687665+09:00</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-07-22 09:31:50.671841+09:00</t>
+          <t>2026-07-22 14:46:48.687665+09:00</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>14611</t>
+          <t>16051</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4166,22 +4166,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
+          <t>한국인터넷진흥원, 보안 인재·글로벌 전문가 교류의 장 열어</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2617&amp;page=1</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>233</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -4197,19 +4197,19 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>14431</t>
+          <t>14611</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>32</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -4250,34 +4250,34 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>14431</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4287,7 +4287,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>53</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -4295,56 +4295,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>14444</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>1493</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
+          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -4352,7 +4348,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr"/>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I73" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -4360,34 +4360,34 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>11331</t>
+          <t>14444</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4397,7 +4397,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -4408,96 +4408,92 @@
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>10981</t>
+          <t>11331</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
+          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>10943</t>
+          <t>10981</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
+          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -4507,7 +4503,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -4515,7 +4511,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr"/>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I76" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -4523,19 +4523,19 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>10663</t>
+          <t>10943</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
+          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
@@ -4576,19 +4576,19 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>9805</t>
+          <t>10663</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -4598,22 +4598,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
+          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -4629,19 +4629,19 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>9691</t>
+          <t>9805</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
+          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -4677,96 +4677,92 @@
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>9321</t>
+          <t>9691</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
+          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>8871</t>
+          <t>9321</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
+          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -4776,35 +4772,39 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>6685</t>
+          <t>8871</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -4814,22 +4814,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
+          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -4840,24 +4840,24 @@
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>6571</t>
+          <t>6685</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
+          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -4882,7 +4882,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -4893,24 +4893,24 @@
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>5591</t>
+          <t>6571</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4920,22 +4920,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
+          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -4951,44 +4951,44 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>5591</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
+          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>33</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -5004,44 +5004,44 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>4762</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>961</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>AI 보안 위협 대응 매뉴얼</t>
+          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -5049,31 +5049,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>4761</t>
+          <t>4762</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5083,12 +5079,12 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>AI 보안 레드티밍 가이드</t>
+          <t>AI 보안 위협 대응 매뉴얼</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5098,7 +5094,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -5130,22 +5126,22 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>4251</t>
+          <t>4761</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
+          <t>AI 보안 레드티밍 가이드</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5155,7 +5151,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -5163,27 +5159,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr"/>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>4251</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5193,12 +5193,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
+          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5208,113 +5208,113 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>191</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t>3867</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
+          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4111</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>959</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
+          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>34</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -5322,31 +5322,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -5356,12 +5352,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
+          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -5371,7 +5367,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -5403,32 +5399,32 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
+          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>105</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -5436,7 +5432,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr"/>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I93" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -5456,22 +5456,22 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1477</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
+          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>386</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -5509,22 +5509,22 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
+          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -5534,19 +5534,15 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>362</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -5566,7 +5562,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -5576,12 +5572,12 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2026년 IoT 보안인증 교육과정 안내</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -5591,7 +5587,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>522</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -5623,40 +5619,44 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
+          <t>2026년 IoT 보안인증 교육과정 안내</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>652</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I97" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -5676,22 +5676,22 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
+          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>1529</t>
+          <t>818</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -5709,11 +5709,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -5733,32 +5729,32 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
+          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>1529</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -5766,7 +5762,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr"/>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I99" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -5774,34 +5774,34 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>76426</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -5822,49 +5822,49 @@
       <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>958</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
+          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>55906</t>
+          <t>76426</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -5892,22 +5892,22 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>956</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
+          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>55329</t>
+          <t>55906</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -5945,32 +5945,32 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>957</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
+          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>34467</t>
+          <t>55329</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -5998,22 +5998,22 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>955</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
+          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6023,39 +6023,35 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2945</t>
+          <t>34467</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6065,27 +6061,27 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>2945</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6112,32 +6108,32 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>145255</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -6145,52 +6141,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr"/>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>954</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>26576</t>
+          <t>145255</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -6218,32 +6218,32 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>953</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
+          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>34290</t>
+          <t>26576</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -6271,32 +6271,32 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
+          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>184573</t>
+          <t>34290</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -6324,32 +6324,32 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>14403</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>951</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>6587</t>
+          <t>184573</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -6357,46 +6357,42 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14403</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
+          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -6406,7 +6402,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>51749</t>
+          <t>6587</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -6414,52 +6410,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr"/>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>950</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>78439</t>
+          <t>51749</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -6487,55 +6487,108 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>949</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>78439</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>보도자료</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
           <t>38805</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr">
+      <c r="B114" t="inlineStr">
         <is>
           <t>공지</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr">
+      <c r="C114" t="inlineStr">
         <is>
           <t>[공유] 지능형 CCTV 성능시험 재개 안내 공지</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr">
+      <c r="D114" t="inlineStr">
         <is>
           <t>https://www.kisa.or.kr/401/form?postSeq=3677&amp;page=1</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr">
+      <c r="E114" t="inlineStr">
         <is>
           <t>2026-06-02</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr">
+      <c r="F114" t="inlineStr">
         <is>
           <t>6525</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr">
+      <c r="G114" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
+      <c r="H114" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>공지사항</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
         <is>
           <t>2026-08-18 17:16:37.364015+09:00</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr">
+      <c r="K114" t="inlineStr">
         <is>
           <t>2026-08-18 17:16:37.364015+09:00</t>
         </is>

--- a/docs/snapshot/downloads/kisa.xlsx
+++ b/docs/snapshot/downloads/kisa.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K114"/>
+  <dimension ref="A1:K115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,22 +476,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>66888</t>
+          <t>70251</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>991</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>(행사 안내) 글로벌 AI 프라이버시 포럼 개최(9.29.)</t>
+          <t>인공지능(AI)·디지털 시대, 새로운 법적 문제 해법 찾는다</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3769&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2640&amp;page=1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -501,7 +501,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>25</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -512,24 +512,24 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-09-23 13:31:32.429525+09:00</t>
+          <t>2026-09-28 08:31:53.468509+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-09-23 13:31:32.429525+09:00</t>
+          <t>2026-09-28 08:31:53.468509+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>65988</t>
+          <t>66888</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -539,22 +539,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026년도 K-Cybersecurity Business Day in Japan 세미나(10/20) 참석 수요조사 안내</t>
+          <t>(행사 안내) 글로벌 AI 프라이버시 포럼 개최(9.29.)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3768&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3769&amp;page=1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -570,19 +570,19 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-09-22 10:01:34.273734+09:00</t>
+          <t>2026-09-23 13:31:32.429525+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-09-22 10:01:34.273734+09:00</t>
+          <t>2026-09-23 13:31:32.429525+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>65748</t>
+          <t>65988</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -592,27 +592,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 26회차 교육생 모집(~10.16)</t>
+          <t>2026년도 K-Cybersecurity Business Day in Japan 세미나(10/20) 참석 수요조사 안내</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3767&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3768&amp;page=1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -623,87 +623,87 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-09-21 17:01:40.203969+09:00</t>
+          <t>2026-09-22 10:01:34.273734+09:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-09-21 17:01:40.203969+09:00</t>
+          <t>2026-09-22 10:01:34.273734+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>64631</t>
+          <t>65748</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 인터넷 주소 자원 관리 역량 국제적 인정받아</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 26회차 교육생 모집(~10.16)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2639&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3767&amp;page=1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-09-20 12:01:47.233521+09:00</t>
+          <t>2026-09-21 17:01:40.203969+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-09-20 12:01:47.233521+09:00</t>
+          <t>2026-09-21 17:01:40.203969+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>63068</t>
+          <t>64631</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>990</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>대국민 혁신 정책·제안 공모전 개최</t>
+          <t>한국인터넷진흥원, 인터넷 주소 자원 관리 역량 국제적 인정받아</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3766&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2639&amp;page=1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -724,24 +724,24 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-09-18 10:46:37.266535+09:00</t>
+          <t>2026-09-20 12:01:47.233521+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-09-18 10:46:37.266535+09:00</t>
+          <t>2026-09-20 12:01:47.233521+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>63051</t>
+          <t>63068</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -751,12 +751,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>세계경제포럼·싱가포르 사이버보안청과 인공지능(AI) 위협 대비 사이버보안 협력 강화</t>
+          <t>대국민 혁신 정책·제안 공모전 개최</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2638&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3766&amp;page=1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -777,49 +777,49 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-09-18 10:31:43.770443+09:00</t>
+          <t>2026-09-18 10:46:37.266535+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-09-18 10:31:43.770443+09:00</t>
+          <t>2026-09-18 10:46:37.266535+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>62781</t>
+          <t>63051</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026년 블록체인 기업성장허브 입주기업 모집(~10월 7일(수) 16:00까지)</t>
+          <t>세계경제포럼·싱가포르 사이버보안청과 인공지능(AI) 위협 대비 사이버보안 협력 강화</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3765&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2638&amp;page=1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -827,46 +827,42 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-09-17 17:16:36.514530+09:00</t>
+          <t>2026-09-18 10:31:43.770443+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-09-17 17:16:36.514530+09:00</t>
+          <t>2026-09-18 10:31:43.770443+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>62507</t>
+          <t>62781</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 25회차 교육생 모집(~10.10)</t>
+          <t>2026년 블록체인 기업성장허브 입주기업 모집(~10월 7일(수) 16:00까지)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3764&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3765&amp;page=1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -876,15 +872,19 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -892,19 +892,19 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-09-17 13:31:33.789948+09:00</t>
+          <t>2026-09-17 17:16:36.514530+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-09-17 13:31:33.789948+09:00</t>
+          <t>2026-09-17 17:16:36.514530+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>62367</t>
+          <t>62507</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 24회차 교육생 모집(~10.9)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 25회차 교육생 모집(~10.10)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3763&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3764&amp;page=1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -945,19 +945,19 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-09-17 11:46:35.719751+09:00</t>
+          <t>2026-09-17 13:31:33.789948+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-09-17 11:46:35.719751+09:00</t>
+          <t>2026-09-17 13:31:33.789948+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>61484</t>
+          <t>62367</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -967,27 +967,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026년 제13회 소프트웨어(SW) 개발보안 경진대회 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 24회차 교육생 모집(~10.9)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3762&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3763&amp;page=1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
@@ -998,19 +998,19 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-09-16 09:46:37.058042+09:00</t>
+          <t>2026-09-17 11:46:35.719751+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-09-16 09:46:37.058042+09:00</t>
+          <t>2026-09-17 11:46:35.719751+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>61111</t>
+          <t>61484</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>민관 합동 ‘자동차 사이버 침해사고 대응 모의훈련’ 실시</t>
+          <t>2026년 제13회 소프트웨어(SW) 개발보안 경진대회 개최</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2637&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3762&amp;page=1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1046,24 +1046,24 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-09-15 15:01:52.747371+09:00</t>
+          <t>2026-09-16 09:46:37.058042+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-09-15 15:01:52.747371+09:00</t>
+          <t>2026-09-16 09:46:37.058042+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>61031</t>
+          <t>61111</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>“새로운 보안 위협, 인공지능(AI)으로 대응” 정보보호 제품 개발 기업 대상 보안 역량 강화 교육 추진</t>
+          <t>민관 합동 ‘자동차 사이버 침해사고 대응 모의훈련’ 실시</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2636&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2637&amp;page=1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1104,44 +1104,44 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-09-15 14:01:52.540884+09:00</t>
+          <t>2026-09-15 15:01:52.747371+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-09-15 14:01:52.540884+09:00</t>
+          <t>2026-09-15 15:01:52.747371+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>57381</t>
+          <t>61031</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026 전자문서 유공 포상 공고</t>
+          <t>“새로운 보안 위협, 인공지능(AI)으로 대응” 정보보호 제품 개발 기업 대상 보안 역량 강화 교육 추진</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3761&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2636&amp;page=1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1149,46 +1149,42 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-09-10 14:16:31.877229+09:00</t>
+          <t>2026-09-15 14:01:52.540884+09:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-09-10 14:16:31.877229+09:00</t>
+          <t>2026-09-15 14:01:52.540884+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>57149</t>
+          <t>57381</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026년 클라우드 서비스 보안인증(CSAP) 교육 안내</t>
+          <t>2026 전자문서 유공 포상 공고</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3760&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3761&amp;page=1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1198,7 +1194,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1206,7 +1202,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1214,19 +1214,19 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-09-10 10:46:38.794916+09:00</t>
+          <t>2026-09-10 14:16:31.877229+09:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-09-10 10:46:38.794916+09:00</t>
+          <t>2026-09-10 14:16:31.877229+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>56431</t>
+          <t>57149</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1236,22 +1236,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>보호나라 챗봇, 국민 생활 속 정보보호 성과 인정</t>
+          <t>2026년 클라우드 서비스 보안인증(CSAP) 교육 안내</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2634&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3760&amp;page=1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1262,92 +1262,92 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-09-09 12:01:35.142670+09:00</t>
+          <t>2026-09-10 10:46:38.794916+09:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-09-09 12:01:35.142670+09:00</t>
+          <t>2026-09-10 10:46:38.794916+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>56969</t>
+          <t>56431</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1522</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>온마이데이터 서비스 이용 이벤트 안내</t>
+          <t>보호나라 챗봇, 국민 생활 속 정보보호 성과 인정</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3758&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2634&amp;page=1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>402</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-09-10 08:31:37.677434+09:00</t>
+          <t>2026-09-09 12:01:35.142670+09:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-09-10 08:31:37.677434+09:00</t>
+          <t>2026-09-09 12:01:35.142670+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>54791</t>
+          <t>56969</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1522</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>국내 캐시 도메인이름시스템(DNS) 운영기관, 신규 암호키 반영 여부 확인하세요</t>
+          <t>온마이데이터 서비스 이용 이벤트 안내</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2633&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3758&amp;page=1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1357,60 +1357,60 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>402</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-09-07 12:01:35.243341+09:00</t>
+          <t>2026-09-10 08:31:37.677434+09:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-09-07 12:01:35.243341+09:00</t>
+          <t>2026-09-10 08:31:37.677434+09:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>54541</t>
+          <t>54791</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(2차, Avalanche)</t>
+          <t>국내 캐시 도메인이름시스템(DNS) 운영기관, 신규 암호키 반영 여부 확인하세요</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3759&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2633&amp;page=1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1418,31 +1418,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-09-07 09:01:25.516098+09:00</t>
+          <t>2026-09-07 12:01:35.243341+09:00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-09-07 09:01:25.516098+09:00</t>
+          <t>2026-09-07 12:01:35.243341+09:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>51281</t>
+          <t>54541</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1452,27 +1448,27 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>(행사 안내) 국외이전 제도 개선 및 CBPR 인증제도 기업 설명회 개최</t>
+          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(2차, Avalanche)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3757&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3759&amp;page=1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1487,52 +1483,56 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-09-03 09:16:26.856224+09:00</t>
+          <t>2026-09-07 09:01:25.516098+09:00</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-09-03 09:16:26.856224+09:00</t>
+          <t>2026-09-07 09:01:25.516098+09:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>56970</t>
+          <t>51281</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1521</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026 부산지역 도메인이름 분쟁해결 세미나 개최 안내(9.11)</t>
+          <t>(행사 안내) 국외이전 제도 개선 및 CBPR 인증제도 기업 설명회 개최</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3755&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3757&amp;page=1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>23</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1540,34 +1540,34 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-09-10 08:31:37.677434+09:00</t>
+          <t>2026-09-03 09:16:26.856224+09:00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-09-10 08:31:37.677434+09:00</t>
+          <t>2026-09-03 09:16:26.856224+09:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>51121</t>
+          <t>56970</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1521</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026년 블록체인 수요공급협의체(ABLE) 블록체인 수요기업(비금융분야) 모집 공고</t>
+          <t>2026 부산지역 도메인이름 분쟁해결 세미나 개최 안내(9.11)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3754&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3755&amp;page=1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>242</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1585,11 +1585,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1597,19 +1593,19 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-09-02 17:31:25.610368+09:00</t>
+          <t>2026-09-10 08:31:37.677434+09:00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-09-02 17:31:25.610368+09:00</t>
+          <t>2026-09-10 08:31:37.677434+09:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>50601</t>
+          <t>51121</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1619,12 +1615,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026년 9차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(9월 추천) (~9.18(금) 18시까지)</t>
+          <t>2026년 블록체인 수요공급협의체(ABLE) 블록체인 수요기업(비금융분야) 모집 공고</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3753&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3754&amp;page=1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1634,7 +1630,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>24</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1654,44 +1650,44 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-09-02 11:01:32.173328+09:00</t>
+          <t>2026-09-02 17:31:25.610368+09:00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-09-02 11:01:32.173328+09:00</t>
+          <t>2026-09-02 17:31:25.610368+09:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>49872</t>
+          <t>50601</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>인공지능(AI) 사이버 위협, 실전 모의훈련으로 대응</t>
+          <t>2026년 9차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(9월 추천) (~9.18(금) 18시까지)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2631&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3753&amp;page=1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1699,27 +1695,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-09-01 12:01:47.858504+09:00</t>
+          <t>2026-09-02 11:01:32.173328+09:00</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-09-01 12:01:47.858504+09:00</t>
+          <t>2026-09-02 11:01:32.173328+09:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>49669</t>
+          <t>49872</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>「2026 위치정보 맞춤형 컨설팅 참여기업 모집」</t>
+          <t>인공지능(AI) 사이버 위협, 실전 모의훈련으로 대응</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3752&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2631&amp;page=1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1744,35 +1744,35 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-09-01 09:31:38.715793+09:00</t>
+          <t>2026-09-01 12:01:47.858504+09:00</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-09-01 09:31:38.715793+09:00</t>
+          <t>2026-09-01 12:01:47.858504+09:00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>49631</t>
+          <t>49669</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1782,12 +1782,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>물리보안 시스템 간 연동 장벽 낮춘다</t>
+          <t>「2026 위치정보 맞춤형 컨설팅 참여기업 모집」</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2632&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3752&amp;page=1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1797,103 +1797,103 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-09-01 09:01:45.980040+09:00</t>
+          <t>2026-09-01 09:31:38.715793+09:00</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-09-01 09:01:45.980040+09:00</t>
+          <t>2026-09-01 09:31:38.715793+09:00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>49589</t>
+          <t>49631</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1517</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 23회차 교육생 모집(~9.18)</t>
+          <t>물리보안 시스템 간 연동 장벽 낮춘다</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3751&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2632&amp;page=1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-09-01 08:31:37.253592+09:00</t>
+          <t>2026-09-01 09:01:45.980040+09:00</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-09-01 08:31:37.253592+09:00</t>
+          <t>2026-09-01 09:01:45.980040+09:00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>48831</t>
+          <t>49589</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1517</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>생성형 인공지능(AI) 기반 실전형 모의해킹 대회 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 23회차 교육생 모집(~9.18)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2630&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3751&amp;page=1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1903,35 +1903,35 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>174</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-08-31 09:16:38.866405+09:00</t>
+          <t>2026-09-01 08:31:37.253592+09:00</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-08-31 09:16:38.866405+09:00</t>
+          <t>2026-09-01 08:31:37.253592+09:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>46011</t>
+          <t>48831</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1941,22 +1941,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>자동차 노리는 사이버 위협, 한국인터넷진흥원-한국교통안전공단이 함께 대응한다</t>
+          <t>생성형 인공지능(AI) 기반 실전형 모의해킹 대회 개최</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2628&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2630&amp;page=1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1972,34 +1972,34 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-08-27 15:01:41.552844+09:00</t>
+          <t>2026-08-31 09:16:38.866405+09:00</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-08-27 15:01:41.552844+09:00</t>
+          <t>2026-08-31 09:16:38.866405+09:00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>45681</t>
+          <t>46011</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>싱가포르 현지 진출 지원 국내 블록체인 기업 모집(~9.16(수) 14시)</t>
+          <t>자동차 노리는 사이버 위협, 한국인터넷진흥원-한국교통안전공단이 함께 대응한다</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3750&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2628&amp;page=1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2017,56 +2017,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-08-27 11:01:31.314899+09:00</t>
+          <t>2026-08-27 15:01:41.552844+09:00</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-08-27 11:01:31.314899+09:00</t>
+          <t>2026-08-27 15:01:41.552844+09:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>45191</t>
+          <t>45681</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 아·태 지역 사이버공격 대응 공동 훈련 실시</t>
+          <t>싱가포르 현지 진출 지원 국내 블록체인 기업 모집(~9.16(수) 14시)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2629&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3750&amp;page=1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2074,42 +2070,46 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-08-26 15:01:47.261933+09:00</t>
+          <t>2026-08-27 11:01:31.314899+09:00</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-08-26 15:01:47.261933+09:00</t>
+          <t>2026-08-27 11:01:31.314899+09:00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>44741</t>
+          <t>45191</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>[3차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~9/16)</t>
+          <t>한국인터넷진흥원, 아·태 지역 사이버공격 대응 공동 훈련 실시</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3749&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2629&amp;page=1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2127,56 +2127,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-08-26 09:31:36.427758+09:00</t>
+          <t>2026-08-26 15:01:47.261933+09:00</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-08-26 09:31:36.427758+09:00</t>
+          <t>2026-08-26 15:01:47.261933+09:00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>44448</t>
+          <t>44741</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 공고</t>
+          <t>[3차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~9/16)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3748&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3749&amp;page=1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2184,7 +2180,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2192,19 +2192,19 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-08-25 16:01:39.626193+09:00</t>
+          <t>2026-08-26 09:31:36.427758+09:00</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-08-25 16:01:39.626193+09:00</t>
+          <t>2026-08-26 09:31:36.427758+09:00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>43767</t>
+          <t>44448</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2214,27 +2214,27 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 21회차 교육생 모집(~9.12)</t>
+          <t>정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 공고</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3747&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3748&amp;page=1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
@@ -2245,19 +2245,19 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-08-24 17:46:42.254577+09:00</t>
+          <t>2026-08-25 16:01:39.626193+09:00</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-08-24 17:46:42.254577+09:00</t>
+          <t>2026-08-25 16:01:39.626193+09:00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>43311</t>
+          <t>43767</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>양자내성암호 전환, 어떻게 준비해야 할까?</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 21회차 교육생 모집(~9.12)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2627&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3747&amp;page=1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2282,50 +2282,50 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-08-24 12:01:45.511381+09:00</t>
+          <t>2026-08-24 17:46:42.254577+09:00</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-08-24 12:01:45.511381+09:00</t>
+          <t>2026-08-24 17:46:42.254577+09:00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>43301</t>
+          <t>43311</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>양자내성암호 전문교육 PQC 실무과정 교육생 모집(8.24~)</t>
+          <t>양자내성암호 전환, 어떻게 준비해야 할까?</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3746&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2627&amp;page=1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2343,31 +2343,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-08-24 12:01:36.271108+09:00</t>
+          <t>2026-08-24 12:01:45.511381+09:00</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-08-24 12:01:36.271108+09:00</t>
+          <t>2026-08-24 12:01:45.511381+09:00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>41161</t>
+          <t>43301</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2377,27 +2373,27 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>「블록체인 기업 맞춤형 보안 고도화 지원」 기업 모집(~8/31)</t>
+          <t>양자내성암호 전문교육 PQC 실무과정 교육생 모집(8.24~)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3745&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3746&amp;page=1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2412,34 +2408,34 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-08-21 16:01:38.087170+09:00</t>
+          <t>2026-08-24 12:01:36.271108+09:00</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-08-21 16:01:38.087170+09:00</t>
+          <t>2026-08-24 12:01:36.271108+09:00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>41086</t>
+          <t>41161</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026년도 인터넷거버넌스 민간전문가 APrIGF 및 IGF 참석자 모집</t>
+          <t>「블록체인 기업 맞춤형 보안 고도화 지원」 기업 모집(~8/31)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3744&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3745&amp;page=1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2449,15 +2445,19 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2465,19 +2465,19 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-08-21 15:01:32.139445+09:00</t>
+          <t>2026-08-21 16:01:38.087170+09:00</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-08-21 15:01:32.139445+09:00</t>
+          <t>2026-08-21 16:01:38.087170+09:00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>34750</t>
+          <t>41086</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2487,22 +2487,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>｢2026 블록체인 진흥주간｣ 전시부스 참가기업 모집 공고(~9.14)</t>
+          <t>2026년도 인터넷거버넌스 민간전문가 APrIGF 및 IGF 참석자 모집</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3743&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3744&amp;page=1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>59</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2518,34 +2518,34 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-08-13 17:46:21.938331+09:00</t>
+          <t>2026-08-21 15:01:32.139445+09:00</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-08-13 17:46:21.938331+09:00</t>
+          <t>2026-08-21 15:01:32.139445+09:00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>34081</t>
+          <t>34750</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026년 하반기 정보보호 전문서비스 기업 지정에 관한 공고</t>
+          <t>｢2026 블록체인 진흥주간｣ 전시부스 참가기업 모집 공고(~9.14)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3742&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3743&amp;page=1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2555,7 +2555,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2563,11 +2563,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2575,44 +2571,44 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:24.927741+09:00</t>
+          <t>2026-08-13 17:46:21.938331+09:00</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:24.927741+09:00</t>
+          <t>2026-08-13 17:46:21.938331+09:00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>34071</t>
+          <t>34081</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>"예방 넘어 대응·복구까지" 랜섬웨어 전주기 대응 방안 논의한다</t>
+          <t>2026년 하반기 정보보호 전문서비스 기업 지정에 관한 공고</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2626&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3742&amp;page=1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2620,42 +2616,46 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-08-13 09:16:35.989405+09:00</t>
+          <t>2026-08-13 09:31:24.927741+09:00</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-08-13 09:16:35.989405+09:00</t>
+          <t>2026-08-13 09:31:24.927741+09:00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>33789</t>
+          <t>34071</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>978</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 21회차 교육생 모집(~9.11)</t>
+          <t>"예방 넘어 대응·복구까지" 랜섬웨어 전주기 대응 방안 논의한다</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3741&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2626&amp;page=1</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2665,35 +2665,35 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-08-12 16:01:25.579701+09:00</t>
+          <t>2026-08-13 09:16:35.989405+09:00</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-08-12 16:01:25.579701+09:00</t>
+          <t>2026-08-13 09:16:35.989405+09:00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>33749</t>
+          <t>33789</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2703,12 +2703,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026년도 블록체인 유공 포상 계획 공고 안내(~9.21 15:00 마감)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 21회차 교육생 모집(~9.11)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3740&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3741&amp;page=1</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2718,12 +2718,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
@@ -2734,44 +2734,44 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-08-12 15:31:25.306307+09:00</t>
+          <t>2026-08-12 16:01:25.579701+09:00</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-08-12 15:31:25.306307+09:00</t>
+          <t>2026-08-12 16:01:25.579701+09:00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>31741</t>
+          <t>33749</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026년 블록체인 수요-공급 협의체 (ABLE) 정례세미나 개최 안내(8.13.목)</t>
+          <t>2026년도 블록체인 유공 포상 계획 공고 안내(~9.21 15:00 마감)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3739&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3740&amp;page=1</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2779,11 +2779,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2791,52 +2787,56 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-08-10 11:01:30.246604+09:00</t>
+          <t>2026-08-12 15:31:25.306307+09:00</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-08-10 11:01:30.246604+09:00</t>
+          <t>2026-08-12 15:31:25.306307+09:00</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>29768</t>
+          <t>31741</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026년 블록체인 신뢰인프라(K-BTF) 활용·확산사업 공모 사전예고</t>
+          <t>2026년 블록체인 수요-공급 협의체 (ABLE) 정례세미나 개최 안내(8.13.목)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3738&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3739&amp;page=1</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I45" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2844,19 +2844,19 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2026-08-07 17:01:29.954014+09:00</t>
+          <t>2026-08-10 11:01:30.246604+09:00</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-08-07 17:01:29.954014+09:00</t>
+          <t>2026-08-10 11:01:30.246604+09:00</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>29728</t>
+          <t>29768</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2866,12 +2866,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026년도 블록체인 산업 실태조사 실시 및 협조 안내</t>
+          <t>2026년 블록체인 신뢰인프라(K-BTF) 활용·확산사업 공모 사전예고</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3737&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3738&amp;page=1</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2897,19 +2897,19 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2026-08-07 16:31:30.938844+09:00</t>
+          <t>2026-08-07 17:01:29.954014+09:00</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-08-07 16:31:30.938844+09:00</t>
+          <t>2026-08-07 17:01:29.954014+09:00</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>28711</t>
+          <t>29728</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2919,50 +2919,50 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원-나주시, 고교생 개인정보·정보보호 진로 탐색 지원</t>
+          <t>2026년도 블록체인 산업 실태조사 실시 및 협조 안내</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2625&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3737&amp;page=1</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2026-08-06 14:01:34.968573+09:00</t>
+          <t>2026-08-07 16:31:30.938844+09:00</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-08-06 14:01:34.968573+09:00</t>
+          <t>2026-08-07 16:31:30.938844+09:00</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>27551</t>
+          <t>28711</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2972,22 +2972,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 기업 맞춤형 사이버 위협 알림 서비스 개시</t>
+          <t>한국인터넷진흥원-나주시, 고교생 개인정보·정보보호 진로 탐색 지원</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2624&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2625&amp;page=1</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3003,44 +3003,44 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-08-05 09:46:34.063806+09:00</t>
+          <t>2026-08-06 14:01:34.968573+09:00</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-08-05 09:46:34.063806+09:00</t>
+          <t>2026-08-06 14:01:34.968573+09:00</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>27511</t>
+          <t>27551</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 기관장 주도 국민 체감 성과 혁신 체계 가동</t>
+          <t>한국인터넷진흥원, 기업 맞춤형 사이버 위협 알림 서비스 개시</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2623&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2624&amp;page=1</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3056,34 +3056,34 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-08-05 09:16:33.823896+09:00</t>
+          <t>2026-08-05 09:46:34.063806+09:00</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-08-05 09:16:33.823896+09:00</t>
+          <t>2026-08-05 09:46:34.063806+09:00</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>27268</t>
+          <t>27511</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>975</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>양자내성암호 국제 표준화 동향 분석</t>
+          <t>한국인터넷진흥원, 기관장 주도 국민 체감 성과 혁신 체계 가동</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3736&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2623&amp;page=1</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>263</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3104,24 +3104,24 @@
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2026-08-04 16:31:26.502205+09:00</t>
+          <t>2026-08-05 09:16:33.823896+09:00</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-08-04 16:31:26.502205+09:00</t>
+          <t>2026-08-05 09:16:33.823896+09:00</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>27128</t>
+          <t>27268</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 20회차 교육생 모집(~9.4)</t>
+          <t>양자내성암호 국제 표준화 동향 분석</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3735&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3736&amp;page=1</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
@@ -3162,19 +3162,19 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2026-08-04 14:46:28.764255+09:00</t>
+          <t>2026-08-04 16:31:26.502205+09:00</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-08-04 14:46:28.764255+09:00</t>
+          <t>2026-08-04 16:31:26.502205+09:00</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>26211</t>
+          <t>27128</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3184,50 +3184,50 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 암호모듈검증 위한 시험 전문인력 양성</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 20회차 교육생 모집(~9.4)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2622&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3735&amp;page=1</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2026-08-03 13:31:41.722921+09:00</t>
+          <t>2026-08-04 14:46:28.764255+09:00</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-08-03 13:31:41.722921+09:00</t>
+          <t>2026-08-04 14:46:28.764255+09:00</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>26188</t>
+          <t>26211</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026년 8차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(8월 추천) (~8.21(금) 18시까지)</t>
+          <t>한국인터넷진흥원, 암호모듈검증 위한 시험 전문인력 양성</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3734&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2622&amp;page=1</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3252,7 +3252,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>273</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3263,24 +3263,24 @@
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2026-08-03 13:16:30.325331+09:00</t>
+          <t>2026-08-03 13:31:41.722921+09:00</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-08-03 13:16:30.325331+09:00</t>
+          <t>2026-08-03 13:31:41.722921+09:00</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>25891</t>
+          <t>26188</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 지역 상생 3대 사업 참여자 모집</t>
+          <t>2026년 8차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(8월 추천) (~8.21(금) 18시까지)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2621&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3734&amp;page=1</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3305,7 +3305,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3316,39 +3316,39 @@
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2026-08-03 09:31:46.854132+09:00</t>
+          <t>2026-08-03 13:16:30.325331+09:00</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-08-03 09:31:46.854132+09:00</t>
+          <t>2026-08-03 13:16:30.325331+09:00</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>25864</t>
+          <t>25891</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026년 전남광주통합특별시 소상공인·사회적경제기업 판로 확대 지원기업 선발 안내(~8.14)</t>
+          <t>한국인터넷진흥원, 지역 상생 3대 사업 참여자 모집</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3730&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2621&amp;page=1</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>80</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3366,31 +3366,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2026-08-03 09:16:35.817723+09:00</t>
+          <t>2026-08-03 09:31:46.854132+09:00</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-08-03 09:16:35.817723+09:00</t>
+          <t>2026-08-03 09:31:46.854132+09:00</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>25863</t>
+          <t>25864</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3400,12 +3396,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026년 전남광주통합특별시 지역문제 해결 프로젝트 공모전 개최 안내(~8.21)</t>
+          <t>2026년 전남광주통합특별시 소상공인·사회적경제기업 판로 확대 지원기업 선발 안내(~8.14)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3731&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3730&amp;page=1</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3415,7 +3411,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3447,7 +3443,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>25862</t>
+          <t>25863</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3457,12 +3453,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026년 한국인터넷진흥원 지역공부방 참여 대학생 장학금 지원자 모집 안내(~8.28)</t>
+          <t>2026년 전남광주통합특별시 지역문제 해결 프로젝트 공모전 개최 안내(~8.21)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3732&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3731&amp;page=1</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3472,7 +3468,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3504,7 +3500,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>25861</t>
+          <t>25862</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3514,12 +3510,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026년 암호모듈 시험자 양성교육 및 필기시험 안내(8.3~8.21)</t>
+          <t>2026년 한국인터넷진흥원 지역공부방 참여 대학생 장학금 지원자 모집 안내(~8.28)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3733&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3732&amp;page=1</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3529,7 +3525,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3561,7 +3557,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>23221</t>
+          <t>25861</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3571,22 +3567,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026년 블록체인 기업성장허브 입주기업 모집(~8월 27일(목) 16:00까지)</t>
+          <t>2026년 암호모듈 시험자 양성교육 및 필기시험 안내(8.3~8.21)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3729&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3733&amp;page=1</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3606,52 +3602,56 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>2026-07-30 17:16:54.540202+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-07-30 17:16:54.540202+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>22504</t>
+          <t>23221</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 19회차 교육생 모집(~8.28)</t>
+          <t>2026년 블록체인 기업성장허브 입주기업 모집(~8월 27일(목) 16:00까지)</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3728&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3729&amp;page=1</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I60" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3659,19 +3659,19 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>2026-07-29 18:32:00.075123+09:00</t>
+          <t>2026-07-30 17:16:54.540202+09:00</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-07-29 18:32:00.075123+09:00</t>
+          <t>2026-07-30 17:16:54.540202+09:00</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>22464</t>
+          <t>22504</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3681,12 +3681,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026년 연계정보 이용기관 안전조치 실태점검 2차 설명회 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 19회차 교육생 모집(~8.28)</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3727&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3728&amp;page=1</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3712,19 +3712,19 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:59.875668+09:00</t>
+          <t>2026-07-29 18:32:00.075123+09:00</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:59.875668+09:00</t>
+          <t>2026-07-29 18:32:00.075123+09:00</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>20771</t>
+          <t>22464</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3734,50 +3734,50 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 성평등가족부와 불법·유해 정보 유통 대응 맞손</t>
+          <t>2026년 연계정보 이용기관 안전조치 실태점검 2차 설명회 개최</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2620&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3727&amp;page=1</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2026-07-27 17:17:05.702970+09:00</t>
+          <t>2026-07-29 18:01:59.875668+09:00</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-07-27 17:17:05.702970+09:00</t>
+          <t>2026-07-29 18:01:59.875668+09:00</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>20191</t>
+          <t>20771</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3787,12 +3787,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 향후 10년 설계한다…전담 추진단(TF) 출범</t>
+          <t>한국인터넷진흥원, 성평등가족부와 불법·유해 정보 유통 대응 맞손</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2619&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2620&amp;page=1</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>150</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -3818,34 +3818,34 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>2026-07-27 10:02:05.338547+09:00</t>
+          <t>2026-07-27 17:17:05.702970+09:00</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-07-27 10:02:05.338547+09:00</t>
+          <t>2026-07-27 17:17:05.702970+09:00</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>20061</t>
+          <t>20191</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(1차, BreakingPoint)</t>
+          <t>아피가(APIGA) 향후 10년 설계한다…전담 추진단(TF) 출범</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3726&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2619&amp;page=1</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3855,7 +3855,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>287</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -3863,64 +3863,64 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>2026-07-27 08:31:55.019743+09:00</t>
+          <t>2026-07-27 10:02:05.338547+09:00</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-07-27 08:31:55.019743+09:00</t>
+          <t>2026-07-27 10:02:05.338547+09:00</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>16785</t>
+          <t>20061</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 17회차 교육생 모집(~8.7)</t>
+          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(1차, BreakingPoint)</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3724&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3726&amp;page=1</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>246</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I65" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3928,34 +3928,34 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 08:31:55.019743+09:00</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 08:31:55.019743+09:00</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>16784</t>
+          <t>16785</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>1497</t>
+          <t>1496</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 18회차 교육생 모집(~8.21)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 17회차 교육생 모집(~8.7)</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3725&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3724&amp;page=1</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>236</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -3993,22 +3993,22 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>16781</t>
+          <t>16784</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1497</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 16회차 교육생 모집(~7.31)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 18회차 교육생 모집(~8.21)</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3723&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3725&amp;page=1</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4018,7 +4018,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>260</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -4026,11 +4026,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -4050,22 +4046,22 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>16691</t>
+          <t>16781</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>'블록체인 기반 예금토큰 결제 인프라 확산' 사업 발대식 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 16회차 교육생 모집(~7.31)</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2618&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3723&amp;page=1</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4075,35 +4071,39 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>242</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>2026-07-22 17:32:01.526863+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-07-22 17:32:01.526863+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>16464</t>
+          <t>16691</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4113,12 +4113,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>[홍보] 정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 안내</t>
+          <t>'블록체인 기반 예금토큰 결제 인프라 확산' 사업 발대식 개최</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3722&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2618&amp;page=1</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4128,35 +4128,35 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>278</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>2026-07-22 14:46:48.687665+09:00</t>
+          <t>2026-07-22 17:32:01.526863+09:00</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-07-22 14:46:48.687665+09:00</t>
+          <t>2026-07-22 17:32:01.526863+09:00</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>16051</t>
+          <t>16464</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 보안 인재·글로벌 전문가 교류의 장 열어</t>
+          <t>[홍보] 정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 안내</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2617&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3722&amp;page=1</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4181,35 +4181,35 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>2026-07-22 09:31:50.671841+09:00</t>
+          <t>2026-07-22 14:46:48.687665+09:00</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-07-22 09:31:50.671841+09:00</t>
+          <t>2026-07-22 14:46:48.687665+09:00</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>14611</t>
+          <t>16051</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4219,22 +4219,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
+          <t>한국인터넷진흥원, 보안 인재·글로벌 전문가 교류의 장 열어</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2617&amp;page=1</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>233</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -4250,19 +4250,19 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>14431</t>
+          <t>14611</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4287,7 +4287,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>32</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -4303,34 +4303,34 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>14431</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>53</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -4348,56 +4348,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>14444</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>1493</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
+          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -4405,7 +4401,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr"/>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I74" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -4413,34 +4413,34 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>11331</t>
+          <t>14444</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4450,7 +4450,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -4461,96 +4461,92 @@
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>10981</t>
+          <t>11331</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
+          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>10943</t>
+          <t>10981</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
+          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -4560,7 +4556,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -4568,7 +4564,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr"/>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I77" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -4576,19 +4576,19 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>10663</t>
+          <t>10943</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -4598,12 +4598,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
+          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -4613,12 +4613,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
@@ -4629,19 +4629,19 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>9805</t>
+          <t>10663</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4651,22 +4651,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
+          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -4682,19 +4682,19 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>9691</t>
+          <t>9805</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -4704,12 +4704,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
+          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -4730,96 +4730,92 @@
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>9321</t>
+          <t>9691</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
+          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>8871</t>
+          <t>9321</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
+          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -4829,35 +4825,39 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>6685</t>
+          <t>8871</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4867,22 +4867,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
+          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -4893,24 +4893,24 @@
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>6571</t>
+          <t>6685</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4920,12 +4920,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
+          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -4935,7 +4935,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -4946,24 +4946,24 @@
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>5591</t>
+          <t>6571</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4973,22 +4973,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
+          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -5004,44 +5004,44 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>5591</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
+          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>33</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -5057,44 +5057,44 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>4762</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>961</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>AI 보안 위협 대응 매뉴얼</t>
+          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -5102,31 +5102,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>4761</t>
+          <t>4762</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5136,12 +5132,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>AI 보안 레드티밍 가이드</t>
+          <t>AI 보안 위협 대응 매뉴얼</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5151,7 +5147,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -5183,22 +5179,22 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>4251</t>
+          <t>4761</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
+          <t>AI 보안 레드티밍 가이드</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5208,7 +5204,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -5216,27 +5212,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr"/>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>4251</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
+          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5261,113 +5261,113 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>191</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t>3867</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
+          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4111</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>959</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
+          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>34</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -5375,31 +5375,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -5409,12 +5405,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
+          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -5424,7 +5420,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -5456,32 +5452,32 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
+          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>105</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -5489,7 +5485,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr"/>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I94" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -5509,22 +5509,22 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1477</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
+          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -5534,7 +5534,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>386</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -5562,22 +5562,22 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
+          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -5587,19 +5587,15 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>362</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -5619,7 +5615,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -5629,12 +5625,12 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2026년 IoT 보안인증 교육과정 안내</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -5644,7 +5640,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>522</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -5676,40 +5672,44 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
+          <t>2026년 IoT 보안인증 교육과정 안내</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>652</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I98" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -5729,22 +5729,22 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
+          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>1529</t>
+          <t>818</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -5762,11 +5762,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -5786,32 +5782,32 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
+          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>1529</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -5819,7 +5815,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr"/>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I100" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -5827,34 +5827,34 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -5864,7 +5864,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>76426</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -5875,49 +5875,49 @@
       <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>958</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
+          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>55906</t>
+          <t>76426</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -5945,22 +5945,22 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>956</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
+          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -5970,7 +5970,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>55329</t>
+          <t>55906</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -5998,32 +5998,32 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>957</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
+          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>34467</t>
+          <t>55329</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -6051,22 +6051,22 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>955</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
+          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -6076,39 +6076,35 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2945</t>
+          <t>34467</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6118,27 +6114,27 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>2945</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -6165,32 +6161,32 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>145255</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -6198,52 +6194,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr"/>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>954</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>26576</t>
+          <t>145255</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -6271,32 +6271,32 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>953</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
+          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>34290</t>
+          <t>26576</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -6324,32 +6324,32 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
+          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>184573</t>
+          <t>34290</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -6377,32 +6377,32 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>14403</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>951</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>6587</t>
+          <t>184573</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -6410,46 +6410,42 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14403</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
+          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -6459,7 +6455,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>51749</t>
+          <t>6587</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -6467,52 +6463,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr"/>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>950</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>78439</t>
+          <t>51749</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -6540,55 +6540,108 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>949</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>78439</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>보도자료</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
           <t>38805</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr">
+      <c r="B115" t="inlineStr">
         <is>
           <t>공지</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr">
+      <c r="C115" t="inlineStr">
         <is>
           <t>[공유] 지능형 CCTV 성능시험 재개 안내 공지</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr">
+      <c r="D115" t="inlineStr">
         <is>
           <t>https://www.kisa.or.kr/401/form?postSeq=3677&amp;page=1</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr">
+      <c r="E115" t="inlineStr">
         <is>
           <t>2026-06-02</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr">
+      <c r="F115" t="inlineStr">
         <is>
           <t>6525</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr">
+      <c r="G115" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
+      <c r="H115" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>공지사항</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr">
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
         <is>
           <t>2026-08-18 17:16:37.364015+09:00</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr">
+      <c r="K115" t="inlineStr">
         <is>
           <t>2026-08-18 17:16:37.364015+09:00</t>
         </is>

--- a/docs/snapshot/downloads/kisa.xlsx
+++ b/docs/snapshot/downloads/kisa.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K115"/>
+  <dimension ref="A1:K118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,60 +476,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>70251</t>
+          <t>70486</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>인공지능(AI)·디지털 시대, 새로운 법적 문제 해법 찾는다</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 27회차 교육생 모집(~10.23)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2640&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3771&amp;page=1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:31:53.468509+09:00</t>
+          <t>2026-09-28 12:01:47.314055+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:31:53.468509+09:00</t>
+          <t>2026-09-28 12:01:47.314055+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>66888</t>
+          <t>70485</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -539,27 +539,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>(행사 안내) 글로벌 AI 프라이버시 포럼 개최(9.29.)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 28회차 교육생 모집(~10.24)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3769&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3772&amp;page=1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -570,19 +570,19 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-09-23 13:31:32.429525+09:00</t>
+          <t>2026-09-28 12:01:47.314055+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-09-23 13:31:32.429525+09:00</t>
+          <t>2026-09-28 12:01:47.314055+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>65988</t>
+          <t>70465</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -592,27 +592,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026년도 K-Cybersecurity Business Day in Japan 세미나(10/20) 참석 수요조사 안내</t>
+          <t>「2026 블록체인 진흥주간」 취업 컨설팅 모집 안내(~10.30)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3768&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3770&amp;page=1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -623,97 +623,97 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-09-22 10:01:34.273734+09:00</t>
+          <t>2026-09-28 11:31:41.790745+09:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-09-22 10:01:34.273734+09:00</t>
+          <t>2026-09-28 11:31:41.790745+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>65748</t>
+          <t>70251</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>991</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 26회차 교육생 모집(~10.16)</t>
+          <t>인공지능(AI)·디지털 시대, 새로운 법적 문제 해법 찾는다</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3767&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2640&amp;page=1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-09-21 17:01:40.203969+09:00</t>
+          <t>2026-09-28 08:31:53.468509+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-09-21 17:01:40.203969+09:00</t>
+          <t>2026-09-28 08:31:53.468509+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>64631</t>
+          <t>66888</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 인터넷 주소 자원 관리 역량 국제적 인정받아</t>
+          <t>(행사 안내) 글로벌 AI 프라이버시 포럼 개최(9.29.)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2639&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3769&amp;page=1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -724,24 +724,24 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-09-20 12:01:47.233521+09:00</t>
+          <t>2026-09-23 13:31:32.429525+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-09-20 12:01:47.233521+09:00</t>
+          <t>2026-09-23 13:31:32.429525+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>63068</t>
+          <t>65988</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -751,22 +751,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>대국민 혁신 정책·제안 공모전 개최</t>
+          <t>2026년도 K-Cybersecurity Business Day in Japan 세미나(10/20) 참석 수요조사 안내</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3766&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3768&amp;page=1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -782,19 +782,19 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-09-18 10:46:37.266535+09:00</t>
+          <t>2026-09-22 10:01:34.273734+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-09-18 10:46:37.266535+09:00</t>
+          <t>2026-09-22 10:01:34.273734+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>63051</t>
+          <t>65748</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -804,75 +804,75 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>세계경제포럼·싱가포르 사이버보안청과 인공지능(AI) 위협 대비 사이버보안 협력 강화</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 26회차 교육생 모집(~10.16)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2638&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3767&amp;page=1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-09-18 10:31:43.770443+09:00</t>
+          <t>2026-09-21 17:01:40.203969+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-09-18 10:31:43.770443+09:00</t>
+          <t>2026-09-21 17:01:40.203969+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>62781</t>
+          <t>64631</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>990</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026년 블록체인 기업성장허브 입주기업 모집(~10월 7일(수) 16:00까지)</t>
+          <t>한국인터넷진흥원, 인터넷 주소 자원 관리 역량 국제적 인정받아</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3765&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2639&amp;page=1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -880,31 +880,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-09-17 17:16:36.514530+09:00</t>
+          <t>2026-09-20 12:01:47.233521+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-09-17 17:16:36.514530+09:00</t>
+          <t>2026-09-20 12:01:47.233521+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>62507</t>
+          <t>63068</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -914,27 +910,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 25회차 교육생 모집(~10.10)</t>
+          <t>대국민 혁신 정책·제안 공모전 개최</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3764&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3766&amp;page=1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
@@ -945,19 +941,19 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-09-17 13:31:33.789948+09:00</t>
+          <t>2026-09-18 10:46:37.266535+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-09-17 13:31:33.789948+09:00</t>
+          <t>2026-09-18 10:46:37.266535+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>62367</t>
+          <t>63051</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -967,75 +963,75 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 24회차 교육생 모집(~10.9)</t>
+          <t>세계경제포럼·싱가포르 사이버보안청과 인공지능(AI) 위협 대비 사이버보안 협력 강화</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3763&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2638&amp;page=1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-09-17 11:46:35.719751+09:00</t>
+          <t>2026-09-18 10:31:43.770443+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-09-17 11:46:35.719751+09:00</t>
+          <t>2026-09-18 10:31:43.770443+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>61484</t>
+          <t>62781</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026년 제13회 소프트웨어(SW) 개발보안 경진대회 개최</t>
+          <t>2026년 블록체인 기업성장허브 입주기업 모집(~10월 7일(수) 16:00까지)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3762&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3765&amp;page=1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1043,7 +1039,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1051,19 +1051,19 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-09-16 09:46:37.058042+09:00</t>
+          <t>2026-09-17 17:16:36.514530+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-09-16 09:46:37.058042+09:00</t>
+          <t>2026-09-17 17:16:36.514530+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>61111</t>
+          <t>62507</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1073,50 +1073,50 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>민관 합동 ‘자동차 사이버 침해사고 대응 모의훈련’ 실시</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 25회차 교육생 모집(~10.10)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2637&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3764&amp;page=1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-09-15 15:01:52.747371+09:00</t>
+          <t>2026-09-17 13:31:33.789948+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-09-15 15:01:52.747371+09:00</t>
+          <t>2026-09-17 13:31:33.789948+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>61031</t>
+          <t>62367</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1126,75 +1126,75 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>“새로운 보안 위협, 인공지능(AI)으로 대응” 정보보호 제품 개발 기업 대상 보안 역량 강화 교육 추진</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 24회차 교육생 모집(~10.9)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2636&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3763&amp;page=1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-09-15 14:01:52.540884+09:00</t>
+          <t>2026-09-17 11:46:35.719751+09:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-09-15 14:01:52.540884+09:00</t>
+          <t>2026-09-17 11:46:35.719751+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>57381</t>
+          <t>61484</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026 전자문서 유공 포상 공고</t>
+          <t>2026년 제13회 소프트웨어(SW) 개발보안 경진대회 개최</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3761&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3762&amp;page=1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>14</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1202,11 +1202,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1214,19 +1210,19 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-09-10 14:16:31.877229+09:00</t>
+          <t>2026-09-16 09:46:37.058042+09:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-09-10 14:16:31.877229+09:00</t>
+          <t>2026-09-16 09:46:37.058042+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>57149</t>
+          <t>61111</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1236,22 +1232,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026년 클라우드 서비스 보안인증(CSAP) 교육 안내</t>
+          <t>민관 합동 ‘자동차 사이버 침해사고 대응 모의훈련’ 실시</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3760&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2637&amp;page=1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1262,24 +1258,24 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-09-10 10:46:38.794916+09:00</t>
+          <t>2026-09-15 15:01:52.747371+09:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-09-10 10:46:38.794916+09:00</t>
+          <t>2026-09-15 15:01:52.747371+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>56431</t>
+          <t>61031</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1289,22 +1285,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>보호나라 챗봇, 국민 생활 속 정보보호 성과 인정</t>
+          <t>“새로운 보안 위협, 인공지능(AI)으로 대응” 정보보호 제품 개발 기업 대상 보안 역량 강화 교육 추진</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2634&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2636&amp;page=1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1320,52 +1316,56 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-09-09 12:01:35.142670+09:00</t>
+          <t>2026-09-15 14:01:52.540884+09:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-09-09 12:01:35.142670+09:00</t>
+          <t>2026-09-15 14:01:52.540884+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>56969</t>
+          <t>57381</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1522</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>온마이데이터 서비스 이용 이벤트 안내</t>
+          <t>2026 전자문서 유공 포상 공고</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3758&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3761&amp;page=1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>402</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1373,19 +1373,19 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-09-10 08:31:37.677434+09:00</t>
+          <t>2026-09-10 14:16:31.877229+09:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-09-10 08:31:37.677434+09:00</t>
+          <t>2026-09-10 14:16:31.877229+09:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>54791</t>
+          <t>57149</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1395,22 +1395,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>국내 캐시 도메인이름시스템(DNS) 운영기관, 신규 암호키 반영 여부 확인하세요</t>
+          <t>2026년 클라우드 서비스 보안인증(CSAP) 교육 안내</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2633&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3760&amp;page=1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1421,49 +1421,49 @@
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-09-07 12:01:35.243341+09:00</t>
+          <t>2026-09-10 10:46:38.794916+09:00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-09-07 12:01:35.243341+09:00</t>
+          <t>2026-09-10 10:46:38.794916+09:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>54541</t>
+          <t>56431</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(2차, Avalanche)</t>
+          <t>보호나라 챗봇, 국민 생활 속 정보보호 성과 인정</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3759&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2634&amp;page=1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1471,56 +1471,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-09-07 09:01:25.516098+09:00</t>
+          <t>2026-09-09 12:01:35.142670+09:00</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-09-07 09:01:25.516098+09:00</t>
+          <t>2026-09-09 12:01:35.142670+09:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>51281</t>
+          <t>56969</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1522</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>(행사 안내) 국외이전 제도 개선 및 CBPR 인증제도 기업 설명회 개최</t>
+          <t>온마이데이터 서비스 이용 이벤트 안내</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3757&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3758&amp;page=1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>402</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1528,11 +1524,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1540,44 +1532,44 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-09-03 09:16:26.856224+09:00</t>
+          <t>2026-09-10 08:31:37.677434+09:00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-09-03 09:16:26.856224+09:00</t>
+          <t>2026-09-10 08:31:37.677434+09:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>56970</t>
+          <t>54791</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1521</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026 부산지역 도메인이름 분쟁해결 세미나 개최 안내(9.11)</t>
+          <t>국내 캐시 도메인이름시스템(DNS) 운영기관, 신규 암호키 반영 여부 확인하세요</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3755&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2633&amp;page=1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1588,24 +1580,24 @@
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-09-10 08:31:37.677434+09:00</t>
+          <t>2026-09-07 12:01:35.243341+09:00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-09-10 08:31:37.677434+09:00</t>
+          <t>2026-09-07 12:01:35.243341+09:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>51121</t>
+          <t>54541</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1615,22 +1607,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026년 블록체인 수요공급협의체(ABLE) 블록체인 수요기업(비금융분야) 모집 공고</t>
+          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(2차, Avalanche)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3754&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3759&amp;page=1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1650,19 +1642,19 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-09-02 17:31:25.610368+09:00</t>
+          <t>2026-09-07 09:01:25.516098+09:00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-09-02 17:31:25.610368+09:00</t>
+          <t>2026-09-07 09:01:25.516098+09:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>50601</t>
+          <t>51281</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1672,27 +1664,27 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026년 9차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(9월 추천) (~9.18(금) 18시까지)</t>
+          <t>(행사 안내) 국외이전 제도 개선 및 CBPR 인증제도 기업 설명회 개최</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3753&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3757&amp;page=1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>23</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1707,44 +1699,44 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-09-02 11:01:32.173328+09:00</t>
+          <t>2026-09-03 09:16:26.856224+09:00</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-09-02 11:01:32.173328+09:00</t>
+          <t>2026-09-03 09:16:26.856224+09:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>49872</t>
+          <t>56970</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1521</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>인공지능(AI) 사이버 위협, 실전 모의훈련으로 대응</t>
+          <t>2026 부산지역 도메인이름 분쟁해결 세미나 개최 안내(9.11)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2631&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3755&amp;page=1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>242</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1755,57 +1747,61 @@
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-09-01 12:01:47.858504+09:00</t>
+          <t>2026-09-10 08:31:37.677434+09:00</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-09-01 12:01:47.858504+09:00</t>
+          <t>2026-09-10 08:31:37.677434+09:00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>49669</t>
+          <t>51121</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>「2026 위치정보 맞춤형 컨설팅 참여기업 모집」</t>
+          <t>2026년 블록체인 수요공급협의체(ABLE) 블록체인 수요기업(비금융분야) 모집 공고</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3752&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3754&amp;page=1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>24</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1813,44 +1809,44 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-09-01 09:31:38.715793+09:00</t>
+          <t>2026-09-02 17:31:25.610368+09:00</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-09-01 09:31:38.715793+09:00</t>
+          <t>2026-09-02 17:31:25.610368+09:00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>49631</t>
+          <t>50601</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>물리보안 시스템 간 연동 장벽 낮춘다</t>
+          <t>2026년 9차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(9월 추천) (~9.18(금) 18시까지)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2632&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3753&amp;page=1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1858,80 +1854,84 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-09-01 09:01:45.980040+09:00</t>
+          <t>2026-09-02 11:01:32.173328+09:00</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-09-01 09:01:45.980040+09:00</t>
+          <t>2026-09-02 11:01:32.173328+09:00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>49589</t>
+          <t>49872</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1517</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 23회차 교육생 모집(~9.18)</t>
+          <t>인공지능(AI) 사이버 위협, 실전 모의훈련으로 대응</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3751&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2631&amp;page=1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-09-01 08:31:37.253592+09:00</t>
+          <t>2026-09-01 12:01:47.858504+09:00</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-09-01 08:31:37.253592+09:00</t>
+          <t>2026-09-01 12:01:47.858504+09:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>48831</t>
+          <t>49669</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1941,50 +1941,50 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>생성형 인공지능(AI) 기반 실전형 모의해킹 대회 개최</t>
+          <t>「2026 위치정보 맞춤형 컨설팅 참여기업 모집」</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2630&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3752&amp;page=1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-08-31 09:16:38.866405+09:00</t>
+          <t>2026-09-01 09:31:38.715793+09:00</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-08-31 09:16:38.866405+09:00</t>
+          <t>2026-09-01 09:31:38.715793+09:00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>46011</t>
+          <t>49631</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1994,22 +1994,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>자동차 노리는 사이버 위협, 한국인터넷진흥원-한국교통안전공단이 함께 대응한다</t>
+          <t>물리보안 시스템 간 연동 장벽 낮춘다</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2628&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2632&amp;page=1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2025,56 +2025,52 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-08-27 15:01:41.552844+09:00</t>
+          <t>2026-09-01 09:01:45.980040+09:00</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-08-27 15:01:41.552844+09:00</t>
+          <t>2026-09-01 09:01:45.980040+09:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>45681</t>
+          <t>49589</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1517</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>싱가포르 현지 진출 지원 국내 블록체인 기업 모집(~9.16(수) 14시)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 23회차 교육생 모집(~9.18)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3750&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3751&amp;page=1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>174</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2082,19 +2078,19 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-08-27 11:01:31.314899+09:00</t>
+          <t>2026-09-01 08:31:37.253592+09:00</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-08-27 11:01:31.314899+09:00</t>
+          <t>2026-09-01 08:31:37.253592+09:00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>45191</t>
+          <t>48831</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2104,22 +2100,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 아·태 지역 사이버공격 대응 공동 훈련 실시</t>
+          <t>생성형 인공지능(AI) 기반 실전형 모의해킹 대회 개최</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2629&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2630&amp;page=1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2135,44 +2131,44 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-08-26 15:01:47.261933+09:00</t>
+          <t>2026-08-31 09:16:38.866405+09:00</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-08-26 15:01:47.261933+09:00</t>
+          <t>2026-08-31 09:16:38.866405+09:00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>44741</t>
+          <t>46011</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>[3차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~9/16)</t>
+          <t>자동차 노리는 사이버 위협, 한국인터넷진흥원-한국교통안전공단이 함께 대응한다</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3749&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2628&amp;page=1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2180,56 +2176,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-08-26 09:31:36.427758+09:00</t>
+          <t>2026-08-27 15:01:41.552844+09:00</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-08-26 09:31:36.427758+09:00</t>
+          <t>2026-08-27 15:01:41.552844+09:00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>44448</t>
+          <t>45681</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 공고</t>
+          <t>싱가포르 현지 진출 지원 국내 블록체인 기업 모집(~9.16(수) 14시)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3748&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3750&amp;page=1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2237,7 +2229,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2245,19 +2241,19 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-08-25 16:01:39.626193+09:00</t>
+          <t>2026-08-27 11:01:31.314899+09:00</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-08-25 16:01:39.626193+09:00</t>
+          <t>2026-08-27 11:01:31.314899+09:00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>43767</t>
+          <t>45191</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2267,75 +2263,75 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 21회차 교육생 모집(~9.12)</t>
+          <t>한국인터넷진흥원, 아·태 지역 사이버공격 대응 공동 훈련 실시</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3747&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2629&amp;page=1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-08-24 17:46:42.254577+09:00</t>
+          <t>2026-08-26 15:01:47.261933+09:00</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-08-24 17:46:42.254577+09:00</t>
+          <t>2026-08-26 15:01:47.261933+09:00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>43311</t>
+          <t>44741</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>양자내성암호 전환, 어떻게 준비해야 할까?</t>
+          <t>[3차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~9/16)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2627&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3749&amp;page=1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2343,52 +2339,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-08-24 12:01:45.511381+09:00</t>
+          <t>2026-08-26 09:31:36.427758+09:00</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-08-24 12:01:45.511381+09:00</t>
+          <t>2026-08-26 09:31:36.427758+09:00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>43301</t>
+          <t>44448</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>양자내성암호 전문교육 PQC 실무과정 교육생 모집(8.24~)</t>
+          <t>정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 공고</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3746&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3748&amp;page=1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2396,11 +2396,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2408,44 +2404,44 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-08-24 12:01:36.271108+09:00</t>
+          <t>2026-08-25 16:01:39.626193+09:00</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-08-24 12:01:36.271108+09:00</t>
+          <t>2026-08-25 16:01:39.626193+09:00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>41161</t>
+          <t>43767</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>「블록체인 기업 맞춤형 보안 고도화 지원」 기업 모집(~8/31)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 21회차 교육생 모집(~9.12)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3745&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3747&amp;page=1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2453,11 +2449,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2465,19 +2457,19 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-08-21 16:01:38.087170+09:00</t>
+          <t>2026-08-24 17:46:42.254577+09:00</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-08-21 16:01:38.087170+09:00</t>
+          <t>2026-08-24 17:46:42.254577+09:00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>41086</t>
+          <t>43311</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2487,22 +2479,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026년도 인터넷거버넌스 민간전문가 APrIGF 및 IGF 참석자 모집</t>
+          <t>양자내성암호 전환, 어떻게 준비해야 할까?</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3744&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2627&amp;page=1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2513,49 +2505,49 @@
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-08-21 15:01:32.139445+09:00</t>
+          <t>2026-08-24 12:01:45.511381+09:00</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-08-21 15:01:32.139445+09:00</t>
+          <t>2026-08-24 12:01:45.511381+09:00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>34750</t>
+          <t>43301</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>｢2026 블록체인 진흥주간｣ 전시부스 참가기업 모집 공고(~9.14)</t>
+          <t>양자내성암호 전문교육 PQC 실무과정 교육생 모집(8.24~)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3743&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3746&amp;page=1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2563,7 +2555,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2571,19 +2567,19 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-08-13 17:46:21.938331+09:00</t>
+          <t>2026-08-24 12:01:36.271108+09:00</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-08-13 17:46:21.938331+09:00</t>
+          <t>2026-08-24 12:01:36.271108+09:00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>34081</t>
+          <t>41161</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2593,27 +2589,27 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026년 하반기 정보보호 전문서비스 기업 지정에 관한 공고</t>
+          <t>「블록체인 기업 맞춤형 보안 고도화 지원」 기업 모집(~8/31)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3742&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3745&amp;page=1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2628,44 +2624,44 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:24.927741+09:00</t>
+          <t>2026-08-21 16:01:38.087170+09:00</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:24.927741+09:00</t>
+          <t>2026-08-21 16:01:38.087170+09:00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>34071</t>
+          <t>41086</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>"예방 넘어 대응·복구까지" 랜섬웨어 전주기 대응 방안 논의한다</t>
+          <t>2026년도 인터넷거버넌스 민간전문가 APrIGF 및 IGF 참석자 모집</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2626&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3744&amp;page=1</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>59</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2676,24 +2672,24 @@
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-08-13 09:16:35.989405+09:00</t>
+          <t>2026-08-21 15:01:32.139445+09:00</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-08-13 09:16:35.989405+09:00</t>
+          <t>2026-08-21 15:01:32.139445+09:00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>33789</t>
+          <t>34750</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2703,27 +2699,27 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 21회차 교육생 모집(~9.11)</t>
+          <t>｢2026 블록체인 진흥주간｣ 전시부스 참가기업 모집 공고(~9.14)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3741&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3743&amp;page=1</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
@@ -2734,44 +2730,44 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-08-12 16:01:25.579701+09:00</t>
+          <t>2026-08-13 17:46:21.938331+09:00</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-08-12 16:01:25.579701+09:00</t>
+          <t>2026-08-13 17:46:21.938331+09:00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>33749</t>
+          <t>34081</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026년도 블록체인 유공 포상 계획 공고 안내(~9.21 15:00 마감)</t>
+          <t>2026년 하반기 정보보호 전문서비스 기업 지정에 관한 공고</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3740&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3742&amp;page=1</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2779,7 +2775,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I44" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -2787,44 +2787,44 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-08-12 15:31:25.306307+09:00</t>
+          <t>2026-08-13 09:31:24.927741+09:00</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-08-12 15:31:25.306307+09:00</t>
+          <t>2026-08-13 09:31:24.927741+09:00</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>31741</t>
+          <t>34071</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>978</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026년 블록체인 수요-공급 협의체 (ABLE) 정례세미나 개최 안내(8.13.목)</t>
+          <t>"예방 넘어 대응·복구까지" 랜섬웨어 전주기 대응 방안 논의한다</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3739&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2626&amp;page=1</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2832,31 +2832,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2026-08-10 11:01:30.246604+09:00</t>
+          <t>2026-08-13 09:16:35.989405+09:00</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-08-10 11:01:30.246604+09:00</t>
+          <t>2026-08-13 09:16:35.989405+09:00</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>29768</t>
+          <t>33789</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2866,22 +2862,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026년 블록체인 신뢰인프라(K-BTF) 활용·확산사업 공모 사전예고</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 21회차 교육생 모집(~9.11)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3738&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3741&amp;page=1</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2897,19 +2893,19 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2026-08-07 17:01:29.954014+09:00</t>
+          <t>2026-08-12 16:01:25.579701+09:00</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-08-07 17:01:29.954014+09:00</t>
+          <t>2026-08-12 16:01:25.579701+09:00</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>29728</t>
+          <t>33749</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2919,27 +2915,27 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026년도 블록체인 산업 실태조사 실시 및 협조 안내</t>
+          <t>2026년도 블록체인 유공 포상 계획 공고 안내(~9.21 15:00 마감)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3737&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3740&amp;page=1</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
@@ -2950,44 +2946,44 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2026-08-07 16:31:30.938844+09:00</t>
+          <t>2026-08-12 15:31:25.306307+09:00</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-08-07 16:31:30.938844+09:00</t>
+          <t>2026-08-12 15:31:25.306307+09:00</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>28711</t>
+          <t>31741</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원-나주시, 고교생 개인정보·정보보호 진로 탐색 지원</t>
+          <t>2026년 블록체인 수요-공급 협의체 (ABLE) 정례세미나 개최 안내(8.13.목)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2625&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3739&amp;page=1</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2995,27 +2991,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-08-06 14:01:34.968573+09:00</t>
+          <t>2026-08-10 11:01:30.246604+09:00</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-08-06 14:01:34.968573+09:00</t>
+          <t>2026-08-10 11:01:30.246604+09:00</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>27551</t>
+          <t>29768</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3025,103 +3025,103 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 기업 맞춤형 사이버 위협 알림 서비스 개시</t>
+          <t>2026년 블록체인 신뢰인프라(K-BTF) 활용·확산사업 공모 사전예고</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2624&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3738&amp;page=1</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-08-05 09:46:34.063806+09:00</t>
+          <t>2026-08-07 17:01:29.954014+09:00</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-08-05 09:46:34.063806+09:00</t>
+          <t>2026-08-07 17:01:29.954014+09:00</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>27511</t>
+          <t>29728</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 기관장 주도 국민 체감 성과 혁신 체계 가동</t>
+          <t>2026년도 블록체인 산업 실태조사 실시 및 협조 안내</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2623&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3737&amp;page=1</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2026-08-05 09:16:33.823896+09:00</t>
+          <t>2026-08-07 16:31:30.938844+09:00</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-08-05 09:16:33.823896+09:00</t>
+          <t>2026-08-07 16:31:30.938844+09:00</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>27268</t>
+          <t>28711</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3131,22 +3131,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>양자내성암호 국제 표준화 동향 분석</t>
+          <t>한국인터넷진흥원-나주시, 고교생 개인정보·정보보호 진로 탐색 지원</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3736&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2625&amp;page=1</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3157,24 +3157,24 @@
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2026-08-04 16:31:26.502205+09:00</t>
+          <t>2026-08-06 14:01:34.968573+09:00</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-08-04 16:31:26.502205+09:00</t>
+          <t>2026-08-06 14:01:34.968573+09:00</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>27128</t>
+          <t>27551</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3184,75 +3184,75 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 20회차 교육생 모집(~9.4)</t>
+          <t>한국인터넷진흥원, 기업 맞춤형 사이버 위협 알림 서비스 개시</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3735&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2624&amp;page=1</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2026-08-04 14:46:28.764255+09:00</t>
+          <t>2026-08-05 09:46:34.063806+09:00</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-08-04 14:46:28.764255+09:00</t>
+          <t>2026-08-05 09:46:34.063806+09:00</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>26211</t>
+          <t>27511</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>975</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 암호모듈검증 위한 시험 전문인력 양성</t>
+          <t>한국인터넷진흥원, 기관장 주도 국민 체감 성과 혁신 체계 가동</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2622&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2623&amp;page=1</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>263</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3268,19 +3268,19 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2026-08-03 13:31:41.722921+09:00</t>
+          <t>2026-08-05 09:16:33.823896+09:00</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-08-03 13:31:41.722921+09:00</t>
+          <t>2026-08-05 09:16:33.823896+09:00</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>26188</t>
+          <t>27268</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3290,17 +3290,17 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026년 8차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(8월 추천) (~8.21(금) 18시까지)</t>
+          <t>양자내성암호 국제 표준화 동향 분석</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3734&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3736&amp;page=1</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -3321,19 +3321,19 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2026-08-03 13:16:30.325331+09:00</t>
+          <t>2026-08-04 16:31:26.502205+09:00</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-08-03 13:16:30.325331+09:00</t>
+          <t>2026-08-04 16:31:26.502205+09:00</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>25891</t>
+          <t>27128</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3343,65 +3343,65 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 지역 상생 3대 사업 참여자 모집</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 20회차 교육생 모집(~9.4)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2621&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3735&amp;page=1</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2026-08-03 09:31:46.854132+09:00</t>
+          <t>2026-08-04 14:46:28.764255+09:00</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-08-03 09:31:46.854132+09:00</t>
+          <t>2026-08-04 14:46:28.764255+09:00</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>25864</t>
+          <t>26211</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026년 전남광주통합특별시 소상공인·사회적경제기업 판로 확대 지원기업 선발 안내(~8.14)</t>
+          <t>한국인터넷진흥원, 암호모듈검증 위한 시험 전문인력 양성</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3730&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2622&amp;page=1</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>273</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3419,46 +3419,42 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2026-08-03 09:16:35.817723+09:00</t>
+          <t>2026-08-03 13:31:41.722921+09:00</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-08-03 09:16:35.817723+09:00</t>
+          <t>2026-08-03 13:31:41.722921+09:00</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>25863</t>
+          <t>26188</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026년 전남광주통합특별시 지역문제 해결 프로젝트 공모전 개최 안내(~8.21)</t>
+          <t>2026년 8차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(8월 추천) (~8.21(금) 18시까지)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3731&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3734&amp;page=1</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3468,7 +3464,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3476,11 +3472,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3488,34 +3480,34 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2026-08-03 09:16:35.817723+09:00</t>
+          <t>2026-08-03 13:16:30.325331+09:00</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-08-03 09:16:35.817723+09:00</t>
+          <t>2026-08-03 13:16:30.325331+09:00</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>25862</t>
+          <t>25891</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026년 한국인터넷진흥원 지역공부방 참여 대학생 장학금 지원자 모집 안내(~8.28)</t>
+          <t>한국인터넷진흥원, 지역 상생 3대 사업 참여자 모집</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3732&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2621&amp;page=1</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3525,7 +3517,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>80</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3533,31 +3525,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>2026-08-03 09:16:35.817723+09:00</t>
+          <t>2026-08-03 09:31:46.854132+09:00</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-08-03 09:16:35.817723+09:00</t>
+          <t>2026-08-03 09:31:46.854132+09:00</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>25861</t>
+          <t>25864</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3567,12 +3555,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026년 암호모듈 시험자 양성교육 및 필기시험 안내(8.3~8.21)</t>
+          <t>2026년 전남광주통합특별시 소상공인·사회적경제기업 판로 확대 지원기업 선발 안내(~8.14)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3733&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3730&amp;page=1</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3582,7 +3570,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3614,7 +3602,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>23221</t>
+          <t>25863</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3624,22 +3612,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026년 블록체인 기업성장허브 입주기업 모집(~8월 27일(목) 16:00까지)</t>
+          <t>2026년 전남광주통합특별시 지역문제 해결 프로젝트 공모전 개최 안내(~8.21)</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3729&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3731&amp;page=1</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3659,52 +3647,56 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>2026-07-30 17:16:54.540202+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-07-30 17:16:54.540202+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>22504</t>
+          <t>25862</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 19회차 교육생 모집(~8.28)</t>
+          <t>2026년 한국인터넷진흥원 지역공부방 참여 대학생 장학금 지원자 모집 안내(~8.28)</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3728&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3732&amp;page=1</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I61" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3712,52 +3704,56 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>2026-07-29 18:32:00.075123+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-07-29 18:32:00.075123+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>22464</t>
+          <t>25861</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026년 연계정보 이용기관 안전조치 실태점검 2차 설명회 개최</t>
+          <t>2026년 암호모듈 시험자 양성교육 및 필기시험 안내(8.3~8.21)</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3727&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3733&amp;page=1</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I62" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3765,44 +3761,44 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:59.875668+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:59.875668+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>20771</t>
+          <t>23221</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 성평등가족부와 불법·유해 정보 유통 대응 맞손</t>
+          <t>2026년 블록체인 기업성장허브 입주기업 모집(~8월 27일(목) 16:00까지)</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2620&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3729&amp;page=1</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -3810,27 +3806,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr"/>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>2026-07-27 17:17:05.702970+09:00</t>
+          <t>2026-07-30 17:16:54.540202+09:00</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-07-27 17:17:05.702970+09:00</t>
+          <t>2026-07-30 17:16:54.540202+09:00</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>20191</t>
+          <t>22504</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3840,87 +3840,83 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 향후 10년 설계한다…전담 추진단(TF) 출범</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 19회차 교육생 모집(~8.28)</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2619&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3728&amp;page=1</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>2026-07-27 10:02:05.338547+09:00</t>
+          <t>2026-07-29 18:32:00.075123+09:00</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-07-27 10:02:05.338547+09:00</t>
+          <t>2026-07-29 18:32:00.075123+09:00</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>20061</t>
+          <t>22464</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(1차, BreakingPoint)</t>
+          <t>2026년 연계정보 이용기관 안전조치 실태점검 2차 설명회 개최</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3726&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3727&amp;page=1</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -3928,125 +3924,125 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>2026-07-27 08:31:55.019743+09:00</t>
+          <t>2026-07-29 18:01:59.875668+09:00</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-07-27 08:31:55.019743+09:00</t>
+          <t>2026-07-29 18:01:59.875668+09:00</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>16785</t>
+          <t>20771</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 17회차 교육생 모집(~8.7)</t>
+          <t>한국인터넷진흥원, 성평등가족부와 불법·유해 정보 유통 대응 맞손</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3724&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2620&amp;page=1</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>150</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 17:17:05.702970+09:00</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 17:17:05.702970+09:00</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>16784</t>
+          <t>20191</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>1497</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 18회차 교육생 모집(~8.21)</t>
+          <t>아피가(APIGA) 향후 10년 설계한다…전담 추진단(TF) 출범</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3725&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2619&amp;page=1</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>287</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 10:02:05.338547+09:00</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 10:02:05.338547+09:00</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>16781</t>
+          <t>20061</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4056,27 +4052,27 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 16회차 교육생 모집(~7.31)</t>
+          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(1차, BreakingPoint)</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3723&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3726&amp;page=1</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>246</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4091,34 +4087,34 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 08:31:55.019743+09:00</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 08:31:55.019743+09:00</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>16691</t>
+          <t>16785</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1496</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>'블록체인 기반 예금토큰 결제 인프라 확산' 사업 발대식 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 17회차 교육생 모집(~8.7)</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2618&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3724&amp;page=1</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4128,50 +4124,50 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>236</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>2026-07-22 17:32:01.526863+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-07-22 17:32:01.526863+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>16464</t>
+          <t>16784</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1497</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>[홍보] 정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 안내</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 18회차 교육생 모집(~8.21)</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3722&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3725&amp;page=1</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4181,7 +4177,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>260</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -4197,34 +4193,34 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>2026-07-22 14:46:48.687665+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-07-22 14:46:48.687665+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>16051</t>
+          <t>16781</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 보안 인재·글로벌 전문가 교류의 장 열어</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 16회차 교육생 모집(~7.31)</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2617&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3723&amp;page=1</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4234,35 +4230,39 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>242</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>2026-07-22 09:31:50.671841+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-07-22 09:31:50.671841+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>14611</t>
+          <t>16691</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4272,22 +4272,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
+          <t>'블록체인 기반 예금토큰 결제 인프라 확산' 사업 발대식 개최</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2618&amp;page=1</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>278</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -4303,19 +4303,19 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-22 17:32:01.526863+09:00</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-22 17:32:01.526863+09:00</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>14431</t>
+          <t>16464</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4325,75 +4325,75 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>[홍보] 정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 안내</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3722&amp;page=1</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-22 14:46:48.687665+09:00</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-22 14:46:48.687665+09:00</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>16051</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>한국인터넷진흥원, 보안 인재·글로벌 전문가 교류의 장 열어</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2617&amp;page=1</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>233</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -4401,56 +4401,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>14444</t>
+          <t>14611</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>1493</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
+          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>32</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -4461,24 +4457,24 @@
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>11331</t>
+          <t>14431</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -4488,22 +4484,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>53</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -4519,19 +4515,19 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>10981</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -4541,17 +4537,17 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
+          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -4561,7 +4557,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -4576,49 +4572,49 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>10943</t>
+          <t>14444</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
@@ -4629,19 +4625,19 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>10663</t>
+          <t>11331</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4651,22 +4647,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
+          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -4677,57 +4673,61 @@
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>9805</t>
+          <t>10981</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
+          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I80" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -4735,19 +4735,19 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>9691</t>
+          <t>10943</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4757,87 +4757,83 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
+          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>9321</t>
+          <t>10663</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
+          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -4845,19 +4841,19 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>8871</t>
+          <t>9805</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4867,22 +4863,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
+          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -4893,24 +4889,24 @@
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>6685</t>
+          <t>9691</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4920,22 +4916,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
+          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -4946,77 +4942,81 @@
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>6571</t>
+          <t>9321</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
+          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>5591</t>
+          <t>8871</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5026,22 +5026,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
+          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -5057,44 +5057,44 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>6685</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
+          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -5105,49 +5105,49 @@
       <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>4762</t>
+          <t>6571</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>AI 보안 위협 대응 매뉴얼</t>
+          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -5155,56 +5155,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>4761</t>
+          <t>5591</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>AI 보안 레드티밍 가이드</t>
+          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>33</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -5212,56 +5208,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>4251</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>961</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
+          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -5277,34 +5269,34 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>4762</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
+          <t>AI 보안 위협 대응 매뉴얼</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5314,15 +5306,19 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I91" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -5330,44 +5326,44 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t>4761</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
+          <t>AI 보안 레드티밍 가이드</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -5375,52 +5371,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr"/>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4251</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
+          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>191</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -5428,68 +5428,60 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3867</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
+          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -5497,44 +5489,44 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4111</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>959</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
+          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>34</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -5545,49 +5537,49 @@
       <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
+          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -5595,7 +5587,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr"/>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I96" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -5615,7 +5611,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -5625,27 +5621,27 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
+          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>105</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -5672,22 +5668,22 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1477</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2026년 IoT 보안인증 교육과정 안내</t>
+          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -5697,19 +5693,15 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>386</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -5729,32 +5721,32 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
+          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>362</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -5782,7 +5774,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -5792,27 +5784,27 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>1529</t>
+          <t>522</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -5839,40 +5831,44 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
+          <t>2026년 IoT 보안인증 교육과정 안내</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>652</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I101" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -5880,44 +5876,44 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
+          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>76426</t>
+          <t>818</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -5928,49 +5924,49 @@
       <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
+          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>55906</t>
+          <t>1529</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -5978,52 +5974,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr"/>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>55329</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -6034,49 +6034,49 @@
       <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>958</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
+          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>34467</t>
+          <t>76426</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -6104,89 +6104,85 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>956</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
+          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2945</t>
+          <t>55906</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>957</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
+          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>55329</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -6194,56 +6190,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>955</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>145255</t>
+          <t>34467</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -6271,85 +6263,89 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>26576</t>
+          <t>2945</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
+          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>34290</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -6357,52 +6353,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr"/>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>954</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>184573</t>
+          <t>145255</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -6430,32 +6430,32 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>14403</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>953</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>6587</t>
+          <t>26576</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -6463,56 +6463,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
+          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>51749</t>
+          <t>34290</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -6540,32 +6536,32 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>951</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>78439</t>
+          <t>184573</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -6593,55 +6589,218 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
+          <t>14403</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>공지</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>6587</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>51749</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>보도자료</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>949</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>78439</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>보도자료</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
           <t>38805</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr">
+      <c r="B118" t="inlineStr">
         <is>
           <t>공지</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr">
+      <c r="C118" t="inlineStr">
         <is>
           <t>[공유] 지능형 CCTV 성능시험 재개 안내 공지</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr">
+      <c r="D118" t="inlineStr">
         <is>
           <t>https://www.kisa.or.kr/401/form?postSeq=3677&amp;page=1</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr">
+      <c r="E118" t="inlineStr">
         <is>
           <t>2026-06-02</t>
         </is>
       </c>
-      <c r="F115" t="inlineStr">
+      <c r="F118" t="inlineStr">
         <is>
           <t>6525</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr">
+      <c r="G118" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
+      <c r="H118" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>공지사항</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
         <is>
           <t>2026-08-18 17:16:37.364015+09:00</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr">
+      <c r="K118" t="inlineStr">
         <is>
           <t>2026-08-18 17:16:37.364015+09:00</t>
         </is>

--- a/docs/snapshot/downloads/kisa.xlsx
+++ b/docs/snapshot/downloads/kisa.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K118"/>
+  <dimension ref="A1:K119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,22 +476,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>70486</t>
+          <t>70581</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 27회차 교육생 모집(~10.23)</t>
+          <t>[공고문] 싱가포르 현지 진출 지원 국내 블록체인 기업 모집 재공고(~10월 8일(목) 14:00까지)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3771&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3773&amp;page=1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -501,15 +501,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -517,19 +521,19 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-09-28 12:01:47.314055+09:00</t>
+          <t>2026-09-28 14:01:40.936617+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-09-28 12:01:47.314055+09:00</t>
+          <t>2026-09-28 14:01:40.936617+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>70485</t>
+          <t>70486</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -539,12 +543,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 28회차 교육생 모집(~10.24)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 27회차 교육생 모집(~10.23)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3772&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3771&amp;page=1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -554,7 +558,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -582,7 +586,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>70465</t>
+          <t>70485</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -592,12 +596,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>「2026 블록체인 진흥주간」 취업 컨설팅 모집 안내(~10.30)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 28회차 교육생 모집(~10.24)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3770&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3772&amp;page=1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -607,7 +611,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -623,87 +627,87 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-09-28 11:31:41.790745+09:00</t>
+          <t>2026-09-28 12:01:47.314055+09:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-09-28 11:31:41.790745+09:00</t>
+          <t>2026-09-28 12:01:47.314055+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>70251</t>
+          <t>70465</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>인공지능(AI)·디지털 시대, 새로운 법적 문제 해법 찾는다</t>
+          <t>「2026 블록체인 진흥주간」 취업 컨설팅 모집 안내(~10.30)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2640&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3770&amp;page=1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-09-28 08:31:53.468509+09:00</t>
+          <t>2026-09-28 11:31:41.790745+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-09-28 08:31:53.468509+09:00</t>
+          <t>2026-09-28 11:31:41.790745+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>66888</t>
+          <t>70251</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>991</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>(행사 안내) 글로벌 AI 프라이버시 포럼 개최(9.29.)</t>
+          <t>인공지능(AI)·디지털 시대, 새로운 법적 문제 해법 찾는다</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3769&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2640&amp;page=1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -713,7 +717,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>25</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -724,24 +728,24 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-09-23 13:31:32.429525+09:00</t>
+          <t>2026-09-28 08:31:53.468509+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-09-23 13:31:32.429525+09:00</t>
+          <t>2026-09-28 08:31:53.468509+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>65988</t>
+          <t>66888</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -751,22 +755,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026년도 K-Cybersecurity Business Day in Japan 세미나(10/20) 참석 수요조사 안내</t>
+          <t>(행사 안내) 글로벌 AI 프라이버시 포럼 개최(9.29.)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3768&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3769&amp;page=1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -782,19 +786,19 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-09-22 10:01:34.273734+09:00</t>
+          <t>2026-09-23 13:31:32.429525+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-09-22 10:01:34.273734+09:00</t>
+          <t>2026-09-23 13:31:32.429525+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>65748</t>
+          <t>65988</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -804,27 +808,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 26회차 교육생 모집(~10.16)</t>
+          <t>2026년도 K-Cybersecurity Business Day in Japan 세미나(10/20) 참석 수요조사 안내</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3767&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3768&amp;page=1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
@@ -835,87 +839,87 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-09-21 17:01:40.203969+09:00</t>
+          <t>2026-09-22 10:01:34.273734+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-09-21 17:01:40.203969+09:00</t>
+          <t>2026-09-22 10:01:34.273734+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>64631</t>
+          <t>65748</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 인터넷 주소 자원 관리 역량 국제적 인정받아</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 26회차 교육생 모집(~10.16)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2639&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3767&amp;page=1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-09-20 12:01:47.233521+09:00</t>
+          <t>2026-09-21 17:01:40.203969+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-09-20 12:01:47.233521+09:00</t>
+          <t>2026-09-21 17:01:40.203969+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>63068</t>
+          <t>64631</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>990</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>대국민 혁신 정책·제안 공모전 개최</t>
+          <t>한국인터넷진흥원, 인터넷 주소 자원 관리 역량 국제적 인정받아</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3766&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2639&amp;page=1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -925,7 +929,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -936,24 +940,24 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-09-18 10:46:37.266535+09:00</t>
+          <t>2026-09-20 12:01:47.233521+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-09-18 10:46:37.266535+09:00</t>
+          <t>2026-09-20 12:01:47.233521+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>63051</t>
+          <t>63068</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -963,12 +967,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>세계경제포럼·싱가포르 사이버보안청과 인공지능(AI) 위협 대비 사이버보안 협력 강화</t>
+          <t>대국민 혁신 정책·제안 공모전 개최</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2638&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3766&amp;page=1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -978,7 +982,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -989,49 +993,49 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-09-18 10:31:43.770443+09:00</t>
+          <t>2026-09-18 10:46:37.266535+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-09-18 10:31:43.770443+09:00</t>
+          <t>2026-09-18 10:46:37.266535+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>62781</t>
+          <t>63051</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026년 블록체인 기업성장허브 입주기업 모집(~10월 7일(수) 16:00까지)</t>
+          <t>세계경제포럼·싱가포르 사이버보안청과 인공지능(AI) 위협 대비 사이버보안 협력 강화</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3765&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2638&amp;page=1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1039,46 +1043,42 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-09-17 17:16:36.514530+09:00</t>
+          <t>2026-09-18 10:31:43.770443+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-09-17 17:16:36.514530+09:00</t>
+          <t>2026-09-18 10:31:43.770443+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>62507</t>
+          <t>62781</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 25회차 교육생 모집(~10.10)</t>
+          <t>2026년 블록체인 기업성장허브 입주기업 모집(~10월 7일(수) 16:00까지)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3764&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3765&amp;page=1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1088,15 +1088,19 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1104,19 +1108,19 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-09-17 13:31:33.789948+09:00</t>
+          <t>2026-09-17 17:16:36.514530+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-09-17 13:31:33.789948+09:00</t>
+          <t>2026-09-17 17:16:36.514530+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>62367</t>
+          <t>62507</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1126,12 +1130,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 24회차 교육생 모집(~10.9)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 25회차 교육생 모집(~10.10)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3763&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3764&amp;page=1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1141,7 +1145,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1157,19 +1161,19 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-09-17 11:46:35.719751+09:00</t>
+          <t>2026-09-17 13:31:33.789948+09:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-09-17 11:46:35.719751+09:00</t>
+          <t>2026-09-17 13:31:33.789948+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>61484</t>
+          <t>62367</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1179,27 +1183,27 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026년 제13회 소프트웨어(SW) 개발보안 경진대회 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 24회차 교육생 모집(~10.9)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3762&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3763&amp;page=1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
@@ -1210,19 +1214,19 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-09-16 09:46:37.058042+09:00</t>
+          <t>2026-09-17 11:46:35.719751+09:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-09-16 09:46:37.058042+09:00</t>
+          <t>2026-09-17 11:46:35.719751+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>61111</t>
+          <t>61484</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1232,22 +1236,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>민관 합동 ‘자동차 사이버 침해사고 대응 모의훈련’ 실시</t>
+          <t>2026년 제13회 소프트웨어(SW) 개발보안 경진대회 개최</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2637&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3762&amp;page=1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1258,24 +1262,24 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-09-15 15:01:52.747371+09:00</t>
+          <t>2026-09-16 09:46:37.058042+09:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-09-15 15:01:52.747371+09:00</t>
+          <t>2026-09-16 09:46:37.058042+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>61031</t>
+          <t>61111</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1285,12 +1289,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>“새로운 보안 위협, 인공지능(AI)으로 대응” 정보보호 제품 개발 기업 대상 보안 역량 강화 교육 추진</t>
+          <t>민관 합동 ‘자동차 사이버 침해사고 대응 모의훈련’ 실시</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2636&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2637&amp;page=1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1316,44 +1320,44 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-09-15 14:01:52.540884+09:00</t>
+          <t>2026-09-15 15:01:52.747371+09:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-09-15 14:01:52.540884+09:00</t>
+          <t>2026-09-15 15:01:52.747371+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>57381</t>
+          <t>61031</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026 전자문서 유공 포상 공고</t>
+          <t>“새로운 보안 위협, 인공지능(AI)으로 대응” 정보보호 제품 개발 기업 대상 보안 역량 강화 교육 추진</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3761&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2636&amp;page=1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1361,46 +1365,42 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-09-10 14:16:31.877229+09:00</t>
+          <t>2026-09-15 14:01:52.540884+09:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-09-10 14:16:31.877229+09:00</t>
+          <t>2026-09-15 14:01:52.540884+09:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>57149</t>
+          <t>57381</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026년 클라우드 서비스 보안인증(CSAP) 교육 안내</t>
+          <t>2026 전자문서 유공 포상 공고</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3760&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3761&amp;page=1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1418,7 +1418,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -1426,19 +1430,19 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-09-10 10:46:38.794916+09:00</t>
+          <t>2026-09-10 14:16:31.877229+09:00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-09-10 10:46:38.794916+09:00</t>
+          <t>2026-09-10 14:16:31.877229+09:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>56431</t>
+          <t>57149</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1448,22 +1452,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>보호나라 챗봇, 국민 생활 속 정보보호 성과 인정</t>
+          <t>2026년 클라우드 서비스 보안인증(CSAP) 교육 안내</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2634&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3760&amp;page=1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1474,92 +1478,92 @@
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-09-09 12:01:35.142670+09:00</t>
+          <t>2026-09-10 10:46:38.794916+09:00</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-09-09 12:01:35.142670+09:00</t>
+          <t>2026-09-10 10:46:38.794916+09:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>56969</t>
+          <t>56431</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1522</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>온마이데이터 서비스 이용 이벤트 안내</t>
+          <t>보호나라 챗봇, 국민 생활 속 정보보호 성과 인정</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3758&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2634&amp;page=1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>402</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-09-10 08:31:37.677434+09:00</t>
+          <t>2026-09-09 12:01:35.142670+09:00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-09-10 08:31:37.677434+09:00</t>
+          <t>2026-09-09 12:01:35.142670+09:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>54791</t>
+          <t>56969</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1522</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>국내 캐시 도메인이름시스템(DNS) 운영기관, 신규 암호키 반영 여부 확인하세요</t>
+          <t>온마이데이터 서비스 이용 이벤트 안내</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2633&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3758&amp;page=1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1569,60 +1573,60 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>402</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-09-07 12:01:35.243341+09:00</t>
+          <t>2026-09-10 08:31:37.677434+09:00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-09-07 12:01:35.243341+09:00</t>
+          <t>2026-09-10 08:31:37.677434+09:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>54541</t>
+          <t>54791</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(2차, Avalanche)</t>
+          <t>국내 캐시 도메인이름시스템(DNS) 운영기관, 신규 암호키 반영 여부 확인하세요</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3759&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2633&amp;page=1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1630,31 +1634,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-